--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17F19A8-C69C-4CE3-9171-74DF15E9B702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C1B5EA-EC63-4FB6-9D0D-1A7B16B99A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="MYxIjE9TGmSeigdKyCHOw3lH9f8J4EUilH0KgCjagDp50KBSM76xHJC56lRzGivfQGZgzVWvoHo9ImRSo1hl1A==" workbookSaltValue="vppty2a252bIjxbLncHPYg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="1" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -35,7 +35,6 @@
     <sheet name="E-SET-TAG-DETAILS" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1671,9 +1670,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1682,6 +1678,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1726,17 +1725,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1748,6 +1736,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1834,18 +1833,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1865,6 +1852,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1932,9 +1931,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1942,6 +1938,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4091,7 +4090,7 @@
       <c r="E205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1d2HCoMdSFeXbl4uekk6nIPwR8M3BDWn0kiAMlUkHLrVPv27HjYgBxMXi9iOe4QbZxgT8rtrs/poxOz9EhUsSw==" saltValue="fW0Q0odrNXjbfKtF1Sur6Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
@@ -4200,25 +4199,25 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
       <c r="B4" s="174"/>
-      <c r="C4" s="170" t="s">
+      <c r="C4" s="166" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="170" t="s">
+      <c r="D4" s="166" t="s">
         <v>135</v>
       </c>
-      <c r="E4" s="170" t="s">
+      <c r="E4" s="166" t="s">
         <v>136</v>
       </c>
       <c r="F4" s="125" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="170" t="s">
+      <c r="G4" s="166" t="s">
         <v>138</v>
       </c>
-      <c r="H4" s="170" t="s">
+      <c r="H4" s="166" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="170" t="s">
+      <c r="I4" s="166" t="s">
         <v>129</v>
       </c>
       <c r="J4" s="141" t="s">
@@ -4238,13 +4237,13 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
       <c r="B5" s="175"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
       <c r="F5" s="126"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
       <c r="J5" s="143"/>
       <c r="K5" s="6" t="s">
         <v>106</v>
@@ -7865,7 +7864,7 @@
       <c r="P205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7yCZUk3R/QGcpOY4CITVRrY9LH01ZI0nnKfSBOUTPiCW+ygDsD8XYB7hx/d3uYg4CpRLlDWLMOQNX1NmrDvusg==" saltValue="yKIsFQZMsnDWFt4tfLh2EQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="C3:P3"/>
@@ -9366,7 +9365,7 @@
       <c r="E205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iiRqro6j+ebRBI2pYrMb5Mm/4IGrc0mmXOsYJnUaLpAZWmx3qgYRT3V3pmNzKdUYY90o5XNlNvF8nS041AvOIQ==" saltValue="yA9MujtCczK/ePPyGf8xyQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
@@ -11063,7 +11062,7 @@
       <c r="F205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9GOwcRzqvwTX2g4xV//HK/if+nED5glmIMf4EwZ4+44WHj22feM2p6c0Ap/Dpckgcc1QF4Sd0tkiUXpzwg9qHw==" saltValue="XHrXEPS/iH54NabQXZd4rQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
@@ -11157,25 +11156,25 @@
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="97"/>
       <c r="B3" s="97"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="168" t="s">
+      <c r="D3" s="168"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="164" t="s">
         <v>215</v>
       </c>
-      <c r="G3" s="172"/>
-      <c r="H3" s="169"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="165"/>
       <c r="I3" s="146" t="s">
         <v>140</v>
       </c>
-      <c r="J3" s="127" t="s">
+      <c r="J3" s="131" t="s">
         <v>145</v>
       </c>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
       <c r="N3" s="134" t="s">
         <v>146</v>
       </c>
@@ -11192,25 +11191,25 @@
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
       <c r="B4" s="97"/>
-      <c r="C4" s="170" t="s">
+      <c r="C4" s="166" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="112" t="s">
+      <c r="D4" s="111" t="s">
         <v>213</v>
       </c>
-      <c r="E4" s="114"/>
-      <c r="F4" s="170" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="166" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="112" t="s">
+      <c r="G4" s="111" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="114"/>
+      <c r="H4" s="113"/>
       <c r="I4" s="146"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
       <c r="N4" s="134"/>
       <c r="O4" s="134"/>
       <c r="P4" s="134"/>
@@ -11219,14 +11218,14 @@
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
       <c r="B5" s="97"/>
-      <c r="C5" s="171"/>
+      <c r="C5" s="167"/>
       <c r="D5" s="71" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="171"/>
+      <c r="F5" s="167"/>
       <c r="G5" s="71" t="s">
         <v>0</v>
       </c>
@@ -15052,13 +15051,8 @@
       <c r="Q205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PhaUvbMO+xRPe4iHeYNQEdteJ0PdHnG64pDWoeZdr6WVKQo9IfwTSNFBhGwg87locIqOOPjC3zO1SgqsNRM0hg==" saltValue="8SoTPqHqCg+dytZdj7iCYg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="O3:O5"/>
     <mergeCell ref="F3:H3"/>
@@ -15068,6 +15062,11 @@
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="J3:M4"/>
     <mergeCell ref="N3:N5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I5 J5:M5 Q3:Q5" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -16347,7 +16346,7 @@
       <c r="D205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/3fYbA56iA+ycQsN9hhLy4ant3mgAgzPiz+Klo3w49//FubDNAaCQDWTRnIQtSW4NZRZIjWgyBLwvMj6jwslXw==" saltValue="iS3Jdq2XShdcZoO9WZL8cQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
@@ -16435,12 +16434,12 @@
       <c r="H3" s="134" t="s">
         <v>234</v>
       </c>
-      <c r="I3" s="127" t="s">
+      <c r="I3" s="131" t="s">
         <v>151</v>
       </c>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
@@ -16451,10 +16450,10 @@
       <c r="F4" s="185"/>
       <c r="G4" s="179"/>
       <c r="H4" s="134"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
@@ -19283,7 +19282,7 @@
       <c r="L205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ymeEdNb9mVI1cYMg8C22T9KMxnfSF9KfuDAS7jso+eFWSxhHIUcWipzFQqZpqVCpSQSwcCSGJ5/DZmy4RbPRzQ==" saltValue="UOgRoS1Iz4l3zEjRi6D39Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="9">
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:L4"/>
@@ -24715,7 +24714,7 @@
       <c r="X204" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VyPGifgbclOYW1bKptTW41aHBUUvMBOoY8rFIyu/1jwS6Pq/YoImn1qw1QRcMW8ZMJHNFrmSnM+QGBjmMV6aeg==" saltValue="I/NmwqO5RLWto1elieFXRw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="13">
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="R3:R4"/>
@@ -24851,7 +24850,7 @@
       <c r="G3" s="200" t="s">
         <v>171</v>
       </c>
-      <c r="H3" s="194" t="s">
+      <c r="H3" s="193" t="s">
         <v>172</v>
       </c>
       <c r="I3" s="100" t="s">
@@ -24862,22 +24861,22 @@
         <v>181</v>
       </c>
       <c r="L3" s="101"/>
-      <c r="M3" s="194" t="s">
+      <c r="M3" s="193" t="s">
         <v>175</v>
       </c>
-      <c r="N3" s="193" t="s">
+      <c r="N3" s="195" t="s">
         <v>190</v>
       </c>
-      <c r="O3" s="193" t="s">
+      <c r="O3" s="195" t="s">
         <v>176</v>
       </c>
-      <c r="P3" s="194" t="s">
+      <c r="P3" s="193" t="s">
         <v>239</v>
       </c>
-      <c r="Q3" s="193" t="s">
+      <c r="Q3" s="195" t="s">
         <v>177</v>
       </c>
-      <c r="R3" s="193" t="s">
+      <c r="R3" s="195" t="s">
         <v>178</v>
       </c>
       <c r="S3" s="148" t="s">
@@ -24893,7 +24892,7 @@
       <c r="E4" s="199"/>
       <c r="F4" s="199"/>
       <c r="G4" s="201"/>
-      <c r="H4" s="195"/>
+      <c r="H4" s="194"/>
       <c r="I4" s="13" t="s">
         <v>173</v>
       </c>
@@ -24906,10 +24905,10 @@
       <c r="L4" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="M4" s="195"/>
+      <c r="M4" s="194"/>
       <c r="N4" s="126"/>
       <c r="O4" s="126"/>
-      <c r="P4" s="195"/>
+      <c r="P4" s="194"/>
       <c r="Q4" s="126"/>
       <c r="R4" s="126"/>
       <c r="S4" s="38" t="s">
@@ -29320,13 +29319,13 @@
       <c r="T204" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="D/L/U4KVpQl3n70DELx6UDXSAiZL+7CPXABj/w3OhTXKaepiO8G1hfcYiXIQ0R6omFujYRZSMaJ2bGCTDpiv5g==" saltValue="1kggktTypYmm30wa+5JpVA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
@@ -29335,11 +29334,11 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:H4 I4:K4 M3:M4 P3:P4 S4:T4 E3:F3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -32047,7 +32046,7 @@
       <c r="K203" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LLgesjn77PG8MmlEQeIP4oKJLS0aWyLX40qYN5kdFoJE2a3G7KlPNGd30+AVvQVb5SWTWej6hWrLivXIn/NF1w==" saltValue="MymlQGrtk86vO76SMvrgLw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="A2:A3"/>
@@ -37478,7 +37477,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eGiVfhPaq40haxuGOvMBWPfR+YoT9MYIPaqncXhutugJ6ON5MOy0jQ30CEhco9hw4ZXsz3YvNuMJbv/gYUev1A==" saltValue="X0Qvp6cUAUoKEbgS8bG3/A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -37586,13 +37585,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="102"/>
-      <c r="B3" s="112" t="s">
+      <c r="B3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="121" t="s">
         <v>24</v>
       </c>
@@ -37604,13 +37603,13 @@
       <c r="K3" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="L3" s="112" t="s">
+      <c r="L3" s="111" t="s">
         <v>291</v>
       </c>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="113"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
@@ -37652,7 +37651,7 @@
         <v>27</v>
       </c>
       <c r="O4" s="97"/>
-      <c r="P4" s="111" t="s">
+      <c r="P4" s="114" t="s">
         <v>28</v>
       </c>
     </row>
@@ -37680,7 +37679,7 @@
       <c r="O5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="111"/>
+      <c r="P5" s="114"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -41283,8 +41282,9 @@
       <c r="P205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eBHF0WldXHa8L7YPgOnKiVo0yJQF9CfjXFG6CVhyt3xSV0UfzVM79wlN/xT+rfbhfPUUCj7wwgj70zvHCdnrqQ==" saltValue="crh6pV7dpCUdKRA5VTsa0g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -41301,7 +41301,6 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 C4:C5 K4 M5 G4:H4 J4" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -44043,7 +44042,7 @@
       <c r="K205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eVQRjX6Vsb0uRRqiwzZHMMXbrSVA8k0AoBljKwsbkL5cqElhJ4gIdDr0dWwQGAAiPuqhzI2TgUDlaghIC1a7eg==" saltValue="gwkJrmhthYyKilD/GBDYgg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:F3"/>
@@ -44171,105 +44170,105 @@
       <c r="A2" s="102" t="s">
         <v>254</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="130" t="s">
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="131"/>
+      <c r="V2" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="W2" s="131"/>
-      <c r="X2" s="131"/>
-      <c r="Y2" s="131"/>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="131"/>
-      <c r="AB2" s="131"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="127" t="s">
+      <c r="W2" s="128"/>
+      <c r="X2" s="128"/>
+      <c r="Y2" s="128"/>
+      <c r="Z2" s="128"/>
+      <c r="AA2" s="128"/>
+      <c r="AB2" s="128"/>
+      <c r="AC2" s="128"/>
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="128"/>
+      <c r="AG2" s="128"/>
+      <c r="AH2" s="129"/>
+      <c r="AI2" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="AJ2" s="127"/>
-      <c r="AK2" s="127"/>
-      <c r="AL2" s="127"/>
-      <c r="AM2" s="127"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="127"/>
-      <c r="AT2" s="127"/>
+      <c r="AJ2" s="131"/>
+      <c r="AK2" s="131"/>
+      <c r="AL2" s="131"/>
+      <c r="AM2" s="131"/>
+      <c r="AN2" s="131"/>
+      <c r="AO2" s="131"/>
+      <c r="AP2" s="131"/>
+      <c r="AQ2" s="131"/>
+      <c r="AR2" s="131"/>
+      <c r="AS2" s="131"/>
+      <c r="AT2" s="131"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="102"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="127"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="131"/>
+      <c r="T3" s="131"/>
+      <c r="U3" s="131"/>
       <c r="V3" s="100"/>
-      <c r="W3" s="133"/>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="133"/>
-      <c r="Z3" s="133"/>
-      <c r="AA3" s="133"/>
-      <c r="AB3" s="133"/>
-      <c r="AC3" s="133"/>
-      <c r="AD3" s="133"/>
-      <c r="AE3" s="133"/>
-      <c r="AF3" s="133"/>
-      <c r="AG3" s="133"/>
+      <c r="W3" s="130"/>
+      <c r="X3" s="130"/>
+      <c r="Y3" s="130"/>
+      <c r="Z3" s="130"/>
+      <c r="AA3" s="130"/>
+      <c r="AB3" s="130"/>
+      <c r="AC3" s="130"/>
+      <c r="AD3" s="130"/>
+      <c r="AE3" s="130"/>
+      <c r="AF3" s="130"/>
+      <c r="AG3" s="130"/>
       <c r="AH3" s="101"/>
-      <c r="AI3" s="127"/>
-      <c r="AJ3" s="127"/>
-      <c r="AK3" s="127"/>
-      <c r="AL3" s="127"/>
-      <c r="AM3" s="127"/>
-      <c r="AN3" s="127"/>
-      <c r="AO3" s="127"/>
-      <c r="AP3" s="127"/>
-      <c r="AQ3" s="127"/>
-      <c r="AR3" s="127"/>
-      <c r="AS3" s="127"/>
-      <c r="AT3" s="127"/>
+      <c r="AI3" s="131"/>
+      <c r="AJ3" s="131"/>
+      <c r="AK3" s="131"/>
+      <c r="AL3" s="131"/>
+      <c r="AM3" s="131"/>
+      <c r="AN3" s="131"/>
+      <c r="AO3" s="131"/>
+      <c r="AP3" s="131"/>
+      <c r="AQ3" s="131"/>
+      <c r="AR3" s="131"/>
+      <c r="AS3" s="131"/>
+      <c r="AT3" s="131"/>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
@@ -44279,7 +44278,7 @@
       <c r="C4" s="109" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="128" t="s">
+      <c r="D4" s="132" t="s">
         <v>36</v>
       </c>
       <c r="E4" s="98" t="s">
@@ -44292,25 +44291,25 @@
       </c>
       <c r="I4" s="98"/>
       <c r="J4" s="98"/>
-      <c r="K4" s="111" t="s">
+      <c r="K4" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111" t="s">
+      <c r="L4" s="114"/>
+      <c r="M4" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111" t="s">
+      <c r="N4" s="114"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="R4" s="111"/>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111" t="s">
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="U4" s="111"/>
+      <c r="U4" s="114"/>
       <c r="V4" s="98" t="s">
         <v>63</v>
       </c>
@@ -44350,32 +44349,32 @@
       <c r="AH4" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="AI4" s="111" t="s">
+      <c r="AI4" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111" t="s">
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111" t="s">
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="AP4" s="111"/>
-      <c r="AQ4" s="111"/>
-      <c r="AR4" s="111" t="s">
+      <c r="AP4" s="114"/>
+      <c r="AQ4" s="114"/>
+      <c r="AR4" s="114" t="s">
         <v>82</v>
       </c>
-      <c r="AS4" s="111"/>
-      <c r="AT4" s="111"/>
+      <c r="AS4" s="114"/>
+      <c r="AT4" s="114"/>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="102"/>
       <c r="B5" s="110"/>
       <c r="C5" s="110"/>
-      <c r="D5" s="129"/>
+      <c r="D5" s="133"/>
       <c r="E5" s="6" t="s">
         <v>47</v>
       </c>
@@ -54078,22 +54077,8 @@
       <c r="AT205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VFnMg6bwIK0FJ+hXg+Dtd+0R27tX6NcWvnqifBdgLkgulIaVokTIorQbRkpmZ2hHT0okluXcfQNmt4SfblwBJA==" saltValue="d7cUXcFtfNp3GllyZxzJzg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="V2:AH3"/>
-    <mergeCell ref="AO4:AQ4"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="B2:U3"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AR4:AT4"/>
     <mergeCell ref="AI2:AT3"/>
     <mergeCell ref="D4:D5"/>
@@ -54110,6 +54095,20 @@
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="M4:P4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="B2:U3"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="V2:AH3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 M5 N5 O5 P5 Q5 R5 S5 AI5 AJ5 AL5 AM5 AO5 AP5 AR5 AS5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -55395,7 +55394,7 @@
       <c r="D205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="72Z9rnNezuhAXysRN0VNk+qrNaxv4iaQhOPkwgadWDKlA9XGHe8kZCO6FxHitXqJRbt/bYqir1NtrMYamWFDEQ==" saltValue="nh5HVE+/+XYTnHDnamKWlw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -55443,13 +55442,13 @@
       <c r="A2" s="141" t="s">
         <v>254</v>
       </c>
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
       <c r="G2" s="135" t="s">
         <v>95</v>
       </c>
@@ -57900,7 +57899,7 @@
       <c r="J204" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rcrG1WpV9C0TGk2zqAjMJYts8aS3syK4FFJ5ptPEzUhC37ivxLLCeLSNH6Dxq7kxbUTEHzx+eMH/Rg/bxTTQeQ==" saltValue="fxPPdq2+9TxXk16Y5++DOg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="G2:J3"/>
     <mergeCell ref="A2:A4"/>
@@ -57986,13 +57985,13 @@
       <c r="J2" s="152"/>
       <c r="K2" s="152"/>
       <c r="L2" s="153"/>
-      <c r="M2" s="130" t="s">
+      <c r="M2" s="127" t="s">
         <v>258</v>
       </c>
-      <c r="N2" s="131"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="132"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="129"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="142"/>
@@ -58026,9 +58025,9 @@
       </c>
       <c r="L3" s="150"/>
       <c r="M3" s="100"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
       <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -61868,7 +61867,7 @@
       <c r="Q204" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gduHT6ae+ZsgoFAXMtcycn2gyCkliIgTv0BJV7Mm1fwpKiX3KxzU+7Ct2u7HJBrjyFCDWFf3tcUXe1jB7xJKag==" saltValue="3u5kMowR2TyHLZYB4s0f7A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B2:L2"/>
@@ -62008,29 +62007,29 @@
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="97"/>
       <c r="B3" s="142"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="164" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="168" t="s">
+      <c r="D3" s="168"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="164" t="s">
         <v>212</v>
       </c>
-      <c r="G3" s="172"/>
-      <c r="H3" s="169"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="165"/>
       <c r="I3" s="26" t="s">
         <v>126</v>
       </c>
       <c r="J3" s="26"/>
-      <c r="K3" s="130" t="s">
+      <c r="K3" s="127" t="s">
         <v>89</v>
       </c>
-      <c r="L3" s="131"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="130" t="s">
+      <c r="L3" s="128"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="127" t="s">
         <v>113</v>
       </c>
-      <c r="O3" s="132"/>
+      <c r="O3" s="129"/>
       <c r="P3" s="97" t="s">
         <v>229</v>
       </c>
@@ -62044,41 +62043,41 @@
         <v>115</v>
       </c>
       <c r="T3" s="102"/>
-      <c r="U3" s="162" t="s">
+      <c r="U3" s="169" t="s">
         <v>261</v>
       </c>
-      <c r="V3" s="163"/>
-      <c r="W3" s="162" t="s">
+      <c r="V3" s="170"/>
+      <c r="W3" s="169" t="s">
         <v>260</v>
       </c>
-      <c r="X3" s="163"/>
+      <c r="X3" s="170"/>
       <c r="Y3" s="102" t="s">
         <v>116</v>
       </c>
       <c r="Z3" s="102"/>
       <c r="AA3" s="102"/>
       <c r="AB3" s="102"/>
-      <c r="AC3" s="111" t="s">
+      <c r="AC3" s="114" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
       <c r="B4" s="142"/>
-      <c r="C4" s="166" t="s">
+      <c r="C4" s="162" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="E4" s="169"/>
-      <c r="F4" s="170" t="s">
+      <c r="E4" s="165"/>
+      <c r="F4" s="166" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="169"/>
+      <c r="H4" s="165"/>
       <c r="I4" s="44" t="s">
         <v>124</v>
       </c>
@@ -62086,7 +62085,7 @@
         <v>85</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="133"/>
+      <c r="L4" s="130"/>
       <c r="M4" s="101"/>
       <c r="N4" s="100"/>
       <c r="O4" s="101"/>
@@ -62095,27 +62094,27 @@
       <c r="R4" s="97"/>
       <c r="S4" s="102"/>
       <c r="T4" s="102"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
-      <c r="W4" s="164"/>
-      <c r="X4" s="165"/>
+      <c r="U4" s="171"/>
+      <c r="V4" s="172"/>
+      <c r="W4" s="171"/>
+      <c r="X4" s="172"/>
       <c r="Y4" s="102"/>
       <c r="Z4" s="102"/>
       <c r="AA4" s="102"/>
       <c r="AB4" s="102"/>
-      <c r="AC4" s="111"/>
+      <c r="AC4" s="114"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
       <c r="B5" s="143"/>
-      <c r="C5" s="167"/>
+      <c r="C5" s="163"/>
       <c r="D5" s="71" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="171"/>
+      <c r="F5" s="167"/>
       <c r="G5" s="71" t="s">
         <v>0</v>
       </c>
@@ -62176,7 +62175,7 @@
       <c r="AB5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AC5" s="111"/>
+      <c r="AC5" s="114"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -68379,8 +68378,16 @@
       <c r="AC205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="n15jzT3UDNrq52d/2Birqz9MmaAnGLtsoXzsWUc8XDs8jPyxo3tASuQIJK3whrU7Z0A7wrG1zSjGbXwKtZRR/w==" saltValue="aDVpfBfzxn3/sMJsNJZXZw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
+    <mergeCell ref="AC3:AC5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:T4"/>
+    <mergeCell ref="Y3:AB4"/>
+    <mergeCell ref="U3:V4"/>
+    <mergeCell ref="W3:X4"/>
     <mergeCell ref="K3:M4"/>
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="A2:A5"/>
@@ -68391,14 +68398,6 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="AC3:AC5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:T4"/>
-    <mergeCell ref="Y3:AB4"/>
-    <mergeCell ref="U3:V4"/>
-    <mergeCell ref="W3:X4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y5:AB5 K5" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C1B5EA-EC63-4FB6-9D0D-1A7B16B99A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3715085-5D6A-46C1-8C68-F99E92BD08CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="MYxIjE9TGmSeigdKyCHOw3lH9f8J4EUilH0KgCjagDp50KBSM76xHJC56lRzGivfQGZgzVWvoHo9ImRSo1hl1A==" workbookSaltValue="vppty2a252bIjxbLncHPYg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
@@ -1670,6 +1670,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1715,15 +1719,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1736,17 +1747,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1833,6 +1833,18 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1852,18 +1864,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4199,25 +4199,25 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
       <c r="B4" s="174"/>
-      <c r="C4" s="166" t="s">
+      <c r="C4" s="170" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="E4" s="166" t="s">
+      <c r="E4" s="170" t="s">
         <v>136</v>
       </c>
       <c r="F4" s="125" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="166" t="s">
+      <c r="G4" s="170" t="s">
         <v>138</v>
       </c>
-      <c r="H4" s="166" t="s">
+      <c r="H4" s="170" t="s">
         <v>128</v>
       </c>
-      <c r="I4" s="166" t="s">
+      <c r="I4" s="170" t="s">
         <v>129</v>
       </c>
       <c r="J4" s="141" t="s">
@@ -4237,13 +4237,13 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
       <c r="B5" s="175"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
       <c r="F5" s="126"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
       <c r="J5" s="143"/>
       <c r="K5" s="6" t="s">
         <v>106</v>
@@ -11156,25 +11156,25 @@
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="97"/>
       <c r="B3" s="97"/>
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="168" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="168"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="164" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="168" t="s">
         <v>215</v>
       </c>
-      <c r="G3" s="168"/>
-      <c r="H3" s="165"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="169"/>
       <c r="I3" s="146" t="s">
         <v>140</v>
       </c>
-      <c r="J3" s="131" t="s">
+      <c r="J3" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
-      <c r="M3" s="131"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
       <c r="N3" s="134" t="s">
         <v>146</v>
       </c>
@@ -11191,25 +11191,25 @@
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
       <c r="B4" s="97"/>
-      <c r="C4" s="166" t="s">
+      <c r="C4" s="170" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="112" t="s">
         <v>213</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="166" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="170" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="111" t="s">
+      <c r="G4" s="112" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="113"/>
+      <c r="H4" s="114"/>
       <c r="I4" s="146"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
+      <c r="J4" s="127"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="127"/>
+      <c r="M4" s="127"/>
       <c r="N4" s="134"/>
       <c r="O4" s="134"/>
       <c r="P4" s="134"/>
@@ -11218,14 +11218,14 @@
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
       <c r="B5" s="97"/>
-      <c r="C5" s="167"/>
+      <c r="C5" s="171"/>
       <c r="D5" s="71" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="167"/>
+      <c r="F5" s="171"/>
       <c r="G5" s="71" t="s">
         <v>0</v>
       </c>
@@ -15053,6 +15053,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="PhaUvbMO+xRPe4iHeYNQEdteJ0PdHnG64pDWoeZdr6WVKQo9IfwTSNFBhGwg87locIqOOPjC3zO1SgqsNRM0hg==" saltValue="8SoTPqHqCg+dytZdj7iCYg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="O3:O5"/>
     <mergeCell ref="F3:H3"/>
@@ -15062,11 +15067,6 @@
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="J3:M4"/>
     <mergeCell ref="N3:N5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I5 J5:M5 Q3:Q5" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -16434,12 +16434,12 @@
       <c r="H3" s="134" t="s">
         <v>234</v>
       </c>
-      <c r="I3" s="131" t="s">
+      <c r="I3" s="127" t="s">
         <v>151</v>
       </c>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
@@ -16450,10 +16450,10 @@
       <c r="F4" s="185"/>
       <c r="G4" s="179"/>
       <c r="H4" s="134"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="127"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
@@ -19440,10 +19440,10 @@
       <c r="R3" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="121" t="s">
+      <c r="S3" s="122" t="s">
         <v>243</v>
       </c>
-      <c r="T3" s="123"/>
+      <c r="T3" s="124"/>
       <c r="U3" s="98" t="s">
         <v>164</v>
       </c>
@@ -29321,11 +29321,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="D/L/U4KVpQl3n70DELx6UDXSAiZL+7CPXABj/w3OhTXKaepiO8G1hfcYiXIQ0R6omFujYRZSMaJ2bGCTDpiv5g==" saltValue="1kggktTypYmm30wa+5JpVA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="S3:T3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
@@ -29334,11 +29330,15 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:H4 I4:K4 M3:M4 P3:P4 S4:T4 E3:F3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -37477,7 +37477,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eGiVfhPaq40haxuGOvMBWPfR+YoT9MYIPaqncXhutugJ6ON5MOy0jQ30CEhco9hw4ZXsz3YvNuMJbv/gYUev1A==" saltValue="X0Qvp6cUAUoKEbgS8bG3/A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jwksL52IvUaNr5N/FWpQtEJzvYvAg7ka8VmKXs1+sj9KKYbCRJlL9p1YGcmV2nyiw/iZgGmkbuSSIuh5bhUZgA==" saltValue="zC3DvL0J0roTIL1YRkOn0Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -37508,7 +37508,7 @@
     <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" xr:uid="{F6A2D174-87CA-4A84-A59B-9C5B3EDFA410}"/>
     <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" xr:uid="{4AD9F6B4-F493-4D51-A425-E40A5E342DD0}"/>
     <hyperlink ref="E5" r:id="rId7" xr:uid="{8E8691ED-310C-4B0D-98E7-1C757A32EA68}"/>
-    <hyperlink ref="J5" r:id="rId8" xr:uid="{FDCA5CD8-C8A1-4C49-864F-2B6D02C8EA6C}"/>
+    <hyperlink ref="J5" r:id="rId8" location="Ports" xr:uid="{FDCA5CD8-C8A1-4C49-864F-2B6D02C8EA6C}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -37585,38 +37585,38 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="102"/>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="121" t="s">
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="122"/>
-      <c r="I3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="124"/>
       <c r="J3" s="23" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="L3" s="111" t="s">
+      <c r="L3" s="112" t="s">
         <v>291</v>
       </c>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="114"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
       <c r="B4" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>182</v>
       </c>
       <c r="D4" s="99" t="s">
@@ -37628,19 +37628,19 @@
       <c r="F4" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="115" t="s">
+      <c r="G4" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="116" t="s">
+      <c r="H4" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="124" t="s">
+      <c r="I4" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="115" t="s">
+      <c r="J4" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="119" t="s">
+      <c r="K4" s="120" t="s">
         <v>42</v>
       </c>
       <c r="L4" s="97" t="s">
@@ -37651,22 +37651,22 @@
         <v>27</v>
       </c>
       <c r="O4" s="97"/>
-      <c r="P4" s="114" t="s">
+      <c r="P4" s="115" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="102"/>
       <c r="B5" s="102"/>
-      <c r="C5" s="118"/>
+      <c r="C5" s="119"/>
       <c r="D5" s="99"/>
       <c r="E5" s="110"/>
       <c r="F5" s="103"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="120"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="24" t="s">
         <v>4</v>
       </c>
@@ -37679,7 +37679,7 @@
       <c r="O5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="114"/>
+      <c r="P5" s="115"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -41282,8 +41282,9 @@
       <c r="P205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eBHF0WldXHa8L7YPgOnKiVo0yJQF9CfjXFG6CVhyt3xSV0UfzVM79wlN/xT+rfbhfPUUCj7wwgj70zvHCdnrqQ==" saltValue="crh6pV7dpCUdKRA5VTsa0g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="u3K3ef31ikOZKhNfRp4jsgl8Qb66qCQAj4oehsA6CCekdwUQq4/fv3vi+kmhZxZKfxp3CqGE0Ei731CernSR1w==" saltValue="WyoC6gLzDlKLlcTNm/5uLQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
@@ -41300,7 +41301,6 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 C4:C5 K4 M5 G4:H4 J4" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -41316,6 +41316,7 @@
     <hyperlink ref="H4" r:id="rId6" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
     <hyperlink ref="J4:J5" r:id="rId7" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{A5788B10-8F6B-429F-8265-63D1A2495C2D}"/>
     <hyperlink ref="K4:K5" r:id="rId8" location="gearGroups" display="MAIN_FISHING_GEAR_CODE" xr:uid="{ADDD99C7-B692-4517-AF11-C5F4715C3781}"/>
+    <hyperlink ref="H4:H5" r:id="rId9" location="Ports" display="PORT_CODE" xr:uid="{4BCE8909-E3DB-4961-B5C5-527D383D1926}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -41393,21 +41394,21 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
       <c r="F4" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="121" t="s">
+      <c r="G4" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="124"/>
       <c r="K4" s="125" t="s">
         <v>235</v>
       </c>
@@ -44042,7 +44043,7 @@
       <c r="K205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eVQRjX6Vsb0uRRqiwzZHMMXbrSVA8k0AoBljKwsbkL5cqElhJ4gIdDr0dWwQGAAiPuqhzI2TgUDlaghIC1a7eg==" saltValue="gwkJrmhthYyKilD/GBDYgg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ERyO8m/IJ32H3YUl02WtVq0mF00aLTtWQ9uob8pyCK7lkdnklhYd4Mc/h0Ue6mmmGK3xLInqhBvHAtpAor3hNQ==" saltValue="KRVfqPv8vx2KbhxaVfsqNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:F3"/>
@@ -44061,8 +44062,8 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" location="countries" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
     <hyperlink ref="G5" r:id="rId2" location="countries" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
+    <hyperlink ref="C5" r:id="rId3" location="Ports" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
+    <hyperlink ref="H5" r:id="rId4" location="Ports" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44170,105 +44171,105 @@
       <c r="A2" s="102" t="s">
         <v>254</v>
       </c>
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="131"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="131"/>
-      <c r="V2" s="127" t="s">
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="130" t="s">
         <v>76</v>
       </c>
-      <c r="W2" s="128"/>
-      <c r="X2" s="128"/>
-      <c r="Y2" s="128"/>
-      <c r="Z2" s="128"/>
-      <c r="AA2" s="128"/>
-      <c r="AB2" s="128"/>
-      <c r="AC2" s="128"/>
-      <c r="AD2" s="128"/>
-      <c r="AE2" s="128"/>
-      <c r="AF2" s="128"/>
-      <c r="AG2" s="128"/>
-      <c r="AH2" s="129"/>
-      <c r="AI2" s="131" t="s">
+      <c r="W2" s="131"/>
+      <c r="X2" s="131"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="131"/>
+      <c r="AA2" s="131"/>
+      <c r="AB2" s="131"/>
+      <c r="AC2" s="131"/>
+      <c r="AD2" s="131"/>
+      <c r="AE2" s="131"/>
+      <c r="AF2" s="131"/>
+      <c r="AG2" s="131"/>
+      <c r="AH2" s="132"/>
+      <c r="AI2" s="127" t="s">
         <v>84</v>
       </c>
-      <c r="AJ2" s="131"/>
-      <c r="AK2" s="131"/>
-      <c r="AL2" s="131"/>
-      <c r="AM2" s="131"/>
-      <c r="AN2" s="131"/>
-      <c r="AO2" s="131"/>
-      <c r="AP2" s="131"/>
-      <c r="AQ2" s="131"/>
-      <c r="AR2" s="131"/>
-      <c r="AS2" s="131"/>
-      <c r="AT2" s="131"/>
+      <c r="AJ2" s="127"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="127"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+      <c r="AT2" s="127"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="102"/>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
-      <c r="M3" s="131"/>
-      <c r="N3" s="131"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="131"/>
-      <c r="S3" s="131"/>
-      <c r="T3" s="131"/>
-      <c r="U3" s="131"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
       <c r="V3" s="100"/>
-      <c r="W3" s="130"/>
-      <c r="X3" s="130"/>
-      <c r="Y3" s="130"/>
-      <c r="Z3" s="130"/>
-      <c r="AA3" s="130"/>
-      <c r="AB3" s="130"/>
-      <c r="AC3" s="130"/>
-      <c r="AD3" s="130"/>
-      <c r="AE3" s="130"/>
-      <c r="AF3" s="130"/>
-      <c r="AG3" s="130"/>
+      <c r="W3" s="133"/>
+      <c r="X3" s="133"/>
+      <c r="Y3" s="133"/>
+      <c r="Z3" s="133"/>
+      <c r="AA3" s="133"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="133"/>
+      <c r="AD3" s="133"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="133"/>
+      <c r="AG3" s="133"/>
       <c r="AH3" s="101"/>
-      <c r="AI3" s="131"/>
-      <c r="AJ3" s="131"/>
-      <c r="AK3" s="131"/>
-      <c r="AL3" s="131"/>
-      <c r="AM3" s="131"/>
-      <c r="AN3" s="131"/>
-      <c r="AO3" s="131"/>
-      <c r="AP3" s="131"/>
-      <c r="AQ3" s="131"/>
-      <c r="AR3" s="131"/>
-      <c r="AS3" s="131"/>
-      <c r="AT3" s="131"/>
+      <c r="AI3" s="127"/>
+      <c r="AJ3" s="127"/>
+      <c r="AK3" s="127"/>
+      <c r="AL3" s="127"/>
+      <c r="AM3" s="127"/>
+      <c r="AN3" s="127"/>
+      <c r="AO3" s="127"/>
+      <c r="AP3" s="127"/>
+      <c r="AQ3" s="127"/>
+      <c r="AR3" s="127"/>
+      <c r="AS3" s="127"/>
+      <c r="AT3" s="127"/>
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
@@ -44278,7 +44279,7 @@
       <c r="C4" s="109" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>36</v>
       </c>
       <c r="E4" s="98" t="s">
@@ -44291,25 +44292,25 @@
       </c>
       <c r="I4" s="98"/>
       <c r="J4" s="98"/>
-      <c r="K4" s="114" t="s">
+      <c r="K4" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114" t="s">
+      <c r="L4" s="115"/>
+      <c r="M4" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114" t="s">
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114" t="s">
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="U4" s="114"/>
+      <c r="U4" s="115"/>
       <c r="V4" s="98" t="s">
         <v>63</v>
       </c>
@@ -44349,32 +44350,32 @@
       <c r="AH4" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="AI4" s="114" t="s">
+      <c r="AI4" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114" t="s">
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114" t="s">
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115" t="s">
         <v>81</v>
       </c>
-      <c r="AP4" s="114"/>
-      <c r="AQ4" s="114"/>
-      <c r="AR4" s="114" t="s">
+      <c r="AP4" s="115"/>
+      <c r="AQ4" s="115"/>
+      <c r="AR4" s="115" t="s">
         <v>82</v>
       </c>
-      <c r="AS4" s="114"/>
-      <c r="AT4" s="114"/>
+      <c r="AS4" s="115"/>
+      <c r="AT4" s="115"/>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="102"/>
       <c r="B5" s="110"/>
       <c r="C5" s="110"/>
-      <c r="D5" s="133"/>
+      <c r="D5" s="129"/>
       <c r="E5" s="6" t="s">
         <v>47</v>
       </c>
@@ -54079,6 +54080,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="VFnMg6bwIK0FJ+hXg+Dtd+0R27tX6NcWvnqifBdgLkgulIaVokTIorQbRkpmZ2hHT0okluXcfQNmt4SfblwBJA==" saltValue="d7cUXcFtfNp3GllyZxzJzg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="V2:AH3"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="B2:U3"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AR4:AT4"/>
     <mergeCell ref="AI2:AT3"/>
     <mergeCell ref="D4:D5"/>
@@ -54095,20 +54110,6 @@
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="M4:P4"/>
-    <mergeCell ref="AO4:AQ4"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="B2:U3"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="V2:AH3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 M5 N5 O5 P5 Q5 R5 S5 AI5 AJ5 AL5 AM5 AO5 AP5 AR5 AS5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -55442,13 +55443,13 @@
       <c r="A2" s="141" t="s">
         <v>254</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
       <c r="G2" s="135" t="s">
         <v>95</v>
       </c>
@@ -57985,13 +57986,13 @@
       <c r="J2" s="152"/>
       <c r="K2" s="152"/>
       <c r="L2" s="153"/>
-      <c r="M2" s="127" t="s">
+      <c r="M2" s="130" t="s">
         <v>258</v>
       </c>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="129"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="132"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="142"/>
@@ -58025,9 +58026,9 @@
       </c>
       <c r="L3" s="150"/>
       <c r="M3" s="100"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
       <c r="Q3" s="101"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -62007,29 +62008,29 @@
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="97"/>
       <c r="B3" s="142"/>
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="168" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="168"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="164" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="168" t="s">
         <v>212</v>
       </c>
-      <c r="G3" s="168"/>
-      <c r="H3" s="165"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="169"/>
       <c r="I3" s="26" t="s">
         <v>126</v>
       </c>
       <c r="J3" s="26"/>
-      <c r="K3" s="127" t="s">
+      <c r="K3" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="L3" s="128"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="127" t="s">
+      <c r="L3" s="131"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="130" t="s">
         <v>113</v>
       </c>
-      <c r="O3" s="129"/>
+      <c r="O3" s="132"/>
       <c r="P3" s="97" t="s">
         <v>229</v>
       </c>
@@ -62043,41 +62044,41 @@
         <v>115</v>
       </c>
       <c r="T3" s="102"/>
-      <c r="U3" s="169" t="s">
+      <c r="U3" s="162" t="s">
         <v>261</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="169" t="s">
+      <c r="V3" s="163"/>
+      <c r="W3" s="162" t="s">
         <v>260</v>
       </c>
-      <c r="X3" s="170"/>
+      <c r="X3" s="163"/>
       <c r="Y3" s="102" t="s">
         <v>116</v>
       </c>
       <c r="Z3" s="102"/>
       <c r="AA3" s="102"/>
       <c r="AB3" s="102"/>
-      <c r="AC3" s="114" t="s">
+      <c r="AC3" s="115" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="97"/>
       <c r="B4" s="142"/>
-      <c r="C4" s="162" t="s">
+      <c r="C4" s="166" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="164" t="s">
+      <c r="D4" s="168" t="s">
         <v>213</v>
       </c>
-      <c r="E4" s="165"/>
-      <c r="F4" s="166" t="s">
+      <c r="E4" s="169"/>
+      <c r="F4" s="170" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="164" t="s">
+      <c r="G4" s="168" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="165"/>
+      <c r="H4" s="169"/>
       <c r="I4" s="44" t="s">
         <v>124</v>
       </c>
@@ -62085,7 +62086,7 @@
         <v>85</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="130"/>
+      <c r="L4" s="133"/>
       <c r="M4" s="101"/>
       <c r="N4" s="100"/>
       <c r="O4" s="101"/>
@@ -62094,27 +62095,27 @@
       <c r="R4" s="97"/>
       <c r="S4" s="102"/>
       <c r="T4" s="102"/>
-      <c r="U4" s="171"/>
-      <c r="V4" s="172"/>
-      <c r="W4" s="171"/>
-      <c r="X4" s="172"/>
+      <c r="U4" s="164"/>
+      <c r="V4" s="165"/>
+      <c r="W4" s="164"/>
+      <c r="X4" s="165"/>
       <c r="Y4" s="102"/>
       <c r="Z4" s="102"/>
       <c r="AA4" s="102"/>
       <c r="AB4" s="102"/>
-      <c r="AC4" s="114"/>
+      <c r="AC4" s="115"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="97"/>
       <c r="B5" s="143"/>
-      <c r="C5" s="163"/>
+      <c r="C5" s="167"/>
       <c r="D5" s="71" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="167"/>
+      <c r="F5" s="171"/>
       <c r="G5" s="71" t="s">
         <v>0</v>
       </c>
@@ -62175,7 +62176,7 @@
       <c r="AB5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AC5" s="114"/>
+      <c r="AC5" s="115"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -68380,14 +68381,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="n15jzT3UDNrq52d/2Birqz9MmaAnGLtsoXzsWUc8XDs8jPyxo3tASuQIJK3whrU7Z0A7wrG1zSjGbXwKtZRR/w==" saltValue="aDVpfBfzxn3/sMJsNJZXZw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
-    <mergeCell ref="AC3:AC5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:T4"/>
-    <mergeCell ref="Y3:AB4"/>
-    <mergeCell ref="U3:V4"/>
-    <mergeCell ref="W3:X4"/>
     <mergeCell ref="K3:M4"/>
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="A2:A5"/>
@@ -68398,6 +68391,14 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="C3:E3"/>
+    <mergeCell ref="AC3:AC5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="S3:T4"/>
+    <mergeCell ref="Y3:AB4"/>
+    <mergeCell ref="U3:V4"/>
+    <mergeCell ref="W3:X4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y5:AB5 K5" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572FFABB-AE42-4937-BE52-0B59947384C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18521BD-DF0E-4F27-9D3E-9002B9472DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="MYxIjE9TGmSeigdKyCHOw3lH9f8J4EUilH0KgCjagDp50KBSM76xHJC56lRzGivfQGZgzVWvoHo9ImRSo1hl1A==" workbookSaltValue="vppty2a252bIjxbLncHPYg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="4" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="7" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -264,21 +264,6 @@
     <t>ADDITIONAL_BRANCHLINE_DETAILS</t>
   </si>
   <si>
-    <t>DEVICE_1_CODE</t>
-  </si>
-  <si>
-    <t>DEVICE_2_CODE</t>
-  </si>
-  <si>
-    <t>DEVICE_3_CODE</t>
-  </si>
-  <si>
-    <t>DEVICE_4_CODE</t>
-  </si>
-  <si>
-    <t>DEVICE_5_CODE</t>
-  </si>
-  <si>
     <t>STREAMER</t>
   </si>
   <si>
@@ -289,9 +274,6 @@
   </si>
   <si>
     <t>TOWED_OBJECTS</t>
-  </si>
-  <si>
-    <t>TORI_LINE_DETAILS</t>
   </si>
   <si>
     <t>CONFIGURATION_NUMBER</t>
@@ -696,9 +678,6 @@
     <t>GEAR</t>
   </si>
   <si>
-    <t>LINE_SETTER/SHOOTER</t>
-  </si>
-  <si>
     <t>Longline general gear specifications &gt; Mitigation devices</t>
   </si>
   <si>
@@ -766,18 +745,6 @@
   </si>
   <si>
     <t>IOTC_ID</t>
-  </si>
-  <si>
-    <t>LINE_LENGTH_MAX (M)</t>
-  </si>
-  <si>
-    <t>LINE_LENGTH_MIN (M)</t>
-  </si>
-  <si>
-    <t>DISTANCE_BETWEEN_STREAMERS (M)</t>
-  </si>
-  <si>
-    <t>TORI_LINE_ATTACHED_HEIGHT (M)</t>
   </si>
   <si>
     <t>PERSONNEL</t>
@@ -915,7 +882,7 @@
     <t>DIAMETER_CM</t>
   </si>
   <si>
-    <t>TORR_LINE_LENGTH</t>
+    <t>TORI_LINE_LENGTH</t>
   </si>
   <si>
     <t>FISH_STORAGE_CAPACITY_M3</t>
@@ -931,6 +898,39 @@
   </si>
   <si>
     <t>REGISTRATION_NUMBER</t>
+  </si>
+  <si>
+    <t>TORI LINE DETAILS</t>
+  </si>
+  <si>
+    <t>LINE_LENGTH_MAX_M</t>
+  </si>
+  <si>
+    <t>LINE_LENGTH_MIN_M</t>
+  </si>
+  <si>
+    <t>DISTANCE_BETWEEN_STREAMERS_M</t>
+  </si>
+  <si>
+    <t>TORI_LINE_ATTACHED_HEIGHT_M</t>
+  </si>
+  <si>
+    <t>DEVICE_1</t>
+  </si>
+  <si>
+    <t>LINE_SETTER_SHOOTER</t>
+  </si>
+  <si>
+    <t>DEVICE_2</t>
+  </si>
+  <si>
+    <t>DEVICE_3</t>
+  </si>
+  <si>
+    <t>DEVICE_4</t>
+  </si>
+  <si>
+    <t>DEVICE_5</t>
   </si>
 </sst>
 </file>
@@ -997,14 +997,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -1040,6 +1032,15 @@
       <b/>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1364,7 +1365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1432,9 +1433,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1468,7 +1466,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1489,7 +1487,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1509,17 +1507,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1541,25 +1532,25 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1853,39 +1844,39 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1895,11 +1886,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1917,6 +1908,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2260,282 +2278,282 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="79" t="s">
-        <v>244</v>
+      <c r="B2" s="76" t="s">
+        <v>233</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="81"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="82"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="42"/>
-      <c r="C4" s="43" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" s="44"/>
+      <c r="F4" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" s="45">
+        <v>1</v>
+      </c>
+      <c r="H4" s="46"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
+    </row>
+    <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B6" s="47"/>
+      <c r="C6" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="47"/>
+      <c r="C8" s="82" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="82"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="82" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="82"/>
+      <c r="H8" s="49"/>
+    </row>
+    <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="47"/>
+      <c r="C9" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="52"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="49"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
+      <c r="C10" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="G10" s="52"/>
+      <c r="H10" s="49"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="47"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="49"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="47"/>
+      <c r="C12" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="55"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
+      <c r="C13" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="49"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="49"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="49"/>
+    </row>
+    <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B16" s="47"/>
+      <c r="C16" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="D4" s="44" t="s">
-        <v>234</v>
-      </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="43" t="s">
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="47"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="49"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="47"/>
+      <c r="C18" s="53" t="s">
         <v>225</v>
       </c>
-      <c r="G4" s="46">
-        <v>1</v>
-      </c>
-      <c r="H4" s="47"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="48"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="50"/>
-    </row>
-    <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B6" s="48"/>
-      <c r="C6" s="51" t="s">
+      <c r="D18" s="57"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="49"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="47"/>
+      <c r="C19" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="85" t="s">
-        <v>246</v>
+      <c r="D19" s="57"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="49"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="47"/>
+      <c r="C20" s="75" t="s">
+        <v>191</v>
       </c>
-      <c r="D8" s="85"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="85" t="s">
-        <v>245</v>
-      </c>
-      <c r="G8" s="85"/>
-      <c r="H8" s="50"/>
-    </row>
-    <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="52" t="s">
+      <c r="D20" s="57"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="49"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="47"/>
+      <c r="C21" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="50"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="54" t="s">
-        <v>229</v>
+      <c r="D21" s="57"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="49"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="47"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="49"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="47"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="49"/>
+    </row>
+    <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B24" s="47"/>
+      <c r="C24" s="50" t="s">
+        <v>193</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49" t="s">
-        <v>229</v>
-      </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="50"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="50"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="54" t="s">
-        <v>230</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="50"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="50"/>
-    </row>
-    <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B16" s="48"/>
-      <c r="C16" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="50"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="48"/>
-      <c r="C18" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="50"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="48"/>
-      <c r="C19" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="50"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="48"/>
-      <c r="C20" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="48"/>
-      <c r="C21" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="48"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="48"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="50"/>
-    </row>
-    <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B24" s="48"/>
-      <c r="C24" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="49"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="48"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="50"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="49"/>
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="48"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="50"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="49"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
-      <c r="D28" s="65"/>
+      <c r="D28" s="64"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
@@ -2576,7 +2594,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2584,45 +2602,45 @@
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="92" t="s">
-        <v>216</v>
+      <c r="B2" s="89" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="120" t="s">
-        <v>81</v>
+      <c r="C2" s="117" t="s">
+        <v>75</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="94" t="s">
-        <v>90</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="91" t="s">
+        <v>84</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="23" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
-      <c r="E5" s="72" t="s">
-        <v>193</v>
+      <c r="E5" s="69" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4070,7 +4088,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4089,115 +4107,115 @@
       <c r="P1" s="16"/>
     </row>
     <row r="2" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="142" t="s">
-        <v>216</v>
+      <c r="B2" s="139" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="128" t="s">
-        <v>81</v>
+      <c r="C2" s="125" t="s">
+        <v>75</v>
       </c>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="130"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="127"/>
     </row>
     <row r="3" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="128" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="130"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="143"/>
-      <c r="C4" s="135" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="135" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="113" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="135" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="135" t="s">
+      <c r="A3" s="89"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="125" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="135" t="s">
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="127"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="89"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="132" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="132" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="121" t="s">
-        <v>219</v>
+      <c r="E4" s="132" t="s">
+        <v>101</v>
       </c>
-      <c r="K4" s="99" t="s">
-        <v>110</v>
+      <c r="F4" s="110" t="s">
+        <v>92</v>
       </c>
-      <c r="L4" s="103"/>
-      <c r="M4" s="145" t="s">
-        <v>108</v>
+      <c r="G4" s="132" t="s">
+        <v>103</v>
       </c>
-      <c r="N4" s="146"/>
-      <c r="O4" s="146"/>
-      <c r="P4" s="147"/>
+      <c r="H4" s="132" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="132" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="118" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="96" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="100"/>
+      <c r="M4" s="142" t="s">
+        <v>102</v>
+      </c>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="144"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="144"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="123"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="120"/>
       <c r="K5" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -7849,7 +7867,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7857,47 +7875,47 @@
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="92" t="s">
-        <v>216</v>
+      <c r="B2" s="89" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="120" t="s">
-        <v>81</v>
+      <c r="C2" s="117" t="s">
+        <v>75</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="145" t="s">
-        <v>154</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="142" t="s">
+        <v>148</v>
       </c>
-      <c r="D3" s="146"/>
-      <c r="E3" s="147"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="144"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="145" t="s">
-        <v>153</v>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="142" t="s">
+        <v>147</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="147"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="144"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="23" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -9339,7 +9357,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9348,53 +9366,53 @@
       <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="92" t="s">
-        <v>216</v>
+      <c r="B2" s="89" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="120" t="s">
-        <v>81</v>
+      <c r="C2" s="117" t="s">
+        <v>75</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="145" t="s">
-        <v>155</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="142" t="s">
+        <v>149</v>
       </c>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="147"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="144"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="145" t="s">
-        <v>151</v>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="142" t="s">
+        <v>145</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="147"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="144"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="23" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -11045,7 +11063,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -11065,126 +11083,126 @@
       <c r="Q1" s="16"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="92" t="s">
-        <v>216</v>
+      <c r="B2" s="89" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="75" t="s">
-        <v>119</v>
+      <c r="C2" s="72" t="s">
+        <v>113</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="77"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="74"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="133" t="s">
-        <v>184</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="130" t="s">
+        <v>178</v>
       </c>
-      <c r="D3" s="137"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="133" t="s">
-        <v>185</v>
+      <c r="D3" s="134"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="130" t="s">
+        <v>179</v>
       </c>
-      <c r="G3" s="137"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="124" t="s">
+      <c r="G3" s="134"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="121" t="s">
+        <v>105</v>
+      </c>
+      <c r="J3" s="116" t="s">
+        <v>110</v>
+      </c>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="117" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="119" t="s">
-        <v>116</v>
+      <c r="O3" s="117" t="s">
+        <v>213</v>
       </c>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="120" t="s">
-        <v>117</v>
+      <c r="P3" s="117" t="s">
+        <v>180</v>
       </c>
-      <c r="O3" s="120" t="s">
-        <v>220</v>
+      <c r="Q3" s="145" t="s">
+        <v>112</v>
       </c>
-      <c r="P3" s="120" t="s">
-        <v>186</v>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="132" t="s">
+        <v>190</v>
       </c>
-      <c r="Q3" s="148" t="s">
-        <v>118</v>
+      <c r="D4" s="106" t="s">
+        <v>177</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="135" t="s">
-        <v>196</v>
+      <c r="E4" s="108"/>
+      <c r="F4" s="132" t="s">
+        <v>190</v>
       </c>
-      <c r="D4" s="109" t="s">
-        <v>183</v>
+      <c r="G4" s="106" t="s">
+        <v>177</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="135" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="109" t="s">
-        <v>183</v>
-      </c>
-      <c r="H4" s="111"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120"/>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="148"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="145"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="67" t="s">
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="136"/>
-      <c r="G5" s="67" t="s">
+      <c r="F5" s="133"/>
+      <c r="G5" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="H5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="124"/>
+      <c r="I5" s="121"/>
       <c r="J5" s="19" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
-      <c r="N5" s="120"/>
-      <c r="O5" s="120"/>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="148"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="145"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -15037,48 +15055,48 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
       <c r="D1" s="16"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="92" t="s">
-        <v>216</v>
+      <c r="B2" s="89" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="120" t="s">
-        <v>119</v>
+      <c r="C2" s="117" t="s">
+        <v>113</v>
       </c>
-      <c r="D2" s="120"/>
+      <c r="D2" s="117"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="149" t="s">
-        <v>156</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="146" t="s">
+        <v>150</v>
       </c>
-      <c r="D3" s="150"/>
+      <c r="D3" s="147"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="149" t="s">
-        <v>82</v>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="146" t="s">
+        <v>76</v>
       </c>
-      <c r="D4" s="150"/>
+      <c r="D4" s="147"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -16317,7 +16335,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -16332,89 +16350,89 @@
       <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="92" t="s">
-        <v>216</v>
+      <c r="B2" s="89" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="92" t="s">
-        <v>221</v>
+      <c r="C2" s="89" t="s">
+        <v>214</v>
       </c>
-      <c r="D2" s="94" t="s">
-        <v>121</v>
+      <c r="D2" s="91" t="s">
+        <v>115</v>
       </c>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="148" t="s">
-        <v>93</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="145" t="s">
+        <v>87</v>
       </c>
-      <c r="E3" s="151" t="s">
-        <v>210</v>
+      <c r="E3" s="148" t="s">
+        <v>204</v>
       </c>
-      <c r="F3" s="152"/>
-      <c r="G3" s="148" t="s">
-        <v>158</v>
+      <c r="F3" s="149"/>
+      <c r="G3" s="145" t="s">
+        <v>152</v>
       </c>
-      <c r="H3" s="120" t="s">
-        <v>195</v>
+      <c r="H3" s="117" t="s">
+        <v>189</v>
       </c>
-      <c r="I3" s="119" t="s">
-        <v>122</v>
+      <c r="I3" s="116" t="s">
+        <v>116</v>
       </c>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="73" t="s">
+      <c r="A5" s="89"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="74" t="s">
-        <v>209</v>
+      <c r="F5" s="71" t="s">
+        <v>203</v>
       </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="120"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="117"/>
       <c r="I5" s="12" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>30</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -19283,7 +19301,7 @@
   <sheetData>
     <row r="1" spans="1:24" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -19310,143 +19328,143 @@
       <c r="X1" s="15"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
-        <v>211</v>
+      <c r="A2" s="154" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="157" t="s">
-        <v>216</v>
+      <c r="B2" s="154" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="157" t="s">
-        <v>221</v>
+      <c r="C2" s="154" t="s">
+        <v>214</v>
       </c>
-      <c r="D2" s="157" t="s">
-        <v>222</v>
+      <c r="D2" s="154" t="s">
+        <v>215</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="158"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="160" t="s">
-        <v>157</v>
+      <c r="A3" s="155"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="157" t="s">
+        <v>151</v>
       </c>
-      <c r="F3" s="160" t="s">
-        <v>158</v>
+      <c r="F3" s="157" t="s">
+        <v>152</v>
       </c>
-      <c r="G3" s="92" t="s">
+      <c r="G3" s="89" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="90" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
+      <c r="R3" s="152" t="s">
+        <v>123</v>
+      </c>
+      <c r="S3" s="103" t="s">
+        <v>198</v>
+      </c>
+      <c r="T3" s="105"/>
+      <c r="U3" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="V3" s="90"/>
+      <c r="W3" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="93" t="s">
-        <v>125</v>
-      </c>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93" t="s">
-        <v>122</v>
-      </c>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="155" t="s">
-        <v>129</v>
-      </c>
-      <c r="S3" s="106" t="s">
-        <v>204</v>
-      </c>
-      <c r="T3" s="108"/>
-      <c r="U3" s="93" t="s">
-        <v>135</v>
-      </c>
-      <c r="V3" s="93"/>
-      <c r="W3" s="93" t="s">
-        <v>130</v>
-      </c>
-      <c r="X3" s="93"/>
+      <c r="X3" s="90"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="159"/>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
+      <c r="A4" s="156"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
       <c r="G4" s="23" t="s">
         <v>32</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="O4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>126</v>
+      <c r="Q4" s="12" t="s">
+        <v>121</v>
       </c>
-      <c r="Q4" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="R4" s="156"/>
+      <c r="R4" s="153"/>
       <c r="S4" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="U4" s="8" t="s">
         <v>31</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -24718,7 +24736,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -24736,101 +24754,101 @@
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
       <c r="Q1" s="15"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
-        <v>211</v>
+      <c r="A2" s="154" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="157" t="s">
-        <v>216</v>
+      <c r="B2" s="154" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="157" t="s">
-        <v>221</v>
+      <c r="C2" s="154" t="s">
+        <v>214</v>
       </c>
-      <c r="D2" s="157" t="s">
-        <v>222</v>
+      <c r="D2" s="154" t="s">
+        <v>215</v>
       </c>
-      <c r="E2" s="162" t="s">
-        <v>150</v>
+      <c r="E2" s="159" t="s">
+        <v>144</v>
       </c>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="158"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="164" t="s">
-        <v>132</v>
+      <c r="A3" s="155"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="161" t="s">
+        <v>126</v>
       </c>
-      <c r="F3" s="164" t="s">
-        <v>133</v>
+      <c r="F3" s="161" t="s">
+        <v>127</v>
       </c>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="163" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="165" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="92" t="s">
+        <v>145</v>
+      </c>
+      <c r="J3" s="93"/>
+      <c r="K3" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="L3" s="93"/>
+      <c r="M3" s="165" t="s">
+        <v>140</v>
+      </c>
+      <c r="N3" s="167" t="s">
+        <v>154</v>
+      </c>
+      <c r="O3" s="167" t="s">
+        <v>141</v>
+      </c>
+      <c r="P3" s="165" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q3" s="167" t="s">
         <v>142</v>
       </c>
-      <c r="H3" s="168" t="s">
+      <c r="R3" s="167" t="s">
         <v>143</v>
       </c>
-      <c r="I3" s="95" t="s">
-        <v>151</v>
+      <c r="S3" s="122" t="s">
+        <v>124</v>
       </c>
-      <c r="J3" s="96"/>
-      <c r="K3" s="95" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="96"/>
-      <c r="M3" s="168" t="s">
-        <v>146</v>
-      </c>
-      <c r="N3" s="170" t="s">
-        <v>160</v>
-      </c>
-      <c r="O3" s="170" t="s">
-        <v>147</v>
-      </c>
-      <c r="P3" s="168" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q3" s="170" t="s">
-        <v>148</v>
-      </c>
-      <c r="R3" s="170" t="s">
-        <v>149</v>
-      </c>
-      <c r="S3" s="125" t="s">
-        <v>130</v>
-      </c>
-      <c r="T3" s="125"/>
+      <c r="T3" s="122"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="159"/>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="165"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="169"/>
+      <c r="A4" s="156"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="166"/>
       <c r="I4" s="12" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>32</v>
@@ -24839,19 +24857,19 @@
         <v>65</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
-      <c r="M4" s="169"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="35" t="s">
-        <v>131</v>
+      <c r="M4" s="166"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="166"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="34" t="s">
+        <v>125</v>
       </c>
-      <c r="T4" s="35" t="s">
-        <v>201</v>
+      <c r="T4" s="34" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -29318,7 +29336,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -29332,53 +29350,53 @@
       <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
-        <v>211</v>
+      <c r="A2" s="154" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="157" t="s">
-        <v>216</v>
+      <c r="B2" s="154" t="s">
+        <v>209</v>
       </c>
-      <c r="C2" s="157" t="s">
-        <v>221</v>
+      <c r="C2" s="154" t="s">
+        <v>214</v>
       </c>
-      <c r="D2" s="157" t="s">
-        <v>222</v>
+      <c r="D2" s="154" t="s">
+        <v>215</v>
       </c>
-      <c r="E2" s="171" t="s">
-        <v>140</v>
+      <c r="E2" s="168" t="s">
+        <v>134</v>
       </c>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="173"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="170"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="159"/>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
+      <c r="A3" s="156"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
       <c r="E3" s="25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="34" t="s">
         <v>32</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -32038,7 +32056,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="17" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -32065,181 +32083,181 @@
       <c r="X1" s="16"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
-        <v>211</v>
+      <c r="A2" s="86" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="97" t="s">
-        <v>288</v>
+      <c r="B2" s="94" t="s">
+        <v>277</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98" t="s">
-        <v>289</v>
+      <c r="C2" s="94"/>
+      <c r="D2" s="95" t="s">
+        <v>278</v>
       </c>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="138" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="193"/>
-      <c r="P2" s="193"/>
-      <c r="Q2" s="193"/>
-      <c r="R2" s="193"/>
-      <c r="S2" s="193"/>
-      <c r="T2" s="193"/>
-      <c r="U2" s="193"/>
-      <c r="V2" s="193"/>
-      <c r="W2" s="193"/>
-      <c r="X2" s="139"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="190"/>
+      <c r="Q2" s="190"/>
+      <c r="R2" s="190"/>
+      <c r="S2" s="190"/>
+      <c r="T2" s="190"/>
+      <c r="U2" s="190"/>
+      <c r="V2" s="190"/>
+      <c r="W2" s="190"/>
+      <c r="X2" s="136"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="99" t="s">
-        <v>179</v>
+      <c r="A3" s="87"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="96" t="s">
+        <v>173</v>
       </c>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="99" t="s">
-        <v>180</v>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="96" t="s">
+        <v>174</v>
       </c>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="140"/>
-      <c r="O3" s="194"/>
-      <c r="P3" s="194"/>
-      <c r="Q3" s="194"/>
-      <c r="R3" s="194"/>
-      <c r="S3" s="194"/>
-      <c r="T3" s="194"/>
-      <c r="U3" s="194"/>
-      <c r="V3" s="194"/>
-      <c r="W3" s="194"/>
-      <c r="X3" s="141"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="137"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="191"/>
+      <c r="Q3" s="191"/>
+      <c r="R3" s="191"/>
+      <c r="S3" s="191"/>
+      <c r="T3" s="191"/>
+      <c r="U3" s="191"/>
+      <c r="V3" s="191"/>
+      <c r="W3" s="191"/>
+      <c r="X3" s="138"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="95" t="s">
-        <v>177</v>
+      <c r="A4" s="87"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="92" t="s">
+        <v>171</v>
       </c>
-      <c r="E4" s="96"/>
-      <c r="F4" s="95" t="s">
-        <v>178</v>
+      <c r="E4" s="93"/>
+      <c r="F4" s="92" t="s">
+        <v>172</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="104" t="s">
-        <v>196</v>
+      <c r="G4" s="93"/>
+      <c r="H4" s="101" t="s">
+        <v>190</v>
       </c>
-      <c r="I4" s="95" t="s">
-        <v>177</v>
+      <c r="I4" s="92" t="s">
+        <v>171</v>
       </c>
-      <c r="J4" s="96"/>
-      <c r="K4" s="95" t="s">
-        <v>178</v>
+      <c r="J4" s="93"/>
+      <c r="K4" s="92" t="s">
+        <v>172</v>
       </c>
-      <c r="L4" s="96"/>
-      <c r="M4" s="101" t="s">
-        <v>196</v>
+      <c r="L4" s="93"/>
+      <c r="M4" s="98" t="s">
+        <v>190</v>
       </c>
-      <c r="N4" s="92" t="s">
-        <v>290</v>
+      <c r="N4" s="89" t="s">
+        <v>279</v>
       </c>
-      <c r="O4" s="92"/>
-      <c r="P4" s="93" t="s">
+      <c r="O4" s="89"/>
+      <c r="P4" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="93"/>
-      <c r="S4" s="93"/>
-      <c r="T4" s="93"/>
-      <c r="U4" s="93" t="s">
+      <c r="Q4" s="90"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="90"/>
+      <c r="U4" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="93"/>
-      <c r="W4" s="93"/>
-      <c r="X4" s="93"/>
+      <c r="V4" s="90"/>
+      <c r="W4" s="90"/>
+      <c r="X4" s="90"/>
     </row>
     <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="91"/>
-      <c r="B5" s="66" t="s">
-        <v>236</v>
+      <c r="A5" s="88"/>
+      <c r="B5" s="65" t="s">
+        <v>229</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="178" t="s">
-        <v>247</v>
+      <c r="D5" s="175" t="s">
+        <v>236</v>
       </c>
-      <c r="E5" s="178" t="s">
+      <c r="E5" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="105"/>
-      <c r="I5" s="178" t="s">
-        <v>247</v>
+      <c r="H5" s="102"/>
+      <c r="I5" s="175" t="s">
+        <v>236</v>
       </c>
-      <c r="J5" s="178" t="s">
+      <c r="J5" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="102"/>
-      <c r="N5" s="66" t="s">
+      <c r="M5" s="99"/>
+      <c r="N5" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="66" t="s">
+      <c r="O5" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="41" t="s">
+      <c r="P5" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="Q5" s="41" t="s">
+      <c r="Q5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="R5" s="41" t="s">
+      <c r="R5" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="S5" s="41" t="s">
+      <c r="S5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="T5" s="41" t="s">
+      <c r="T5" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="U5" s="179" t="s">
-        <v>248</v>
+      <c r="U5" s="176" t="s">
+        <v>237</v>
       </c>
-      <c r="V5" s="179" t="s">
-        <v>249</v>
+      <c r="V5" s="176" t="s">
+        <v>238</v>
       </c>
-      <c r="W5" s="179" t="s">
-        <v>250</v>
+      <c r="W5" s="176" t="s">
+        <v>239</v>
       </c>
-      <c r="X5" s="179" t="s">
-        <v>251</v>
+      <c r="X5" s="176" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -37483,7 +37501,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -37502,8 +37520,8 @@
       <c r="P1" s="16"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>211</v>
+      <c r="A2" s="94" t="s">
+        <v>205</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>26</v>
@@ -37524,102 +37542,102 @@
       <c r="P2" s="27"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="109" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="106" t="s">
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="107"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="187" t="s">
+      <c r="H3" s="104"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="40" t="s">
-        <v>212</v>
+      <c r="K3" s="39" t="s">
+        <v>206</v>
       </c>
-      <c r="L3" s="109" t="s">
+      <c r="L3" s="106" t="s">
+        <v>230</v>
+      </c>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="108"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="94"/>
+      <c r="B4" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="177" t="s">
         <v>241</v>
       </c>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="111"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="180" t="s">
-        <v>252</v>
-      </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="104" t="s">
+      <c r="E4" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="98" t="s">
+      <c r="F4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="181" t="s">
-        <v>247</v>
+      <c r="G4" s="178" t="s">
+        <v>236</v>
       </c>
-      <c r="H4" s="182" t="s">
+      <c r="H4" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="195" t="s">
-        <v>291</v>
+      <c r="I4" s="192" t="s">
+        <v>280</v>
       </c>
-      <c r="J4" s="181" t="s">
-        <v>253</v>
+      <c r="J4" s="178" t="s">
+        <v>242</v>
       </c>
-      <c r="K4" s="184" t="s">
-        <v>254</v>
+      <c r="K4" s="181" t="s">
+        <v>243</v>
       </c>
-      <c r="L4" s="92" t="s">
+      <c r="L4" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="92"/>
-      <c r="N4" s="92" t="s">
+      <c r="M4" s="89"/>
+      <c r="N4" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="92"/>
-      <c r="P4" s="98" t="s">
+      <c r="O4" s="89"/>
+      <c r="P4" s="95" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="195"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="185"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="192"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="182"/>
       <c r="L5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="186" t="s">
+      <c r="M5" s="183" t="s">
         <v>5</v>
       </c>
       <c r="N5" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="186" t="s">
+      <c r="O5" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="98"/>
+      <c r="P5" s="95"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -41285,7 +41303,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -41299,88 +41317,88 @@
       <c r="K1" s="16"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>211</v>
+      <c r="A2" s="94" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="99" t="s">
+      <c r="A4" s="94"/>
+      <c r="B4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="104" t="s">
-        <v>196</v>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="101" t="s">
+        <v>190</v>
       </c>
-      <c r="G4" s="99" t="s">
+      <c r="G4" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="101" t="s">
-        <v>196</v>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="98" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="97"/>
-      <c r="B5" s="178" t="s">
-        <v>247</v>
+      <c r="A5" s="94"/>
+      <c r="B5" s="175" t="s">
+        <v>236</v>
       </c>
-      <c r="C5" s="178" t="s">
+      <c r="C5" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="191" t="s">
+      <c r="D5" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="191" t="s">
+      <c r="E5" s="188" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="105"/>
-      <c r="G5" s="178" t="s">
-        <v>247</v>
+      <c r="F5" s="102"/>
+      <c r="G5" s="175" t="s">
+        <v>236</v>
       </c>
-      <c r="H5" s="178" t="s">
+      <c r="H5" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="191" t="s">
+      <c r="I5" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="191" t="s">
+      <c r="J5" s="188" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="99"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -44061,7 +44079,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -44105,207 +44123,207 @@
       <c r="AO1" s="15"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>211</v>
+      <c r="A2" s="94" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="115" t="s">
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="116"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="115" t="s">
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
+      <c r="AE2" s="113"/>
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="114"/>
+      <c r="AH2" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="AI2" s="116"/>
-      <c r="AJ2" s="116"/>
-      <c r="AK2" s="116"/>
-      <c r="AL2" s="116"/>
-      <c r="AM2" s="116"/>
-      <c r="AN2" s="116"/>
-      <c r="AO2" s="117"/>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="113"/>
+      <c r="AK2" s="113"/>
+      <c r="AL2" s="113"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="114"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="95"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="118"/>
-      <c r="X3" s="118"/>
-      <c r="Y3" s="118"/>
-      <c r="Z3" s="118"/>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="118"/>
-      <c r="AD3" s="118"/>
-      <c r="AE3" s="118"/>
-      <c r="AF3" s="118"/>
-      <c r="AG3" s="96"/>
-      <c r="AH3" s="95"/>
-      <c r="AI3" s="118"/>
-      <c r="AJ3" s="118"/>
-      <c r="AK3" s="118"/>
-      <c r="AL3" s="118"/>
-      <c r="AM3" s="118"/>
-      <c r="AN3" s="118"/>
-      <c r="AO3" s="96"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="116"/>
+      <c r="R3" s="116"/>
+      <c r="S3" s="116"/>
+      <c r="T3" s="116"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="93"/>
+      <c r="AH3" s="92"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="93"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="104" t="s">
-        <v>256</v>
+      <c r="A4" s="94"/>
+      <c r="B4" s="101" t="s">
+        <v>245</v>
       </c>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="101" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="186" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="90" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="101" t="s">
+        <v>276</v>
+      </c>
+      <c r="L4" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" s="90"/>
+      <c r="U4" s="95" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="189" t="s">
-        <v>258</v>
-      </c>
-      <c r="E4" s="93" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="104" t="s">
-        <v>287</v>
-      </c>
-      <c r="L4" s="93" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="93"/>
-      <c r="S4" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" s="93"/>
-      <c r="U4" s="98" t="s">
-        <v>268</v>
-      </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="W4" s="98" t="s">
+      <c r="W4" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="X4" s="98" t="s">
+      <c r="X4" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="Y4" s="98" t="s">
+      <c r="Y4" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="Z4" s="98" t="s">
+      <c r="Z4" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="AA4" s="98" t="s">
+      <c r="AA4" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="AB4" s="98" t="s">
+      <c r="AB4" s="95" t="s">
         <v>50</v>
       </c>
-      <c r="AC4" s="98" t="s">
+      <c r="AC4" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="AD4" s="98" t="s">
+      <c r="AD4" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="AE4" s="98" t="s">
+      <c r="AE4" s="95" t="s">
         <v>53</v>
       </c>
-      <c r="AF4" s="98" t="s">
-        <v>260</v>
+      <c r="AF4" s="95" t="s">
+        <v>249</v>
       </c>
-      <c r="AG4" s="98" t="s">
+      <c r="AG4" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="106" t="s">
+      <c r="AH4" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="AI4" s="108"/>
-      <c r="AJ4" s="93" t="s">
+      <c r="AI4" s="105"/>
+      <c r="AJ4" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="AK4" s="93"/>
-      <c r="AL4" s="93" t="s">
+      <c r="AK4" s="90"/>
+      <c r="AL4" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="AM4" s="93"/>
-      <c r="AN4" s="93" t="s">
+      <c r="AM4" s="90"/>
+      <c r="AN4" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="AO4" s="93"/>
+      <c r="AO4" s="90"/>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A5" s="97"/>
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="190"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="187"/>
       <c r="E5" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="188" t="s">
-        <v>255</v>
+      <c r="G5" s="185" t="s">
+        <v>244</v>
       </c>
       <c r="H5" s="25" t="s">
         <v>37</v>
@@ -44313,73 +44331,73 @@
       <c r="I5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="188" t="s">
+      <c r="J5" s="185" t="s">
+        <v>244</v>
+      </c>
+      <c r="K5" s="102"/>
+      <c r="L5" s="176" t="s">
+        <v>248</v>
+      </c>
+      <c r="M5" s="176" t="s">
+        <v>251</v>
+      </c>
+      <c r="N5" s="176" t="s">
+        <v>252</v>
+      </c>
+      <c r="O5" s="176" t="s">
+        <v>253</v>
+      </c>
+      <c r="P5" s="176" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q5" s="176" t="s">
         <v>255</v>
       </c>
-      <c r="K5" s="105"/>
-      <c r="L5" s="179" t="s">
-        <v>259</v>
-      </c>
-      <c r="M5" s="179" t="s">
-        <v>262</v>
-      </c>
-      <c r="N5" s="179" t="s">
-        <v>263</v>
-      </c>
-      <c r="O5" s="179" t="s">
-        <v>264</v>
-      </c>
-      <c r="P5" s="179" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q5" s="179" t="s">
-        <v>266</v>
-      </c>
-      <c r="R5" s="179" t="s">
-        <v>267</v>
+      <c r="R5" s="176" t="s">
+        <v>256</v>
       </c>
       <c r="S5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="188" t="s">
+      <c r="T5" s="185" t="s">
+        <v>250</v>
+      </c>
+      <c r="U5" s="95"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="95"/>
+      <c r="X5" s="95"/>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="95"/>
+      <c r="AA5" s="95"/>
+      <c r="AB5" s="95"/>
+      <c r="AC5" s="95"/>
+      <c r="AD5" s="95"/>
+      <c r="AE5" s="95"/>
+      <c r="AF5" s="95"/>
+      <c r="AG5" s="95"/>
+      <c r="AH5" s="176" t="s">
+        <v>258</v>
+      </c>
+      <c r="AI5" s="176" t="s">
+        <v>259</v>
+      </c>
+      <c r="AJ5" s="176" t="s">
+        <v>260</v>
+      </c>
+      <c r="AK5" s="176" t="s">
         <v>261</v>
       </c>
-      <c r="U5" s="98"/>
-      <c r="V5" s="98"/>
-      <c r="W5" s="98"/>
-      <c r="X5" s="98"/>
-      <c r="Y5" s="98"/>
-      <c r="Z5" s="98"/>
-      <c r="AA5" s="98"/>
-      <c r="AB5" s="98"/>
-      <c r="AC5" s="98"/>
-      <c r="AD5" s="98"/>
-      <c r="AE5" s="98"/>
-      <c r="AF5" s="98"/>
-      <c r="AG5" s="98"/>
-      <c r="AH5" s="179" t="s">
-        <v>269</v>
+      <c r="AL5" s="176" t="s">
+        <v>262</v>
       </c>
-      <c r="AI5" s="179" t="s">
-        <v>270</v>
+      <c r="AM5" s="176" t="s">
+        <v>263</v>
       </c>
-      <c r="AJ5" s="179" t="s">
-        <v>271</v>
+      <c r="AN5" s="176" t="s">
+        <v>264</v>
       </c>
-      <c r="AK5" s="179" t="s">
-        <v>272</v>
-      </c>
-      <c r="AL5" s="179" t="s">
-        <v>273</v>
-      </c>
-      <c r="AM5" s="179" t="s">
-        <v>274</v>
-      </c>
-      <c r="AN5" s="179" t="s">
-        <v>275</v>
-      </c>
-      <c r="AO5" s="179" t="s">
-        <v>276</v>
+      <c r="AO5" s="176" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -52983,7 +53001,7 @@
       <c r="AO205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bdyCQ1qbwvPeawoc8hB7j1eM3+0at+J/KVx8jfWYor+mGz6e52Vxp8Kxhppii9kljlqncXdac0Stj3/E8g2WWA==" saltValue="Ul4zYB9s4JdZdrH9J5pmTw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH2:AO3"/>
@@ -53059,49 +53077,49 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>211</v>
+      <c r="A2" s="94" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="97" t="s">
-        <v>213</v>
+      <c r="A3" s="130"/>
+      <c r="B3" s="94" t="s">
+        <v>287</v>
       </c>
-      <c r="C3" s="134" t="s">
+      <c r="C3" s="131" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="94" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="133"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="97"/>
+      <c r="A4" s="130"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="94"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="133"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="97"/>
+      <c r="A5" s="130"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="94"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="192"/>
+      <c r="B6" s="189"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
@@ -54300,7 +54318,7 @@
       <c r="D205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nrA/J4zBGR80COd2iPCeyQKzj6apxsLrJ+dUy7JPrvb7JclMTfUI4MLaxhlDQ6TMG8+ikPCi0bHA9yGu34hY+A==" saltValue="VjnPj9tjX0orMQKjAOrpTA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uvTpkrLsktAunA9S+XlYlTnvwA2HnPU9YSSMq5ZpoUHDC+2Hym15nxRB2vQ8B4b7AViQn0daTOn9hKRllZBaLg==" saltValue="Q9Dmn/rAHhKzakhl7MM4DQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="5">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -54334,7 +54352,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -54347,63 +54365,63 @@
       <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
-        <v>211</v>
+      <c r="A2" s="86" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="98" t="s">
-        <v>80</v>
+      <c r="B2" s="95" t="s">
+        <v>74</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="115" t="s">
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="117"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="114"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="104" t="s">
-        <v>277</v>
+      <c r="A3" s="87"/>
+      <c r="B3" s="101" t="s">
+        <v>266</v>
       </c>
-      <c r="C3" s="104" t="s">
-        <v>278</v>
+      <c r="C3" s="101" t="s">
+        <v>267</v>
       </c>
-      <c r="D3" s="181" t="s">
-        <v>279</v>
+      <c r="D3" s="178" t="s">
+        <v>268</v>
       </c>
-      <c r="E3" s="98" t="s">
-        <v>284</v>
+      <c r="E3" s="95" t="s">
+        <v>273</v>
       </c>
-      <c r="F3" s="117" t="s">
-        <v>285</v>
+      <c r="F3" s="114" t="s">
+        <v>274</v>
       </c>
-      <c r="G3" s="95"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="96"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="93"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="91"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="178" t="s">
-        <v>280</v>
+      <c r="A4" s="88"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="175" t="s">
+        <v>269</v>
       </c>
-      <c r="H4" s="178" t="s">
-        <v>281</v>
+      <c r="H4" s="175" t="s">
+        <v>270</v>
       </c>
-      <c r="I4" s="178" t="s">
-        <v>282</v>
+      <c r="I4" s="175" t="s">
+        <v>271</v>
       </c>
-      <c r="J4" s="178" t="s">
-        <v>283</v>
+      <c r="J4" s="175" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -56856,7 +56874,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="31"/>
@@ -56875,97 +56893,97 @@
       <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
-        <v>211</v>
+      <c r="A2" s="86" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="133" t="s">
-        <v>78</v>
+      <c r="B2" s="130" t="s">
+        <v>281</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="115" t="s">
-        <v>215</v>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="112" t="s">
+        <v>208</v>
       </c>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="117"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="114"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="176" t="s">
+      <c r="A3" s="87"/>
+      <c r="B3" s="173" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="196" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="197"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="171" t="s">
+        <v>284</v>
+      </c>
+      <c r="I3" s="173" t="s">
+        <v>285</v>
+      </c>
+      <c r="J3" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="124"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="93"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="88"/>
+      <c r="B4" s="174"/>
+      <c r="C4" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="194" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="195" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="194" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="195" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="172"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="200" t="s">
         <v>286</v>
       </c>
-      <c r="C3" s="69" t="s">
-        <v>74</v>
+      <c r="M4" s="199" t="s">
+        <v>288</v>
       </c>
-      <c r="D3" s="174" t="s">
-        <v>76</v>
+      <c r="N4" s="199" t="s">
+        <v>289</v>
       </c>
-      <c r="E3" s="176" t="s">
-        <v>237</v>
+      <c r="O4" s="199" t="s">
+        <v>290</v>
       </c>
-      <c r="F3" s="174" t="s">
-        <v>238</v>
-      </c>
-      <c r="G3" s="176" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="174" t="s">
-        <v>239</v>
-      </c>
-      <c r="I3" s="176" t="s">
-        <v>240</v>
-      </c>
-      <c r="J3" s="126" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="127"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="118"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="96"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="91"/>
-      <c r="B4" s="177"/>
-      <c r="C4" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="177"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="O4" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="P4" s="32" t="s">
-        <v>73</v>
+      <c r="P4" s="199" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -60570,31 +60588,28 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="11">
+  <mergeCells count="8">
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="L2:P3"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:P4 C4" xr:uid="{CD6651F3-A46F-4145-A884-D4B65D9D832A}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 N4 O4 P4" xr:uid="{CD6651F3-A46F-4145-A884-D4B65D9D832A}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" location="streamerTypes" xr:uid="{F5B00754-CAA7-4970-9267-C564E10BAB15}"/>
-    <hyperlink ref="L4" r:id="rId2" location="mitigationDevices" xr:uid="{E64F730D-939F-45B5-880D-5F6B514D9768}"/>
-    <hyperlink ref="M4" r:id="rId3" location="mitigationDevices" xr:uid="{9ED9D614-FD6F-49CD-865E-6F4E2F134AB8}"/>
-    <hyperlink ref="N4" r:id="rId4" location="mitigationDevices" xr:uid="{FD249156-8181-4617-AA2E-7D78285B2BA7}"/>
-    <hyperlink ref="O4" r:id="rId5" location="mitigationDevices" xr:uid="{93C2D1ED-DD7E-4C3A-94FD-7C83A902B4EA}"/>
-    <hyperlink ref="P4" r:id="rId6" location="mitigationDevices" xr:uid="{468402CE-24B4-4147-BA53-73E2855BBFD5}"/>
+    <hyperlink ref="C4" r:id="rId1" location="streamerTypes" display="TYPE_CODE" xr:uid="{F5B00754-CAA7-4970-9267-C564E10BAB15}"/>
+    <hyperlink ref="L4" r:id="rId2" location="mitigationDevices" display="DEVICE_1_CODE" xr:uid="{E64F730D-939F-45B5-880D-5F6B514D9768}"/>
+    <hyperlink ref="M4" r:id="rId3" location="mitigationDevices" display="DEVICE_2_CODE" xr:uid="{9ED9D614-FD6F-49CD-865E-6F4E2F134AB8}"/>
+    <hyperlink ref="N4" r:id="rId4" location="mitigationDevices" display="DEVICE_3_CODE" xr:uid="{FD249156-8181-4617-AA2E-7D78285B2BA7}"/>
+    <hyperlink ref="O4" r:id="rId5" location="mitigationDevices" display="DEVICE_4_CODE" xr:uid="{93C2D1ED-DD7E-4C3A-94FD-7C83A902B4EA}"/>
+    <hyperlink ref="P4" r:id="rId6" location="mitigationDevices" display="DEVICE_5_CODE" xr:uid="{468402CE-24B4-4147-BA53-73E2855BBFD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -60637,7 +60652,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -60669,14 +60684,14 @@
       <c r="AC1" s="16"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
-        <v>211</v>
+      <c r="A2" s="89" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="121" t="s">
-        <v>216</v>
+      <c r="B2" s="118" t="s">
+        <v>209</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
@@ -60706,127 +60721,127 @@
       <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="133" t="s">
-        <v>181</v>
+      <c r="A3" s="89"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="130" t="s">
+        <v>175</v>
       </c>
-      <c r="D3" s="137"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="133" t="s">
-        <v>182</v>
+      <c r="D3" s="134"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="130" t="s">
+        <v>176</v>
       </c>
-      <c r="G3" s="137"/>
-      <c r="H3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="131"/>
       <c r="I3" s="24" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J3" s="24"/>
-      <c r="K3" s="115" t="s">
+      <c r="K3" s="112" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="116"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="115" t="s">
-        <v>84</v>
+      <c r="L3" s="113"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="112" t="s">
+        <v>78</v>
       </c>
-      <c r="O3" s="117"/>
-      <c r="P3" s="92" t="s">
+      <c r="O3" s="114"/>
+      <c r="P3" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q3" s="90" t="s">
+        <v>185</v>
+      </c>
+      <c r="R3" s="89" t="s">
+        <v>186</v>
+      </c>
+      <c r="S3" s="94" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" s="94"/>
+      <c r="U3" s="135" t="s">
+        <v>211</v>
+      </c>
+      <c r="V3" s="136"/>
+      <c r="W3" s="135" t="s">
+        <v>210</v>
+      </c>
+      <c r="X3" s="136"/>
+      <c r="Y3" s="94" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
+      <c r="AB3" s="94"/>
+      <c r="AC3" s="109" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="89"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="128" t="s">
         <v>190</v>
       </c>
-      <c r="Q3" s="93" t="s">
-        <v>191</v>
+      <c r="D4" s="130" t="s">
+        <v>177</v>
       </c>
-      <c r="R3" s="92" t="s">
-        <v>192</v>
+      <c r="E4" s="131"/>
+      <c r="F4" s="132" t="s">
+        <v>190</v>
       </c>
-      <c r="S3" s="97" t="s">
-        <v>86</v>
+      <c r="G4" s="130" t="s">
+        <v>177</v>
       </c>
-      <c r="T3" s="97"/>
-      <c r="U3" s="138" t="s">
-        <v>218</v>
+      <c r="H4" s="131"/>
+      <c r="I4" s="39" t="s">
+        <v>89</v>
       </c>
-      <c r="V3" s="139"/>
-      <c r="W3" s="138" t="s">
-        <v>217</v>
-      </c>
-      <c r="X3" s="139"/>
-      <c r="Y3" s="97" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
-      <c r="AB3" s="97"/>
-      <c r="AC3" s="112" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="131" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="133" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="134"/>
-      <c r="F4" s="135" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="133" t="s">
-        <v>183</v>
-      </c>
-      <c r="H4" s="134"/>
-      <c r="I4" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" s="68" t="s">
+      <c r="J4" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="95"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="140"/>
-      <c r="V4" s="141"/>
-      <c r="W4" s="140"/>
-      <c r="X4" s="141"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97"/>
-      <c r="AA4" s="97"/>
-      <c r="AB4" s="97"/>
-      <c r="AC4" s="112"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="138"/>
+      <c r="W4" s="137"/>
+      <c r="X4" s="138"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="109"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
-      <c r="B5" s="123"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="67" t="s">
+      <c r="A5" s="89"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="136"/>
-      <c r="G5" s="67" t="s">
+      <c r="F5" s="133"/>
+      <c r="G5" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="H5" s="66" t="s">
         <v>1</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
-      <c r="J5" s="67" t="s">
-        <v>207</v>
+      <c r="J5" s="66" t="s">
+        <v>201</v>
       </c>
       <c r="K5" s="21" t="s">
         <v>65</v>
@@ -60834,35 +60849,35 @@
       <c r="L5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="34" t="s">
-        <v>205</v>
+      <c r="M5" s="33" t="s">
+        <v>199</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="40" t="s">
+      <c r="P5" s="89"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="U5" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="T5" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="U5" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="W5" s="40" t="s">
+      <c r="W5" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="X5" s="71" t="s">
-        <v>206</v>
+      <c r="X5" s="68" t="s">
+        <v>200</v>
       </c>
       <c r="Y5" s="23" t="s">
         <v>33</v>
@@ -60876,7 +60891,7 @@
       <c r="AB5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AC5" s="112"/>
+      <c r="AC5" s="109"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C88779-00B4-49F6-8166-F6636EA19FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0726C35-FAE2-4A3F-86C6-8A01CD91CA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="6" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28755" yWindow="315" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="11" activeTab="18" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="277">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>SEX</t>
-  </si>
-  <si>
-    <t>DEPREDATION_DETAILS</t>
   </si>
   <si>
     <t>PRESERVATION_METHOD</t>
@@ -705,12 +702,6 @@
     <t>SAMPLE COLLECTED</t>
   </si>
   <si>
-    <t>SPECIMEN DETAILS</t>
-  </si>
-  <si>
-    <t>ADDITIONAL CATCH DETAILS FOR SPECIES OF SPECIAL INTEREST (SSI)</t>
-  </si>
-  <si>
     <t>MATERIAL</t>
   </si>
   <si>
@@ -718,9 +709,6 @@
   </si>
   <si>
     <t>POSITIONS OF OFFAL DISPOSAL</t>
-  </si>
-  <si>
-    <t>HAULING OPERATIONS</t>
   </si>
   <si>
     <t>POSITION_2</t>
@@ -741,13 +729,7 @@
     <t>NUMBER_HOOKS_RETRIEVED_DURING_OBSERVATION</t>
   </si>
   <si>
-    <t>SETTING OPERATIONS</t>
-  </si>
-  <si>
     <t>HOOKS</t>
-  </si>
-  <si>
-    <t>ATTACHED LIGHTS</t>
   </si>
   <si>
     <t>NUMBER_OF_LIGHTS</t>
@@ -859,12 +841,6 @@
   </si>
   <si>
     <t>NUMBER FISHING SETS</t>
-  </si>
-  <si>
-    <t>CATCH DETAILS</t>
-  </si>
-  <si>
-    <t>TAG DETAILS</t>
   </si>
   <si>
     <t>LENGTH_VALUE</t>
@@ -1015,7 +991,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1031,12 +1007,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1327,7 +1297,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1336,64 +1306,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
@@ -1443,9 +1413,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1479,45 +1446,45 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1581,8 +1548,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1592,6 +1560,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1641,10 +1612,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1663,9 +1630,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1673,6 +1637,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1729,26 +1696,17 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2087,36 +2045,36 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="65" t="s">
-        <v>135</v>
+      <c r="B2" s="64" t="s">
+        <v>134</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="67"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="66"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="12"/>
       <c r="C4" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G4" s="16">
         <v>1</v>
@@ -2135,7 +2093,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
@@ -2154,26 +2112,26 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="18"/>
-      <c r="C8" s="71" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="71" t="s">
+      <c r="C8" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="G8" s="71"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="70"/>
       <c r="H8" s="20"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="18"/>
       <c r="C9" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="19"/>
       <c r="F9" s="22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="20"/>
@@ -2181,12 +2139,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="18"/>
       <c r="C10" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="19"/>
       <c r="F10" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="20"/>
@@ -2203,7 +2161,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="18"/>
       <c r="C12" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="19"/>
@@ -2214,7 +2172,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="18"/>
       <c r="C13" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="19"/>
@@ -2243,7 +2201,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="18"/>
       <c r="C16" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -2263,7 +2221,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="18"/>
       <c r="C18" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="19"/>
@@ -2274,7 +2232,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="18"/>
       <c r="C19" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="19"/>
@@ -2285,7 +2243,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="18"/>
       <c r="C20" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="19"/>
@@ -2296,7 +2254,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
       <c r="C21" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="19"/>
@@ -2325,7 +2283,7 @@
     <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="C24" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="19"/>
@@ -2344,11 +2302,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="73"/>
       <c r="H26" s="20"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2365,7 +2323,7 @@
       <c r="D28" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2391,7 +2349,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -2403,38 +2361,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+    <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="141" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>113</v>
+      <c r="B2" s="141" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="117" t="s">
-        <v>230</v>
-      </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="118"/>
-    </row>
-    <row r="3" spans="1:5" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="57" t="s">
+      <c r="C2" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="57" t="s">
-        <v>232</v>
+      <c r="D2" s="56" t="s">
+        <v>226</v>
       </c>
-      <c r="E3" s="61" t="s">
-        <v>231</v>
+      <c r="E2" s="60" t="s">
+        <v>225</v>
       </c>
+    </row>
+    <row r="3" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -3829,28 +3785,16 @@
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" s="2"/>
-      <c r="B203" s="2"/>
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="o9/vwn6+8Krm9F9Oq/hb0svuyl95KTT1/9Y34nbbG4qNR9BnrFVCJsOkjG0nXmC/dB0rTLS1383/tXVExtsY0A==" saltValue="7Rv6rC538bGZWueNlXhgCA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="3">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-  </mergeCells>
+  <sheetProtection algorithmName="SHA-512" hashValue="wVE8X29TiN8k0u6CAaXleHjaeKeeNYW1Jxx66FWjwTFdxabMjONKA3DSKN5UvjorZe/FwRx6p50117Nuzy0Gyw==" saltValue="vxV/5HrQxq/RlGmG7jI6MQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 D3" xr:uid="{B060D15A-6570-447A-A9A0-240DB07B3A95}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 D2" xr:uid="{B060D15A-6570-447A-A9A0-240DB07B3A95}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" location="lightTypes" display="TYPE_CODE" xr:uid="{AC363CAB-A43B-4DB4-A094-DE575BF2F4E8}"/>
-    <hyperlink ref="D3" r:id="rId2" location="lightColours" display="COLOR_CODE" xr:uid="{B23721E8-F134-4C00-B1EF-0698947F363C}"/>
+    <hyperlink ref="C2" r:id="rId1" location="lightTypes" display="TYPE_CODE" xr:uid="{AC363CAB-A43B-4DB4-A094-DE575BF2F4E8}"/>
+    <hyperlink ref="D2" r:id="rId2" location="lightColours" display="COLOR_CODE" xr:uid="{B23721E8-F134-4C00-B1EF-0698947F363C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3879,7 +3823,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3896,72 +3840,72 @@
       <c r="N1" s="5"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:15" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+    <row r="2" spans="1:15" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>113</v>
+      <c r="B2" s="120" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="119" t="s">
-        <v>261</v>
+      <c r="C2" s="120" t="s">
+        <v>255</v>
       </c>
-      <c r="D2" s="119" t="s">
-        <v>262</v>
+      <c r="D2" s="120" t="s">
+        <v>256</v>
       </c>
-      <c r="E2" s="94" t="s">
+      <c r="E2" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="119" t="s">
-        <v>263</v>
+      <c r="F2" s="120" t="s">
+        <v>257</v>
       </c>
-      <c r="G2" s="119" t="s">
-        <v>260</v>
+      <c r="G2" s="120" t="s">
+        <v>254</v>
       </c>
-      <c r="H2" s="119" t="s">
+      <c r="H2" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="119" t="s">
-        <v>115</v>
+      <c r="I2" s="120" t="s">
+        <v>114</v>
       </c>
-      <c r="J2" s="89" t="s">
-        <v>254</v>
+      <c r="J2" s="88" t="s">
+        <v>248</v>
       </c>
-      <c r="K2" s="93"/>
-      <c r="L2" s="117" t="s">
-        <v>255</v>
+      <c r="K2" s="92"/>
+      <c r="L2" s="116" t="s">
+        <v>249</v>
       </c>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="118"/>
-    </row>
-    <row r="3" spans="1:15" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="117"/>
+    </row>
+    <row r="3" spans="1:15" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="75"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
       <c r="J3" s="42" t="s">
         <v>47</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
-      <c r="L3" s="57" t="s">
-        <v>256</v>
+      <c r="L3" s="56" t="s">
+        <v>250</v>
       </c>
-      <c r="M3" s="57" t="s">
-        <v>257</v>
+      <c r="M3" s="56" t="s">
+        <v>251</v>
       </c>
-      <c r="N3" s="57" t="s">
-        <v>258</v>
+      <c r="N3" s="56" t="s">
+        <v>252</v>
       </c>
-      <c r="O3" s="57" t="s">
-        <v>259</v>
+      <c r="O3" s="56" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -7366,17 +7310,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ZHZ61xEMWo2GozKFDfIGwtbJZnm3eVYJpvIE2b76e/O5EaOFEu4qUPnEZ+3+QLMo4fMOZjuAZJWBGppNj6h0fg==" saltValue="p7UsgbvwfBAQ3S2mqNofIA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="I2:I3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 M3 N3 O3" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7410,30 +7354,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+    <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>113</v>
+      <c r="B2" s="120" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="117" t="s">
-        <v>229</v>
+      <c r="C2" s="116" t="s">
+        <v>224</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="118"/>
-    </row>
-    <row r="3" spans="1:5" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="57" t="s">
+      <c r="D2" s="123"/>
+      <c r="E2" s="117"/>
+    </row>
+    <row r="3" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="75"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="56" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="42" t="s">
@@ -8875,7 +8819,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8883,28 +8827,28 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:6" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+    <row r="2" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>113</v>
+      <c r="B2" s="120" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="117" t="s">
-        <v>75</v>
+      <c r="C2" s="116" t="s">
+        <v>74</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="118"/>
-    </row>
-    <row r="3" spans="1:6" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="57" t="s">
-        <v>201</v>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="117"/>
+    </row>
+    <row r="3" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="75"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="56" t="s">
+        <v>200</v>
       </c>
-      <c r="D3" s="57" t="s">
-        <v>144</v>
+      <c r="D3" s="56" t="s">
+        <v>143</v>
       </c>
       <c r="E3" s="39" t="s">
         <v>54</v>
@@ -10538,7 +10482,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Q205"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -10559,7 +10503,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10578,127 +10522,125 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="6"/>
     </row>
-    <row r="2" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
+    <row r="2" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="87" t="s">
-        <v>113</v>
+      <c r="B2" s="120" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="C2" s="116" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="123"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="116" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" s="123"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="98" t="s">
+        <v>217</v>
+      </c>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="86" t="s">
+        <v>222</v>
+      </c>
+      <c r="P2" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q2" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="118"/>
-    </row>
-    <row r="3" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="117" t="s">
-        <v>236</v>
+    </row>
+    <row r="3" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="120" t="s">
+        <v>100</v>
       </c>
-      <c r="D3" s="124"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="117" t="s">
-        <v>237</v>
+      <c r="D3" s="116" t="s">
+        <v>98</v>
       </c>
-      <c r="G3" s="124"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="99" t="s">
-        <v>59</v>
+      <c r="E3" s="117"/>
+      <c r="F3" s="120" t="s">
+        <v>100</v>
       </c>
-      <c r="J3" s="95" t="s">
+      <c r="G3" s="116" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="117"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="133"/>
+    </row>
+    <row r="4" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="75"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="75"/>
+      <c r="G4" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="99"/>
+      <c r="J4" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="K4" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="M4" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="O3" s="87" t="s">
-        <v>226</v>
-      </c>
-      <c r="P3" s="87" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q3" s="134" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="119" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="117" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="119" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="117" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="134"/>
-    </row>
-    <row r="5" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="99"/>
-      <c r="J5" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="K5" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="L5" s="50" t="s">
-        <v>223</v>
-      </c>
-      <c r="M5" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="134"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="133"/>
+    </row>
+    <row r="5" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -14481,56 +14423,36 @@
       <c r="P204" s="2"/>
       <c r="Q204" s="2"/>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="M74ASMxvLHqMV/bhUGoUyAHsdb/wCjpUR3HR9leTF40NhTPM0ygEfL3aXXrR0tRjeBJs360zim1E4oZB7ovEJw==" saltValue="6qk3b9BH270RrT3PRgzbiw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="15">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C2:Q2"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:M4"/>
-    <mergeCell ref="N3:N5"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6+yDI0OgPd4WYm3G6Z5geZ6OVSItsmzuI6pvXBhnqIBLkRwqZYhw/9myNYQcHogXrON+p0Vn9Al4arNGxWcvhQ==" saltValue="yoKDrVsoZTsh8FbYtsclwg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="14">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:M3"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I5 M5 J5 K5 L5 Q3:Q5" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 Q2:Q4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q3:Q5" r:id="rId1" location="samplingProtocols" display="SAMPLING_PROTOCOL_CODE" xr:uid="{C0C4727C-9767-4664-8796-43CDF0860627}"/>
-    <hyperlink ref="I3:I5" r:id="rId2" location="offalManagementTypes" display="OFFAL_MANAGEMENT" xr:uid="{408DFBD1-078D-43D4-8B22-538A09E39B98}"/>
-    <hyperlink ref="J5" r:id="rId3" location="vesselSections" xr:uid="{140540DF-7251-4F70-BF34-280C13EE47A9}"/>
-    <hyperlink ref="K5" r:id="rId4" location="vesselSections" xr:uid="{C6B0B34F-D5B5-4396-BD53-32117C4E0387}"/>
-    <hyperlink ref="L5" r:id="rId5" location="vesselSections" xr:uid="{DEEDA3F4-54C9-4377-BF9D-5DFE24657492}"/>
-    <hyperlink ref="M5" r:id="rId6" location="vesselSections" xr:uid="{9AEF6B48-E740-4F53-8676-B0739C3029D5}"/>
+    <hyperlink ref="Q2:Q4" r:id="rId1" location="samplingProtocols" display="SAMPLING_PROTOCOL_CODE" xr:uid="{C0C4727C-9767-4664-8796-43CDF0860627}"/>
+    <hyperlink ref="I2:I4" r:id="rId2" location="offalManagementTypes" display="OFFAL_MANAGEMENT" xr:uid="{408DFBD1-078D-43D4-8B22-538A09E39B98}"/>
+    <hyperlink ref="J4" r:id="rId3" location="vesselSections" xr:uid="{140540DF-7251-4F70-BF34-280C13EE47A9}"/>
+    <hyperlink ref="K4" r:id="rId4" location="vesselSections" xr:uid="{C6B0B34F-D5B5-4396-BD53-32117C4E0387}"/>
+    <hyperlink ref="L4" r:id="rId5" location="vesselSections" xr:uid="{DEEDA3F4-54C9-4377-BF9D-5DFE24657492}"/>
+    <hyperlink ref="M4" r:id="rId6" location="vesselSections" xr:uid="{9AEF6B48-E740-4F53-8676-B0739C3029D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14552,32 +14474,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+    <row r="2" spans="1:4" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>113</v>
+      <c r="B2" s="120" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="93"/>
-    </row>
-    <row r="3" spans="1:4" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
+      <c r="D2" s="92"/>
+    </row>
+    <row r="3" spans="1:4" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="75"/>
+      <c r="B3" s="75"/>
       <c r="C3" s="42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15796,7 +15718,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -15813,7 +15735,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -15826,85 +15748,83 @@
       <c r="J1" s="5"/>
       <c r="K1" s="6"/>
     </row>
-    <row r="2" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="87" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="87" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="117" t="s">
-        <v>268</v>
-      </c>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="118"/>
-    </row>
-    <row r="3" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="134" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="135" t="s">
+    <row r="2" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="120" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="136"/>
-      <c r="G3" s="134" t="s">
-        <v>207</v>
+      <c r="B2" s="120" t="s">
+        <v>112</v>
       </c>
-      <c r="H3" s="87" t="s">
-        <v>239</v>
+      <c r="C2" s="120" t="s">
+        <v>115</v>
       </c>
-      <c r="I3" s="113" t="s">
+      <c r="D2" s="133" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="134" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="135"/>
+      <c r="G2" s="133" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" s="86" t="s">
+        <v>233</v>
+      </c>
+      <c r="I2" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="114"/>
-      <c r="K3" s="115"/>
-    </row>
-    <row r="4" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="86"/>
-    </row>
-    <row r="5" spans="1:11" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="57" t="s">
+      <c r="J2" s="113"/>
+      <c r="K2" s="114"/>
+    </row>
+    <row r="3" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="85"/>
+    </row>
+    <row r="4" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="75"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="57" t="s">
-        <v>108</v>
+      <c r="F4" s="56" t="s">
+        <v>107</v>
       </c>
-      <c r="G5" s="134"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="50" t="s">
-        <v>209</v>
+      <c r="G4" s="133"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="50" t="s">
+        <v>208</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J4" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="K5" s="50" t="s">
-        <v>233</v>
+      <c r="K4" s="50" t="s">
+        <v>227</v>
       </c>
+    </row>
+    <row r="5" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -18493,44 +18413,30 @@
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nA4e6WuXEMiqXVediq2P9T3XFlP7nrKiCV/OvHQ5X1W1y+bOcIrg95/yuKtxtHp2R14+yylfaCdCZHgmA/4+wg==" saltValue="2Xn8qAQR0T/01o5I3/M2FA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="I3:K4"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="E3:F4"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gc1id5LPeJu7xzDsDxM69tmPrQzpr31mQ0LRa1Xo4B/9vlcogcEe/te2kZH7B/hYeHV0dP6Q8Z/in87rf9obdw==" saltValue="FtRpvabY8g/m0+SLrIoiOA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="E2:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5 G3:G5 F5 D3:D5 E5 K5" xr:uid="{4E0B6771-5993-41A9-BE9D-F553134C1037}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4 G2:G4 F4 D2:D4 E4 K4" xr:uid="{4E0B6771-5993-41A9-BE9D-F553134C1037}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D3:D5" r:id="rId1" location="species" display="SPECIES_CODE" xr:uid="{E368770C-29BB-4DD7-A588-292C8EBBACA5}"/>
-    <hyperlink ref="I5" r:id="rId2" location="weightMeasurements" xr:uid="{779410D5-0433-4C34-84B6-98A10CA2B249}"/>
-    <hyperlink ref="K5" r:id="rId3" location="weightMeasurementTools" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
-    <hyperlink ref="G3:G5" r:id="rId4" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{6D1D8620-4A5B-4D09-B9FB-01FDEF4F969A}"/>
-    <hyperlink ref="E5" r:id="rId5" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
-    <hyperlink ref="F5" r:id="rId6" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
+    <hyperlink ref="D2:D4" r:id="rId1" location="species" display="SPECIES_CODE" xr:uid="{E368770C-29BB-4DD7-A588-292C8EBBACA5}"/>
+    <hyperlink ref="I4" r:id="rId2" location="weightMeasurements" xr:uid="{779410D5-0433-4C34-84B6-98A10CA2B249}"/>
+    <hyperlink ref="K4" r:id="rId3" location="weightMeasurementTools" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
+    <hyperlink ref="G2:G4" r:id="rId4" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{6D1D8620-4A5B-4D09-B9FB-01FDEF4F969A}"/>
+    <hyperlink ref="E4" r:id="rId5" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
+    <hyperlink ref="F4" r:id="rId6" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
@@ -18542,7 +18448,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Y204"/>
+  <dimension ref="A1:Y203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -18574,7 +18480,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -18601,150 +18507,148 @@
       <c r="X1" s="5"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139" t="s">
-        <v>110</v>
+    <row r="2" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="138" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="139" t="s">
-        <v>113</v>
+      <c r="B2" s="138" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="138" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="139" t="s">
-        <v>117</v>
+      <c r="E2" s="107" t="s">
+        <v>205</v>
       </c>
-      <c r="E2" s="96" t="s">
-        <v>216</v>
-      </c>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="42"/>
-    </row>
-    <row r="3" spans="1:25" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="140"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="107" t="s">
+      <c r="F2" s="107" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="107" t="s">
-        <v>207</v>
+      <c r="G2" s="86" t="s">
+        <v>209</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="98" t="s">
+        <v>211</v>
+      </c>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98" t="s">
+        <v>61</v>
+      </c>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" s="88" t="s">
+        <v>106</v>
+      </c>
+      <c r="T2" s="92"/>
+      <c r="U2" s="88" t="s">
+        <v>214</v>
+      </c>
+      <c r="V2" s="89"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="98" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y2" s="98"/>
+    </row>
+    <row r="3" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="139"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="95" t="s">
+      <c r="J3" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="O3" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="P3" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="R3" s="106"/>
+      <c r="S3" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="U3" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="W3" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="95" t="s">
-        <v>61</v>
-      </c>
-      <c r="P3" s="95"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="S3" s="89" t="s">
-        <v>107</v>
-      </c>
-      <c r="T3" s="93"/>
-      <c r="U3" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="V3" s="90"/>
-      <c r="W3" s="93"/>
-      <c r="X3" s="95" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y3" s="95"/>
-    </row>
-    <row r="4" spans="1:25" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="141"/>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="M4" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="N4" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="O4" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="P4" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q4" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="R4" s="106"/>
-      <c r="S4" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="T4" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="U4" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="V4" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="W4" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="X4" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y4" s="50" t="s">
+      <c r="X3" s="50" t="s">
         <v>202</v>
       </c>
+      <c r="Y3" s="50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -24119,68 +24023,40 @@
       <c r="X203" s="9"/>
       <c r="Y203" s="9"/>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
-      <c r="M204" s="2"/>
-      <c r="N204" s="2"/>
-      <c r="O204" s="2"/>
-      <c r="P204" s="2"/>
-      <c r="Q204" s="2"/>
-      <c r="R204" s="2"/>
-      <c r="S204" s="2"/>
-      <c r="T204" s="2"/>
-      <c r="U204" s="2"/>
-      <c r="V204" s="2"/>
-      <c r="W204" s="2"/>
-      <c r="X204" s="9"/>
-      <c r="Y204" s="9"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KY0VYSDMLJzYhZPsvz/pfbCAfnLh1igrByWLaHPri/rrL5aOsLcY39KJNqgtbvL9SFgCCXHgtzvoCV81HJiplg==" saltValue="XUTmh0CaJbkwdaK96rf5KQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="14">
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="U3:W3"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="e/mZipJ4AXPmTDIqBREzT6xE/UbCF4PciHFB1N4ngnHGkbhMYq2UP1EcRbtVoIsbMk/soeRGswyOaMGay/157g==" saltValue="feKRClgbT3qIjWu79ykSJg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 F3:F4 G4 I4 K4 Q4 Y4 R3:R4 E3:E4 X4 O4" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 F2:F3 G3 I3 K3 Q3 Y3 R2:R3 E2:E3 X3 O3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E3:E4" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
-    <hyperlink ref="X4" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
-    <hyperlink ref="Y4" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
-    <hyperlink ref="F3:F4" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
-    <hyperlink ref="I4" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
-    <hyperlink ref="M4" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
-    <hyperlink ref="G4" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
-    <hyperlink ref="K4" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
-    <hyperlink ref="Q4" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
-    <hyperlink ref="O4" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
-    <hyperlink ref="R3:R4" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
+    <hyperlink ref="E2:E3" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
+    <hyperlink ref="X3" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
+    <hyperlink ref="Y3" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
+    <hyperlink ref="F2:F3" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
+    <hyperlink ref="I3" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
+    <hyperlink ref="M3" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
+    <hyperlink ref="G3" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
+    <hyperlink ref="K3" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
+    <hyperlink ref="Q3" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
+    <hyperlink ref="O3" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
+    <hyperlink ref="R2:R3" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24191,7 +24067,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:T204"/>
+  <dimension ref="A1:T203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -24216,7 +24092,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -24238,119 +24114,117 @@
       <c r="S1" s="5"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:20" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139" t="s">
-        <v>110</v>
+    <row r="2" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="138" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="139" t="s">
-        <v>113</v>
+      <c r="B2" s="138" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="138" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="139" t="s">
-        <v>117</v>
+      <c r="E2" s="107" t="s">
+        <v>196</v>
       </c>
-      <c r="E2" s="117" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="124"/>
-      <c r="T2" s="118"/>
-    </row>
-    <row r="3" spans="1:20" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="140"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="107" t="s">
+      <c r="F2" s="107" t="s">
         <v>197</v>
       </c>
-      <c r="F3" s="107" t="s">
+      <c r="G2" s="107" t="s">
         <v>198</v>
       </c>
-      <c r="G3" s="107" t="s">
+      <c r="H2" s="105" t="s">
         <v>199</v>
       </c>
-      <c r="H3" s="105" t="s">
+      <c r="I2" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="85"/>
+      <c r="K2" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="83"/>
+      <c r="M2" s="105" t="s">
+        <v>204</v>
+      </c>
+      <c r="N2" s="140" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="140" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="105" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q2" s="140" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="140" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" s="87" t="s">
+        <v>213</v>
+      </c>
+      <c r="T2" s="87"/>
+    </row>
+    <row r="3" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="139"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="I3" s="85" t="s">
-        <v>75</v>
+      <c r="J3" s="50" t="s">
+        <v>23</v>
       </c>
-      <c r="J3" s="86"/>
-      <c r="K3" s="85" t="s">
-        <v>76</v>
+      <c r="K3" s="56" t="s">
+        <v>215</v>
       </c>
-      <c r="L3" s="86"/>
-      <c r="M3" s="105" t="s">
-        <v>205</v>
+      <c r="L3" s="42" t="s">
+        <v>70</v>
       </c>
-      <c r="N3" s="142" t="s">
-        <v>78</v>
+      <c r="M3" s="106"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="106"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="50" t="s">
+        <v>202</v>
       </c>
-      <c r="O3" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" s="105" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q3" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="142" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" s="88" t="s">
-        <v>65</v>
-      </c>
-      <c r="T3" s="88"/>
-    </row>
-    <row r="4" spans="1:20" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="141"/>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="50" t="s">
+      <c r="T3" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="J4" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" s="106"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="T4" s="50" t="s">
-        <v>202</v>
-      </c>
+    </row>
+    <row r="4" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -28730,69 +28604,46 @@
       <c r="S203" s="9"/>
       <c r="T203" s="9"/>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
-      <c r="M204" s="2"/>
-      <c r="N204" s="2"/>
-      <c r="O204" s="2"/>
-      <c r="P204" s="2"/>
-      <c r="Q204" s="2"/>
-      <c r="R204" s="2"/>
-      <c r="S204" s="9"/>
-      <c r="T204" s="9"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="b7iFD3stCEc8CDvBX5E4A9iy6RRh33YXJjHdXCt7s3ppl2exdvef7TiLo5HcJUPYwM+0qCY/VpIgXOQug/Lugg==" saltValue="LcDlqIl4FIJJQci8+Agnng==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="18">
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="E2:T2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="owrGYnA0RoV/U9MjDeglShzyfAHibWrOJ91U+dfsJvx7FpXhtP7KXYqD/XawmrJ8WUgOAZj9nC2wQr9dD2KQZw==" saltValue="h+hFQsEVq78bir+WDv8nRA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="17">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F4 H3:H4 P3:P4 S4 J4 E3:E4 G3:G4 I4 M3:M4 T4" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 H2:H3 P2:P3 S3 J3 E2:E3 G2:G3 I3 M2:M3 T3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G3:G4" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
-    <hyperlink ref="H3:H4" r:id="rId2" location="hookTypes" display="HOOK_TYPE_CODE" xr:uid="{FC3E5B48-31F4-4395-B266-CAE8F0285CBE}"/>
-    <hyperlink ref="I4" r:id="rId3" location="baitConditions" display="CONDITION_CODE" xr:uid="{A5E5073A-7EA6-4050-99BD-3A2C3C210913}"/>
-    <hyperlink ref="M3:M4" r:id="rId4" location="dehookerTypes" display="DE_HOOKER_DEVICE_CODE" xr:uid="{223FF70D-0F50-400C-91DF-40947EEFC402}"/>
-    <hyperlink ref="K4" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{8BD5CD8E-6908-4DE0-9B07-7CCA6FB5C649}"/>
-    <hyperlink ref="P3:P4" r:id="rId6" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
-    <hyperlink ref="J4" r:id="rId7" location="baitTypes" display="TYPE_CODE" xr:uid="{8E341D36-948A-422D-9D66-B4F0241035EC}"/>
-    <hyperlink ref="E3" r:id="rId8" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{26B5C55C-6931-4D84-B6B4-4AA585019D2E}"/>
-    <hyperlink ref="F3" r:id="rId9" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{312D6457-0D67-4610-B478-F5AE649B98F6}"/>
-    <hyperlink ref="S4" r:id="rId10" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
-    <hyperlink ref="T4" r:id="rId11" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{AD1EB751-9874-431A-A9CC-CB89B7E2E48C}"/>
-    <hyperlink ref="F3:F4" r:id="rId12" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{7022269F-0B3D-487B-821A-D8677291ECA9}"/>
-    <hyperlink ref="E3:E4" r:id="rId13" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{46C1F397-FDC9-4F56-B765-948CEB3929A4}"/>
+    <hyperlink ref="G2:G3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
+    <hyperlink ref="H2:H3" r:id="rId2" location="hookTypes" display="HOOK_TYPE_CODE" xr:uid="{FC3E5B48-31F4-4395-B266-CAE8F0285CBE}"/>
+    <hyperlink ref="I3" r:id="rId3" location="baitConditions" display="CONDITION_CODE" xr:uid="{A5E5073A-7EA6-4050-99BD-3A2C3C210913}"/>
+    <hyperlink ref="M2:M3" r:id="rId4" location="dehookerTypes" display="DE_HOOKER_DEVICE_CODE" xr:uid="{223FF70D-0F50-400C-91DF-40947EEFC402}"/>
+    <hyperlink ref="K3" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{8BD5CD8E-6908-4DE0-9B07-7CCA6FB5C649}"/>
+    <hyperlink ref="P2:P3" r:id="rId6" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
+    <hyperlink ref="J3" r:id="rId7" location="baitTypes" display="TYPE_CODE" xr:uid="{8E341D36-948A-422D-9D66-B4F0241035EC}"/>
+    <hyperlink ref="E2" r:id="rId8" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{26B5C55C-6931-4D84-B6B4-4AA585019D2E}"/>
+    <hyperlink ref="F2" r:id="rId9" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{312D6457-0D67-4610-B478-F5AE649B98F6}"/>
+    <hyperlink ref="S3" r:id="rId10" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
+    <hyperlink ref="T3" r:id="rId11" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{AD1EB751-9874-431A-A9CC-CB89B7E2E48C}"/>
+    <hyperlink ref="F2:F3" r:id="rId12" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{7022269F-0B3D-487B-821A-D8677291ECA9}"/>
+    <hyperlink ref="E2:E3" r:id="rId13" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{46C1F397-FDC9-4F56-B765-948CEB3929A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
@@ -28804,7 +28655,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K203"/>
+  <dimension ref="A1:K202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -28816,7 +28667,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -28829,68 +28680,66 @@
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:11" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139" t="s">
-        <v>110</v>
+    <row r="2" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="142" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="139" t="s">
-        <v>113</v>
+      <c r="B2" s="142" t="s">
+        <v>112</v>
       </c>
-      <c r="C2" s="139" t="s">
+      <c r="C2" s="142" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="142" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="139" t="s">
-        <v>117</v>
+      <c r="E2" s="42" t="s">
+        <v>66</v>
       </c>
-      <c r="E2" s="143" t="s">
-        <v>269</v>
-      </c>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="145"/>
-    </row>
-    <row r="3" spans="1:11" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="42" t="s">
+      <c r="F2" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="G2" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="42" t="s">
+      <c r="I2" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="42" t="s">
-        <v>70</v>
+      <c r="J2" s="42" t="s">
+        <v>132</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="K2" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="42" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
+    </row>
+    <row r="3" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+    </row>
+    <row r="4" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -31466,35 +31315,15 @@
       <c r="J202" s="9"/>
       <c r="K202" s="9"/>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A203" s="2"/>
-      <c r="B203" s="2"/>
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="G203" s="9"/>
-      <c r="H203" s="9"/>
-      <c r="I203" s="9"/>
-      <c r="J203" s="9"/>
-      <c r="K203" s="9"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="652cnaNhgPtepd908V5jgcWve9J7dYBphcGiJP3Pdj1MsyJp82UAvLygMNnNNUJf2S9gcHHWbBweLWp1xH0XNw==" saltValue="c0ZGX15kpEKLjHx3iOtM5w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="5">
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-  </mergeCells>
+  <sheetProtection algorithmName="SHA-512" hashValue="qOApQt+f2TsOI5aABva9oFhDaMC8tY6SmLrXY5zZMla4EE44P/H2PtJCJ3eAXXCegs0uTPk+51WoRp//Mv+vlg==" saltValue="LQGXhg9x1P3A7pPeXXmcRw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" location="tagTypes" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
+    <hyperlink ref="G2" r:id="rId1" location="tagTypes" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31535,153 +31364,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="7" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>240</v>
+      <c r="A1" s="61" t="s">
+        <v>234</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="64"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="63"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
-        <v>110</v>
+      <c r="A2" s="74" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="75" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="87" t="s">
         <v>179</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="88" t="s">
-        <v>180</v>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="78" t="s">
+        <v>235</v>
       </c>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="79" t="s">
-        <v>241</v>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="53"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="74"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="88" t="s">
+        <v>94</v>
       </c>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="54"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="89" t="s">
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="89" t="s">
-        <v>96</v>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="83"/>
+      <c r="Y3" s="53"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="74"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="84" t="s">
+        <v>92</v>
       </c>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="54"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="85" t="s">
+      <c r="E4" s="85"/>
+      <c r="F4" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="86"/>
-      <c r="F4" s="85" t="s">
-        <v>94</v>
+      <c r="G4" s="85"/>
+      <c r="H4" s="93" t="s">
+        <v>100</v>
       </c>
-      <c r="G4" s="86"/>
-      <c r="H4" s="94" t="s">
-        <v>101</v>
+      <c r="I4" s="84" t="s">
+        <v>92</v>
       </c>
-      <c r="I4" s="85" t="s">
+      <c r="J4" s="85"/>
+      <c r="K4" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="J4" s="86"/>
-      <c r="K4" s="85" t="s">
-        <v>94</v>
+      <c r="L4" s="85"/>
+      <c r="M4" s="90" t="s">
+        <v>100</v>
       </c>
-      <c r="L4" s="86"/>
-      <c r="M4" s="91" t="s">
-        <v>101</v>
+      <c r="N4" s="76" t="s">
+        <v>261</v>
       </c>
-      <c r="N4" s="77" t="s">
-        <v>267</v>
+      <c r="O4" s="76"/>
+      <c r="P4" s="77" t="s">
+        <v>259</v>
       </c>
-      <c r="O4" s="77"/>
-      <c r="P4" s="78" t="s">
-        <v>265</v>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77" t="s">
+        <v>260</v>
       </c>
-      <c r="Q4" s="78"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="78"/>
-      <c r="T4" s="78"/>
-      <c r="U4" s="78" t="s">
-        <v>266</v>
-      </c>
-      <c r="V4" s="78"/>
-      <c r="W4" s="78"/>
-      <c r="X4" s="78"/>
-    </row>
-    <row r="5" spans="1:25" s="55" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
+      <c r="V4" s="77"/>
+      <c r="W4" s="77"/>
+      <c r="X4" s="77"/>
+    </row>
+    <row r="5" spans="1:25" s="54" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="75"/>
       <c r="B5" s="39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>4</v>
@@ -31692,9 +31521,9 @@
       <c r="G5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="88"/>
+      <c r="H5" s="87"/>
       <c r="I5" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J5" s="50" t="s">
         <v>4</v>
@@ -31705,7 +31534,7 @@
       <c r="L5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="92"/>
+      <c r="M5" s="91"/>
       <c r="N5" s="39" t="s">
         <v>5</v>
       </c>
@@ -31728,16 +31557,16 @@
         <v>10</v>
       </c>
       <c r="U5" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="V5" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="V5" s="38" t="s">
+      <c r="W5" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="W5" s="38" t="s">
+      <c r="X5" s="38" t="s">
         <v>141</v>
-      </c>
-      <c r="X5" s="38" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -36981,7 +36810,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -37000,36 +36829,36 @@
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
+      <c r="A2" s="86" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="96" t="s">
-        <v>251</v>
+      <c r="B2" s="95" t="s">
+        <v>245</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="98"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="97"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="96" t="s">
+      <c r="A3" s="86"/>
+      <c r="B3" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="98"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="97"/>
       <c r="G3" s="109" t="s">
         <v>16</v>
       </c>
@@ -37038,84 +36867,84 @@
       <c r="J3" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="53" t="s">
-        <v>111</v>
+      <c r="K3" s="52" t="s">
+        <v>110</v>
       </c>
-      <c r="L3" s="96" t="s">
-        <v>132</v>
+      <c r="L3" s="95" t="s">
+        <v>131</v>
       </c>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="98"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="97"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="87" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="86" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="98" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H4" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="112" t="s">
-        <v>181</v>
+      <c r="I4" s="94" t="s">
+        <v>180</v>
       </c>
       <c r="J4" s="105"/>
       <c r="K4" s="107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77" t="s">
+      <c r="M4" s="76"/>
+      <c r="N4" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="77"/>
-      <c r="P4" s="95" t="s">
+      <c r="O4" s="76"/>
+      <c r="P4" s="98" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="87"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="86"/>
       <c r="C5" s="102"/>
       <c r="D5" s="103"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="95"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="98"/>
       <c r="G5" s="99"/>
       <c r="H5" s="101"/>
-      <c r="I5" s="112"/>
+      <c r="I5" s="94"/>
       <c r="J5" s="106"/>
       <c r="K5" s="108"/>
       <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="57" t="s">
-        <v>264</v>
+      <c r="M5" s="56" t="s">
+        <v>258</v>
       </c>
       <c r="N5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="57" t="s">
-        <v>264</v>
+      <c r="O5" s="56" t="s">
+        <v>258</v>
       </c>
-      <c r="P5" s="95"/>
+      <c r="P5" s="98"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -40720,6 +40549,8 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9TADddINtH3/s8+B+YSEyrbqN3sXm6gNvmsaihCGVKf7Pla3vF7K/W63Z2DPtXhM7gpZzMQTmkRfISjjfsW2DA==" saltValue="PE4zbTBOxopTV3TBfcOFrw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
@@ -40736,8 +40567,6 @@
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 J6 K4:K5 G4:I5 O5" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40781,7 +40610,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -40795,88 +40624,88 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
+      <c r="A2" s="86" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="95" t="s">
-        <v>242</v>
+      <c r="B2" s="98" t="s">
+        <v>236</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="95" t="s">
-        <v>243</v>
+      <c r="A3" s="86"/>
+      <c r="B3" s="98" t="s">
+        <v>237</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95" t="s">
-        <v>244</v>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98" t="s">
+        <v>238</v>
       </c>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="89" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="94" t="s">
-        <v>101</v>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="93" t="s">
+        <v>100</v>
       </c>
-      <c r="G4" s="89" t="s">
+      <c r="G4" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="94" t="s">
-        <v>101</v>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="93" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
+      <c r="A5" s="86"/>
       <c r="B5" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="88"/>
+      <c r="F5" s="87"/>
       <c r="G5" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="52" t="s">
+      <c r="J5" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="88"/>
+      <c r="K5" s="87"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -43554,7 +43383,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -43598,198 +43427,198 @@
       <c r="AO1" s="5"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
+      <c r="A2" s="86" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="98" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="98"/>
+      <c r="U2" s="112" t="s">
+        <v>239</v>
+      </c>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
+      <c r="AE2" s="113"/>
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="114"/>
+      <c r="AH2" s="112" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="113"/>
+      <c r="AK2" s="113"/>
+      <c r="AL2" s="113"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="114"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="86"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="84"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="115"/>
+      <c r="AO3" s="85"/>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A4" s="86"/>
+      <c r="B4" s="93" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="104" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="77" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="113" t="s">
-        <v>245</v>
-      </c>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="114"/>
-      <c r="AG2" s="115"/>
-      <c r="AH2" s="113" t="s">
-        <v>246</v>
-      </c>
-      <c r="AI2" s="114"/>
-      <c r="AJ2" s="114"/>
-      <c r="AK2" s="114"/>
-      <c r="AL2" s="114"/>
-      <c r="AM2" s="114"/>
-      <c r="AN2" s="114"/>
-      <c r="AO2" s="115"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="95"/>
-      <c r="P3" s="95"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="95"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="95"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="116"/>
-      <c r="W3" s="116"/>
-      <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
-      <c r="Z3" s="116"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="116"/>
-      <c r="AD3" s="116"/>
-      <c r="AE3" s="116"/>
-      <c r="AF3" s="116"/>
-      <c r="AG3" s="86"/>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="116"/>
-      <c r="AJ3" s="116"/>
-      <c r="AK3" s="116"/>
-      <c r="AL3" s="116"/>
-      <c r="AM3" s="116"/>
-      <c r="AN3" s="116"/>
-      <c r="AO3" s="86"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="94" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="94" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="104" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="78" t="s">
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77" t="s">
         <v>195</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78" t="s">
-        <v>196</v>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="93" t="s">
+        <v>177</v>
       </c>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="94" t="s">
-        <v>178</v>
-      </c>
-      <c r="L4" s="78" t="s">
+      <c r="L4" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78" t="s">
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="78"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="78" t="s">
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="T4" s="78"/>
-      <c r="U4" s="95" t="s">
-        <v>159</v>
+      <c r="T4" s="77"/>
+      <c r="U4" s="98" t="s">
+        <v>158</v>
       </c>
-      <c r="V4" s="95" t="s">
+      <c r="V4" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="95" t="s">
+      <c r="W4" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="X4" s="95" t="s">
+      <c r="X4" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="95" t="s">
+      <c r="Y4" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="95" t="s">
+      <c r="Z4" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="95" t="s">
+      <c r="AA4" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="AB4" s="95" t="s">
+      <c r="AB4" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="AC4" s="95" t="s">
+      <c r="AC4" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="AD4" s="95" t="s">
+      <c r="AD4" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="AE4" s="95" t="s">
+      <c r="AE4" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="95" t="s">
-        <v>151</v>
+      <c r="AF4" s="98" t="s">
+        <v>150</v>
       </c>
-      <c r="AG4" s="95" t="s">
+      <c r="AG4" s="98" t="s">
         <v>39</v>
       </c>
       <c r="AH4" s="109" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AI4" s="111"/>
-      <c r="AJ4" s="78" t="s">
-        <v>248</v>
+      <c r="AJ4" s="77" t="s">
+        <v>242</v>
       </c>
-      <c r="AK4" s="78"/>
-      <c r="AL4" s="78" t="s">
-        <v>249</v>
+      <c r="AK4" s="77"/>
+      <c r="AL4" s="77" t="s">
+        <v>243</v>
       </c>
-      <c r="AM4" s="78"/>
-      <c r="AN4" s="78" t="s">
-        <v>250</v>
+      <c r="AM4" s="77"/>
+      <c r="AN4" s="77" t="s">
+        <v>244</v>
       </c>
-      <c r="AO4" s="78"/>
+      <c r="AO4" s="77"/>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
       <c r="D5" s="106"/>
       <c r="E5" s="41" t="s">
         <v>25</v>
@@ -43798,7 +43627,7 @@
         <v>26</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H5" s="41" t="s">
         <v>25</v>
@@ -43807,72 +43636,72 @@
         <v>26</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
-      <c r="K5" s="88"/>
+      <c r="K5" s="87"/>
       <c r="L5" s="38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M5" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="N5" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="N5" s="38" t="s">
+      <c r="O5" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="O5" s="38" t="s">
+      <c r="P5" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="P5" s="38" t="s">
+      <c r="Q5" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="Q5" s="38" t="s">
+      <c r="R5" s="38" t="s">
         <v>157</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>158</v>
       </c>
       <c r="S5" s="41" t="s">
         <v>22</v>
       </c>
       <c r="T5" s="44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
-      <c r="U5" s="95"/>
-      <c r="V5" s="95"/>
-      <c r="W5" s="95"/>
-      <c r="X5" s="95"/>
-      <c r="Y5" s="95"/>
-      <c r="Z5" s="95"/>
-      <c r="AA5" s="95"/>
-      <c r="AB5" s="95"/>
-      <c r="AC5" s="95"/>
-      <c r="AD5" s="95"/>
-      <c r="AE5" s="95"/>
-      <c r="AF5" s="95"/>
-      <c r="AG5" s="95"/>
+      <c r="U5" s="98"/>
+      <c r="V5" s="98"/>
+      <c r="W5" s="98"/>
+      <c r="X5" s="98"/>
+      <c r="Y5" s="98"/>
+      <c r="Z5" s="98"/>
+      <c r="AA5" s="98"/>
+      <c r="AB5" s="98"/>
+      <c r="AC5" s="98"/>
+      <c r="AD5" s="98"/>
+      <c r="AE5" s="98"/>
+      <c r="AF5" s="98"/>
+      <c r="AG5" s="98"/>
       <c r="AH5" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI5" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="AI5" s="38" t="s">
+      <c r="AJ5" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="AJ5" s="38" t="s">
+      <c r="AK5" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="AK5" s="38" t="s">
+      <c r="AL5" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="AL5" s="38" t="s">
+      <c r="AM5" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="AM5" s="38" t="s">
+      <c r="AN5" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="AN5" s="38" t="s">
+      <c r="AO5" s="38" t="s">
         <v>166</v>
-      </c>
-      <c r="AO5" s="38" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -52478,20 +52307,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NiKKXtjpQMePcsqc5jjUDaSQ7PwYr9+sjfqfZD87x0KbSUAFE8Baue/7fXFs4bMxVWpKhzgpmVEg8+jmkTDZbw==" saltValue="/cWUcVxNNlNaEWVwXWfzkw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH2:AO3"/>
     <mergeCell ref="D4:D5"/>
@@ -52508,6 +52323,20 @@
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 R5 AI5 AK5 AM5 L5 M5 N5 O5 P5 Q5 AO5 AJ5 AL5 AN5 AH5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -52552,45 +52381,45 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
+      <c r="A2" s="86" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="87" t="s">
-        <v>193</v>
+      <c r="B2" s="86" t="s">
+        <v>192</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="117"/>
-      <c r="B3" s="87" t="s">
-        <v>188</v>
+      <c r="A3" s="116"/>
+      <c r="B3" s="86" t="s">
+        <v>187</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="86" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="117"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="87"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="86"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="117"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="87"/>
+      <c r="A5" s="116"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="86"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -53827,7 +53656,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -53840,64 +53669,64 @@
       <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="95" t="s">
-        <v>234</v>
+      <c r="B2" s="98" t="s">
+        <v>228</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="89" t="s">
-        <v>235</v>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="88" t="s">
+        <v>229</v>
       </c>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="93"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="94" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="93" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="D3" s="99" t="s">
         <v>169</v>
       </c>
-      <c r="D3" s="99" t="s">
+      <c r="E3" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" s="114" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" s="104" t="s">
         <v>170</v>
       </c>
-      <c r="E3" s="95" t="s">
-        <v>175</v>
-      </c>
-      <c r="F3" s="115" t="s">
-        <v>176</v>
-      </c>
-      <c r="G3" s="104" t="s">
+      <c r="H3" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H3" s="104" t="s">
+      <c r="I3" s="104" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="104" t="s">
+      <c r="J3" s="118" t="s">
         <v>173</v>
       </c>
-      <c r="J3" s="120" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="99"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="86"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="85"/>
       <c r="G4" s="106"/>
       <c r="H4" s="106"/>
       <c r="I4" s="106"/>
-      <c r="J4" s="121"/>
+      <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -56302,11 +56131,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="rbaELUtMLiFIUzK2Lo99z9d9U/+7pUd8ywEap5Et9u8xKeEcXwzK/YHzlDzNf0b31XcPQzpRtM0zLEm0RaQL/w==" saltValue="qBVdEFs3JSBOU1K55aehjA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
@@ -56314,6 +56138,11 @@
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 G3 H3 I3 J3" xr:uid="{17D462F2-8B43-4EF8-AF0E-D9F26228FDD4}">
@@ -56353,7 +56182,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11"/>
@@ -56372,60 +56201,60 @@
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="119" t="s">
-        <v>110</v>
+      <c r="A2" s="120" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="117" t="s">
-        <v>182</v>
+      <c r="B2" s="116" t="s">
+        <v>181</v>
       </c>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="113" t="s">
-        <v>252</v>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="112" t="s">
+        <v>246</v>
       </c>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="114"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="125" t="s">
-        <v>177</v>
+      <c r="A3" s="74"/>
+      <c r="B3" s="124" t="s">
+        <v>176</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="C3" s="128" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="127" t="s">
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="126" t="s">
+        <v>184</v>
+      </c>
+      <c r="I3" s="124" t="s">
         <v>185</v>
       </c>
-      <c r="I3" s="125" t="s">
-        <v>186</v>
+      <c r="J3" s="121" t="s">
+        <v>247</v>
       </c>
-      <c r="J3" s="122" t="s">
-        <v>253</v>
-      </c>
-      <c r="K3" s="123"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="86"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="85"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="126"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="125"/>
       <c r="C4" s="47" t="s">
         <v>23</v>
       </c>
@@ -56433,16 +56262,16 @@
         <v>46</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G4" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="128"/>
-      <c r="I4" s="126"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="125"/>
       <c r="J4" s="48" t="s">
         <v>23</v>
       </c>
@@ -56450,19 +56279,19 @@
         <v>15</v>
       </c>
       <c r="L4" s="49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M4" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="N4" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="N4" s="40" t="s">
+      <c r="O4" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="O4" s="40" t="s">
+      <c r="P4" s="40" t="s">
         <v>191</v>
-      </c>
-      <c r="P4" s="40" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -60134,7 +59963,7 @@
   <sheetData>
     <row r="1" spans="1:31" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -60167,223 +59996,221 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="6"/>
     </row>
-    <row r="2" spans="1:31" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>110</v>
+    <row r="2" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="86" t="s">
+        <v>109</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="86" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="116" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="123"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="120" t="s">
+        <v>264</v>
+      </c>
+      <c r="J2" s="120" t="s">
+        <v>265</v>
+      </c>
+      <c r="K2" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="113"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="114"/>
+      <c r="P2" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q2" s="98" t="s">
+        <v>267</v>
+      </c>
+      <c r="R2" s="86" t="s">
+        <v>268</v>
+      </c>
+      <c r="S2" s="86" t="s">
+        <v>52</v>
+      </c>
+      <c r="T2" s="86"/>
+      <c r="U2" s="131" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="117" t="s">
-        <v>228</v>
+      <c r="V2" s="132"/>
+      <c r="W2" s="131" t="s">
+        <v>275</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="124"/>
-      <c r="T2" s="124"/>
-      <c r="U2" s="124"/>
-      <c r="V2" s="124"/>
-      <c r="W2" s="124"/>
-      <c r="X2" s="124"/>
-      <c r="Y2" s="124"/>
-      <c r="Z2" s="124"/>
-      <c r="AA2" s="124"/>
-      <c r="AB2" s="124"/>
-      <c r="AC2" s="124"/>
-      <c r="AD2" s="124"/>
-      <c r="AE2" s="118"/>
-    </row>
-    <row r="3" spans="1:31" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="87"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87" t="s">
-        <v>97</v>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="131" t="s">
+        <v>274</v>
       </c>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="117" t="s">
+      <c r="Z2" s="132"/>
+      <c r="AA2" s="86" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="86"/>
+      <c r="AD2" s="86"/>
+      <c r="AE2" s="98" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="116" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="124"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="119" t="s">
+      <c r="E3" s="117"/>
+      <c r="F3" s="120" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="116" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="117"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="86"/>
+      <c r="T3" s="86"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="83"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="83"/>
+      <c r="AA3" s="86"/>
+      <c r="AB3" s="86"/>
+      <c r="AC3" s="86"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="98"/>
+    </row>
+    <row r="4" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="75"/>
+      <c r="G4" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="M4" s="59" t="s">
+        <v>263</v>
+      </c>
+      <c r="N4" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="86"/>
+      <c r="S4" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="U4" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="X4" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y4" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA4" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB4" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC4" s="50" t="s">
         <v>272</v>
       </c>
-      <c r="J3" s="119" t="s">
+      <c r="AD4" s="50" t="s">
         <v>273</v>
       </c>
-      <c r="K3" s="113" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="113" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="115"/>
-      <c r="P3" s="87" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q3" s="95" t="s">
-        <v>275</v>
-      </c>
-      <c r="R3" s="87" t="s">
-        <v>276</v>
-      </c>
-      <c r="S3" s="87" t="s">
-        <v>52</v>
-      </c>
-      <c r="T3" s="87"/>
-      <c r="U3" s="132" t="s">
-        <v>114</v>
-      </c>
-      <c r="V3" s="133"/>
-      <c r="W3" s="132" t="s">
-        <v>283</v>
-      </c>
-      <c r="X3" s="133"/>
-      <c r="Y3" s="132" t="s">
-        <v>282</v>
-      </c>
-      <c r="Z3" s="133"/>
-      <c r="AA3" s="87" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
-      <c r="AE3" s="95" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="117" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="119" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="117" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="87"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="84"/>
-      <c r="W4" s="82"/>
-      <c r="X4" s="84"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="84"/>
-      <c r="AA4" s="87"/>
-      <c r="AB4" s="87"/>
-      <c r="AC4" s="87"/>
-      <c r="AD4" s="87"/>
-      <c r="AE4" s="95"/>
-    </row>
-    <row r="5" spans="1:31" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="50" t="s">
-        <v>218</v>
-      </c>
-      <c r="L5" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="M5" s="60" t="s">
-        <v>271</v>
-      </c>
-      <c r="N5" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="T5" s="42" t="s">
-        <v>277</v>
-      </c>
-      <c r="U5" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="V5" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="X5" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y5" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA5" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="AB5" s="50" t="s">
-        <v>279</v>
-      </c>
-      <c r="AC5" s="50" t="s">
-        <v>280</v>
-      </c>
-      <c r="AD5" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE5" s="95"/>
+      <c r="AE4" s="98"/>
+    </row>
+    <row r="5" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="86"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -60436,10 +60263,10 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="146"/>
-      <c r="S7" s="146"/>
-      <c r="T7" s="146"/>
-      <c r="U7" s="146"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
@@ -60469,10 +60296,10 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="146"/>
-      <c r="S8" s="146"/>
-      <c r="T8" s="146"/>
-      <c r="U8" s="146"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
@@ -60502,10 +60329,10 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="146"/>
-      <c r="S9" s="146"/>
-      <c r="T9" s="146"/>
-      <c r="U9" s="146"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
@@ -60535,10 +60362,10 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="146"/>
-      <c r="S10" s="146"/>
-      <c r="T10" s="146"/>
-      <c r="U10" s="146"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
@@ -66955,73 +66782,43 @@
     <row r="205" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-      <c r="R205" s="2"/>
-      <c r="S205" s="2"/>
-      <c r="T205" s="2"/>
-      <c r="U205" s="2"/>
-      <c r="V205" s="2"/>
-      <c r="W205" s="2"/>
-      <c r="X205" s="2"/>
-      <c r="Y205" s="2"/>
-      <c r="Z205" s="2"/>
-      <c r="AA205" s="2"/>
-      <c r="AB205" s="2"/>
-      <c r="AC205" s="2"/>
-      <c r="AD205" s="2"/>
-      <c r="AE205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pKPsmdou0EF2TCODYF/pnS+Phr+bI+HgjTIhrSHfvz1Kutindr4Dbe09CEFUGEi3QO3HMwvvFlvYHVklaH4Zaw==" saltValue="6oLDoJ48d3ScSYjbrjzxUg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="22">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C2:AE2"/>
-    <mergeCell ref="AE3:AE5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="S3:T4"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/ZqmwluKBbPQ7rPO4bmBi5UFYgKml1LJiwluKeUOtSTft292ATg40pfSxiPFYf8xvzhTf3E8RNme/7bc6tamdg==" saltValue="F1hbaB/uaVyj31IJBgSu1Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="21">
+    <mergeCell ref="N2:O3"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="Y3:Z4"/>
-    <mergeCell ref="AA3:AD4"/>
-    <mergeCell ref="U3:V4"/>
-    <mergeCell ref="W3:X4"/>
-    <mergeCell ref="K3:M4"/>
-    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:T3"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="Y2:Z3"/>
+    <mergeCell ref="AA2:AD3"/>
+    <mergeCell ref="U2:V3"/>
+    <mergeCell ref="W2:X3"/>
+    <mergeCell ref="K2:M3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5 AA5:AD5" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4 AA4:AD4" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AA5" r:id="rId1" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{2BC6450F-A7B4-4044-BEA6-59E54066E449}"/>
-    <hyperlink ref="AB5" r:id="rId2" location="targetSpecies" display="SPECIES_2_CODE" xr:uid="{9EEA8352-0631-4B4E-BB1B-FF880D8B8ED2}"/>
-    <hyperlink ref="AC5" r:id="rId3" location="targetSpecies" display="SPECIES_3_CODE" xr:uid="{B78A1E77-3003-40C6-9B0C-101A94179479}"/>
-    <hyperlink ref="AD5" r:id="rId4" location="targetSpecies" display="SPECIES_4_CODE" xr:uid="{22DD36F0-D891-4763-8CC9-508C73D63CC9}"/>
-    <hyperlink ref="K5" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{53874CDA-60F7-44F3-A738-546AA82ACA2B}"/>
+    <hyperlink ref="AA4" r:id="rId1" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{2BC6450F-A7B4-4044-BEA6-59E54066E449}"/>
+    <hyperlink ref="AB4" r:id="rId2" location="targetSpecies" display="SPECIES_2_CODE" xr:uid="{9EEA8352-0631-4B4E-BB1B-FF880D8B8ED2}"/>
+    <hyperlink ref="AC4" r:id="rId3" location="targetSpecies" display="SPECIES_3_CODE" xr:uid="{B78A1E77-3003-40C6-9B0C-101A94179479}"/>
+    <hyperlink ref="AD4" r:id="rId4" location="targetSpecies" display="SPECIES_4_CODE" xr:uid="{22DD36F0-D891-4763-8CC9-508C73D63CC9}"/>
+    <hyperlink ref="K4" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{53874CDA-60F7-44F3-A738-546AA82ACA2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0726C35-FAE2-4A3F-86C6-8A01CD91CA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245EE23D-1A7D-44F3-9CA1-EF893FD22309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28755" yWindow="315" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="11" activeTab="18" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="275">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -211,12 +211,6 @@
   </si>
   <si>
     <t>SET</t>
-  </si>
-  <si>
-    <t>SHARK_LINES</t>
-  </si>
-  <si>
-    <t>VMS_ON</t>
   </si>
   <si>
     <t>PERCENTAGE</t>
@@ -394,9 +388,6 @@
   </si>
   <si>
     <t>SET_ID</t>
-  </si>
-  <si>
-    <t>LEADER_MATERIAL</t>
   </si>
   <si>
     <t>HOOK_PODS</t>
@@ -765,9 +756,6 @@
     <t>OBSERVED TRIP SUMMARY</t>
   </si>
   <si>
-    <t>TRIP DETAILS</t>
-  </si>
-  <si>
     <t>VESSEL DEPARTURE</t>
   </si>
   <si>
@@ -879,13 +867,19 @@
     <t>SPECIES_4</t>
   </si>
   <si>
-    <t>BRANCHLINE_LENGTH_MAXIMUM</t>
+    <t>TARGET SPECIES</t>
   </si>
   <si>
-    <t>BRANCHLINE_LENGTH_MINIMUM</t>
+    <t>SHARK LINES</t>
   </si>
   <si>
-    <t>TARGET SPECIES</t>
+    <t>LEADER MATERIAL</t>
+  </si>
+  <si>
+    <t>BRANCHLINE LENGTH MINIMUM</t>
+  </si>
+  <si>
+    <t>BRANCHLINE LENGTH MAXIMUM</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2040,7 @@
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="64" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C2" s="65"/>
       <c r="D2" s="65"/>
@@ -2067,14 +2061,14 @@
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="12"/>
       <c r="C4" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G4" s="16">
         <v>1</v>
@@ -2093,7 +2087,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
@@ -2113,12 +2107,12 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="18"/>
       <c r="C8" s="70" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="19"/>
       <c r="F8" s="70" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G8" s="70"/>
       <c r="H8" s="20"/>
@@ -2126,12 +2120,12 @@
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="18"/>
       <c r="C9" s="22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="19"/>
       <c r="F9" s="22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="20"/>
@@ -2139,12 +2133,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="18"/>
       <c r="C10" s="24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="19"/>
       <c r="F10" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="20"/>
@@ -2161,7 +2155,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="18"/>
       <c r="C12" s="24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="19"/>
@@ -2172,7 +2166,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="18"/>
       <c r="C13" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="19"/>
@@ -2201,7 +2195,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="18"/>
       <c r="C16" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -2221,7 +2215,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="18"/>
       <c r="C18" s="24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="19"/>
@@ -2232,7 +2226,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="18"/>
       <c r="C19" s="29" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="19"/>
@@ -2243,7 +2237,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="18"/>
       <c r="C20" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="19"/>
@@ -2254,7 +2248,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
       <c r="C21" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="19"/>
@@ -2283,7 +2277,7 @@
     <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="C24" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="19"/>
@@ -2361,7 +2355,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2370,19 +2364,19 @@
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="141" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="141" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -3823,7 +3817,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3842,38 +3836,38 @@
     </row>
     <row r="2" spans="1:15" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="120" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D2" s="120" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E2" s="93" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F2" s="120" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G2" s="120" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H2" s="120" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I2" s="120" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J2" s="88" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K2" s="92"/>
       <c r="L2" s="116" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="M2" s="123"/>
       <c r="N2" s="123"/>
@@ -3893,19 +3887,19 @@
         <v>47</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M3" s="56" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N3" s="56" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O3" s="56" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -7354,7 +7348,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -7363,13 +7357,13 @@
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="116" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D2" s="123"/>
       <c r="E2" s="117"/>
@@ -7381,10 +7375,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8819,7 +8813,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8829,13 +8823,13 @@
     </row>
     <row r="2" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="116" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2" s="123"/>
       <c r="E2" s="123"/>
@@ -8845,16 +8839,16 @@
       <c r="A3" s="75"/>
       <c r="B3" s="75"/>
       <c r="C3" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10503,7 +10497,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10524,58 +10518,58 @@
     </row>
     <row r="2" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="116" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D2" s="123"/>
       <c r="E2" s="117"/>
       <c r="F2" s="116" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G2" s="123"/>
       <c r="H2" s="117"/>
       <c r="I2" s="99" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J2" s="98" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K2" s="98"/>
       <c r="L2" s="98"/>
       <c r="M2" s="98"/>
       <c r="N2" s="86" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O2" s="86" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P2" s="86" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q2" s="133" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="74"/>
       <c r="B3" s="74"/>
       <c r="C3" s="120" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" s="117"/>
       <c r="F3" s="120" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G3" s="116" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="99"/>
@@ -10607,16 +10601,16 @@
       </c>
       <c r="I4" s="99"/>
       <c r="J4" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="K4" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" s="50" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="50" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="50" t="s">
-        <v>219</v>
-      </c>
       <c r="M4" s="50" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N4" s="86"/>
       <c r="O4" s="86"/>
@@ -14474,7 +14468,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -14482,10 +14476,10 @@
     </row>
     <row r="2" spans="1:4" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="88" t="s">
         <v>48</v>
@@ -14496,10 +14490,10 @@
       <c r="A3" s="75"/>
       <c r="B3" s="75"/>
       <c r="C3" s="42" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15735,7 +15729,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -15750,29 +15744,29 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="120" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="120" t="s">
-        <v>115</v>
-      </c>
       <c r="D2" s="133" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" s="134" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="133" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H2" s="86" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I2" s="112" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J2" s="113"/>
       <c r="K2" s="114"/>
@@ -15799,18 +15793,18 @@
         <v>23</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G4" s="133"/>
       <c r="H4" s="86"/>
       <c r="I4" s="50" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K4" s="50" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -18480,7 +18474,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -18509,54 +18503,54 @@
     </row>
     <row r="2" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="138" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="138" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="138" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="138" t="s">
-        <v>115</v>
-      </c>
       <c r="D2" s="138" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2" s="107" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F2" s="107" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G2" s="86" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H2" s="86"/>
       <c r="I2" s="86"/>
       <c r="J2" s="86"/>
       <c r="K2" s="98" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L2" s="98"/>
       <c r="M2" s="98"/>
       <c r="N2" s="98"/>
       <c r="O2" s="98" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P2" s="98"/>
       <c r="Q2" s="98"/>
       <c r="R2" s="104" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S2" s="88" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T2" s="92"/>
       <c r="U2" s="88" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V2" s="89"/>
       <c r="W2" s="92"/>
       <c r="X2" s="98" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Y2" s="98"/>
     </row>
@@ -18571,56 +18565,56 @@
         <v>23</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J3" s="39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K3" s="50" t="s">
         <v>23</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M3" s="50" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O3" s="50" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q3" s="50" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R3" s="106"/>
       <c r="S3" s="43" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T3" s="43" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U3" s="59" t="s">
         <v>23</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="W3" s="42" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="X3" s="50" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Y3" s="50" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -24092,7 +24086,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -24116,57 +24110,57 @@
     </row>
     <row r="2" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="138" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="138" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="138" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="138" t="s">
-        <v>115</v>
-      </c>
       <c r="D2" s="138" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2" s="107" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" s="107" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="105" t="s">
         <v>196</v>
       </c>
-      <c r="F2" s="107" t="s">
-        <v>197</v>
-      </c>
-      <c r="G2" s="107" t="s">
-        <v>198</v>
-      </c>
-      <c r="H2" s="105" t="s">
-        <v>199</v>
-      </c>
       <c r="I2" s="84" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J2" s="85"/>
       <c r="K2" s="81" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L2" s="83"/>
       <c r="M2" s="105" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N2" s="140" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O2" s="140" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="105" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q2" s="140" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="105" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q2" s="140" t="s">
-        <v>72</v>
-      </c>
-      <c r="R2" s="140" t="s">
-        <v>73</v>
-      </c>
       <c r="S2" s="87" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="T2" s="87"/>
     </row>
@@ -24180,16 +24174,16 @@
       <c r="G3" s="108"/>
       <c r="H3" s="106"/>
       <c r="I3" s="50" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J3" s="50" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="56" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M3" s="106"/>
       <c r="N3" s="87"/>
@@ -24198,10 +24192,10 @@
       <c r="Q3" s="87"/>
       <c r="R3" s="87"/>
       <c r="S3" s="50" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="T3" s="50" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -28667,7 +28661,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -28682,37 +28676,37 @@
     </row>
     <row r="2" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="142" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="142" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="142" t="s">
-        <v>115</v>
-      </c>
       <c r="D2" s="142" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2" s="50" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I2" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K2" s="42" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
@@ -31365,7 +31359,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="7" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -31393,14 +31387,14 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C2" s="75"/>
       <c r="D2" s="87" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E2" s="87"/>
       <c r="F2" s="87"/>
@@ -31412,7 +31406,7 @@
       <c r="L2" s="87"/>
       <c r="M2" s="87"/>
       <c r="N2" s="78" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="O2" s="79"/>
       <c r="P2" s="79"/>
@@ -31431,14 +31425,14 @@
       <c r="B3" s="86"/>
       <c r="C3" s="86"/>
       <c r="D3" s="88" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" s="89"/>
       <c r="F3" s="89"/>
       <c r="G3" s="89"/>
       <c r="H3" s="92"/>
       <c r="I3" s="88" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J3" s="89"/>
       <c r="K3" s="89"/>
@@ -31462,40 +31456,40 @@
       <c r="B4" s="86"/>
       <c r="C4" s="86"/>
       <c r="D4" s="84" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" s="85"/>
       <c r="F4" s="84" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G4" s="85"/>
       <c r="H4" s="93" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I4" s="84" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J4" s="85"/>
       <c r="K4" s="84" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L4" s="85"/>
       <c r="M4" s="90" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N4" s="76" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="O4" s="76"/>
       <c r="P4" s="77" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Q4" s="77"/>
       <c r="R4" s="77"/>
       <c r="S4" s="77"/>
       <c r="T4" s="77"/>
       <c r="U4" s="77" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="V4" s="77"/>
       <c r="W4" s="77"/>
@@ -31504,13 +31498,13 @@
     <row r="5" spans="1:25" s="54" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="75"/>
       <c r="B5" s="39" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>4</v>
@@ -31523,7 +31517,7 @@
       </c>
       <c r="H5" s="87"/>
       <c r="I5" s="50" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J5" s="50" t="s">
         <v>4</v>
@@ -31557,16 +31551,16 @@
         <v>10</v>
       </c>
       <c r="U5" s="38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="V5" s="38" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="W5" s="38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="X5" s="38" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -36810,7 +36804,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -36830,10 +36824,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="95" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C2" s="96"/>
       <c r="D2" s="96"/>
@@ -36868,10 +36862,10 @@
         <v>17</v>
       </c>
       <c r="K3" s="52" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L3" s="95" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M3" s="96"/>
       <c r="N3" s="96"/>
@@ -36884,7 +36878,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>2</v>
@@ -36896,17 +36890,17 @@
         <v>14</v>
       </c>
       <c r="G4" s="99" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H4" s="100" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="94" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J4" s="105"/>
       <c r="K4" s="107" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L4" s="76" t="s">
         <v>18</v>
@@ -36936,13 +36930,13 @@
         <v>3</v>
       </c>
       <c r="M5" s="56" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="56" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P5" s="98"/>
     </row>
@@ -40592,7 +40586,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -40610,7 +40604,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -40624,88 +40618,86 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
-        <v>109</v>
+      <c r="A2" s="120" t="s">
+        <v>107</v>
       </c>
       <c r="B2" s="98" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C2" s="98"/>
       <c r="D2" s="98"/>
       <c r="E2" s="98"/>
       <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
+      <c r="G2" s="98" t="s">
+        <v>234</v>
+      </c>
       <c r="H2" s="98"/>
       <c r="I2" s="98"/>
       <c r="J2" s="98"/>
       <c r="K2" s="98"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="98" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98" t="s">
-        <v>238</v>
-      </c>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="88" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="93" t="s">
-        <v>100</v>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="93" t="s">
+        <v>98</v>
       </c>
-      <c r="G4" s="88" t="s">
+      <c r="G3" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="93" t="s">
-        <v>100</v>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="93" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="50" t="s">
-        <v>137</v>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="75"/>
+      <c r="B4" s="50" t="s">
+        <v>134</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D4" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="87"/>
-      <c r="G5" s="50" t="s">
-        <v>137</v>
+      <c r="F4" s="87"/>
+      <c r="G4" s="50" t="s">
+        <v>134</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I4" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="87"/>
+      <c r="K4" s="87"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -43294,41 +43286,27 @@
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5ViTLvN4HPP3AA5qTwoTg4YbHRHPn9wiNwJ56Sy7jeYcXp+QZSBRtXRm3+wK54ZTdMgKWAvWuHysclXNV/5DTQ==" saltValue="5SKnDs0ZbE5I3qvVevS/eA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="8">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G4:J4"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="u8pXLSYhOVbviCjMnAbnq7QuW/5rhXgGJG1eFeVlUlduAeybGPslcLzuVz4XyLFP1j/6v1ftio6sP6s2dukYSA==" saltValue="CawdL5I7cgplaq9Fy5TfQw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <mergeCells count="7">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:C5 G5:H5" xr:uid="{E97A6FE4-6BFF-4959-9F92-FB6DF23A11A6}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C4 G4:H4" xr:uid="{E97A6FE4-6BFF-4959-9F92-FB6DF23A11A6}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
-    <hyperlink ref="G5" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
-    <hyperlink ref="C5" r:id="rId3" location="Ports" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
-    <hyperlink ref="H5" r:id="rId4" location="Ports" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
+    <hyperlink ref="B4" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
+    <hyperlink ref="G4" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
+    <hyperlink ref="C4" r:id="rId3" location="Ports" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
+    <hyperlink ref="H4" r:id="rId4" location="Ports" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -43383,7 +43361,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -43428,10 +43406,10 @@
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="98" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C2" s="98"/>
       <c r="D2" s="98"/>
@@ -43452,7 +43430,7 @@
       <c r="S2" s="98"/>
       <c r="T2" s="98"/>
       <c r="U2" s="112" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V2" s="113"/>
       <c r="W2" s="113"/>
@@ -43467,7 +43445,7 @@
       <c r="AF2" s="113"/>
       <c r="AG2" s="114"/>
       <c r="AH2" s="112" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AI2" s="113"/>
       <c r="AJ2" s="113"/>
@@ -43523,26 +43501,26 @@
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="86"/>
       <c r="B4" s="93" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C4" s="93" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D4" s="104" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E4" s="77" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F4" s="77"/>
       <c r="G4" s="77"/>
       <c r="H4" s="77" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I4" s="77"/>
       <c r="J4" s="77"/>
       <c r="K4" s="93" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L4" s="77" t="s">
         <v>27</v>
@@ -43560,7 +43538,7 @@
       </c>
       <c r="T4" s="77"/>
       <c r="U4" s="98" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="V4" s="98" t="s">
         <v>30</v>
@@ -43593,25 +43571,25 @@
         <v>38</v>
       </c>
       <c r="AF4" s="98" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AG4" s="98" t="s">
         <v>39</v>
       </c>
       <c r="AH4" s="109" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AI4" s="111"/>
       <c r="AJ4" s="77" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AK4" s="77"/>
       <c r="AL4" s="77" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AM4" s="77"/>
       <c r="AN4" s="77" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AO4" s="77"/>
     </row>
@@ -43627,7 +43605,7 @@
         <v>26</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H5" s="41" t="s">
         <v>25</v>
@@ -43636,35 +43614,35 @@
         <v>26</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K5" s="87"/>
       <c r="L5" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="N5" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="O5" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="P5" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="N5" s="38" t="s">
+      <c r="Q5" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="O5" s="38" t="s">
+      <c r="R5" s="38" t="s">
         <v>154</v>
-      </c>
-      <c r="P5" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>157</v>
       </c>
       <c r="S5" s="41" t="s">
         <v>22</v>
       </c>
       <c r="T5" s="44" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="U5" s="98"/>
       <c r="V5" s="98"/>
@@ -43680,28 +43658,28 @@
       <c r="AF5" s="98"/>
       <c r="AG5" s="98"/>
       <c r="AH5" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI5" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="AJ5" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK5" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="AI5" s="38" t="s">
+      <c r="AL5" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="AJ5" s="38" t="s">
+      <c r="AM5" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="AK5" s="38" t="s">
+      <c r="AN5" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="AL5" s="38" t="s">
+      <c r="AO5" s="38" t="s">
         <v>163</v>
-      </c>
-      <c r="AM5" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="AN5" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO5" s="38" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -52381,7 +52359,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="5"/>
@@ -52389,10 +52367,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C2" s="86"/>
       <c r="D2" s="86"/>
@@ -52400,7 +52378,7 @@
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="116"/>
       <c r="B3" s="86" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C3" s="117" t="s">
         <v>41</v>
@@ -53656,7 +53634,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -53670,17 +53648,17 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="98" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C2" s="98"/>
       <c r="D2" s="98"/>
       <c r="E2" s="98"/>
       <c r="F2" s="98"/>
       <c r="G2" s="88" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H2" s="89"/>
       <c r="I2" s="89"/>
@@ -53689,31 +53667,31 @@
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="74"/>
       <c r="B3" s="93" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="93" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="99" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="114" t="s">
+        <v>172</v>
+      </c>
+      <c r="G3" s="104" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="H3" s="104" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="99" t="s">
+      <c r="I3" s="104" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="98" t="s">
-        <v>174</v>
-      </c>
-      <c r="F3" s="114" t="s">
-        <v>175</v>
-      </c>
-      <c r="G3" s="104" t="s">
+      <c r="J3" s="118" t="s">
         <v>170</v>
-      </c>
-      <c r="H3" s="104" t="s">
-        <v>171</v>
-      </c>
-      <c r="I3" s="104" t="s">
-        <v>172</v>
-      </c>
-      <c r="J3" s="118" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -56182,7 +56160,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11"/>
@@ -56202,10 +56180,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="120" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="116" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C2" s="123"/>
       <c r="D2" s="123"/>
@@ -56217,7 +56195,7 @@
       <c r="J2" s="123"/>
       <c r="K2" s="117"/>
       <c r="L2" s="112" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="M2" s="113"/>
       <c r="N2" s="113"/>
@@ -56227,7 +56205,7 @@
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="74"/>
       <c r="B3" s="124" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C3" s="128" t="s">
         <v>44</v>
@@ -56237,13 +56215,13 @@
       <c r="F3" s="129"/>
       <c r="G3" s="130"/>
       <c r="H3" s="126" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I3" s="124" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J3" s="121" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K3" s="122"/>
       <c r="L3" s="84"/>
@@ -56262,10 +56240,10 @@
         <v>46</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G4" s="45" t="s">
         <v>45</v>
@@ -56279,19 +56257,19 @@
         <v>15</v>
       </c>
       <c r="L4" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="M4" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="N4" s="40" t="s">
-        <v>189</v>
-      </c>
       <c r="O4" s="40" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -59928,7 +59906,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AE205"/>
+  <dimension ref="A1:AD205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
@@ -59958,12 +59936,11 @@
     <col min="25" max="25" width="16.28515625" style="3" customWidth="1"/>
     <col min="26" max="26" width="17" style="3" customWidth="1"/>
     <col min="27" max="30" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -59994,30 +59971,29 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="6"/>
-    </row>
-    <row r="2" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D2" s="86"/>
       <c r="E2" s="86"/>
       <c r="F2" s="116" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2" s="123"/>
       <c r="H2" s="117"/>
       <c r="I2" s="120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J2" s="120" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K2" s="112" t="s">
         <v>43</v>
@@ -60029,24 +60005,24 @@
       </c>
       <c r="O2" s="114"/>
       <c r="P2" s="86" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Q2" s="98" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="R2" s="86" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="S2" s="86" t="s">
-        <v>52</v>
+        <v>271</v>
       </c>
       <c r="T2" s="86"/>
       <c r="U2" s="131" t="s">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="V2" s="132"/>
       <c r="W2" s="131" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="X2" s="132"/>
       <c r="Y2" s="131" t="s">
@@ -60054,30 +60030,27 @@
       </c>
       <c r="Z2" s="132"/>
       <c r="AA2" s="86" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AB2" s="86"/>
       <c r="AC2" s="86"/>
       <c r="AD2" s="86"/>
-      <c r="AE2" s="98" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="86"/>
       <c r="B3" s="86"/>
       <c r="C3" s="78" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" s="117"/>
       <c r="F3" s="120" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G3" s="116" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="74"/>
@@ -60102,9 +60075,8 @@
       <c r="AB3" s="86"/>
       <c r="AC3" s="86"/>
       <c r="AD3" s="86"/>
-      <c r="AE3" s="98"/>
-    </row>
-    <row r="4" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="86"/>
       <c r="B4" s="86"/>
       <c r="C4" s="81"/>
@@ -60124,13 +60096,13 @@
       <c r="I4" s="75"/>
       <c r="J4" s="75"/>
       <c r="K4" s="50" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="M4" s="59" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N4" s="42" t="s">
         <v>48</v>
@@ -60145,41 +60117,40 @@
         <v>51</v>
       </c>
       <c r="T4" s="42" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="U4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="V4" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="W4" s="39" t="s">
         <v>22</v>
       </c>
       <c r="X4" s="39" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>22</v>
       </c>
       <c r="Z4" s="39" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AA4" s="56" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AB4" s="50" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AC4" s="50" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AD4" s="50" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
-      <c r="AE4" s="98"/>
-    </row>
-    <row r="5" spans="1:31" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="86"/>
       <c r="B5" s="86"/>
       <c r="C5" s="2"/>
@@ -60210,9 +60181,8 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -60243,9 +60213,8 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -60276,9 +60245,8 @@
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
-      <c r="AE7" s="2"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -60309,9 +60277,8 @@
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -60342,9 +60309,8 @@
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -60375,9 +60341,8 @@
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -60408,9 +60373,8 @@
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -60441,9 +60405,8 @@
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -60474,9 +60437,8 @@
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
-      <c r="AE13" s="2"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -60507,9 +60469,8 @@
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -60540,9 +60501,8 @@
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
-      <c r="AE15" s="2"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -60573,9 +60533,8 @@
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="2"/>
-      <c r="AE16" s="2"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -60606,9 +60565,8 @@
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
-      <c r="AE17" s="2"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -60639,9 +60597,8 @@
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
-      <c r="AE18" s="2"/>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -60672,9 +60629,8 @@
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -60705,9 +60661,8 @@
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -60738,9 +60693,8 @@
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -60771,9 +60725,8 @@
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -60804,9 +60757,8 @@
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -60837,9 +60789,8 @@
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -60870,9 +60821,8 @@
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="2"/>
-      <c r="AE25" s="2"/>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -60903,9 +60853,8 @@
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="2"/>
-      <c r="AE26" s="2"/>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -60936,9 +60885,8 @@
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="2"/>
-      <c r="AE27" s="2"/>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -60969,9 +60917,8 @@
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="2"/>
-      <c r="AE28" s="2"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -61002,9 +60949,8 @@
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="2"/>
-      <c r="AE29" s="2"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -61035,9 +60981,8 @@
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="2"/>
-      <c r="AE30" s="2"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -61068,9 +61013,8 @@
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="2"/>
-      <c r="AE31" s="2"/>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -61101,9 +61045,8 @@
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="2"/>
-      <c r="AE32" s="2"/>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -61134,9 +61077,8 @@
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
-      <c r="AE33" s="2"/>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -61167,9 +61109,8 @@
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="2"/>
-      <c r="AE34" s="2"/>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -61200,9 +61141,8 @@
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="2"/>
-      <c r="AE35" s="2"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -61233,9 +61173,8 @@
       <c r="AB36" s="2"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="2"/>
-      <c r="AE36" s="2"/>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -61266,9 +61205,8 @@
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
-      <c r="AE37" s="2"/>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -61299,9 +61237,8 @@
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="2"/>
-      <c r="AE38" s="2"/>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -61332,9 +61269,8 @@
       <c r="AB39" s="2"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="2"/>
-      <c r="AE39" s="2"/>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -61365,9 +61301,8 @@
       <c r="AB40" s="2"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="2"/>
-      <c r="AE40" s="2"/>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -61398,9 +61333,8 @@
       <c r="AB41" s="2"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="2"/>
-      <c r="AE41" s="2"/>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -61431,9 +61365,8 @@
       <c r="AB42" s="2"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="2"/>
-      <c r="AE42" s="2"/>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -61464,9 +61397,8 @@
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="2"/>
-      <c r="AE43" s="2"/>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -61497,9 +61429,8 @@
       <c r="AB44" s="2"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="2"/>
-      <c r="AE44" s="2"/>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -61530,9 +61461,8 @@
       <c r="AB45" s="2"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="2"/>
-      <c r="AE45" s="2"/>
-    </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -61563,9 +61493,8 @@
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="2"/>
-      <c r="AE46" s="2"/>
-    </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -61596,9 +61525,8 @@
       <c r="AB47" s="2"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="2"/>
-      <c r="AE47" s="2"/>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -61629,9 +61557,8 @@
       <c r="AB48" s="2"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="2"/>
-      <c r="AE48" s="2"/>
-    </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -61662,9 +61589,8 @@
       <c r="AB49" s="2"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="2"/>
-      <c r="AE49" s="2"/>
-    </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -61695,9 +61621,8 @@
       <c r="AB50" s="2"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="2"/>
-      <c r="AE50" s="2"/>
-    </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -61728,9 +61653,8 @@
       <c r="AB51" s="2"/>
       <c r="AC51" s="2"/>
       <c r="AD51" s="2"/>
-      <c r="AE51" s="2"/>
-    </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -61761,9 +61685,8 @@
       <c r="AB52" s="2"/>
       <c r="AC52" s="2"/>
       <c r="AD52" s="2"/>
-      <c r="AE52" s="2"/>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -61794,9 +61717,8 @@
       <c r="AB53" s="2"/>
       <c r="AC53" s="2"/>
       <c r="AD53" s="2"/>
-      <c r="AE53" s="2"/>
-    </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -61827,9 +61749,8 @@
       <c r="AB54" s="2"/>
       <c r="AC54" s="2"/>
       <c r="AD54" s="2"/>
-      <c r="AE54" s="2"/>
-    </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -61860,9 +61781,8 @@
       <c r="AB55" s="2"/>
       <c r="AC55" s="2"/>
       <c r="AD55" s="2"/>
-      <c r="AE55" s="2"/>
-    </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -61893,9 +61813,8 @@
       <c r="AB56" s="2"/>
       <c r="AC56" s="2"/>
       <c r="AD56" s="2"/>
-      <c r="AE56" s="2"/>
-    </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -61926,9 +61845,8 @@
       <c r="AB57" s="2"/>
       <c r="AC57" s="2"/>
       <c r="AD57" s="2"/>
-      <c r="AE57" s="2"/>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -61959,9 +61877,8 @@
       <c r="AB58" s="2"/>
       <c r="AC58" s="2"/>
       <c r="AD58" s="2"/>
-      <c r="AE58" s="2"/>
-    </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -61992,9 +61909,8 @@
       <c r="AB59" s="2"/>
       <c r="AC59" s="2"/>
       <c r="AD59" s="2"/>
-      <c r="AE59" s="2"/>
-    </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -62025,9 +61941,8 @@
       <c r="AB60" s="2"/>
       <c r="AC60" s="2"/>
       <c r="AD60" s="2"/>
-      <c r="AE60" s="2"/>
-    </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -62058,9 +61973,8 @@
       <c r="AB61" s="2"/>
       <c r="AC61" s="2"/>
       <c r="AD61" s="2"/>
-      <c r="AE61" s="2"/>
-    </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -62091,9 +62005,8 @@
       <c r="AB62" s="2"/>
       <c r="AC62" s="2"/>
       <c r="AD62" s="2"/>
-      <c r="AE62" s="2"/>
-    </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -62124,9 +62037,8 @@
       <c r="AB63" s="2"/>
       <c r="AC63" s="2"/>
       <c r="AD63" s="2"/>
-      <c r="AE63" s="2"/>
-    </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -62157,9 +62069,8 @@
       <c r="AB64" s="2"/>
       <c r="AC64" s="2"/>
       <c r="AD64" s="2"/>
-      <c r="AE64" s="2"/>
-    </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -62190,9 +62101,8 @@
       <c r="AB65" s="2"/>
       <c r="AC65" s="2"/>
       <c r="AD65" s="2"/>
-      <c r="AE65" s="2"/>
-    </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -62223,9 +62133,8 @@
       <c r="AB66" s="2"/>
       <c r="AC66" s="2"/>
       <c r="AD66" s="2"/>
-      <c r="AE66" s="2"/>
-    </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -62256,9 +62165,8 @@
       <c r="AB67" s="2"/>
       <c r="AC67" s="2"/>
       <c r="AD67" s="2"/>
-      <c r="AE67" s="2"/>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -62289,9 +62197,8 @@
       <c r="AB68" s="2"/>
       <c r="AC68" s="2"/>
       <c r="AD68" s="2"/>
-      <c r="AE68" s="2"/>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -62322,9 +62229,8 @@
       <c r="AB69" s="2"/>
       <c r="AC69" s="2"/>
       <c r="AD69" s="2"/>
-      <c r="AE69" s="2"/>
-    </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -62355,9 +62261,8 @@
       <c r="AB70" s="2"/>
       <c r="AC70" s="2"/>
       <c r="AD70" s="2"/>
-      <c r="AE70" s="2"/>
-    </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -62388,9 +62293,8 @@
       <c r="AB71" s="2"/>
       <c r="AC71" s="2"/>
       <c r="AD71" s="2"/>
-      <c r="AE71" s="2"/>
-    </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -62421,9 +62325,8 @@
       <c r="AB72" s="2"/>
       <c r="AC72" s="2"/>
       <c r="AD72" s="2"/>
-      <c r="AE72" s="2"/>
-    </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -62454,9 +62357,8 @@
       <c r="AB73" s="2"/>
       <c r="AC73" s="2"/>
       <c r="AD73" s="2"/>
-      <c r="AE73" s="2"/>
-    </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -62487,9 +62389,8 @@
       <c r="AB74" s="2"/>
       <c r="AC74" s="2"/>
       <c r="AD74" s="2"/>
-      <c r="AE74" s="2"/>
-    </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -62520,9 +62421,8 @@
       <c r="AB75" s="2"/>
       <c r="AC75" s="2"/>
       <c r="AD75" s="2"/>
-      <c r="AE75" s="2"/>
-    </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -62553,9 +62453,8 @@
       <c r="AB76" s="2"/>
       <c r="AC76" s="2"/>
       <c r="AD76" s="2"/>
-      <c r="AE76" s="2"/>
-    </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -62586,9 +62485,8 @@
       <c r="AB77" s="2"/>
       <c r="AC77" s="2"/>
       <c r="AD77" s="2"/>
-      <c r="AE77" s="2"/>
-    </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -62619,9 +62517,8 @@
       <c r="AB78" s="2"/>
       <c r="AC78" s="2"/>
       <c r="AD78" s="2"/>
-      <c r="AE78" s="2"/>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -62652,9 +62549,8 @@
       <c r="AB79" s="2"/>
       <c r="AC79" s="2"/>
       <c r="AD79" s="2"/>
-      <c r="AE79" s="2"/>
-    </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -62685,9 +62581,8 @@
       <c r="AB80" s="2"/>
       <c r="AC80" s="2"/>
       <c r="AD80" s="2"/>
-      <c r="AE80" s="2"/>
-    </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -62718,9 +62613,8 @@
       <c r="AB81" s="2"/>
       <c r="AC81" s="2"/>
       <c r="AD81" s="2"/>
-      <c r="AE81" s="2"/>
-    </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -62751,9 +62645,8 @@
       <c r="AB82" s="2"/>
       <c r="AC82" s="2"/>
       <c r="AD82" s="2"/>
-      <c r="AE82" s="2"/>
-    </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -62784,9 +62677,8 @@
       <c r="AB83" s="2"/>
       <c r="AC83" s="2"/>
       <c r="AD83" s="2"/>
-      <c r="AE83" s="2"/>
-    </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -62817,9 +62709,8 @@
       <c r="AB84" s="2"/>
       <c r="AC84" s="2"/>
       <c r="AD84" s="2"/>
-      <c r="AE84" s="2"/>
-    </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -62850,9 +62741,8 @@
       <c r="AB85" s="2"/>
       <c r="AC85" s="2"/>
       <c r="AD85" s="2"/>
-      <c r="AE85" s="2"/>
-    </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -62883,9 +62773,8 @@
       <c r="AB86" s="2"/>
       <c r="AC86" s="2"/>
       <c r="AD86" s="2"/>
-      <c r="AE86" s="2"/>
-    </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -62916,9 +62805,8 @@
       <c r="AB87" s="2"/>
       <c r="AC87" s="2"/>
       <c r="AD87" s="2"/>
-      <c r="AE87" s="2"/>
-    </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -62949,9 +62837,8 @@
       <c r="AB88" s="2"/>
       <c r="AC88" s="2"/>
       <c r="AD88" s="2"/>
-      <c r="AE88" s="2"/>
-    </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -62982,9 +62869,8 @@
       <c r="AB89" s="2"/>
       <c r="AC89" s="2"/>
       <c r="AD89" s="2"/>
-      <c r="AE89" s="2"/>
-    </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -63015,9 +62901,8 @@
       <c r="AB90" s="2"/>
       <c r="AC90" s="2"/>
       <c r="AD90" s="2"/>
-      <c r="AE90" s="2"/>
-    </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -63048,9 +62933,8 @@
       <c r="AB91" s="2"/>
       <c r="AC91" s="2"/>
       <c r="AD91" s="2"/>
-      <c r="AE91" s="2"/>
-    </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -63081,9 +62965,8 @@
       <c r="AB92" s="2"/>
       <c r="AC92" s="2"/>
       <c r="AD92" s="2"/>
-      <c r="AE92" s="2"/>
-    </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -63114,9 +62997,8 @@
       <c r="AB93" s="2"/>
       <c r="AC93" s="2"/>
       <c r="AD93" s="2"/>
-      <c r="AE93" s="2"/>
-    </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -63147,9 +63029,8 @@
       <c r="AB94" s="2"/>
       <c r="AC94" s="2"/>
       <c r="AD94" s="2"/>
-      <c r="AE94" s="2"/>
-    </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -63180,9 +63061,8 @@
       <c r="AB95" s="2"/>
       <c r="AC95" s="2"/>
       <c r="AD95" s="2"/>
-      <c r="AE95" s="2"/>
-    </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -63213,9 +63093,8 @@
       <c r="AB96" s="2"/>
       <c r="AC96" s="2"/>
       <c r="AD96" s="2"/>
-      <c r="AE96" s="2"/>
-    </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -63246,9 +63125,8 @@
       <c r="AB97" s="2"/>
       <c r="AC97" s="2"/>
       <c r="AD97" s="2"/>
-      <c r="AE97" s="2"/>
-    </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -63279,9 +63157,8 @@
       <c r="AB98" s="2"/>
       <c r="AC98" s="2"/>
       <c r="AD98" s="2"/>
-      <c r="AE98" s="2"/>
-    </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -63312,9 +63189,8 @@
       <c r="AB99" s="2"/>
       <c r="AC99" s="2"/>
       <c r="AD99" s="2"/>
-      <c r="AE99" s="2"/>
-    </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -63345,9 +63221,8 @@
       <c r="AB100" s="2"/>
       <c r="AC100" s="2"/>
       <c r="AD100" s="2"/>
-      <c r="AE100" s="2"/>
-    </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -63378,9 +63253,8 @@
       <c r="AB101" s="2"/>
       <c r="AC101" s="2"/>
       <c r="AD101" s="2"/>
-      <c r="AE101" s="2"/>
-    </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -63411,9 +63285,8 @@
       <c r="AB102" s="2"/>
       <c r="AC102" s="2"/>
       <c r="AD102" s="2"/>
-      <c r="AE102" s="2"/>
-    </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -63444,9 +63317,8 @@
       <c r="AB103" s="2"/>
       <c r="AC103" s="2"/>
       <c r="AD103" s="2"/>
-      <c r="AE103" s="2"/>
-    </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -63477,9 +63349,8 @@
       <c r="AB104" s="2"/>
       <c r="AC104" s="2"/>
       <c r="AD104" s="2"/>
-      <c r="AE104" s="2"/>
-    </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -63510,9 +63381,8 @@
       <c r="AB105" s="2"/>
       <c r="AC105" s="2"/>
       <c r="AD105" s="2"/>
-      <c r="AE105" s="2"/>
-    </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -63543,9 +63413,8 @@
       <c r="AB106" s="2"/>
       <c r="AC106" s="2"/>
       <c r="AD106" s="2"/>
-      <c r="AE106" s="2"/>
-    </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -63576,9 +63445,8 @@
       <c r="AB107" s="2"/>
       <c r="AC107" s="2"/>
       <c r="AD107" s="2"/>
-      <c r="AE107" s="2"/>
-    </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -63609,9 +63477,8 @@
       <c r="AB108" s="2"/>
       <c r="AC108" s="2"/>
       <c r="AD108" s="2"/>
-      <c r="AE108" s="2"/>
-    </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -63642,9 +63509,8 @@
       <c r="AB109" s="2"/>
       <c r="AC109" s="2"/>
       <c r="AD109" s="2"/>
-      <c r="AE109" s="2"/>
-    </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -63675,9 +63541,8 @@
       <c r="AB110" s="2"/>
       <c r="AC110" s="2"/>
       <c r="AD110" s="2"/>
-      <c r="AE110" s="2"/>
-    </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -63708,9 +63573,8 @@
       <c r="AB111" s="2"/>
       <c r="AC111" s="2"/>
       <c r="AD111" s="2"/>
-      <c r="AE111" s="2"/>
-    </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -63741,9 +63605,8 @@
       <c r="AB112" s="2"/>
       <c r="AC112" s="2"/>
       <c r="AD112" s="2"/>
-      <c r="AE112" s="2"/>
-    </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -63774,9 +63637,8 @@
       <c r="AB113" s="2"/>
       <c r="AC113" s="2"/>
       <c r="AD113" s="2"/>
-      <c r="AE113" s="2"/>
-    </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -63807,9 +63669,8 @@
       <c r="AB114" s="2"/>
       <c r="AC114" s="2"/>
       <c r="AD114" s="2"/>
-      <c r="AE114" s="2"/>
-    </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -63840,9 +63701,8 @@
       <c r="AB115" s="2"/>
       <c r="AC115" s="2"/>
       <c r="AD115" s="2"/>
-      <c r="AE115" s="2"/>
-    </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -63873,9 +63733,8 @@
       <c r="AB116" s="2"/>
       <c r="AC116" s="2"/>
       <c r="AD116" s="2"/>
-      <c r="AE116" s="2"/>
-    </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -63906,9 +63765,8 @@
       <c r="AB117" s="2"/>
       <c r="AC117" s="2"/>
       <c r="AD117" s="2"/>
-      <c r="AE117" s="2"/>
-    </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -63939,9 +63797,8 @@
       <c r="AB118" s="2"/>
       <c r="AC118" s="2"/>
       <c r="AD118" s="2"/>
-      <c r="AE118" s="2"/>
-    </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -63972,9 +63829,8 @@
       <c r="AB119" s="2"/>
       <c r="AC119" s="2"/>
       <c r="AD119" s="2"/>
-      <c r="AE119" s="2"/>
-    </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -64005,9 +63861,8 @@
       <c r="AB120" s="2"/>
       <c r="AC120" s="2"/>
       <c r="AD120" s="2"/>
-      <c r="AE120" s="2"/>
-    </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -64038,9 +63893,8 @@
       <c r="AB121" s="2"/>
       <c r="AC121" s="2"/>
       <c r="AD121" s="2"/>
-      <c r="AE121" s="2"/>
-    </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -64071,9 +63925,8 @@
       <c r="AB122" s="2"/>
       <c r="AC122" s="2"/>
       <c r="AD122" s="2"/>
-      <c r="AE122" s="2"/>
-    </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -64104,9 +63957,8 @@
       <c r="AB123" s="2"/>
       <c r="AC123" s="2"/>
       <c r="AD123" s="2"/>
-      <c r="AE123" s="2"/>
-    </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -64137,9 +63989,8 @@
       <c r="AB124" s="2"/>
       <c r="AC124" s="2"/>
       <c r="AD124" s="2"/>
-      <c r="AE124" s="2"/>
-    </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -64170,9 +64021,8 @@
       <c r="AB125" s="2"/>
       <c r="AC125" s="2"/>
       <c r="AD125" s="2"/>
-      <c r="AE125" s="2"/>
-    </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -64203,9 +64053,8 @@
       <c r="AB126" s="2"/>
       <c r="AC126" s="2"/>
       <c r="AD126" s="2"/>
-      <c r="AE126" s="2"/>
-    </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -64236,9 +64085,8 @@
       <c r="AB127" s="2"/>
       <c r="AC127" s="2"/>
       <c r="AD127" s="2"/>
-      <c r="AE127" s="2"/>
-    </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -64269,9 +64117,8 @@
       <c r="AB128" s="2"/>
       <c r="AC128" s="2"/>
       <c r="AD128" s="2"/>
-      <c r="AE128" s="2"/>
-    </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -64302,9 +64149,8 @@
       <c r="AB129" s="2"/>
       <c r="AC129" s="2"/>
       <c r="AD129" s="2"/>
-      <c r="AE129" s="2"/>
-    </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -64335,9 +64181,8 @@
       <c r="AB130" s="2"/>
       <c r="AC130" s="2"/>
       <c r="AD130" s="2"/>
-      <c r="AE130" s="2"/>
-    </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -64368,9 +64213,8 @@
       <c r="AB131" s="2"/>
       <c r="AC131" s="2"/>
       <c r="AD131" s="2"/>
-      <c r="AE131" s="2"/>
-    </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -64401,9 +64245,8 @@
       <c r="AB132" s="2"/>
       <c r="AC132" s="2"/>
       <c r="AD132" s="2"/>
-      <c r="AE132" s="2"/>
-    </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -64434,9 +64277,8 @@
       <c r="AB133" s="2"/>
       <c r="AC133" s="2"/>
       <c r="AD133" s="2"/>
-      <c r="AE133" s="2"/>
-    </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -64467,9 +64309,8 @@
       <c r="AB134" s="2"/>
       <c r="AC134" s="2"/>
       <c r="AD134" s="2"/>
-      <c r="AE134" s="2"/>
-    </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -64500,9 +64341,8 @@
       <c r="AB135" s="2"/>
       <c r="AC135" s="2"/>
       <c r="AD135" s="2"/>
-      <c r="AE135" s="2"/>
-    </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -64533,9 +64373,8 @@
       <c r="AB136" s="2"/>
       <c r="AC136" s="2"/>
       <c r="AD136" s="2"/>
-      <c r="AE136" s="2"/>
-    </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -64566,9 +64405,8 @@
       <c r="AB137" s="2"/>
       <c r="AC137" s="2"/>
       <c r="AD137" s="2"/>
-      <c r="AE137" s="2"/>
-    </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -64599,9 +64437,8 @@
       <c r="AB138" s="2"/>
       <c r="AC138" s="2"/>
       <c r="AD138" s="2"/>
-      <c r="AE138" s="2"/>
-    </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -64632,9 +64469,8 @@
       <c r="AB139" s="2"/>
       <c r="AC139" s="2"/>
       <c r="AD139" s="2"/>
-      <c r="AE139" s="2"/>
-    </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -64665,9 +64501,8 @@
       <c r="AB140" s="2"/>
       <c r="AC140" s="2"/>
       <c r="AD140" s="2"/>
-      <c r="AE140" s="2"/>
-    </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -64698,9 +64533,8 @@
       <c r="AB141" s="2"/>
       <c r="AC141" s="2"/>
       <c r="AD141" s="2"/>
-      <c r="AE141" s="2"/>
-    </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -64731,9 +64565,8 @@
       <c r="AB142" s="2"/>
       <c r="AC142" s="2"/>
       <c r="AD142" s="2"/>
-      <c r="AE142" s="2"/>
-    </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -64764,9 +64597,8 @@
       <c r="AB143" s="2"/>
       <c r="AC143" s="2"/>
       <c r="AD143" s="2"/>
-      <c r="AE143" s="2"/>
-    </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -64797,9 +64629,8 @@
       <c r="AB144" s="2"/>
       <c r="AC144" s="2"/>
       <c r="AD144" s="2"/>
-      <c r="AE144" s="2"/>
-    </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -64830,9 +64661,8 @@
       <c r="AB145" s="2"/>
       <c r="AC145" s="2"/>
       <c r="AD145" s="2"/>
-      <c r="AE145" s="2"/>
-    </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -64863,9 +64693,8 @@
       <c r="AB146" s="2"/>
       <c r="AC146" s="2"/>
       <c r="AD146" s="2"/>
-      <c r="AE146" s="2"/>
-    </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -64896,9 +64725,8 @@
       <c r="AB147" s="2"/>
       <c r="AC147" s="2"/>
       <c r="AD147" s="2"/>
-      <c r="AE147" s="2"/>
-    </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -64929,9 +64757,8 @@
       <c r="AB148" s="2"/>
       <c r="AC148" s="2"/>
       <c r="AD148" s="2"/>
-      <c r="AE148" s="2"/>
-    </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -64962,9 +64789,8 @@
       <c r="AB149" s="2"/>
       <c r="AC149" s="2"/>
       <c r="AD149" s="2"/>
-      <c r="AE149" s="2"/>
-    </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -64995,9 +64821,8 @@
       <c r="AB150" s="2"/>
       <c r="AC150" s="2"/>
       <c r="AD150" s="2"/>
-      <c r="AE150" s="2"/>
-    </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -65028,9 +64853,8 @@
       <c r="AB151" s="2"/>
       <c r="AC151" s="2"/>
       <c r="AD151" s="2"/>
-      <c r="AE151" s="2"/>
-    </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -65061,9 +64885,8 @@
       <c r="AB152" s="2"/>
       <c r="AC152" s="2"/>
       <c r="AD152" s="2"/>
-      <c r="AE152" s="2"/>
-    </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -65094,9 +64917,8 @@
       <c r="AB153" s="2"/>
       <c r="AC153" s="2"/>
       <c r="AD153" s="2"/>
-      <c r="AE153" s="2"/>
-    </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -65127,9 +64949,8 @@
       <c r="AB154" s="2"/>
       <c r="AC154" s="2"/>
       <c r="AD154" s="2"/>
-      <c r="AE154" s="2"/>
-    </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -65160,9 +64981,8 @@
       <c r="AB155" s="2"/>
       <c r="AC155" s="2"/>
       <c r="AD155" s="2"/>
-      <c r="AE155" s="2"/>
-    </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -65193,9 +65013,8 @@
       <c r="AB156" s="2"/>
       <c r="AC156" s="2"/>
       <c r="AD156" s="2"/>
-      <c r="AE156" s="2"/>
-    </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -65226,9 +65045,8 @@
       <c r="AB157" s="2"/>
       <c r="AC157" s="2"/>
       <c r="AD157" s="2"/>
-      <c r="AE157" s="2"/>
-    </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -65259,9 +65077,8 @@
       <c r="AB158" s="2"/>
       <c r="AC158" s="2"/>
       <c r="AD158" s="2"/>
-      <c r="AE158" s="2"/>
-    </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -65292,9 +65109,8 @@
       <c r="AB159" s="2"/>
       <c r="AC159" s="2"/>
       <c r="AD159" s="2"/>
-      <c r="AE159" s="2"/>
-    </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -65325,9 +65141,8 @@
       <c r="AB160" s="2"/>
       <c r="AC160" s="2"/>
       <c r="AD160" s="2"/>
-      <c r="AE160" s="2"/>
-    </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -65358,9 +65173,8 @@
       <c r="AB161" s="2"/>
       <c r="AC161" s="2"/>
       <c r="AD161" s="2"/>
-      <c r="AE161" s="2"/>
-    </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -65391,9 +65205,8 @@
       <c r="AB162" s="2"/>
       <c r="AC162" s="2"/>
       <c r="AD162" s="2"/>
-      <c r="AE162" s="2"/>
-    </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -65424,9 +65237,8 @@
       <c r="AB163" s="2"/>
       <c r="AC163" s="2"/>
       <c r="AD163" s="2"/>
-      <c r="AE163" s="2"/>
-    </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -65457,9 +65269,8 @@
       <c r="AB164" s="2"/>
       <c r="AC164" s="2"/>
       <c r="AD164" s="2"/>
-      <c r="AE164" s="2"/>
-    </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -65490,9 +65301,8 @@
       <c r="AB165" s="2"/>
       <c r="AC165" s="2"/>
       <c r="AD165" s="2"/>
-      <c r="AE165" s="2"/>
-    </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -65523,9 +65333,8 @@
       <c r="AB166" s="2"/>
       <c r="AC166" s="2"/>
       <c r="AD166" s="2"/>
-      <c r="AE166" s="2"/>
-    </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -65556,9 +65365,8 @@
       <c r="AB167" s="2"/>
       <c r="AC167" s="2"/>
       <c r="AD167" s="2"/>
-      <c r="AE167" s="2"/>
-    </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -65589,9 +65397,8 @@
       <c r="AB168" s="2"/>
       <c r="AC168" s="2"/>
       <c r="AD168" s="2"/>
-      <c r="AE168" s="2"/>
-    </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -65622,9 +65429,8 @@
       <c r="AB169" s="2"/>
       <c r="AC169" s="2"/>
       <c r="AD169" s="2"/>
-      <c r="AE169" s="2"/>
-    </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -65655,9 +65461,8 @@
       <c r="AB170" s="2"/>
       <c r="AC170" s="2"/>
       <c r="AD170" s="2"/>
-      <c r="AE170" s="2"/>
-    </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -65688,9 +65493,8 @@
       <c r="AB171" s="2"/>
       <c r="AC171" s="2"/>
       <c r="AD171" s="2"/>
-      <c r="AE171" s="2"/>
-    </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -65721,9 +65525,8 @@
       <c r="AB172" s="2"/>
       <c r="AC172" s="2"/>
       <c r="AD172" s="2"/>
-      <c r="AE172" s="2"/>
-    </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -65754,9 +65557,8 @@
       <c r="AB173" s="2"/>
       <c r="AC173" s="2"/>
       <c r="AD173" s="2"/>
-      <c r="AE173" s="2"/>
-    </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -65787,9 +65589,8 @@
       <c r="AB174" s="2"/>
       <c r="AC174" s="2"/>
       <c r="AD174" s="2"/>
-      <c r="AE174" s="2"/>
-    </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -65820,9 +65621,8 @@
       <c r="AB175" s="2"/>
       <c r="AC175" s="2"/>
       <c r="AD175" s="2"/>
-      <c r="AE175" s="2"/>
-    </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -65853,9 +65653,8 @@
       <c r="AB176" s="2"/>
       <c r="AC176" s="2"/>
       <c r="AD176" s="2"/>
-      <c r="AE176" s="2"/>
-    </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -65886,9 +65685,8 @@
       <c r="AB177" s="2"/>
       <c r="AC177" s="2"/>
       <c r="AD177" s="2"/>
-      <c r="AE177" s="2"/>
-    </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -65919,9 +65717,8 @@
       <c r="AB178" s="2"/>
       <c r="AC178" s="2"/>
       <c r="AD178" s="2"/>
-      <c r="AE178" s="2"/>
-    </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -65952,9 +65749,8 @@
       <c r="AB179" s="2"/>
       <c r="AC179" s="2"/>
       <c r="AD179" s="2"/>
-      <c r="AE179" s="2"/>
-    </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -65985,9 +65781,8 @@
       <c r="AB180" s="2"/>
       <c r="AC180" s="2"/>
       <c r="AD180" s="2"/>
-      <c r="AE180" s="2"/>
-    </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -66018,9 +65813,8 @@
       <c r="AB181" s="2"/>
       <c r="AC181" s="2"/>
       <c r="AD181" s="2"/>
-      <c r="AE181" s="2"/>
-    </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -66051,9 +65845,8 @@
       <c r="AB182" s="2"/>
       <c r="AC182" s="2"/>
       <c r="AD182" s="2"/>
-      <c r="AE182" s="2"/>
-    </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -66084,9 +65877,8 @@
       <c r="AB183" s="2"/>
       <c r="AC183" s="2"/>
       <c r="AD183" s="2"/>
-      <c r="AE183" s="2"/>
-    </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -66117,9 +65909,8 @@
       <c r="AB184" s="2"/>
       <c r="AC184" s="2"/>
       <c r="AD184" s="2"/>
-      <c r="AE184" s="2"/>
-    </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -66150,9 +65941,8 @@
       <c r="AB185" s="2"/>
       <c r="AC185" s="2"/>
       <c r="AD185" s="2"/>
-      <c r="AE185" s="2"/>
-    </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -66183,9 +65973,8 @@
       <c r="AB186" s="2"/>
       <c r="AC186" s="2"/>
       <c r="AD186" s="2"/>
-      <c r="AE186" s="2"/>
-    </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -66216,9 +66005,8 @@
       <c r="AB187" s="2"/>
       <c r="AC187" s="2"/>
       <c r="AD187" s="2"/>
-      <c r="AE187" s="2"/>
-    </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -66249,9 +66037,8 @@
       <c r="AB188" s="2"/>
       <c r="AC188" s="2"/>
       <c r="AD188" s="2"/>
-      <c r="AE188" s="2"/>
-    </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -66282,9 +66069,8 @@
       <c r="AB189" s="2"/>
       <c r="AC189" s="2"/>
       <c r="AD189" s="2"/>
-      <c r="AE189" s="2"/>
-    </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -66315,9 +66101,8 @@
       <c r="AB190" s="2"/>
       <c r="AC190" s="2"/>
       <c r="AD190" s="2"/>
-      <c r="AE190" s="2"/>
-    </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -66348,9 +66133,8 @@
       <c r="AB191" s="2"/>
       <c r="AC191" s="2"/>
       <c r="AD191" s="2"/>
-      <c r="AE191" s="2"/>
-    </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -66381,9 +66165,8 @@
       <c r="AB192" s="2"/>
       <c r="AC192" s="2"/>
       <c r="AD192" s="2"/>
-      <c r="AE192" s="2"/>
-    </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -66414,9 +66197,8 @@
       <c r="AB193" s="2"/>
       <c r="AC193" s="2"/>
       <c r="AD193" s="2"/>
-      <c r="AE193" s="2"/>
-    </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -66447,9 +66229,8 @@
       <c r="AB194" s="2"/>
       <c r="AC194" s="2"/>
       <c r="AD194" s="2"/>
-      <c r="AE194" s="2"/>
-    </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -66480,9 +66261,8 @@
       <c r="AB195" s="2"/>
       <c r="AC195" s="2"/>
       <c r="AD195" s="2"/>
-      <c r="AE195" s="2"/>
-    </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -66513,9 +66293,8 @@
       <c r="AB196" s="2"/>
       <c r="AC196" s="2"/>
       <c r="AD196" s="2"/>
-      <c r="AE196" s="2"/>
-    </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -66546,9 +66325,8 @@
       <c r="AB197" s="2"/>
       <c r="AC197" s="2"/>
       <c r="AD197" s="2"/>
-      <c r="AE197" s="2"/>
-    </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -66579,9 +66357,8 @@
       <c r="AB198" s="2"/>
       <c r="AC198" s="2"/>
       <c r="AD198" s="2"/>
-      <c r="AE198" s="2"/>
-    </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -66612,9 +66389,8 @@
       <c r="AB199" s="2"/>
       <c r="AC199" s="2"/>
       <c r="AD199" s="2"/>
-      <c r="AE199" s="2"/>
-    </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -66645,9 +66421,8 @@
       <c r="AB200" s="2"/>
       <c r="AC200" s="2"/>
       <c r="AD200" s="2"/>
-      <c r="AE200" s="2"/>
-    </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -66678,9 +66453,8 @@
       <c r="AB201" s="2"/>
       <c r="AC201" s="2"/>
       <c r="AD201" s="2"/>
-      <c r="AE201" s="2"/>
-    </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -66711,9 +66485,8 @@
       <c r="AB202" s="2"/>
       <c r="AC202" s="2"/>
       <c r="AD202" s="2"/>
-      <c r="AE202" s="2"/>
-    </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -66744,9 +66517,8 @@
       <c r="AB203" s="2"/>
       <c r="AC203" s="2"/>
       <c r="AD203" s="2"/>
-      <c r="AE203" s="2"/>
-    </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -66777,15 +66549,14 @@
       <c r="AB204" s="2"/>
       <c r="AC204" s="2"/>
       <c r="AD204" s="2"/>
-      <c r="AE204" s="2"/>
-    </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/ZqmwluKBbPQ7rPO4bmBi5UFYgKml1LJiwluKeUOtSTft292ATg40pfSxiPFYf8xvzhTf3E8RNme/7bc6tamdg==" saltValue="F1hbaB/uaVyj31IJBgSu1Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="21">
+  <sheetProtection algorithmName="SHA-512" hashValue="zQSoqCh6NklK+XOlfBHn5L/gkA8bUhEBpKNPR/UWtjP7LqyKJ82YTrw2gHO9hiqZ9v7JIRNMdfA8g75dUAbLKw==" saltValue="Ukda4p/GuI/wk/l5mCii6g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="20">
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:B5"/>
@@ -66795,7 +66566,6 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="AE2:AE4"/>
     <mergeCell ref="P2:P4"/>
     <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="R2:R4"/>

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245EE23D-1A7D-44F3-9CA1-EF893FD22309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69718F07-E18E-47F4-97CE-F6ADAE11F97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28755" yWindow="315" windowWidth="27705" windowHeight="15090" tabRatio="879" firstSheet="11" activeTab="18" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" firstSheet="5" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1449,6 +1449,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1542,6 +1548,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1589,22 +1612,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1631,9 +1640,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1695,12 +1701,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2039,24 +2039,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="68"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="12"/>
@@ -2106,15 +2106,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="18"/>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="72"/>
       <c r="E8" s="19"/>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="70"/>
+      <c r="G8" s="72"/>
       <c r="H8" s="20"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2296,11 +2296,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
       <c r="H26" s="20"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2363,10 +2363,10 @@
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="64" t="s">
         <v>110</v>
       </c>
       <c r="C2" s="56" t="s">
@@ -3835,54 +3835,54 @@
       <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="120" t="s">
+      <c r="C2" s="114" t="s">
         <v>251</v>
       </c>
-      <c r="D2" s="120" t="s">
+      <c r="D2" s="114" t="s">
         <v>252</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="120" t="s">
+      <c r="F2" s="114" t="s">
         <v>253</v>
       </c>
-      <c r="G2" s="120" t="s">
+      <c r="G2" s="114" t="s">
         <v>250</v>
       </c>
-      <c r="H2" s="120" t="s">
+      <c r="H2" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="120" t="s">
+      <c r="I2" s="114" t="s">
         <v>111</v>
       </c>
-      <c r="J2" s="88" t="s">
+      <c r="J2" s="90" t="s">
         <v>244</v>
       </c>
-      <c r="K2" s="92"/>
-      <c r="L2" s="116" t="s">
+      <c r="K2" s="94"/>
+      <c r="L2" s="119" t="s">
         <v>245</v>
       </c>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="117"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="120"/>
     </row>
     <row r="3" spans="1:15" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
       <c r="J3" s="42" t="s">
         <v>47</v>
       </c>
@@ -7304,17 +7304,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ZHZ61xEMWo2GozKFDfIGwtbJZnm3eVYJpvIE2b76e/O5EaOFEu4qUPnEZ+3+QLMo4fMOZjuAZJWBGppNj6h0fg==" saltValue="p7UsgbvwfBAQ3S2mqNofIA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 M3 N3 O3" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7356,21 +7356,21 @@
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="119" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="117"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="120"/>
     </row>
     <row r="3" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="56" t="s">
         <v>23</v>
       </c>
@@ -8822,22 +8822,22 @@
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="117"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="120"/>
     </row>
     <row r="3" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="56" t="s">
         <v>197</v>
       </c>
@@ -10517,89 +10517,89 @@
       <c r="Q1" s="6"/>
     </row>
     <row r="2" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="119" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="116" t="s">
+      <c r="D2" s="125"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="119" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="123"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="99" t="s">
+      <c r="G2" s="125"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="98" t="s">
+      <c r="J2" s="105" t="s">
         <v>214</v>
       </c>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="86" t="s">
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="86" t="s">
+      <c r="O2" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="P2" s="86" t="s">
+      <c r="P2" s="88" t="s">
         <v>220</v>
       </c>
-      <c r="Q2" s="133" t="s">
+      <c r="Q2" s="135" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="120" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="114" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="120" t="s">
+      <c r="E3" s="120"/>
+      <c r="F3" s="114" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="116" t="s">
+      <c r="G3" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="H3" s="117"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="133"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="135"/>
     </row>
     <row r="4" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
       <c r="D4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="75"/>
+      <c r="F4" s="77"/>
       <c r="G4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="99"/>
+      <c r="I4" s="106"/>
       <c r="J4" s="50" t="s">
         <v>213</v>
       </c>
@@ -10612,10 +10612,10 @@
       <c r="M4" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="133"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="135"/>
     </row>
     <row r="5" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -14420,6 +14420,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="6+yDI0OgPd4WYm3G6Z5geZ6OVSItsmzuI6pvXBhnqIBLkRwqZYhw/9myNYQcHogXrON+p0Vn9Al4arNGxWcvhQ==" saltValue="yoKDrVsoZTsh8FbYtsclwg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C3:C4"/>
@@ -14433,7 +14434,6 @@
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:M3"/>
     <mergeCell ref="N2:N4"/>
-    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 Q2:Q4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14475,20 +14475,20 @@
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="92"/>
+      <c r="D2" s="94"/>
     </row>
     <row r="3" spans="1:4" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="42" t="s">
         <v>164</v>
       </c>
@@ -15743,60 +15743,60 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="120" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="120" t="s">
+      <c r="C2" s="114" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="133" t="s">
+      <c r="D2" s="135" t="s">
         <v>140</v>
       </c>
-      <c r="E2" s="134" t="s">
+      <c r="E2" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="133" t="s">
+      <c r="F2" s="137"/>
+      <c r="G2" s="135" t="s">
         <v>203</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="88" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="112" t="s">
+      <c r="I2" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="85"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="87"/>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="133"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="135"/>
       <c r="E4" s="56" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="133"/>
-      <c r="H4" s="86"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="88"/>
       <c r="I4" s="50" t="s">
         <v>205</v>
       </c>
@@ -18502,65 +18502,65 @@
       <c r="Y1" s="6"/>
     </row>
     <row r="2" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="138" t="s">
+      <c r="B2" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="138" t="s">
+      <c r="C2" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="138" t="s">
+      <c r="D2" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="E2" s="96" t="s">
         <v>202</v>
       </c>
-      <c r="F2" s="107" t="s">
+      <c r="F2" s="96" t="s">
         <v>203</v>
       </c>
-      <c r="G2" s="86" t="s">
+      <c r="G2" s="88" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="98" t="s">
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98" t="s">
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="104" t="s">
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="S2" s="88" t="s">
+      <c r="S2" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="92"/>
-      <c r="U2" s="88" t="s">
+      <c r="T2" s="94"/>
+      <c r="U2" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="V2" s="89"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="98" t="s">
+      <c r="V2" s="91"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="105" t="s">
         <v>210</v>
       </c>
-      <c r="Y2" s="98"/>
+      <c r="Y2" s="105"/>
     </row>
     <row r="3" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
       <c r="G3" s="56" t="s">
         <v>23</v>
       </c>
@@ -18594,7 +18594,7 @@
       <c r="Q3" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="R3" s="106"/>
+      <c r="R3" s="113"/>
       <c r="S3" s="43" t="s">
         <v>102</v>
       </c>
@@ -24109,70 +24109,70 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="138" t="s">
+      <c r="B2" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="138" t="s">
+      <c r="C2" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="138" t="s">
+      <c r="D2" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="E2" s="96" t="s">
         <v>193</v>
       </c>
-      <c r="F2" s="107" t="s">
+      <c r="F2" s="96" t="s">
         <v>194</v>
       </c>
-      <c r="G2" s="107" t="s">
+      <c r="G2" s="96" t="s">
         <v>195</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="85"/>
-      <c r="K2" s="81" t="s">
+      <c r="J2" s="87"/>
+      <c r="K2" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="83"/>
-      <c r="M2" s="105" t="s">
+      <c r="L2" s="85"/>
+      <c r="M2" s="112" t="s">
         <v>201</v>
       </c>
-      <c r="N2" s="140" t="s">
+      <c r="N2" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="140" t="s">
+      <c r="O2" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="105" t="s">
+      <c r="P2" s="112" t="s">
         <v>200</v>
       </c>
-      <c r="Q2" s="140" t="s">
+      <c r="Q2" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="R2" s="140" t="s">
+      <c r="R2" s="142" t="s">
         <v>71</v>
       </c>
-      <c r="S2" s="87" t="s">
+      <c r="S2" s="89" t="s">
         <v>210</v>
       </c>
-      <c r="T2" s="87"/>
+      <c r="T2" s="89"/>
     </row>
     <row r="3" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="106"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="113"/>
       <c r="I3" s="50" t="s">
         <v>197</v>
       </c>
@@ -24185,12 +24185,12 @@
       <c r="L3" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="106"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="113"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
       <c r="S3" s="50" t="s">
         <v>199</v>
       </c>
@@ -28601,16 +28601,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="owrGYnA0RoV/U9MjDeglShzyfAHibWrOJ91U+dfsJvx7FpXhtP7KXYqD/XawmrJ8WUgOAZj9nC2wQr9dD2KQZw==" saltValue="h+hFQsEVq78bir+WDv8nRA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="H2:H3"/>
@@ -28618,6 +28608,16 @@
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 H2:H3 P2:P3 S3 J3 E2:E3 G2:G3 I3 M2:M3 T3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -28675,16 +28675,16 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="142" t="s">
+      <c r="C2" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="142" t="s">
+      <c r="D2" s="65" t="s">
         <v>113</v>
       </c>
       <c r="E2" s="42" t="s">
@@ -31386,117 +31386,117 @@
       <c r="X1" s="63"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="87" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="78" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="80"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="82"/>
       <c r="Y2" s="53"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="88" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="88" t="s">
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="83"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="85"/>
       <c r="Y3" s="53"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="74"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="84" t="s">
+      <c r="A4" s="76"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="85"/>
-      <c r="F4" s="84" t="s">
+      <c r="E4" s="87"/>
+      <c r="F4" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="85"/>
-      <c r="H4" s="93" t="s">
+      <c r="G4" s="87"/>
+      <c r="H4" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="I4" s="84" t="s">
+      <c r="I4" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="85"/>
-      <c r="K4" s="84" t="s">
+      <c r="J4" s="87"/>
+      <c r="K4" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="85"/>
-      <c r="M4" s="90" t="s">
+      <c r="L4" s="87"/>
+      <c r="M4" s="92" t="s">
         <v>98</v>
       </c>
-      <c r="N4" s="76" t="s">
+      <c r="N4" s="78" t="s">
         <v>257</v>
       </c>
-      <c r="O4" s="76"/>
-      <c r="P4" s="77" t="s">
+      <c r="O4" s="78"/>
+      <c r="P4" s="79" t="s">
         <v>255</v>
       </c>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77" t="s">
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79" t="s">
         <v>256</v>
       </c>
-      <c r="V4" s="77"/>
-      <c r="W4" s="77"/>
-      <c r="X4" s="77"/>
+      <c r="V4" s="79"/>
+      <c r="W4" s="79"/>
+      <c r="X4" s="79"/>
     </row>
     <row r="5" spans="1:25" s="54" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75"/>
+      <c r="A5" s="77"/>
       <c r="B5" s="39" t="s">
         <v>127</v>
       </c>
@@ -31515,7 +31515,7 @@
       <c r="G5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="87"/>
+      <c r="H5" s="89"/>
       <c r="I5" s="50" t="s">
         <v>134</v>
       </c>
@@ -31528,7 +31528,7 @@
       <c r="L5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="91"/>
+      <c r="M5" s="93"/>
       <c r="N5" s="39" t="s">
         <v>5</v>
       </c>
@@ -36823,109 +36823,109 @@
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="102" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="97"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="104"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="95" t="s">
+      <c r="A3" s="88"/>
+      <c r="B3" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="109" t="s">
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="104" t="s">
+      <c r="H3" s="99"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="111" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="L3" s="95" t="s">
+      <c r="L3" s="102" t="s">
         <v>128</v>
       </c>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="97"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="104"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86" t="s">
+      <c r="A4" s="88"/>
+      <c r="B4" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="102" t="s">
+      <c r="C4" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="D4" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="93" t="s">
+      <c r="E4" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="98" t="s">
+      <c r="F4" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="99" t="s">
+      <c r="G4" s="106" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="100" t="s">
+      <c r="H4" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="94" t="s">
+      <c r="I4" s="101" t="s">
         <v>177</v>
       </c>
-      <c r="J4" s="105"/>
-      <c r="K4" s="107" t="s">
+      <c r="J4" s="112"/>
+      <c r="K4" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="76" t="s">
+      <c r="L4" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76" t="s">
+      <c r="M4" s="78"/>
+      <c r="N4" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="76"/>
-      <c r="P4" s="98" t="s">
+      <c r="O4" s="78"/>
+      <c r="P4" s="105" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="108"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="97"/>
       <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
@@ -36938,7 +36938,7 @@
       <c r="O5" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="P5" s="98"/>
+      <c r="P5" s="105"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -40543,6 +40543,8 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9TADddINtH3/s8+B+YSEyrbqN3sXm6gNvmsaihCGVKf7Pla3vF7K/W63Z2DPtXhM7gpZzMQTmkRfISjjfsW2DA==" saltValue="PE4zbTBOxopTV3TBfcOFrw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="I4:I5"/>
@@ -40559,8 +40561,6 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="B2:P2"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 J6 K4:K5 G4:I5 O5" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40618,47 +40618,47 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="105" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98" t="s">
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105" t="s">
         <v>234</v>
       </c>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="93" t="s">
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="88" t="s">
+      <c r="G3" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="93" t="s">
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="95" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
+      <c r="A4" s="77"/>
       <c r="B4" s="50" t="s">
         <v>134</v>
       </c>
@@ -40671,7 +40671,7 @@
       <c r="E4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="87"/>
+      <c r="F4" s="89"/>
       <c r="G4" s="50" t="s">
         <v>134</v>
       </c>
@@ -40684,7 +40684,7 @@
       <c r="J4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="87"/>
+      <c r="K4" s="89"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -43289,13 +43289,13 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="u8pXLSYhOVbviCjMnAbnq7QuW/5rhXgGJG1eFeVlUlduAeybGPslcLzuVz4XyLFP1j/6v1ftio6sP6s2dukYSA==" saltValue="CawdL5I7cgplaq9Fy5TfQw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="7">
+    <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="G3:J3"/>
-    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C4 G4:H4" xr:uid="{E97A6FE4-6BFF-4959-9F92-FB6DF23A11A6}">
@@ -43405,199 +43405,199 @@
       <c r="AO1" s="5"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="105" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="112" t="s">
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
+      <c r="U2" s="115" t="s">
         <v>235</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
-      <c r="AE2" s="113"/>
-      <c r="AF2" s="113"/>
-      <c r="AG2" s="114"/>
-      <c r="AH2" s="112" t="s">
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
+      <c r="AE2" s="116"/>
+      <c r="AF2" s="116"/>
+      <c r="AG2" s="117"/>
+      <c r="AH2" s="115" t="s">
         <v>236</v>
       </c>
-      <c r="AI2" s="113"/>
-      <c r="AJ2" s="113"/>
-      <c r="AK2" s="113"/>
-      <c r="AL2" s="113"/>
-      <c r="AM2" s="113"/>
-      <c r="AN2" s="113"/>
-      <c r="AO2" s="114"/>
+      <c r="AI2" s="116"/>
+      <c r="AJ2" s="116"/>
+      <c r="AK2" s="116"/>
+      <c r="AL2" s="116"/>
+      <c r="AM2" s="116"/>
+      <c r="AN2" s="116"/>
+      <c r="AO2" s="117"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="115"/>
-      <c r="W3" s="115"/>
-      <c r="X3" s="115"/>
-      <c r="Y3" s="115"/>
-      <c r="Z3" s="115"/>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="115"/>
-      <c r="AC3" s="115"/>
-      <c r="AD3" s="115"/>
-      <c r="AE3" s="115"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="85"/>
-      <c r="AH3" s="84"/>
-      <c r="AI3" s="115"/>
-      <c r="AJ3" s="115"/>
-      <c r="AK3" s="115"/>
-      <c r="AL3" s="115"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="115"/>
-      <c r="AO3" s="85"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="105"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="105"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
+      <c r="T3" s="105"/>
+      <c r="U3" s="86"/>
+      <c r="V3" s="118"/>
+      <c r="W3" s="118"/>
+      <c r="X3" s="118"/>
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118"/>
+      <c r="AA3" s="118"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="118"/>
+      <c r="AD3" s="118"/>
+      <c r="AE3" s="118"/>
+      <c r="AF3" s="118"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="86"/>
+      <c r="AI3" s="118"/>
+      <c r="AJ3" s="118"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="87"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="93" t="s">
+      <c r="A4" s="88"/>
+      <c r="B4" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="104" t="s">
+      <c r="D4" s="111" t="s">
         <v>145</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77" t="s">
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="93" t="s">
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77" t="s">
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77" t="s">
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="T4" s="77"/>
-      <c r="U4" s="98" t="s">
+      <c r="T4" s="79"/>
+      <c r="U4" s="105" t="s">
         <v>155</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="98" t="s">
+      <c r="W4" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="X4" s="98" t="s">
+      <c r="X4" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="98" t="s">
+      <c r="Y4" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="98" t="s">
+      <c r="Z4" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="98" t="s">
+      <c r="AA4" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="AB4" s="98" t="s">
+      <c r="AB4" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="AC4" s="98" t="s">
+      <c r="AC4" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="AD4" s="98" t="s">
+      <c r="AD4" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="AE4" s="98" t="s">
+      <c r="AE4" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="98" t="s">
+      <c r="AF4" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="AG4" s="98" t="s">
+      <c r="AG4" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="AH4" s="109" t="s">
+      <c r="AH4" s="98" t="s">
         <v>237</v>
       </c>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="77" t="s">
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="79" t="s">
         <v>238</v>
       </c>
-      <c r="AK4" s="77"/>
-      <c r="AL4" s="77" t="s">
+      <c r="AK4" s="79"/>
+      <c r="AL4" s="79" t="s">
         <v>239</v>
       </c>
-      <c r="AM4" s="77"/>
-      <c r="AN4" s="77" t="s">
+      <c r="AM4" s="79"/>
+      <c r="AN4" s="79" t="s">
         <v>240</v>
       </c>
-      <c r="AO4" s="77"/>
+      <c r="AO4" s="79"/>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="106"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="113"/>
       <c r="E5" s="41" t="s">
         <v>25</v>
       </c>
@@ -43616,7 +43616,7 @@
       <c r="J5" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="K5" s="87"/>
+      <c r="K5" s="89"/>
       <c r="L5" s="38" t="s">
         <v>146</v>
       </c>
@@ -43644,19 +43644,19 @@
       <c r="T5" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="U5" s="98"/>
-      <c r="V5" s="98"/>
-      <c r="W5" s="98"/>
-      <c r="X5" s="98"/>
-      <c r="Y5" s="98"/>
-      <c r="Z5" s="98"/>
-      <c r="AA5" s="98"/>
-      <c r="AB5" s="98"/>
-      <c r="AC5" s="98"/>
-      <c r="AD5" s="98"/>
-      <c r="AE5" s="98"/>
-      <c r="AF5" s="98"/>
-      <c r="AG5" s="98"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="105"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="105"/>
+      <c r="Y5" s="105"/>
+      <c r="Z5" s="105"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
+      <c r="AC5" s="105"/>
+      <c r="AD5" s="105"/>
+      <c r="AE5" s="105"/>
+      <c r="AF5" s="105"/>
+      <c r="AG5" s="105"/>
       <c r="AH5" s="38" t="s">
         <v>156</v>
       </c>
@@ -52285,6 +52285,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NiKKXtjpQMePcsqc5jjUDaSQ7PwYr9+sjfqfZD87x0KbSUAFE8Baue/7fXFs4bMxVWpKhzgpmVEg8+jmkTDZbw==" saltValue="/cWUcVxNNlNaEWVwXWfzkw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH2:AO3"/>
     <mergeCell ref="D4:D5"/>
@@ -52301,20 +52315,6 @@
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 R5 AI5 AK5 AM5 L5 M5 N5 O5 P5 Q5 AO5 AJ5 AL5 AN5 AH5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -52366,38 +52366,38 @@
       <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="88" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="116"/>
-      <c r="B3" s="86" t="s">
+      <c r="A3" s="119"/>
+      <c r="B3" s="88" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="88" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="116"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="86"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="88"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="116"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="86"/>
+      <c r="A5" s="119"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="88"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -53647,64 +53647,64 @@
       <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="105" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="88" t="s">
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="90" t="s">
         <v>226</v>
       </c>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="92"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="93" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="95" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="99" t="s">
+      <c r="D3" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="98" t="s">
+      <c r="E3" s="105" t="s">
         <v>171</v>
       </c>
-      <c r="F3" s="114" t="s">
+      <c r="F3" s="117" t="s">
         <v>172</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="104" t="s">
+      <c r="H3" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="I3" s="104" t="s">
+      <c r="I3" s="111" t="s">
         <v>169</v>
       </c>
-      <c r="J3" s="118" t="s">
+      <c r="J3" s="121" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="119"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -56109,6 +56109,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="rbaELUtMLiFIUzK2Lo99z9d9U/+7pUd8ywEap5Et9u8xKeEcXwzK/YHzlDzNf0b31XcPQzpRtM0zLEm0RaQL/w==" saltValue="qBVdEFs3JSBOU1K55aehjA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
@@ -56116,11 +56121,6 @@
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 G3 H3 I3 J3" xr:uid="{17D462F2-8B43-4EF8-AF0E-D9F26228FDD4}">
@@ -56179,60 +56179,60 @@
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="112" t="s">
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="115" t="s">
         <v>242</v>
       </c>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="114"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="117"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="124" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="126" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="126" t="s">
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="128" t="s">
         <v>181</v>
       </c>
-      <c r="I3" s="124" t="s">
+      <c r="I3" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="J3" s="121" t="s">
+      <c r="J3" s="123" t="s">
         <v>243</v>
       </c>
-      <c r="K3" s="122"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="85"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="118"/>
+      <c r="N3" s="118"/>
+      <c r="O3" s="118"/>
+      <c r="P3" s="87"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="125"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="127"/>
       <c r="C4" s="47" t="s">
         <v>23</v>
       </c>
@@ -56248,8 +56248,8 @@
       <c r="G4" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="127"/>
-      <c r="I4" s="125"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="127"/>
       <c r="J4" s="48" t="s">
         <v>23</v>
       </c>
@@ -59906,7 +59906,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AD205"/>
+  <dimension ref="A1:AD204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
@@ -59973,128 +59973,128 @@
       <c r="AD1" s="5"/>
     </row>
     <row r="2" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="116" t="s">
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="119" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="123"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="120" t="s">
+      <c r="G2" s="125"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="114" t="s">
         <v>260</v>
       </c>
-      <c r="J2" s="120" t="s">
+      <c r="J2" s="114" t="s">
         <v>261</v>
       </c>
-      <c r="K2" s="112" t="s">
+      <c r="K2" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="112" t="s">
+      <c r="L2" s="116"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="114"/>
-      <c r="P2" s="86" t="s">
+      <c r="O2" s="117"/>
+      <c r="P2" s="88" t="s">
         <v>262</v>
       </c>
-      <c r="Q2" s="98" t="s">
+      <c r="Q2" s="105" t="s">
         <v>263</v>
       </c>
-      <c r="R2" s="86" t="s">
+      <c r="R2" s="88" t="s">
         <v>264</v>
       </c>
-      <c r="S2" s="86" t="s">
+      <c r="S2" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="T2" s="86"/>
-      <c r="U2" s="131" t="s">
+      <c r="T2" s="88"/>
+      <c r="U2" s="133" t="s">
         <v>272</v>
       </c>
-      <c r="V2" s="132"/>
-      <c r="W2" s="131" t="s">
+      <c r="V2" s="134"/>
+      <c r="W2" s="133" t="s">
         <v>273</v>
       </c>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="131" t="s">
+      <c r="X2" s="134"/>
+      <c r="Y2" s="133" t="s">
         <v>274</v>
       </c>
-      <c r="Z2" s="132"/>
-      <c r="AA2" s="86" t="s">
+      <c r="Z2" s="134"/>
+      <c r="AA2" s="88" t="s">
         <v>270</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="86"/>
-      <c r="AD2" s="86"/>
+      <c r="AB2" s="88"/>
+      <c r="AC2" s="88"/>
+      <c r="AD2" s="88"/>
     </row>
     <row r="3" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="78" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="120" t="s">
+      <c r="E3" s="120"/>
+      <c r="F3" s="114" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="116" t="s">
+      <c r="G3" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="H3" s="117"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="83"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="83"/>
-      <c r="AA3" s="86"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="86"/>
-      <c r="AD3" s="86"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="105"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="83"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="83"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="88"/>
+      <c r="AB3" s="88"/>
+      <c r="AC3" s="88"/>
+      <c r="AD3" s="88"/>
     </row>
     <row r="4" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="81"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="75"/>
+      <c r="F4" s="77"/>
       <c r="G4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
       <c r="K4" s="50" t="s">
         <v>212</v>
       </c>
@@ -60110,9 +60110,9 @@
       <c r="O4" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="86"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="88"/>
       <c r="S4" s="39" t="s">
         <v>51</v>
       </c>
@@ -60150,9 +60150,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -66521,62 +66521,30 @@
     <row r="204" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
-      <c r="M204" s="2"/>
-      <c r="N204" s="2"/>
-      <c r="O204" s="2"/>
-      <c r="P204" s="2"/>
-      <c r="Q204" s="2"/>
-      <c r="R204" s="2"/>
-      <c r="S204" s="2"/>
-      <c r="T204" s="2"/>
-      <c r="U204" s="2"/>
-      <c r="V204" s="2"/>
-      <c r="W204" s="2"/>
-      <c r="X204" s="2"/>
-      <c r="Y204" s="2"/>
-      <c r="Z204" s="2"/>
-      <c r="AA204" s="2"/>
-      <c r="AB204" s="2"/>
-      <c r="AC204" s="2"/>
-      <c r="AD204" s="2"/>
-    </row>
-    <row r="205" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zQSoqCh6NklK+XOlfBHn5L/gkA8bUhEBpKNPR/UWtjP7LqyKJ82YTrw2gHO9hiqZ9v7JIRNMdfA8g75dUAbLKw==" saltValue="Ukda4p/GuI/wk/l5mCii6g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Npdc6hR1jWNwlUd78HFJSJlOVnyVZEkwE3li2w9MaNYbr3qpWORdGSkVHRoIs6ZmqiHg7fNUc25lo9m1DLSPvg==" saltValue="CpsBwfeTpFYKyUOX8eB08w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Y2:Z3"/>
+    <mergeCell ref="AA2:AD3"/>
+    <mergeCell ref="U2:V3"/>
+    <mergeCell ref="W2:X3"/>
+    <mergeCell ref="K2:M3"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:T3"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="N2:O3"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="P2:P4"/>
-    <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="S2:T3"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="Y2:Z3"/>
-    <mergeCell ref="AA2:AD3"/>
-    <mergeCell ref="U2:V3"/>
-    <mergeCell ref="W2:X3"/>
-    <mergeCell ref="K2:M3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4 AA4:AD4" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69718F07-E18E-47F4-97CE-F6ADAE11F97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE237DD-1B0B-44E3-951A-85282E8A3179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" firstSheet="5" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="274">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -715,9 +715,6 @@
   </si>
   <si>
     <t>NUMBER_BRANCHLINE_HAULINGS_OBSERVED</t>
-  </si>
-  <si>
-    <t>NUMBER_HOOKS_RETRIEVED_DURING_OBSERVATION</t>
   </si>
   <si>
     <t>HOOKS</t>
@@ -1548,6 +1545,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1578,9 +1590,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1599,18 +1608,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2373,10 +2370,10 @@
         <v>23</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -3842,19 +3839,19 @@
         <v>110</v>
       </c>
       <c r="C2" s="114" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D2" s="114" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E2" s="95" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="114" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G2" s="114" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H2" s="114" t="s">
         <v>56</v>
@@ -3863,11 +3860,11 @@
         <v>111</v>
       </c>
       <c r="J2" s="90" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K2" s="94"/>
       <c r="L2" s="119" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M2" s="125"/>
       <c r="N2" s="125"/>
@@ -3890,16 +3887,16 @@
         <v>97</v>
       </c>
       <c r="L3" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="M3" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="M3" s="56" t="s">
+      <c r="N3" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="N3" s="56" t="s">
+      <c r="O3" s="56" t="s">
         <v>248</v>
-      </c>
-      <c r="O3" s="56" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -7304,17 +7301,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ZHZ61xEMWo2GozKFDfIGwtbJZnm3eVYJpvIE2b76e/O5EaOFEu4qUPnEZ+3+QLMo4fMOZjuAZJWBGppNj6h0fg==" saltValue="p7UsgbvwfBAQ3S2mqNofIA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="I2:I3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 M3 N3 O3" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7363,7 +7360,7 @@
         <v>110</v>
       </c>
       <c r="C2" s="119" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D2" s="125"/>
       <c r="E2" s="120"/>
@@ -8813,7 +8810,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10476,7 +10473,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Q204"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -10491,11 +10488,10 @@
     <col min="10" max="13" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="33.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="42.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="49.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>85</v>
       </c>
@@ -10513,10 +10509,9 @@
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="6"/>
+    </row>
+    <row r="2" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
@@ -10524,38 +10519,35 @@
         <v>110</v>
       </c>
       <c r="C2" s="119" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D2" s="125"/>
       <c r="E2" s="120"/>
       <c r="F2" s="119" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G2" s="125"/>
       <c r="H2" s="120"/>
-      <c r="I2" s="106" t="s">
+      <c r="I2" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="105" t="s">
+      <c r="J2" s="99" t="s">
         <v>214</v>
       </c>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
       <c r="N2" s="88" t="s">
         <v>58</v>
       </c>
       <c r="O2" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="P2" s="88" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q2" s="135" t="s">
+      <c r="P2" s="135" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
       <c r="B3" s="76"/>
       <c r="C3" s="114" t="s">
@@ -10572,17 +10564,16 @@
         <v>96</v>
       </c>
       <c r="H3" s="120"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
       <c r="N3" s="88"/>
       <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="135"/>
-    </row>
-    <row r="4" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="135"/>
+    </row>
+    <row r="4" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="77"/>
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
@@ -10599,7 +10590,7 @@
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="106"/>
+      <c r="I4" s="109"/>
       <c r="J4" s="50" t="s">
         <v>213</v>
       </c>
@@ -10614,10 +10605,9 @@
       </c>
       <c r="N4" s="88"/>
       <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="135"/>
-    </row>
-    <row r="5" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P4" s="135"/>
+    </row>
+    <row r="5" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -10634,9 +10624,8 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -10653,9 +10642,8 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -10672,9 +10660,8 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -10691,9 +10678,8 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -10710,9 +10696,8 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -10729,9 +10714,8 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10748,9 +10732,8 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -10767,9 +10750,8 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10786,9 +10768,8 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -10805,9 +10786,8 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -10824,9 +10804,8 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -10843,9 +10822,8 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -10862,9 +10840,8 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -10881,9 +10858,8 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -10900,9 +10876,8 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -10919,9 +10894,8 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10938,9 +10912,8 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -10957,9 +10930,8 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10976,9 +10948,8 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -10995,9 +10966,8 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -11014,9 +10984,8 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -11033,9 +11002,8 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -11052,9 +11020,8 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -11071,9 +11038,8 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11090,9 +11056,8 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -11109,9 +11074,8 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -11128,9 +11092,8 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -11147,9 +11110,8 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11166,9 +11128,8 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -11185,9 +11146,8 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11204,9 +11164,8 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11223,9 +11182,8 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -11242,9 +11200,8 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -11261,9 +11218,8 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -11280,9 +11236,8 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -11299,9 +11254,8 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -11318,9 +11272,8 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11337,9 +11290,8 @@
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -11356,9 +11308,8 @@
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -11375,9 +11326,8 @@
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -11394,9 +11344,8 @@
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -11413,9 +11362,8 @@
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -11432,9 +11380,8 @@
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -11451,9 +11398,8 @@
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -11470,9 +11416,8 @@
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -11489,9 +11434,8 @@
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -11508,9 +11452,8 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -11527,9 +11470,8 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -11546,9 +11488,8 @@
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -11565,9 +11506,8 @@
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
-      <c r="Q54" s="2"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -11584,9 +11524,8 @@
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -11603,9 +11542,8 @@
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
-      <c r="Q56" s="2"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -11622,9 +11560,8 @@
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -11641,9 +11578,8 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -11660,9 +11596,8 @@
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -11679,9 +11614,8 @@
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -11698,9 +11632,8 @@
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
-      <c r="Q61" s="2"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -11717,9 +11650,8 @@
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
-      <c r="Q62" s="2"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -11736,9 +11668,8 @@
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -11755,9 +11686,8 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
-      <c r="Q64" s="2"/>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -11774,9 +11704,8 @@
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -11793,9 +11722,8 @@
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -11812,9 +11740,8 @@
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -11831,9 +11758,8 @@
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -11850,9 +11776,8 @@
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -11869,9 +11794,8 @@
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -11888,9 +11812,8 @@
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -11907,9 +11830,8 @@
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -11926,9 +11848,8 @@
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -11945,9 +11866,8 @@
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -11964,9 +11884,8 @@
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -11983,9 +11902,8 @@
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -12002,9 +11920,8 @@
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -12021,9 +11938,8 @@
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -12040,9 +11956,8 @@
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -12059,9 +11974,8 @@
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -12078,9 +11992,8 @@
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
-      <c r="Q81" s="2"/>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -12097,9 +12010,8 @@
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -12116,9 +12028,8 @@
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
-      <c r="Q83" s="2"/>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -12135,9 +12046,8 @@
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
-      <c r="Q84" s="2"/>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -12154,9 +12064,8 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -12173,9 +12082,8 @@
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
-      <c r="Q86" s="2"/>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -12192,9 +12100,8 @@
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -12211,9 +12118,8 @@
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -12230,9 +12136,8 @@
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -12249,9 +12154,8 @@
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -12268,9 +12172,8 @@
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -12287,9 +12190,8 @@
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -12306,9 +12208,8 @@
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
-      <c r="Q93" s="2"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -12325,9 +12226,8 @@
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
-      <c r="Q94" s="2"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -12344,9 +12244,8 @@
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
-      <c r="Q95" s="2"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -12363,9 +12262,8 @@
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
-      <c r="Q96" s="2"/>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -12382,9 +12280,8 @@
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
-      <c r="Q97" s="2"/>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -12401,9 +12298,8 @@
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
-      <c r="Q98" s="2"/>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -12420,9 +12316,8 @@
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
-      <c r="Q99" s="2"/>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -12439,9 +12334,8 @@
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
-      <c r="Q100" s="2"/>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -12458,9 +12352,8 @@
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
-      <c r="Q101" s="2"/>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -12477,9 +12370,8 @@
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
-      <c r="Q102" s="2"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -12496,9 +12388,8 @@
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
-      <c r="Q103" s="2"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -12515,9 +12406,8 @@
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
-      <c r="Q104" s="2"/>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -12534,9 +12424,8 @@
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
-      <c r="Q105" s="2"/>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -12553,9 +12442,8 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
-      <c r="Q106" s="2"/>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -12572,9 +12460,8 @@
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
-      <c r="Q107" s="2"/>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -12591,9 +12478,8 @@
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
-      <c r="Q108" s="2"/>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -12610,9 +12496,8 @@
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
-      <c r="Q109" s="2"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -12629,9 +12514,8 @@
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
-      <c r="Q110" s="2"/>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -12648,9 +12532,8 @@
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
-      <c r="Q111" s="2"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -12667,9 +12550,8 @@
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
-      <c r="Q112" s="2"/>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -12686,9 +12568,8 @@
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
-      <c r="Q113" s="2"/>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -12705,9 +12586,8 @@
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
-      <c r="Q114" s="2"/>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -12724,9 +12604,8 @@
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
-      <c r="Q115" s="2"/>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -12743,9 +12622,8 @@
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
-      <c r="Q116" s="2"/>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -12762,9 +12640,8 @@
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
-      <c r="Q117" s="2"/>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -12781,9 +12658,8 @@
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
-      <c r="Q118" s="2"/>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -12800,9 +12676,8 @@
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
-      <c r="Q119" s="2"/>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -12819,9 +12694,8 @@
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
-      <c r="Q120" s="2"/>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -12838,9 +12712,8 @@
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
-      <c r="Q121" s="2"/>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -12857,9 +12730,8 @@
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
-      <c r="Q122" s="2"/>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -12876,9 +12748,8 @@
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
-      <c r="Q123" s="2"/>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -12895,9 +12766,8 @@
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
-      <c r="Q124" s="2"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -12914,9 +12784,8 @@
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
-      <c r="Q125" s="2"/>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -12933,9 +12802,8 @@
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
-      <c r="Q126" s="2"/>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -12952,9 +12820,8 @@
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
-      <c r="Q127" s="2"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -12971,9 +12838,8 @@
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
-      <c r="Q128" s="2"/>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -12990,9 +12856,8 @@
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
-      <c r="Q129" s="2"/>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -13009,9 +12874,8 @@
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
-      <c r="Q130" s="2"/>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -13028,9 +12892,8 @@
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
-      <c r="Q131" s="2"/>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -13047,9 +12910,8 @@
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
-      <c r="Q132" s="2"/>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -13066,9 +12928,8 @@
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
-      <c r="Q133" s="2"/>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -13085,9 +12946,8 @@
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
-      <c r="Q134" s="2"/>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -13104,9 +12964,8 @@
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
-      <c r="Q135" s="2"/>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -13123,9 +12982,8 @@
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
-      <c r="Q136" s="2"/>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -13142,9 +13000,8 @@
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
-      <c r="Q137" s="2"/>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -13161,9 +13018,8 @@
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
-      <c r="Q138" s="2"/>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -13180,9 +13036,8 @@
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
-      <c r="Q139" s="2"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -13199,9 +13054,8 @@
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
-      <c r="Q140" s="2"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -13218,9 +13072,8 @@
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
-      <c r="Q141" s="2"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -13237,9 +13090,8 @@
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
-      <c r="Q142" s="2"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -13256,9 +13108,8 @@
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
-      <c r="Q143" s="2"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -13275,9 +13126,8 @@
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
-      <c r="Q144" s="2"/>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -13294,9 +13144,8 @@
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
-      <c r="Q145" s="2"/>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -13313,9 +13162,8 @@
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
-      <c r="Q146" s="2"/>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -13332,9 +13180,8 @@
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
-      <c r="Q147" s="2"/>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -13351,9 +13198,8 @@
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
-      <c r="Q148" s="2"/>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -13370,9 +13216,8 @@
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
-      <c r="Q149" s="2"/>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -13389,9 +13234,8 @@
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
-      <c r="Q150" s="2"/>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -13408,9 +13252,8 @@
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
-      <c r="Q151" s="2"/>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -13427,9 +13270,8 @@
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
-      <c r="Q152" s="2"/>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -13446,9 +13288,8 @@
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
-      <c r="Q153" s="2"/>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -13465,9 +13306,8 @@
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
-      <c r="Q154" s="2"/>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -13484,9 +13324,8 @@
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
-      <c r="Q155" s="2"/>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -13503,9 +13342,8 @@
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
-      <c r="Q156" s="2"/>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -13522,9 +13360,8 @@
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
-      <c r="Q157" s="2"/>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -13541,9 +13378,8 @@
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
-      <c r="Q158" s="2"/>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -13560,9 +13396,8 @@
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
-      <c r="Q159" s="2"/>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -13579,9 +13414,8 @@
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
-      <c r="Q160" s="2"/>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -13598,9 +13432,8 @@
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
-      <c r="Q161" s="2"/>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -13617,9 +13450,8 @@
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
-      <c r="Q162" s="2"/>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -13636,9 +13468,8 @@
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
-      <c r="Q163" s="2"/>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -13655,9 +13486,8 @@
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
-      <c r="Q164" s="2"/>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -13674,9 +13504,8 @@
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
-      <c r="Q165" s="2"/>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -13693,9 +13522,8 @@
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
-      <c r="Q166" s="2"/>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -13712,9 +13540,8 @@
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
-      <c r="Q167" s="2"/>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -13731,9 +13558,8 @@
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
-      <c r="Q168" s="2"/>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -13750,9 +13576,8 @@
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
-      <c r="Q169" s="2"/>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -13769,9 +13594,8 @@
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
-      <c r="Q170" s="2"/>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -13788,9 +13612,8 @@
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
-      <c r="Q171" s="2"/>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -13807,9 +13630,8 @@
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
-      <c r="Q172" s="2"/>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -13826,9 +13648,8 @@
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
-      <c r="Q173" s="2"/>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -13845,9 +13666,8 @@
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
-      <c r="Q174" s="2"/>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -13864,9 +13684,8 @@
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
-      <c r="Q175" s="2"/>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -13883,9 +13702,8 @@
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
-      <c r="Q176" s="2"/>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -13902,9 +13720,8 @@
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
-      <c r="Q177" s="2"/>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -13921,9 +13738,8 @@
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
-      <c r="Q178" s="2"/>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -13940,9 +13756,8 @@
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
-      <c r="Q179" s="2"/>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -13959,9 +13774,8 @@
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
-      <c r="Q180" s="2"/>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -13978,9 +13792,8 @@
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
-      <c r="Q181" s="2"/>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -13997,9 +13810,8 @@
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
-      <c r="Q182" s="2"/>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -14016,9 +13828,8 @@
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" s="2"/>
-      <c r="Q183" s="2"/>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -14035,9 +13846,8 @@
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
-      <c r="Q184" s="2"/>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -14054,9 +13864,8 @@
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
-      <c r="Q185" s="2"/>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -14073,9 +13882,8 @@
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
-      <c r="Q186" s="2"/>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -14092,9 +13900,8 @@
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
-      <c r="Q187" s="2"/>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -14111,9 +13918,8 @@
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
-      <c r="Q188" s="2"/>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -14130,9 +13936,8 @@
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
-      <c r="Q189" s="2"/>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -14149,9 +13954,8 @@
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
-      <c r="Q190" s="2"/>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -14168,9 +13972,8 @@
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
-      <c r="Q191" s="2"/>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -14187,9 +13990,8 @@
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
-      <c r="Q192" s="2"/>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -14206,9 +14008,8 @@
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
-      <c r="Q193" s="2"/>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -14225,9 +14026,8 @@
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
-      <c r="Q194" s="2"/>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -14244,9 +14044,8 @@
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" s="2"/>
-      <c r="Q195" s="2"/>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -14263,9 +14062,8 @@
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
-      <c r="Q196" s="2"/>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -14282,9 +14080,8 @@
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
-      <c r="Q197" s="2"/>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -14301,9 +14098,8 @@
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
       <c r="P198" s="2"/>
-      <c r="Q198" s="2"/>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -14320,9 +14116,8 @@
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" s="2"/>
-      <c r="Q199" s="2"/>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -14339,9 +14134,8 @@
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" s="2"/>
-      <c r="Q200" s="2"/>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -14358,9 +14152,8 @@
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
-      <c r="Q201" s="2"/>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -14377,9 +14170,8 @@
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
-      <c r="Q202" s="2"/>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -14396,9 +14188,8 @@
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
-      <c r="Q203" s="2"/>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -14415,33 +14206,31 @@
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
-      <c r="Q204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6+yDI0OgPd4WYm3G6Z5geZ6OVSItsmzuI6pvXBhnqIBLkRwqZYhw/9myNYQcHogXrON+p0Vn9Al4arNGxWcvhQ==" saltValue="yoKDrVsoZTsh8FbYtsclwg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="14">
+  <sheetProtection algorithmName="SHA-512" hashValue="PoLs1kxIM/xJUmr7urrblsJ/5hObRoOum4QkrLl5n6UkTskAAW1rlDkj4UAOAaNPAxaZOLfva1Eeyyy3ErcvXg==" saltValue="hHLCZEhHQHH5LRknKlGm2A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="13">
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:M3"/>
+    <mergeCell ref="N2:N4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="P2:P4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:M3"/>
-    <mergeCell ref="N2:N4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 Q2:Q4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 P2:P4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q2:Q4" r:id="rId1" location="samplingProtocols" display="SAMPLING_PROTOCOL_CODE" xr:uid="{C0C4727C-9767-4664-8796-43CDF0860627}"/>
+    <hyperlink ref="P2:P4" r:id="rId1" location="samplingProtocols" display="SAMPLING_PROTOCOL_CODE" xr:uid="{C0C4727C-9767-4664-8796-43CDF0860627}"/>
     <hyperlink ref="I2:I4" r:id="rId2" location="offalManagementTypes" display="OFFAL_MANAGEMENT" xr:uid="{408DFBD1-078D-43D4-8B22-538A09E39B98}"/>
     <hyperlink ref="J4" r:id="rId3" location="vesselSections" xr:uid="{140540DF-7251-4F70-BF34-280C13EE47A9}"/>
     <hyperlink ref="K4" r:id="rId4" location="vesselSections" xr:uid="{C6B0B34F-D5B5-4396-BD53-32117C4E0387}"/>
@@ -15763,7 +15552,7 @@
         <v>203</v>
       </c>
       <c r="H2" s="88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I2" s="115" t="s">
         <v>59</v>
@@ -15804,7 +15593,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -18514,10 +18303,10 @@
       <c r="D2" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="E2" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="100" t="s">
         <v>203</v>
       </c>
       <c r="G2" s="88" t="s">
@@ -18526,18 +18315,18 @@
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
       <c r="J2" s="88"/>
-      <c r="K2" s="105" t="s">
+      <c r="K2" s="99" t="s">
         <v>208</v>
       </c>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105" t="s">
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="111" t="s">
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="96" t="s">
         <v>62</v>
       </c>
       <c r="S2" s="90" t="s">
@@ -18549,18 +18338,18 @@
       </c>
       <c r="V2" s="91"/>
       <c r="W2" s="94"/>
-      <c r="X2" s="105" t="s">
+      <c r="X2" s="99" t="s">
         <v>210</v>
       </c>
-      <c r="Y2" s="105"/>
+      <c r="Y2" s="99"/>
     </row>
     <row r="3" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="141"/>
       <c r="B3" s="141"/>
       <c r="C3" s="141"/>
       <c r="D3" s="141"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
       <c r="G3" s="56" t="s">
         <v>23</v>
       </c>
@@ -18592,9 +18381,9 @@
         <v>60</v>
       </c>
       <c r="Q3" s="50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
-      <c r="R3" s="113"/>
+      <c r="R3" s="98"/>
       <c r="S3" s="43" t="s">
         <v>102</v>
       </c>
@@ -24121,16 +23910,16 @@
       <c r="D2" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="E2" s="100" t="s">
         <v>193</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="100" t="s">
         <v>194</v>
       </c>
-      <c r="G2" s="96" t="s">
+      <c r="G2" s="100" t="s">
         <v>195</v>
       </c>
-      <c r="H2" s="112" t="s">
+      <c r="H2" s="97" t="s">
         <v>196</v>
       </c>
       <c r="I2" s="86" t="s">
@@ -24141,7 +23930,7 @@
         <v>73</v>
       </c>
       <c r="L2" s="85"/>
-      <c r="M2" s="112" t="s">
+      <c r="M2" s="97" t="s">
         <v>201</v>
       </c>
       <c r="N2" s="142" t="s">
@@ -24150,7 +23939,7 @@
       <c r="O2" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="112" t="s">
+      <c r="P2" s="97" t="s">
         <v>200</v>
       </c>
       <c r="Q2" s="142" t="s">
@@ -24169,10 +23958,10 @@
       <c r="B3" s="141"/>
       <c r="C3" s="141"/>
       <c r="D3" s="141"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="113"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="98"/>
       <c r="I3" s="50" t="s">
         <v>197</v>
       </c>
@@ -24185,10 +23974,10 @@
       <c r="L3" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="113"/>
+      <c r="M3" s="98"/>
       <c r="N3" s="89"/>
       <c r="O3" s="89"/>
-      <c r="P3" s="113"/>
+      <c r="P3" s="98"/>
       <c r="Q3" s="89"/>
       <c r="R3" s="89"/>
       <c r="S3" s="50" t="s">
@@ -28601,6 +28390,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="owrGYnA0RoV/U9MjDeglShzyfAHibWrOJ91U+dfsJvx7FpXhtP7KXYqD/XawmrJ8WUgOAZj9nC2wQr9dD2KQZw==" saltValue="h+hFQsEVq78bir+WDv8nRA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="H2:H3"/>
@@ -28608,16 +28407,6 @@
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 H2:H3 P2:P3 S3 J3 E2:E3 G2:G3 I3 M2:M3 T3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -31359,7 +31148,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="7" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -31406,7 +31195,7 @@
       <c r="L2" s="89"/>
       <c r="M2" s="89"/>
       <c r="N2" s="80" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O2" s="81"/>
       <c r="P2" s="81"/>
@@ -31478,18 +31267,18 @@
         <v>98</v>
       </c>
       <c r="N4" s="78" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O4" s="78"/>
       <c r="P4" s="79" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q4" s="79"/>
       <c r="R4" s="79"/>
       <c r="S4" s="79"/>
       <c r="T4" s="79"/>
       <c r="U4" s="79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V4" s="79"/>
       <c r="W4" s="79"/>
@@ -36826,80 +36615,80 @@
       <c r="A2" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="102" t="s">
-        <v>241</v>
+      <c r="B2" s="106" t="s">
+        <v>240</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="104"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="108"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="98" t="s">
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="99"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="111" t="s">
+      <c r="H3" s="103"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="96" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="L3" s="102" t="s">
+      <c r="L3" s="106" t="s">
         <v>128</v>
       </c>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="104"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="108"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="112" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="113" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="105" t="s">
+      <c r="F4" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="106" t="s">
+      <c r="G4" s="109" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="107" t="s">
+      <c r="H4" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="101" t="s">
+      <c r="I4" s="105" t="s">
         <v>177</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="96" t="s">
+      <c r="J4" s="97"/>
+      <c r="K4" s="100" t="s">
         <v>141</v>
       </c>
       <c r="L4" s="78" t="s">
@@ -36910,35 +36699,35 @@
         <v>19</v>
       </c>
       <c r="O4" s="78"/>
-      <c r="P4" s="105" t="s">
+      <c r="P4" s="99" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="88"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="113"/>
       <c r="E5" s="89"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="97"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="101"/>
       <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
-      <c r="P5" s="105"/>
+      <c r="P5" s="99"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -40543,11 +40332,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9TADddINtH3/s8+B+YSEyrbqN3sXm6gNvmsaihCGVKf7Pla3vF7K/W63Z2DPtXhM7gpZzMQTmkRfISjjfsW2DA==" saltValue="PE4zbTBOxopTV3TBfcOFrw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -40561,6 +40345,11 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="B2:P2"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 J6 K4:K5 G4:I5 O5" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40621,20 +40410,20 @@
       <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="99" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
@@ -43408,29 +43197,29 @@
       <c r="A2" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="99" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
       <c r="U2" s="115" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V2" s="116"/>
       <c r="W2" s="116"/>
@@ -43445,7 +43234,7 @@
       <c r="AF2" s="116"/>
       <c r="AG2" s="117"/>
       <c r="AH2" s="115" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AI2" s="116"/>
       <c r="AJ2" s="116"/>
@@ -43457,25 +43246,25 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="105"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="105"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-      <c r="T3" s="105"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
       <c r="U3" s="86"/>
       <c r="V3" s="118"/>
       <c r="W3" s="118"/>
@@ -43506,7 +43295,7 @@
       <c r="C4" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="96" t="s">
         <v>145</v>
       </c>
       <c r="E4" s="79" t="s">
@@ -43537,59 +43326,59 @@
         <v>28</v>
       </c>
       <c r="T4" s="79"/>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="99" t="s">
         <v>155</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="105" t="s">
+      <c r="W4" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="X4" s="105" t="s">
+      <c r="X4" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="105" t="s">
+      <c r="Y4" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="105" t="s">
+      <c r="Z4" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="105" t="s">
+      <c r="AA4" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="AB4" s="105" t="s">
+      <c r="AB4" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="AC4" s="105" t="s">
+      <c r="AC4" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="AD4" s="105" t="s">
+      <c r="AD4" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="AE4" s="105" t="s">
+      <c r="AE4" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="105" t="s">
+      <c r="AF4" s="99" t="s">
         <v>147</v>
       </c>
-      <c r="AG4" s="105" t="s">
+      <c r="AG4" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="AH4" s="98" t="s">
+      <c r="AH4" s="102" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI4" s="104"/>
+      <c r="AJ4" s="79" t="s">
         <v>237</v>
-      </c>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="79" t="s">
-        <v>238</v>
       </c>
       <c r="AK4" s="79"/>
       <c r="AL4" s="79" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AM4" s="79"/>
       <c r="AN4" s="79" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AO4" s="79"/>
     </row>
@@ -43597,7 +43386,7 @@
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
-      <c r="D5" s="113"/>
+      <c r="D5" s="98"/>
       <c r="E5" s="41" t="s">
         <v>25</v>
       </c>
@@ -43644,19 +43433,19 @@
       <c r="T5" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="U5" s="105"/>
-      <c r="V5" s="105"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="105"/>
-      <c r="Y5" s="105"/>
-      <c r="Z5" s="105"/>
-      <c r="AA5" s="105"/>
-      <c r="AB5" s="105"/>
-      <c r="AC5" s="105"/>
-      <c r="AD5" s="105"/>
-      <c r="AE5" s="105"/>
-      <c r="AF5" s="105"/>
-      <c r="AG5" s="105"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="99"/>
+      <c r="AD5" s="99"/>
+      <c r="AE5" s="99"/>
+      <c r="AF5" s="99"/>
+      <c r="AG5" s="99"/>
       <c r="AH5" s="38" t="s">
         <v>156</v>
       </c>
@@ -52285,20 +52074,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NiKKXtjpQMePcsqc5jjUDaSQ7PwYr9+sjfqfZD87x0KbSUAFE8Baue/7fXFs4bMxVWpKhzgpmVEg8+jmkTDZbw==" saltValue="/cWUcVxNNlNaEWVwXWfzkw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH2:AO3"/>
     <mergeCell ref="D4:D5"/>
@@ -52315,6 +52090,20 @@
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 R5 AI5 AK5 AM5 L5 M5 N5 O5 P5 Q5 AO5 AJ5 AL5 AN5 AH5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -53650,15 +53439,15 @@
       <c r="A2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="99" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="90" t="s">
         <v>225</v>
-      </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="90" t="s">
-        <v>226</v>
       </c>
       <c r="H2" s="91"/>
       <c r="I2" s="91"/>
@@ -53672,22 +53461,22 @@
       <c r="C3" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="109" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="105" t="s">
+      <c r="E3" s="99" t="s">
         <v>171</v>
       </c>
       <c r="F3" s="117" t="s">
         <v>172</v>
       </c>
-      <c r="G3" s="111" t="s">
+      <c r="G3" s="96" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="111" t="s">
+      <c r="H3" s="96" t="s">
         <v>168</v>
       </c>
-      <c r="I3" s="111" t="s">
+      <c r="I3" s="96" t="s">
         <v>169</v>
       </c>
       <c r="J3" s="121" t="s">
@@ -53698,12 +53487,12 @@
       <c r="A4" s="77"/>
       <c r="B4" s="89"/>
       <c r="C4" s="89"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="105"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="99"/>
       <c r="F4" s="87"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
       <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -56109,11 +55898,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="rbaELUtMLiFIUzK2Lo99z9d9U/+7pUd8ywEap5Et9u8xKeEcXwzK/YHzlDzNf0b31XcPQzpRtM0zLEm0RaQL/w==" saltValue="qBVdEFs3JSBOU1K55aehjA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
@@ -56121,6 +55905,11 @@
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 G3 H3 I3 J3" xr:uid="{17D462F2-8B43-4EF8-AF0E-D9F26228FDD4}">
@@ -56195,7 +55984,7 @@
       <c r="J2" s="125"/>
       <c r="K2" s="120"/>
       <c r="L2" s="115" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M2" s="116"/>
       <c r="N2" s="116"/>
@@ -56221,7 +56010,7 @@
         <v>182</v>
       </c>
       <c r="J3" s="123" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K3" s="124"/>
       <c r="L3" s="86"/>
@@ -59990,10 +59779,10 @@
       <c r="G2" s="125"/>
       <c r="H2" s="120"/>
       <c r="I2" s="114" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J2" s="114" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K2" s="115" t="s">
         <v>43</v>
@@ -60005,32 +59794,32 @@
       </c>
       <c r="O2" s="117"/>
       <c r="P2" s="88" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q2" s="99" t="s">
         <v>262</v>
       </c>
-      <c r="Q2" s="105" t="s">
+      <c r="R2" s="88" t="s">
         <v>263</v>
       </c>
-      <c r="R2" s="88" t="s">
-        <v>264</v>
-      </c>
       <c r="S2" s="88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T2" s="88"/>
       <c r="U2" s="133" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="V2" s="134"/>
       <c r="W2" s="133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="X2" s="134"/>
       <c r="Y2" s="133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z2" s="134"/>
       <c r="AA2" s="88" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AB2" s="88"/>
       <c r="AC2" s="88"/>
@@ -60061,7 +59850,7 @@
       <c r="N3" s="86"/>
       <c r="O3" s="87"/>
       <c r="P3" s="88"/>
-      <c r="Q3" s="105"/>
+      <c r="Q3" s="99"/>
       <c r="R3" s="88"/>
       <c r="S3" s="88"/>
       <c r="T3" s="88"/>
@@ -60099,10 +59888,10 @@
         <v>212</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M4" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N4" s="42" t="s">
         <v>48</v>
@@ -60111,13 +59900,13 @@
         <v>49</v>
       </c>
       <c r="P4" s="88"/>
-      <c r="Q4" s="105"/>
+      <c r="Q4" s="99"/>
       <c r="R4" s="88"/>
       <c r="S4" s="39" t="s">
         <v>51</v>
       </c>
       <c r="T4" s="42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U4" s="39" t="s">
         <v>23</v>
@@ -60138,16 +59927,16 @@
         <v>148</v>
       </c>
       <c r="AA4" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB4" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="AB4" s="50" t="s">
+      <c r="AC4" s="50" t="s">
         <v>267</v>
       </c>
-      <c r="AC4" s="50" t="s">
+      <c r="AD4" s="50" t="s">
         <v>268</v>
-      </c>
-      <c r="AD4" s="50" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -66525,6 +66314,10 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Npdc6hR1jWNwlUd78HFJSJlOVnyVZEkwE3li2w9MaNYbr3qpWORdGSkVHRoIs6ZmqiHg7fNUc25lo9m1DLSPvg==" saltValue="CpsBwfeTpFYKyUOX8eB08w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="Y2:Z3"/>
@@ -66541,10 +66334,6 @@
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4 AA4:AD4" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE237DD-1B0B-44E3-951A-85282E8A3179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F68486-8307-4B9B-8B70-28C6DC801163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="272">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>TYPE</t>
-  </si>
-  <si>
-    <t>TYPE_CODE</t>
   </si>
   <si>
     <t>MAKE</t>
@@ -253,12 +250,6 @@
   </si>
   <si>
     <t>RECOVERY</t>
-  </si>
-  <si>
-    <t>TAG_NUMBER_1</t>
-  </si>
-  <si>
-    <t>TAG_NUMBER_2</t>
   </si>
   <si>
     <t>DIAMETER_MM</t>
@@ -813,9 +804,6 @@
     <t>MINIMUM_DECK_LIGHTING_USED</t>
   </si>
   <si>
-    <t>AVERAGE_BRANCHLINE_WEIGHT_G</t>
-  </si>
-  <si>
     <t>NATIONALITY</t>
   </si>
   <si>
@@ -849,9 +837,6 @@
     <t>NUMBER_HOOKS_BETWEEN_FLOATS</t>
   </si>
   <si>
-    <t>NUMBER_LINES</t>
-  </si>
-  <si>
     <t>SPECIES_1</t>
   </si>
   <si>
@@ -877,6 +862,15 @@
   </si>
   <si>
     <t>BRANCHLINE LENGTH MAXIMUM</t>
+  </si>
+  <si>
+    <t>AVERAGE_SINKER_WEIGHT_G</t>
+  </si>
+  <si>
+    <t>TAG_ID_1</t>
+  </si>
+  <si>
+    <t>TAG_ID_2</t>
   </si>
 </sst>
 </file>
@@ -1450,7 +1444,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1545,29 +1539,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1590,6 +1561,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1608,6 +1582,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2037,7 +2031,7 @@
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="66" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C2" s="67"/>
       <c r="D2" s="67"/>
@@ -2058,14 +2052,14 @@
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="12"/>
       <c r="C4" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G4" s="16">
         <v>1</v>
@@ -2084,7 +2078,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
@@ -2104,12 +2098,12 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="18"/>
       <c r="C8" s="72" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D8" s="72"/>
       <c r="E8" s="19"/>
       <c r="F8" s="72" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G8" s="72"/>
       <c r="H8" s="20"/>
@@ -2117,12 +2111,12 @@
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="18"/>
       <c r="C9" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="19"/>
       <c r="F9" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="20"/>
@@ -2130,12 +2124,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="18"/>
       <c r="C10" s="24" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="19"/>
       <c r="F10" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="20"/>
@@ -2152,7 +2146,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="18"/>
       <c r="C12" s="24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="19"/>
@@ -2163,7 +2157,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="18"/>
       <c r="C13" s="24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="19"/>
@@ -2192,7 +2186,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="18"/>
       <c r="C16" s="21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -2212,7 +2206,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="18"/>
       <c r="C18" s="24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="19"/>
@@ -2223,7 +2217,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="18"/>
       <c r="C19" s="29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D19" s="28"/>
       <c r="E19" s="19"/>
@@ -2234,7 +2228,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="18"/>
       <c r="C20" s="36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="19"/>
@@ -2245,7 +2239,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
       <c r="C21" s="24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D21" s="28"/>
       <c r="E21" s="19"/>
@@ -2274,7 +2268,7 @@
     <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="C24" s="21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="19"/>
@@ -2352,7 +2346,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2361,19 +2355,19 @@
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -3814,7 +3808,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3833,38 +3827,38 @@
     </row>
     <row r="2" spans="1:15" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="114" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D2" s="114" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E2" s="95" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="114" t="s">
+        <v>269</v>
+      </c>
+      <c r="G2" s="114" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="114" t="s">
-        <v>252</v>
-      </c>
-      <c r="G2" s="114" t="s">
-        <v>249</v>
-      </c>
-      <c r="H2" s="114" t="s">
-        <v>56</v>
-      </c>
       <c r="I2" s="114" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J2" s="90" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="K2" s="94"/>
       <c r="L2" s="119" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="M2" s="125"/>
       <c r="N2" s="125"/>
@@ -3881,22 +3875,22 @@
       <c r="H3" s="77"/>
       <c r="I3" s="77"/>
       <c r="J3" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L3" s="56" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M3" s="56" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N3" s="56" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O3" s="56" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -7299,7 +7293,7 @@
       <c r="O203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZHZ61xEMWo2GozKFDfIGwtbJZnm3eVYJpvIE2b76e/O5EaOFEu4qUPnEZ+3+QLMo4fMOZjuAZJWBGppNj6h0fg==" saltValue="p7UsgbvwfBAQ3S2mqNofIA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="i54u068XThYDfxhseUVm7j5UOX6o6sLA/paOyFGBfnG2ueK1l9vp0KVJDHX+jDagofUZDK+i4w0EkGdmr+cm5A==" saltValue="YMFvCB9MnqWRAENMsMJcZw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -7345,7 +7339,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -7354,13 +7348,13 @@
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="119" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D2" s="125"/>
       <c r="E2" s="120"/>
@@ -7372,10 +7366,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8810,7 +8804,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8820,13 +8814,13 @@
     </row>
     <row r="2" spans="1:6" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="119" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2" s="125"/>
       <c r="E2" s="125"/>
@@ -8836,16 +8830,16 @@
       <c r="A3" s="77"/>
       <c r="B3" s="77"/>
       <c r="C3" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10493,7 +10487,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10513,62 +10507,62 @@
     </row>
     <row r="2" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="119" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D2" s="125"/>
       <c r="E2" s="120"/>
       <c r="F2" s="119" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G2" s="125"/>
       <c r="H2" s="120"/>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="104" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="103" t="s">
+        <v>211</v>
+      </c>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="99" t="s">
-        <v>214</v>
-      </c>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="88" t="s">
-        <v>58</v>
-      </c>
       <c r="O2" s="88" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P2" s="135" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
       <c r="B3" s="76"/>
       <c r="C3" s="114" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" s="119" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E3" s="120"/>
       <c r="F3" s="114" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H3" s="120"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
       <c r="N3" s="88"/>
       <c r="O3" s="88"/>
       <c r="P3" s="135"/>
@@ -10590,18 +10584,18 @@
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="109"/>
+      <c r="I4" s="104"/>
       <c r="J4" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="K4" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="L4" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="K4" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="L4" s="50" t="s">
-        <v>216</v>
-      </c>
       <c r="M4" s="50" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N4" s="88"/>
       <c r="O4" s="88"/>
@@ -14257,7 +14251,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -14265,13 +14259,13 @@
     </row>
     <row r="2" spans="1:4" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="90" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="94"/>
     </row>
@@ -14279,10 +14273,10 @@
       <c r="A3" s="77"/>
       <c r="B3" s="77"/>
       <c r="C3" s="42" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15518,7 +15512,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -15533,29 +15527,29 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D2" s="135" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E2" s="136" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F2" s="137"/>
       <c r="G2" s="135" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H2" s="88" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I2" s="115" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J2" s="116"/>
       <c r="K2" s="117"/>
@@ -15582,18 +15576,18 @@
         <v>23</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G4" s="135"/>
       <c r="H4" s="88"/>
       <c r="I4" s="50" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K4" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -18263,7 +18257,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -18292,118 +18286,118 @@
     </row>
     <row r="2" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="140" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="140" t="s">
+      <c r="C2" s="140" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="140" t="s">
-        <v>112</v>
+      <c r="E2" s="112" t="s">
+        <v>199</v>
       </c>
-      <c r="D2" s="140" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="100" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="100" t="s">
-        <v>203</v>
+      <c r="F2" s="112" t="s">
+        <v>200</v>
       </c>
       <c r="G2" s="88" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
       <c r="J2" s="88"/>
-      <c r="K2" s="99" t="s">
-        <v>208</v>
+      <c r="K2" s="103" t="s">
+        <v>205</v>
       </c>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99" t="s">
-        <v>59</v>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103" t="s">
+        <v>58</v>
       </c>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="96" t="s">
-        <v>62</v>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="109" t="s">
+        <v>61</v>
       </c>
       <c r="S2" s="90" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T2" s="94"/>
       <c r="U2" s="90" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="V2" s="91"/>
       <c r="W2" s="94"/>
-      <c r="X2" s="99" t="s">
-        <v>210</v>
+      <c r="X2" s="103" t="s">
+        <v>207</v>
       </c>
-      <c r="Y2" s="99"/>
+      <c r="Y2" s="103"/>
     </row>
     <row r="3" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="141"/>
       <c r="B3" s="141"/>
       <c r="C3" s="141"/>
       <c r="D3" s="141"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="56" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J3" s="39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K3" s="50" t="s">
         <v>23</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M3" s="50" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O3" s="50" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
-      <c r="R3" s="98"/>
+      <c r="R3" s="111"/>
       <c r="S3" s="43" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T3" s="43" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="U3" s="59" t="s">
         <v>23</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="W3" s="42" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="X3" s="50" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Y3" s="50" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -23807,7 +23801,7 @@
       <c r="Y203" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="e/mZipJ4AXPmTDIqBREzT6xE/UbCF4PciHFB1N4ngnHGkbhMYq2UP1EcRbtVoIsbMk/soeRGswyOaMGay/157g==" saltValue="feKRClgbT3qIjWu79ykSJg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="i+NWJhJ/dANY4y8V6yR0b2FD2rG8VYPEOJeWH5E9k/YJLZu+zWXk6/2fi7RZql3z8q9ENi+0H/lJGiOCaKLA2g==" saltValue="hNILL3j2lqXU8lRHPxsxbw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="13">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -23875,7 +23869,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -23899,57 +23893,57 @@
     </row>
     <row r="2" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="140" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="140" t="s">
+      <c r="C2" s="140" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="140" t="s">
-        <v>112</v>
+      <c r="E2" s="112" t="s">
+        <v>190</v>
       </c>
-      <c r="D2" s="140" t="s">
-        <v>113</v>
+      <c r="F2" s="112" t="s">
+        <v>191</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="G2" s="112" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="110" t="s">
         <v>193</v>
       </c>
-      <c r="F2" s="100" t="s">
-        <v>194</v>
-      </c>
-      <c r="G2" s="100" t="s">
-        <v>195</v>
-      </c>
-      <c r="H2" s="97" t="s">
-        <v>196</v>
-      </c>
       <c r="I2" s="86" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J2" s="87"/>
       <c r="K2" s="83" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L2" s="85"/>
-      <c r="M2" s="97" t="s">
-        <v>201</v>
+      <c r="M2" s="110" t="s">
+        <v>198</v>
       </c>
       <c r="N2" s="142" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O2" s="142" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
-      <c r="P2" s="97" t="s">
-        <v>200</v>
+      <c r="P2" s="110" t="s">
+        <v>197</v>
       </c>
       <c r="Q2" s="142" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R2" s="142" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S2" s="89" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="T2" s="89"/>
     </row>
@@ -23958,33 +23952,33 @@
       <c r="B3" s="141"/>
       <c r="C3" s="141"/>
       <c r="D3" s="141"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="98"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="111"/>
       <c r="I3" s="50" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J3" s="50" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="56" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
-      <c r="M3" s="98"/>
+      <c r="M3" s="111"/>
       <c r="N3" s="89"/>
       <c r="O3" s="89"/>
-      <c r="P3" s="98"/>
+      <c r="P3" s="111"/>
       <c r="Q3" s="89"/>
       <c r="R3" s="89"/>
       <c r="S3" s="50" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="T3" s="50" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="55" customFormat="1" x14ac:dyDescent="0.25">
@@ -28450,7 +28444,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -28465,37 +28459,37 @@
     </row>
     <row r="2" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="C2" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="65" t="s">
-        <v>112</v>
+      <c r="E2" s="42" t="s">
+        <v>63</v>
       </c>
-      <c r="D2" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="42" t="s">
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="42" t="s">
-        <v>65</v>
-      </c>
       <c r="G2" s="50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>66</v>
+        <v>270</v>
       </c>
       <c r="I2" s="42" t="s">
-        <v>67</v>
+        <v>271</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K2" s="42" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="53" customFormat="1" x14ac:dyDescent="0.25">
@@ -31099,14 +31093,14 @@
       <c r="K202" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qOApQt+f2TsOI5aABva9oFhDaMC8tY6SmLrXY5zZMla4EE44P/H2PtJCJ3eAXXCegs0uTPk+51WoRp//Mv+vlg==" saltValue="LQGXhg9x1P3A7pPeXXmcRw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PSeRJ1qUwmkn/r+zZDXNQ6Dr0J7lATaoNihkurJ9p93KMKe4NwkwW4CfN9Klss8IHE2M6laOf+tSvLGiZISszQ==" saltValue="L+SeJSUOmI8CoOgPWC3lYQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" location="tagTypes" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
+    <hyperlink ref="G2" r:id="rId1" location="tagTypes" display="TYPE_CODE" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31148,7 +31142,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="7" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -31176,14 +31170,14 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="76" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B2" s="77" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C2" s="77"/>
       <c r="D2" s="89" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E2" s="89"/>
       <c r="F2" s="89"/>
@@ -31195,7 +31189,7 @@
       <c r="L2" s="89"/>
       <c r="M2" s="89"/>
       <c r="N2" s="80" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O2" s="81"/>
       <c r="P2" s="81"/>
@@ -31214,14 +31208,14 @@
       <c r="B3" s="88"/>
       <c r="C3" s="88"/>
       <c r="D3" s="90" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E3" s="91"/>
       <c r="F3" s="91"/>
       <c r="G3" s="91"/>
       <c r="H3" s="94"/>
       <c r="I3" s="90" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J3" s="91"/>
       <c r="K3" s="91"/>
@@ -31245,40 +31239,40 @@
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>
       <c r="D4" s="86" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E4" s="87"/>
       <c r="F4" s="86" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G4" s="87"/>
       <c r="H4" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I4" s="86" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J4" s="87"/>
       <c r="K4" s="86" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L4" s="87"/>
       <c r="M4" s="92" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N4" s="78" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O4" s="78"/>
       <c r="P4" s="79" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="Q4" s="79"/>
       <c r="R4" s="79"/>
       <c r="S4" s="79"/>
       <c r="T4" s="79"/>
       <c r="U4" s="79" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="V4" s="79"/>
       <c r="W4" s="79"/>
@@ -31287,13 +31281,13 @@
     <row r="5" spans="1:25" s="54" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="77"/>
       <c r="B5" s="39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C5" s="42" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>4</v>
@@ -31306,7 +31300,7 @@
       </c>
       <c r="H5" s="89"/>
       <c r="I5" s="50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J5" s="50" t="s">
         <v>4</v>
@@ -31340,16 +31334,16 @@
         <v>10</v>
       </c>
       <c r="U5" s="38" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="V5" s="38" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="W5" s="38" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="X5" s="38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -36593,7 +36587,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -36613,83 +36607,83 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
-      <c r="B2" s="106" t="s">
-        <v>240</v>
+      <c r="B2" s="100" t="s">
+        <v>237</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="108"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="102"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="102" t="s">
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="96" t="s">
+      <c r="H3" s="97"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="109" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="52" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
-      <c r="L3" s="106" t="s">
-        <v>128</v>
+      <c r="L3" s="100" t="s">
+        <v>125</v>
       </c>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="108"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="102"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="112" t="s">
-        <v>139</v>
+      <c r="C4" s="107" t="s">
+        <v>136</v>
       </c>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="108" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="99" t="s">
+      <c r="F4" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="109" t="s">
-        <v>134</v>
+      <c r="G4" s="104" t="s">
+        <v>131</v>
       </c>
-      <c r="H4" s="110" t="s">
+      <c r="H4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="105" t="s">
-        <v>177</v>
+      <c r="I4" s="99" t="s">
+        <v>174</v>
       </c>
-      <c r="J4" s="97"/>
-      <c r="K4" s="100" t="s">
-        <v>141</v>
+      <c r="J4" s="110"/>
+      <c r="K4" s="112" t="s">
+        <v>138</v>
       </c>
       <c r="L4" s="78" t="s">
         <v>18</v>
@@ -36699,35 +36693,35 @@
         <v>19</v>
       </c>
       <c r="O4" s="78"/>
-      <c r="P4" s="99" t="s">
+      <c r="P4" s="103" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="88"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="113"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="108"/>
       <c r="E5" s="89"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="101"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="113"/>
       <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="56" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="56" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
-      <c r="P5" s="99"/>
+      <c r="P5" s="103"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -40332,6 +40326,10 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9TADddINtH3/s8+B+YSEyrbqN3sXm6gNvmsaihCGVKf7Pla3vF7K/W63Z2DPtXhM7gpZzMQTmkRfISjjfsW2DA==" saltValue="PE4zbTBOxopTV3TBfcOFrw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
@@ -40346,10 +40344,6 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 J6 K4:K5 G4:I5 O5" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40393,7 +40387,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -40408,22 +40402,22 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
-      <c r="B2" s="99" t="s">
-        <v>232</v>
+      <c r="B2" s="103" t="s">
+        <v>229</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99" t="s">
-        <v>233</v>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103" t="s">
+        <v>230</v>
       </c>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
@@ -40434,7 +40428,7 @@
       <c r="D3" s="91"/>
       <c r="E3" s="91"/>
       <c r="F3" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G3" s="90" t="s">
         <v>4</v>
@@ -40443,13 +40437,13 @@
       <c r="I3" s="91"/>
       <c r="J3" s="94"/>
       <c r="K3" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="77"/>
       <c r="B4" s="50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C4" s="50" t="s">
         <v>4</v>
@@ -40462,7 +40456,7 @@
       </c>
       <c r="F4" s="89"/>
       <c r="G4" s="50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H4" s="50" t="s">
         <v>4</v>
@@ -43150,7 +43144,7 @@
   <sheetData>
     <row r="1" spans="1:41" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -43195,31 +43189,31 @@
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
-      <c r="B2" s="99" t="s">
-        <v>190</v>
+      <c r="B2" s="103" t="s">
+        <v>187</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="103"/>
+      <c r="T2" s="103"/>
       <c r="U2" s="115" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="V2" s="116"/>
       <c r="W2" s="116"/>
@@ -43234,7 +43228,7 @@
       <c r="AF2" s="116"/>
       <c r="AG2" s="117"/>
       <c r="AH2" s="115" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AI2" s="116"/>
       <c r="AJ2" s="116"/>
@@ -43246,25 +43240,25 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
       <c r="U3" s="86"/>
       <c r="V3" s="118"/>
       <c r="W3" s="118"/>
@@ -43290,95 +43284,95 @@
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="95" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C4" s="95" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
-      <c r="D4" s="96" t="s">
-        <v>145</v>
+      <c r="D4" s="109" t="s">
+        <v>142</v>
       </c>
       <c r="E4" s="79" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F4" s="79"/>
       <c r="G4" s="79"/>
       <c r="H4" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I4" s="79"/>
       <c r="J4" s="79"/>
       <c r="K4" s="95" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L4" s="79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M4" s="79"/>
       <c r="N4" s="79"/>
       <c r="O4" s="79"/>
       <c r="P4" s="79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="79"/>
       <c r="R4" s="79"/>
       <c r="S4" s="79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T4" s="79"/>
-      <c r="U4" s="99" t="s">
-        <v>155</v>
+      <c r="U4" s="103" t="s">
+        <v>152</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="W4" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="99" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="99" t="s">
+      <c r="Y4" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="99" t="s">
+      <c r="Z4" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="99" t="s">
+      <c r="AA4" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="99" t="s">
+      <c r="AB4" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="AB4" s="99" t="s">
+      <c r="AC4" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="AC4" s="99" t="s">
+      <c r="AD4" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="AD4" s="99" t="s">
+      <c r="AE4" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="AE4" s="99" t="s">
+      <c r="AF4" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="AG4" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="99" t="s">
-        <v>147</v>
+      <c r="AH4" s="96" t="s">
+        <v>233</v>
       </c>
-      <c r="AG4" s="99" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH4" s="102" t="s">
-        <v>236</v>
-      </c>
-      <c r="AI4" s="104"/>
+      <c r="AI4" s="98"/>
       <c r="AJ4" s="79" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AK4" s="79"/>
       <c r="AL4" s="79" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AM4" s="79"/>
       <c r="AN4" s="79" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AO4" s="79"/>
     </row>
@@ -43386,89 +43380,89 @@
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
-      <c r="D5" s="98"/>
+      <c r="D5" s="111"/>
       <c r="E5" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="41" t="s">
-        <v>26</v>
-      </c>
       <c r="G5" s="44" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H5" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="41" t="s">
-        <v>26</v>
-      </c>
       <c r="J5" s="44" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K5" s="89"/>
       <c r="L5" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="M5" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="N5" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="O5" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="P5" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="N5" s="38" t="s">
+      <c r="Q5" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="O5" s="38" t="s">
+      <c r="R5" s="38" t="s">
         <v>151</v>
-      </c>
-      <c r="P5" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>154</v>
       </c>
       <c r="S5" s="41" t="s">
         <v>22</v>
       </c>
       <c r="T5" s="44" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="99"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
+      <c r="Y5" s="103"/>
+      <c r="Z5" s="103"/>
+      <c r="AA5" s="103"/>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="103"/>
+      <c r="AD5" s="103"/>
+      <c r="AE5" s="103"/>
+      <c r="AF5" s="103"/>
+      <c r="AG5" s="103"/>
       <c r="AH5" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI5" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ5" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK5" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="AI5" s="38" t="s">
+      <c r="AL5" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="AJ5" s="38" t="s">
+      <c r="AM5" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="AK5" s="38" t="s">
+      <c r="AN5" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="AL5" s="38" t="s">
+      <c r="AO5" s="38" t="s">
         <v>160</v>
-      </c>
-      <c r="AM5" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="AN5" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="AO5" s="38" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -52148,7 +52142,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="5"/>
@@ -52156,10 +52150,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="88" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C2" s="88"/>
       <c r="D2" s="88"/>
@@ -52167,13 +52161,13 @@
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="119"/>
       <c r="B3" s="88" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C3" s="120" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -53423,7 +53417,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -53437,17 +53431,17 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
-      <c r="B2" s="99" t="s">
-        <v>224</v>
+      <c r="B2" s="103" t="s">
+        <v>221</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
       <c r="G2" s="90" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H2" s="91"/>
       <c r="I2" s="91"/>
@@ -53456,43 +53450,43 @@
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
       <c r="B3" s="95" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="95" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="103" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="109" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="H3" s="109" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="I3" s="109" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="99" t="s">
-        <v>171</v>
-      </c>
-      <c r="F3" s="117" t="s">
-        <v>172</v>
-      </c>
-      <c r="G3" s="96" t="s">
+      <c r="J3" s="121" t="s">
         <v>167</v>
-      </c>
-      <c r="H3" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="I3" s="96" t="s">
-        <v>169</v>
-      </c>
-      <c r="J3" s="121" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="77"/>
       <c r="B4" s="89"/>
       <c r="C4" s="89"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="99"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="103"/>
       <c r="F4" s="87"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
       <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -55949,7 +55943,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11"/>
@@ -55969,10 +55963,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B2" s="119" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C2" s="125"/>
       <c r="D2" s="125"/>
@@ -55984,7 +55978,7 @@
       <c r="J2" s="125"/>
       <c r="K2" s="120"/>
       <c r="L2" s="115" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M2" s="116"/>
       <c r="N2" s="116"/>
@@ -55994,23 +55988,23 @@
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
       <c r="B3" s="126" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C3" s="130" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="131"/>
       <c r="E3" s="131"/>
       <c r="F3" s="131"/>
       <c r="G3" s="132"/>
       <c r="H3" s="128" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I3" s="126" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J3" s="123" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K3" s="124"/>
       <c r="L3" s="86"/>
@@ -56026,16 +56020,16 @@
         <v>23</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H4" s="129"/>
       <c r="I4" s="127"/>
@@ -56046,19 +56040,19 @@
         <v>15</v>
       </c>
       <c r="L4" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="N4" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="N4" s="40" t="s">
-        <v>186</v>
-      </c>
       <c r="O4" s="40" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -59729,7 +59723,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -59763,63 +59757,63 @@
     </row>
     <row r="2" spans="1:30" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>110</v>
-      </c>
       <c r="C2" s="88" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D2" s="88"/>
       <c r="E2" s="88"/>
       <c r="F2" s="119" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G2" s="125"/>
       <c r="H2" s="120"/>
       <c r="I2" s="114" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J2" s="114" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K2" s="115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L2" s="116"/>
       <c r="M2" s="117"/>
       <c r="N2" s="115" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O2" s="117"/>
       <c r="P2" s="88" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
-      <c r="Q2" s="99" t="s">
-        <v>262</v>
+      <c r="Q2" s="103" t="s">
+        <v>258</v>
       </c>
       <c r="R2" s="88" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="S2" s="88" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="T2" s="88"/>
       <c r="U2" s="133" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="V2" s="134"/>
       <c r="W2" s="133" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="X2" s="134"/>
       <c r="Y2" s="133" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Z2" s="134"/>
       <c r="AA2" s="88" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AB2" s="88"/>
       <c r="AC2" s="88"/>
@@ -59829,17 +59823,17 @@
       <c r="A3" s="76"/>
       <c r="B3" s="76"/>
       <c r="C3" s="80" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" s="119" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E3" s="120"/>
       <c r="F3" s="114" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H3" s="120"/>
       <c r="I3" s="76"/>
@@ -59850,7 +59844,7 @@
       <c r="N3" s="86"/>
       <c r="O3" s="87"/>
       <c r="P3" s="88"/>
-      <c r="Q3" s="99"/>
+      <c r="Q3" s="103"/>
       <c r="R3" s="88"/>
       <c r="S3" s="88"/>
       <c r="T3" s="88"/>
@@ -59885,58 +59879,58 @@
       <c r="I4" s="77"/>
       <c r="J4" s="77"/>
       <c r="K4" s="50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L4" s="42" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M4" s="59" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N4" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="42" t="s">
-        <v>49</v>
-      </c>
       <c r="P4" s="88"/>
-      <c r="Q4" s="99"/>
+      <c r="Q4" s="103"/>
       <c r="R4" s="88"/>
       <c r="S4" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T4" s="42" t="s">
-        <v>264</v>
+        <v>15</v>
       </c>
       <c r="U4" s="39" t="s">
         <v>23</v>
       </c>
       <c r="V4" s="39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W4" s="39" t="s">
         <v>22</v>
       </c>
       <c r="X4" s="39" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>22</v>
       </c>
       <c r="Z4" s="39" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AA4" s="56" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AB4" s="50" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AC4" s="50" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AD4" s="50" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -66312,12 +66306,8 @@
       <c r="B204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Npdc6hR1jWNwlUd78HFJSJlOVnyVZEkwE3li2w9MaNYbr3qpWORdGSkVHRoIs6ZmqiHg7fNUc25lo9m1DLSPvg==" saltValue="CpsBwfeTpFYKyUOX8eB08w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="d21qlgp65jSu5W9pa5yJ5h6FXV3pmxRSPPtHFMi6kL/5Q045jK8F1FxQGWC8ChuBu/i/+ceDsCkP7hrPZBzfYg==" saltValue="OgP3geBPxDkKLe5cj3oUgQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C2:E2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="Y2:Z3"/>
@@ -66334,6 +66324,10 @@
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4 AA4:AD4" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F68486-8307-4B9B-8B70-28C6DC801163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA32078-A1D4-4834-9D8A-4E8AA48401A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="33285" yWindow="375" windowWidth="22035" windowHeight="14955" tabRatio="879" firstSheet="12" activeTab="16" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="273">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -872,6 +872,9 @@
   <si>
     <t>TAG_ID_2</t>
   </si>
+  <si>
+    <t>NUMBER_OF_HOOKS_RETRIEVED_DURING_OBSERVATION</t>
+  </si>
 </sst>
 </file>
 
@@ -1282,7 +1285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1539,6 +1542,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1560,9 +1574,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1592,14 +1603,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1691,6 +1694,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7295,17 +7313,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i54u068XThYDfxhseUVm7j5UOX6o6sLA/paOyFGBfnG2ueK1l9vp0KVJDHX+jDagofUZDK+i4w0EkGdmr+cm5A==" saltValue="YMFvCB9MnqWRAENMsMJcZw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 M3 N3 O3" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -10467,7 +10485,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:P204"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -10482,10 +10500,11 @@
     <col min="10" max="13" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="33.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="42.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.42578125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="27.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>82</v>
       </c>
@@ -10503,9 +10522,10 @@
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
         <v>104</v>
       </c>
@@ -10522,26 +10542,29 @@
       </c>
       <c r="G2" s="125"/>
       <c r="H2" s="120"/>
-      <c r="I2" s="104" t="s">
+      <c r="I2" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="103" t="s">
+      <c r="J2" s="96" t="s">
         <v>211</v>
       </c>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
       <c r="N2" s="88" t="s">
         <v>57</v>
       </c>
       <c r="O2" s="88" t="s">
         <v>216</v>
       </c>
-      <c r="P2" s="135" t="s">
+      <c r="P2" s="143" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q2" s="135" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
       <c r="B3" s="76"/>
       <c r="C3" s="114" t="s">
@@ -10558,16 +10581,17 @@
         <v>93</v>
       </c>
       <c r="H3" s="120"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
       <c r="N3" s="88"/>
       <c r="O3" s="88"/>
-      <c r="P3" s="135"/>
-    </row>
-    <row r="4" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="144"/>
+      <c r="Q3" s="135"/>
+    </row>
+    <row r="4" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="77"/>
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
@@ -10584,7 +10608,7 @@
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="104"/>
+      <c r="I4" s="106"/>
       <c r="J4" s="50" t="s">
         <v>210</v>
       </c>
@@ -10599,9 +10623,10 @@
       </c>
       <c r="N4" s="88"/>
       <c r="O4" s="88"/>
-      <c r="P4" s="135"/>
-    </row>
-    <row r="5" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P4" s="145"/>
+      <c r="Q4" s="135"/>
+    </row>
+    <row r="5" spans="1:17" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -10618,8 +10643,9 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" s="2"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -10636,8 +10662,9 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -10654,8 +10681,9 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -10672,8 +10700,9 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -10690,8 +10719,9 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -10708,8 +10738,9 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10726,8 +10757,9 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -10744,8 +10776,9 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" s="2"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10762,8 +10795,9 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -10780,8 +10814,9 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -10798,8 +10833,9 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -10816,8 +10852,9 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -10834,8 +10871,9 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -10852,8 +10890,9 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -10870,8 +10909,9 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -10888,8 +10928,9 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10906,8 +10947,9 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" s="2"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -10924,8 +10966,9 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" s="2"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10942,8 +10985,9 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" s="2"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -10960,8 +11004,9 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24" s="2"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -10978,8 +11023,9 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25" s="2"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -10996,8 +11042,9 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26" s="2"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -11014,8 +11061,9 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="2"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -11032,8 +11080,9 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="2"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11050,8 +11099,9 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q29" s="2"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -11068,8 +11118,9 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" s="2"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -11086,8 +11137,9 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -11104,8 +11156,9 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" s="2"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11122,8 +11175,9 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" s="2"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -11140,8 +11194,9 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" s="2"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11158,8 +11213,9 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q35" s="2"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11176,8 +11232,9 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q36" s="2"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -11194,8 +11251,9 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q37" s="2"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -11212,8 +11270,9 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -11230,8 +11289,9 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" s="2"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -11248,8 +11308,9 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" s="2"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -11266,8 +11327,9 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q41" s="2"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11284,8 +11346,9 @@
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" s="2"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -11302,8 +11365,9 @@
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q43" s="2"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -11320,8 +11384,9 @@
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q44" s="2"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -11338,8 +11403,9 @@
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q45" s="2"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -11356,8 +11422,9 @@
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q46" s="2"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -11374,8 +11441,9 @@
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q47" s="2"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -11392,8 +11460,9 @@
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q48" s="2"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -11410,8 +11479,9 @@
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q49" s="2"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -11428,8 +11498,9 @@
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q50" s="2"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -11446,8 +11517,9 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q51" s="2"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -11464,8 +11536,9 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q52" s="2"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -11482,8 +11555,9 @@
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q53" s="2"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -11500,8 +11574,9 @@
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" s="2"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -11518,8 +11593,9 @@
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q55" s="2"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -11536,8 +11612,9 @@
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q56" s="2"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -11554,8 +11631,9 @@
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q57" s="2"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -11572,8 +11650,9 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q58" s="2"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -11590,8 +11669,9 @@
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q59" s="2"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -11608,8 +11688,9 @@
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q60" s="2"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -11626,8 +11707,9 @@
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q61" s="2"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -11644,8 +11726,9 @@
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q62" s="2"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -11662,8 +11745,9 @@
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q63" s="2"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -11680,8 +11764,9 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q64" s="2"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -11698,8 +11783,9 @@
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q65" s="2"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -11716,8 +11802,9 @@
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q66" s="2"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -11734,8 +11821,9 @@
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q67" s="2"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -11752,8 +11840,9 @@
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q68" s="2"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -11770,8 +11859,9 @@
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q69" s="2"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -11788,8 +11878,9 @@
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q70" s="2"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -11806,8 +11897,9 @@
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q71" s="2"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -11824,8 +11916,9 @@
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q72" s="2"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -11842,8 +11935,9 @@
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q73" s="2"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -11860,8 +11954,9 @@
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q74" s="2"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -11878,8 +11973,9 @@
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q75" s="2"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -11896,8 +11992,9 @@
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q76" s="2"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -11914,8 +12011,9 @@
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q77" s="2"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -11932,8 +12030,9 @@
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q78" s="2"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -11950,8 +12049,9 @@
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q79" s="2"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -11968,8 +12068,9 @@
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -11986,8 +12087,9 @@
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q81" s="2"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -12004,8 +12106,9 @@
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" s="2"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -12022,8 +12125,9 @@
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q83" s="2"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -12040,8 +12144,9 @@
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q84" s="2"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -12058,8 +12163,9 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q85" s="2"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -12076,8 +12182,9 @@
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q86" s="2"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -12094,8 +12201,9 @@
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q87" s="2"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -12112,8 +12220,9 @@
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q88" s="2"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -12130,8 +12239,9 @@
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q89" s="2"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -12148,8 +12258,9 @@
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q90" s="2"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -12166,8 +12277,9 @@
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q91" s="2"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -12184,8 +12296,9 @@
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q92" s="2"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -12202,8 +12315,9 @@
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q93" s="2"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -12220,8 +12334,9 @@
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q94" s="2"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -12238,8 +12353,9 @@
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q95" s="2"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -12256,8 +12372,9 @@
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q96" s="2"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -12274,8 +12391,9 @@
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" s="2"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -12292,8 +12410,9 @@
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q98" s="2"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -12310,8 +12429,9 @@
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q99" s="2"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -12328,8 +12448,9 @@
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q100" s="2"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -12346,8 +12467,9 @@
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q101" s="2"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -12364,8 +12486,9 @@
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q102" s="2"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -12382,8 +12505,9 @@
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q103" s="2"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -12400,8 +12524,9 @@
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q104" s="2"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -12418,8 +12543,9 @@
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q105" s="2"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -12436,8 +12562,9 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q106" s="2"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -12454,8 +12581,9 @@
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q107" s="2"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -12472,8 +12600,9 @@
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q108" s="2"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -12490,8 +12619,9 @@
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q109" s="2"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -12508,8 +12638,9 @@
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q110" s="2"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -12526,8 +12657,9 @@
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q111" s="2"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -12544,8 +12676,9 @@
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q112" s="2"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -12562,8 +12695,9 @@
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q113" s="2"/>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -12580,8 +12714,9 @@
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q114" s="2"/>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -12598,8 +12733,9 @@
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q115" s="2"/>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -12616,8 +12752,9 @@
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q116" s="2"/>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -12634,8 +12771,9 @@
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q117" s="2"/>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -12652,8 +12790,9 @@
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q118" s="2"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -12670,8 +12809,9 @@
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q119" s="2"/>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -12688,8 +12828,9 @@
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q120" s="2"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -12706,8 +12847,9 @@
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q121" s="2"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -12724,8 +12866,9 @@
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q122" s="2"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -12742,8 +12885,9 @@
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q123" s="2"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -12760,8 +12904,9 @@
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q124" s="2"/>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -12778,8 +12923,9 @@
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q125" s="2"/>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -12796,8 +12942,9 @@
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q126" s="2"/>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -12814,8 +12961,9 @@
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q127" s="2"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -12832,8 +12980,9 @@
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q128" s="2"/>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -12850,8 +12999,9 @@
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q129" s="2"/>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -12868,8 +13018,9 @@
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q130" s="2"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -12886,8 +13037,9 @@
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q131" s="2"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -12904,8 +13056,9 @@
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q132" s="2"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -12922,8 +13075,9 @@
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q133" s="2"/>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -12940,8 +13094,9 @@
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q134" s="2"/>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -12958,8 +13113,9 @@
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q135" s="2"/>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -12976,8 +13132,9 @@
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q136" s="2"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -12994,8 +13151,9 @@
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q137" s="2"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -13012,8 +13170,9 @@
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q138" s="2"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -13030,8 +13189,9 @@
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q139" s="2"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -13048,8 +13208,9 @@
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q140" s="2"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -13066,8 +13227,9 @@
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q141" s="2"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -13084,8 +13246,9 @@
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q142" s="2"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -13102,8 +13265,9 @@
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q143" s="2"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -13120,8 +13284,9 @@
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q144" s="2"/>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -13138,8 +13303,9 @@
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q145" s="2"/>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -13156,8 +13322,9 @@
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q146" s="2"/>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -13174,8 +13341,9 @@
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q147" s="2"/>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -13192,8 +13360,9 @@
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q148" s="2"/>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -13210,8 +13379,9 @@
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q149" s="2"/>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -13228,8 +13398,9 @@
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q150" s="2"/>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -13246,8 +13417,9 @@
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q151" s="2"/>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -13264,8 +13436,9 @@
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q152" s="2"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -13282,8 +13455,9 @@
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q153" s="2"/>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -13300,8 +13474,9 @@
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q154" s="2"/>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -13318,8 +13493,9 @@
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q155" s="2"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -13336,8 +13512,9 @@
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q156" s="2"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -13354,8 +13531,9 @@
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q157" s="2"/>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -13372,8 +13550,9 @@
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q158" s="2"/>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -13390,8 +13569,9 @@
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q159" s="2"/>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -13408,8 +13588,9 @@
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q160" s="2"/>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -13426,8 +13607,9 @@
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q161" s="2"/>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -13444,8 +13626,9 @@
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q162" s="2"/>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -13462,8 +13645,9 @@
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q163" s="2"/>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -13480,8 +13664,9 @@
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q164" s="2"/>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -13498,8 +13683,9 @@
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q165" s="2"/>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -13516,8 +13702,9 @@
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q166" s="2"/>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -13534,8 +13721,9 @@
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q167" s="2"/>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -13552,8 +13740,9 @@
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q168" s="2"/>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -13570,8 +13759,9 @@
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q169" s="2"/>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -13588,8 +13778,9 @@
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q170" s="2"/>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -13606,8 +13797,9 @@
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q171" s="2"/>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -13624,8 +13816,9 @@
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q172" s="2"/>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -13642,8 +13835,9 @@
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q173" s="2"/>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -13660,8 +13854,9 @@
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q174" s="2"/>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -13678,8 +13873,9 @@
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q175" s="2"/>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -13696,8 +13892,9 @@
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q176" s="2"/>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -13714,8 +13911,9 @@
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q177" s="2"/>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -13732,8 +13930,9 @@
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q178" s="2"/>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -13750,8 +13949,9 @@
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q179" s="2"/>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -13768,8 +13968,9 @@
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q180" s="2"/>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -13786,8 +13987,9 @@
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q181" s="2"/>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -13804,8 +14006,9 @@
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q182" s="2"/>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -13822,8 +14025,9 @@
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" s="2"/>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q183" s="2"/>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -13840,8 +14044,9 @@
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q184" s="2"/>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -13858,8 +14063,9 @@
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q185" s="2"/>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -13876,8 +14082,9 @@
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q186" s="2"/>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -13894,8 +14101,9 @@
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q187" s="2"/>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -13912,8 +14120,9 @@
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q188" s="2"/>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -13930,8 +14139,9 @@
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q189" s="2"/>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -13948,8 +14158,9 @@
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q190" s="2"/>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -13966,8 +14177,9 @@
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q191" s="2"/>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -13984,8 +14196,9 @@
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q192" s="2"/>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -14002,8 +14215,9 @@
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q193" s="2"/>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -14020,8 +14234,9 @@
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q194" s="2"/>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -14038,8 +14253,9 @@
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" s="2"/>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q195" s="2"/>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -14056,8 +14272,9 @@
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q196" s="2"/>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -14074,8 +14291,9 @@
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q197" s="2"/>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -14092,8 +14310,9 @@
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
       <c r="P198" s="2"/>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q198" s="2"/>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -14110,8 +14329,9 @@
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" s="2"/>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q199" s="2"/>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -14128,8 +14348,9 @@
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" s="2"/>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q200" s="2"/>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -14146,8 +14367,9 @@
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q201" s="2"/>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -14164,8 +14386,9 @@
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q202" s="2"/>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -14182,8 +14405,9 @@
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q203" s="2"/>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -14200,11 +14424,17 @@
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
+      <c r="Q204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PoLs1kxIM/xJUmr7urrblsJ/5hObRoOum4QkrLl5n6UkTskAAW1rlDkj4UAOAaNPAxaZOLfva1Eeyyy3ErcvXg==" saltValue="hHLCZEhHQHH5LRknKlGm2A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="13">
-    <mergeCell ref="P2:P4"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dlFj2sPqiSv9eFeao1SBDLarE133CE5VD8yNCCeOHNQfNXNZi7oFUlGnOiN0L8Mfj1AOHWL4yBs29kJ5VkLUsg==" saltValue="J7Ti7XS+RGy13SKXPsV6rA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="14">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="F3:F4"/>
@@ -14212,19 +14442,15 @@
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:M3"/>
     <mergeCell ref="N2:N4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="P2:P4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 P2:P4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 Q2:Q4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="P2:P4" r:id="rId1" location="samplingProtocols" display="SAMPLING_PROTOCOL_CODE" xr:uid="{C0C4727C-9767-4664-8796-43CDF0860627}"/>
+    <hyperlink ref="Q2:Q4" r:id="rId1" location="samplingProtocols" display="SAMPLING_PROTOCOL_CODE" xr:uid="{C0C4727C-9767-4664-8796-43CDF0860627}"/>
     <hyperlink ref="I2:I4" r:id="rId2" location="offalManagementTypes" display="OFFAL_MANAGEMENT" xr:uid="{408DFBD1-078D-43D4-8B22-538A09E39B98}"/>
     <hyperlink ref="J4" r:id="rId3" location="vesselSections" xr:uid="{140540DF-7251-4F70-BF34-280C13EE47A9}"/>
     <hyperlink ref="K4" r:id="rId4" location="vesselSections" xr:uid="{C6B0B34F-D5B5-4396-BD53-32117C4E0387}"/>
@@ -18225,37 +18451,38 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Y203"/>
+  <dimension ref="A1:Z203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.85546875" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="3"/>
-    <col min="19" max="19" width="14.5703125" style="3" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.5703125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="30.7109375" customWidth="1"/>
-    <col min="25" max="25" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.85546875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="3"/>
+    <col min="20" max="20" width="14.5703125" style="3" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="3" customWidth="1"/>
+    <col min="22" max="22" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.5703125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="30.7109375" customWidth="1"/>
+    <col min="26" max="26" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>85</v>
       </c>
@@ -18282,9 +18509,10 @@
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
-      <c r="Y1" s="6"/>
-    </row>
-    <row r="2" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2" spans="1:26" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="140" t="s">
         <v>104</v>
       </c>
@@ -18297,110 +18525,114 @@
       <c r="D2" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="146" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="97" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="112" t="s">
+      <c r="G2" s="97" t="s">
         <v>200</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="H2" s="88" t="s">
         <v>203</v>
       </c>
-      <c r="H2" s="88"/>
       <c r="I2" s="88"/>
       <c r="J2" s="88"/>
-      <c r="K2" s="103" t="s">
+      <c r="K2" s="88"/>
+      <c r="L2" s="96" t="s">
         <v>205</v>
       </c>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103" t="s">
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="109" t="s">
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="90" t="s">
+      <c r="T2" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="T2" s="94"/>
-      <c r="U2" s="90" t="s">
+      <c r="U2" s="94"/>
+      <c r="V2" s="90" t="s">
         <v>208</v>
       </c>
-      <c r="V2" s="91"/>
-      <c r="W2" s="94"/>
-      <c r="X2" s="103" t="s">
+      <c r="W2" s="91"/>
+      <c r="X2" s="94"/>
+      <c r="Y2" s="96" t="s">
         <v>207</v>
       </c>
-      <c r="Y2" s="103"/>
-    </row>
-    <row r="3" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z2" s="96"/>
+    </row>
+    <row r="3" spans="1:26" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="141"/>
       <c r="B3" s="141"/>
       <c r="C3" s="141"/>
       <c r="D3" s="141"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="56" t="s">
+      <c r="E3" s="147"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="39" t="s">
+      <c r="I3" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="J3" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="K3" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="L3" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="M3" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="50" t="s">
+      <c r="N3" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="O3" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="O3" s="50" t="s">
+      <c r="P3" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="Q3" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="Q3" s="50" t="s">
+      <c r="R3" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="R3" s="111"/>
-      <c r="S3" s="43" t="s">
+      <c r="S3" s="113"/>
+      <c r="T3" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="T3" s="43" t="s">
+      <c r="U3" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="U3" s="59" t="s">
+      <c r="V3" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="42" t="s">
+      <c r="W3" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="W3" s="42" t="s">
+      <c r="X3" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="X3" s="50" t="s">
+      <c r="Y3" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="Y3" s="50" t="s">
+      <c r="Z3" s="50" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -18424,10 +18656,11 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="9"/>
+      <c r="X4" s="2"/>
       <c r="Y4" s="9"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z4" s="9"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -18451,10 +18684,11 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
-      <c r="X5" s="9"/>
+      <c r="X5" s="2"/>
       <c r="Y5" s="9"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z5" s="9"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -18478,10 +18712,11 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="9"/>
+      <c r="X6" s="2"/>
       <c r="Y6" s="9"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z6" s="9"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -18505,10 +18740,11 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="9"/>
+      <c r="X7" s="2"/>
       <c r="Y7" s="9"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z7" s="9"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -18532,10 +18768,11 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
-      <c r="X8" s="9"/>
+      <c r="X8" s="2"/>
       <c r="Y8" s="9"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z8" s="9"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -18559,10 +18796,11 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
-      <c r="X9" s="9"/>
+      <c r="X9" s="2"/>
       <c r="Y9" s="9"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z9" s="9"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -18586,10 +18824,11 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="9"/>
+      <c r="X10" s="2"/>
       <c r="Y10" s="9"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z10" s="9"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -18613,10 +18852,11 @@
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
-      <c r="X11" s="9"/>
+      <c r="X11" s="2"/>
       <c r="Y11" s="9"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z11" s="9"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -18640,10 +18880,11 @@
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
-      <c r="X12" s="9"/>
+      <c r="X12" s="2"/>
       <c r="Y12" s="9"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z12" s="9"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -18667,10 +18908,11 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
-      <c r="X13" s="9"/>
+      <c r="X13" s="2"/>
       <c r="Y13" s="9"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z13" s="9"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -18694,10 +18936,11 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
-      <c r="X14" s="9"/>
+      <c r="X14" s="2"/>
       <c r="Y14" s="9"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z14" s="9"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -18721,10 +18964,11 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
-      <c r="X15" s="9"/>
+      <c r="X15" s="2"/>
       <c r="Y15" s="9"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z15" s="9"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -18748,10 +18992,11 @@
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
-      <c r="X16" s="9"/>
+      <c r="X16" s="2"/>
       <c r="Y16" s="9"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z16" s="9"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -18775,10 +19020,11 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
-      <c r="X17" s="9"/>
+      <c r="X17" s="2"/>
       <c r="Y17" s="9"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z17" s="9"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -18802,10 +19048,11 @@
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
-      <c r="X18" s="9"/>
+      <c r="X18" s="2"/>
       <c r="Y18" s="9"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z18" s="9"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -18829,10 +19076,11 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
-      <c r="X19" s="9"/>
+      <c r="X19" s="2"/>
       <c r="Y19" s="9"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z19" s="9"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -18856,10 +19104,11 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
-      <c r="X20" s="9"/>
+      <c r="X20" s="2"/>
       <c r="Y20" s="9"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z20" s="9"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -18883,10 +19132,11 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
-      <c r="X21" s="9"/>
+      <c r="X21" s="2"/>
       <c r="Y21" s="9"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z21" s="9"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -18910,10 +19160,11 @@
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
-      <c r="X22" s="9"/>
+      <c r="X22" s="2"/>
       <c r="Y22" s="9"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z22" s="9"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -18937,10 +19188,11 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
-      <c r="X23" s="9"/>
+      <c r="X23" s="2"/>
       <c r="Y23" s="9"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z23" s="9"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -18964,10 +19216,11 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
-      <c r="X24" s="9"/>
+      <c r="X24" s="2"/>
       <c r="Y24" s="9"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z24" s="9"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -18991,10 +19244,11 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
-      <c r="X25" s="9"/>
+      <c r="X25" s="2"/>
       <c r="Y25" s="9"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z25" s="9"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -19018,10 +19272,11 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
-      <c r="X26" s="9"/>
+      <c r="X26" s="2"/>
       <c r="Y26" s="9"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z26" s="9"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -19045,10 +19300,11 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
-      <c r="X27" s="9"/>
+      <c r="X27" s="2"/>
       <c r="Y27" s="9"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z27" s="9"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -19072,10 +19328,11 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
-      <c r="X28" s="9"/>
+      <c r="X28" s="2"/>
       <c r="Y28" s="9"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z28" s="9"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -19099,10 +19356,11 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
-      <c r="X29" s="9"/>
+      <c r="X29" s="2"/>
       <c r="Y29" s="9"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z29" s="9"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -19126,10 +19384,11 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
-      <c r="X30" s="9"/>
+      <c r="X30" s="2"/>
       <c r="Y30" s="9"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z30" s="9"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -19153,10 +19412,11 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
-      <c r="X31" s="9"/>
+      <c r="X31" s="2"/>
       <c r="Y31" s="9"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z31" s="9"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -19180,10 +19440,11 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
-      <c r="X32" s="9"/>
+      <c r="X32" s="2"/>
       <c r="Y32" s="9"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z32" s="9"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -19207,10 +19468,11 @@
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
-      <c r="X33" s="9"/>
+      <c r="X33" s="2"/>
       <c r="Y33" s="9"/>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z33" s="9"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -19234,10 +19496,11 @@
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
-      <c r="X34" s="9"/>
+      <c r="X34" s="2"/>
       <c r="Y34" s="9"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z34" s="9"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -19261,10 +19524,11 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
-      <c r="X35" s="9"/>
+      <c r="X35" s="2"/>
       <c r="Y35" s="9"/>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z35" s="9"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -19288,10 +19552,11 @@
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
-      <c r="X36" s="9"/>
+      <c r="X36" s="2"/>
       <c r="Y36" s="9"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z36" s="9"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -19315,10 +19580,11 @@
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
-      <c r="X37" s="9"/>
+      <c r="X37" s="2"/>
       <c r="Y37" s="9"/>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z37" s="9"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -19342,10 +19608,11 @@
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
-      <c r="X38" s="9"/>
+      <c r="X38" s="2"/>
       <c r="Y38" s="9"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z38" s="9"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -19369,10 +19636,11 @@
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
-      <c r="X39" s="9"/>
+      <c r="X39" s="2"/>
       <c r="Y39" s="9"/>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z39" s="9"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -19396,10 +19664,11 @@
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
-      <c r="X40" s="9"/>
+      <c r="X40" s="2"/>
       <c r="Y40" s="9"/>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z40" s="9"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -19423,10 +19692,11 @@
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
-      <c r="X41" s="9"/>
+      <c r="X41" s="2"/>
       <c r="Y41" s="9"/>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z41" s="9"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -19450,10 +19720,11 @@
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
-      <c r="X42" s="9"/>
+      <c r="X42" s="2"/>
       <c r="Y42" s="9"/>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z42" s="9"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -19477,10 +19748,11 @@
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
-      <c r="X43" s="9"/>
+      <c r="X43" s="2"/>
       <c r="Y43" s="9"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z43" s="9"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -19504,10 +19776,11 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
-      <c r="X44" s="9"/>
+      <c r="X44" s="2"/>
       <c r="Y44" s="9"/>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z44" s="9"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -19531,10 +19804,11 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
-      <c r="X45" s="9"/>
+      <c r="X45" s="2"/>
       <c r="Y45" s="9"/>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z45" s="9"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -19558,10 +19832,11 @@
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
-      <c r="X46" s="9"/>
+      <c r="X46" s="2"/>
       <c r="Y46" s="9"/>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z46" s="9"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -19585,10 +19860,11 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
-      <c r="X47" s="9"/>
+      <c r="X47" s="2"/>
       <c r="Y47" s="9"/>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z47" s="9"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -19612,10 +19888,11 @@
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
-      <c r="X48" s="9"/>
+      <c r="X48" s="2"/>
       <c r="Y48" s="9"/>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z48" s="9"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -19639,10 +19916,11 @@
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
-      <c r="X49" s="9"/>
+      <c r="X49" s="2"/>
       <c r="Y49" s="9"/>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z49" s="9"/>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -19666,10 +19944,11 @@
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
-      <c r="X50" s="9"/>
+      <c r="X50" s="2"/>
       <c r="Y50" s="9"/>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z50" s="9"/>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -19693,10 +19972,11 @@
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
-      <c r="X51" s="9"/>
+      <c r="X51" s="2"/>
       <c r="Y51" s="9"/>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z51" s="9"/>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -19720,10 +20000,11 @@
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
-      <c r="X52" s="9"/>
+      <c r="X52" s="2"/>
       <c r="Y52" s="9"/>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z52" s="9"/>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -19747,10 +20028,11 @@
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
-      <c r="X53" s="9"/>
+      <c r="X53" s="2"/>
       <c r="Y53" s="9"/>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z53" s="9"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -19774,10 +20056,11 @@
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
-      <c r="X54" s="9"/>
+      <c r="X54" s="2"/>
       <c r="Y54" s="9"/>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z54" s="9"/>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -19801,10 +20084,11 @@
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
-      <c r="X55" s="9"/>
+      <c r="X55" s="2"/>
       <c r="Y55" s="9"/>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z55" s="9"/>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -19828,10 +20112,11 @@
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
-      <c r="X56" s="9"/>
+      <c r="X56" s="2"/>
       <c r="Y56" s="9"/>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z56" s="9"/>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -19855,10 +20140,11 @@
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
-      <c r="X57" s="9"/>
+      <c r="X57" s="2"/>
       <c r="Y57" s="9"/>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z57" s="9"/>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -19882,10 +20168,11 @@
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
-      <c r="X58" s="9"/>
+      <c r="X58" s="2"/>
       <c r="Y58" s="9"/>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z58" s="9"/>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -19909,10 +20196,11 @@
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
-      <c r="X59" s="9"/>
+      <c r="X59" s="2"/>
       <c r="Y59" s="9"/>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z59" s="9"/>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -19936,10 +20224,11 @@
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
-      <c r="X60" s="9"/>
+      <c r="X60" s="2"/>
       <c r="Y60" s="9"/>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z60" s="9"/>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -19963,10 +20252,11 @@
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
-      <c r="X61" s="9"/>
+      <c r="X61" s="2"/>
       <c r="Y61" s="9"/>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z61" s="9"/>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -19990,10 +20280,11 @@
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
-      <c r="X62" s="9"/>
+      <c r="X62" s="2"/>
       <c r="Y62" s="9"/>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z62" s="9"/>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -20017,10 +20308,11 @@
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
-      <c r="X63" s="9"/>
+      <c r="X63" s="2"/>
       <c r="Y63" s="9"/>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z63" s="9"/>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -20044,10 +20336,11 @@
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
-      <c r="X64" s="9"/>
+      <c r="X64" s="2"/>
       <c r="Y64" s="9"/>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z64" s="9"/>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -20071,10 +20364,11 @@
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
-      <c r="X65" s="9"/>
+      <c r="X65" s="2"/>
       <c r="Y65" s="9"/>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z65" s="9"/>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -20098,10 +20392,11 @@
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
-      <c r="X66" s="9"/>
+      <c r="X66" s="2"/>
       <c r="Y66" s="9"/>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z66" s="9"/>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -20125,10 +20420,11 @@
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
       <c r="W67" s="2"/>
-      <c r="X67" s="9"/>
+      <c r="X67" s="2"/>
       <c r="Y67" s="9"/>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z67" s="9"/>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -20152,10 +20448,11 @@
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
       <c r="W68" s="2"/>
-      <c r="X68" s="9"/>
+      <c r="X68" s="2"/>
       <c r="Y68" s="9"/>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z68" s="9"/>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -20179,10 +20476,11 @@
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
       <c r="W69" s="2"/>
-      <c r="X69" s="9"/>
+      <c r="X69" s="2"/>
       <c r="Y69" s="9"/>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z69" s="9"/>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -20206,10 +20504,11 @@
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
       <c r="W70" s="2"/>
-      <c r="X70" s="9"/>
+      <c r="X70" s="2"/>
       <c r="Y70" s="9"/>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z70" s="9"/>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -20233,10 +20532,11 @@
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
-      <c r="X71" s="9"/>
+      <c r="X71" s="2"/>
       <c r="Y71" s="9"/>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z71" s="9"/>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -20260,10 +20560,11 @@
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
-      <c r="X72" s="9"/>
+      <c r="X72" s="2"/>
       <c r="Y72" s="9"/>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z72" s="9"/>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -20287,10 +20588,11 @@
       <c r="U73" s="2"/>
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
-      <c r="X73" s="9"/>
+      <c r="X73" s="2"/>
       <c r="Y73" s="9"/>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z73" s="9"/>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -20314,10 +20616,11 @@
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
-      <c r="X74" s="9"/>
+      <c r="X74" s="2"/>
       <c r="Y74" s="9"/>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z74" s="9"/>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -20341,10 +20644,11 @@
       <c r="U75" s="2"/>
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
-      <c r="X75" s="9"/>
+      <c r="X75" s="2"/>
       <c r="Y75" s="9"/>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z75" s="9"/>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -20368,10 +20672,11 @@
       <c r="U76" s="2"/>
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
-      <c r="X76" s="9"/>
+      <c r="X76" s="2"/>
       <c r="Y76" s="9"/>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z76" s="9"/>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -20395,10 +20700,11 @@
       <c r="U77" s="2"/>
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
-      <c r="X77" s="9"/>
+      <c r="X77" s="2"/>
       <c r="Y77" s="9"/>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z77" s="9"/>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -20422,10 +20728,11 @@
       <c r="U78" s="2"/>
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
-      <c r="X78" s="9"/>
+      <c r="X78" s="2"/>
       <c r="Y78" s="9"/>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z78" s="9"/>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -20449,10 +20756,11 @@
       <c r="U79" s="2"/>
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
-      <c r="X79" s="9"/>
+      <c r="X79" s="2"/>
       <c r="Y79" s="9"/>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z79" s="9"/>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -20476,10 +20784,11 @@
       <c r="U80" s="2"/>
       <c r="V80" s="2"/>
       <c r="W80" s="2"/>
-      <c r="X80" s="9"/>
+      <c r="X80" s="2"/>
       <c r="Y80" s="9"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z80" s="9"/>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -20503,10 +20812,11 @@
       <c r="U81" s="2"/>
       <c r="V81" s="2"/>
       <c r="W81" s="2"/>
-      <c r="X81" s="9"/>
+      <c r="X81" s="2"/>
       <c r="Y81" s="9"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z81" s="9"/>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -20530,10 +20840,11 @@
       <c r="U82" s="2"/>
       <c r="V82" s="2"/>
       <c r="W82" s="2"/>
-      <c r="X82" s="9"/>
+      <c r="X82" s="2"/>
       <c r="Y82" s="9"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z82" s="9"/>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -20557,10 +20868,11 @@
       <c r="U83" s="2"/>
       <c r="V83" s="2"/>
       <c r="W83" s="2"/>
-      <c r="X83" s="9"/>
+      <c r="X83" s="2"/>
       <c r="Y83" s="9"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z83" s="9"/>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -20584,10 +20896,11 @@
       <c r="U84" s="2"/>
       <c r="V84" s="2"/>
       <c r="W84" s="2"/>
-      <c r="X84" s="9"/>
+      <c r="X84" s="2"/>
       <c r="Y84" s="9"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z84" s="9"/>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -20611,10 +20924,11 @@
       <c r="U85" s="2"/>
       <c r="V85" s="2"/>
       <c r="W85" s="2"/>
-      <c r="X85" s="9"/>
+      <c r="X85" s="2"/>
       <c r="Y85" s="9"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z85" s="9"/>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -20638,10 +20952,11 @@
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
       <c r="W86" s="2"/>
-      <c r="X86" s="9"/>
+      <c r="X86" s="2"/>
       <c r="Y86" s="9"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z86" s="9"/>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -20665,10 +20980,11 @@
       <c r="U87" s="2"/>
       <c r="V87" s="2"/>
       <c r="W87" s="2"/>
-      <c r="X87" s="9"/>
+      <c r="X87" s="2"/>
       <c r="Y87" s="9"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z87" s="9"/>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -20692,10 +21008,11 @@
       <c r="U88" s="2"/>
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
-      <c r="X88" s="9"/>
+      <c r="X88" s="2"/>
       <c r="Y88" s="9"/>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z88" s="9"/>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -20719,10 +21036,11 @@
       <c r="U89" s="2"/>
       <c r="V89" s="2"/>
       <c r="W89" s="2"/>
-      <c r="X89" s="9"/>
+      <c r="X89" s="2"/>
       <c r="Y89" s="9"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z89" s="9"/>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -20746,10 +21064,11 @@
       <c r="U90" s="2"/>
       <c r="V90" s="2"/>
       <c r="W90" s="2"/>
-      <c r="X90" s="9"/>
+      <c r="X90" s="2"/>
       <c r="Y90" s="9"/>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z90" s="9"/>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -20773,10 +21092,11 @@
       <c r="U91" s="2"/>
       <c r="V91" s="2"/>
       <c r="W91" s="2"/>
-      <c r="X91" s="9"/>
+      <c r="X91" s="2"/>
       <c r="Y91" s="9"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z91" s="9"/>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -20800,10 +21120,11 @@
       <c r="U92" s="2"/>
       <c r="V92" s="2"/>
       <c r="W92" s="2"/>
-      <c r="X92" s="9"/>
+      <c r="X92" s="2"/>
       <c r="Y92" s="9"/>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z92" s="9"/>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -20827,10 +21148,11 @@
       <c r="U93" s="2"/>
       <c r="V93" s="2"/>
       <c r="W93" s="2"/>
-      <c r="X93" s="9"/>
+      <c r="X93" s="2"/>
       <c r="Y93" s="9"/>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z93" s="9"/>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -20854,10 +21176,11 @@
       <c r="U94" s="2"/>
       <c r="V94" s="2"/>
       <c r="W94" s="2"/>
-      <c r="X94" s="9"/>
+      <c r="X94" s="2"/>
       <c r="Y94" s="9"/>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z94" s="9"/>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -20881,10 +21204,11 @@
       <c r="U95" s="2"/>
       <c r="V95" s="2"/>
       <c r="W95" s="2"/>
-      <c r="X95" s="9"/>
+      <c r="X95" s="2"/>
       <c r="Y95" s="9"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z95" s="9"/>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -20908,10 +21232,11 @@
       <c r="U96" s="2"/>
       <c r="V96" s="2"/>
       <c r="W96" s="2"/>
-      <c r="X96" s="9"/>
+      <c r="X96" s="2"/>
       <c r="Y96" s="9"/>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z96" s="9"/>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -20935,10 +21260,11 @@
       <c r="U97" s="2"/>
       <c r="V97" s="2"/>
       <c r="W97" s="2"/>
-      <c r="X97" s="9"/>
+      <c r="X97" s="2"/>
       <c r="Y97" s="9"/>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z97" s="9"/>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -20962,10 +21288,11 @@
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
       <c r="W98" s="2"/>
-      <c r="X98" s="9"/>
+      <c r="X98" s="2"/>
       <c r="Y98" s="9"/>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z98" s="9"/>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -20989,10 +21316,11 @@
       <c r="U99" s="2"/>
       <c r="V99" s="2"/>
       <c r="W99" s="2"/>
-      <c r="X99" s="9"/>
+      <c r="X99" s="2"/>
       <c r="Y99" s="9"/>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z99" s="9"/>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -21016,10 +21344,11 @@
       <c r="U100" s="2"/>
       <c r="V100" s="2"/>
       <c r="W100" s="2"/>
-      <c r="X100" s="9"/>
+      <c r="X100" s="2"/>
       <c r="Y100" s="9"/>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z100" s="9"/>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -21043,10 +21372,11 @@
       <c r="U101" s="2"/>
       <c r="V101" s="2"/>
       <c r="W101" s="2"/>
-      <c r="X101" s="9"/>
+      <c r="X101" s="2"/>
       <c r="Y101" s="9"/>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z101" s="9"/>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -21070,10 +21400,11 @@
       <c r="U102" s="2"/>
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
-      <c r="X102" s="9"/>
+      <c r="X102" s="2"/>
       <c r="Y102" s="9"/>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z102" s="9"/>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -21097,10 +21428,11 @@
       <c r="U103" s="2"/>
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
-      <c r="X103" s="9"/>
+      <c r="X103" s="2"/>
       <c r="Y103" s="9"/>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z103" s="9"/>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -21124,10 +21456,11 @@
       <c r="U104" s="2"/>
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
-      <c r="X104" s="9"/>
+      <c r="X104" s="2"/>
       <c r="Y104" s="9"/>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z104" s="9"/>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -21151,10 +21484,11 @@
       <c r="U105" s="2"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
-      <c r="X105" s="9"/>
+      <c r="X105" s="2"/>
       <c r="Y105" s="9"/>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z105" s="9"/>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -21178,10 +21512,11 @@
       <c r="U106" s="2"/>
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
-      <c r="X106" s="9"/>
+      <c r="X106" s="2"/>
       <c r="Y106" s="9"/>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z106" s="9"/>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -21205,10 +21540,11 @@
       <c r="U107" s="2"/>
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
-      <c r="X107" s="9"/>
+      <c r="X107" s="2"/>
       <c r="Y107" s="9"/>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z107" s="9"/>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -21232,10 +21568,11 @@
       <c r="U108" s="2"/>
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
-      <c r="X108" s="9"/>
+      <c r="X108" s="2"/>
       <c r="Y108" s="9"/>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z108" s="9"/>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -21259,10 +21596,11 @@
       <c r="U109" s="2"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
-      <c r="X109" s="9"/>
+      <c r="X109" s="2"/>
       <c r="Y109" s="9"/>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z109" s="9"/>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -21286,10 +21624,11 @@
       <c r="U110" s="2"/>
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
-      <c r="X110" s="9"/>
+      <c r="X110" s="2"/>
       <c r="Y110" s="9"/>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z110" s="9"/>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -21313,10 +21652,11 @@
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
-      <c r="X111" s="9"/>
+      <c r="X111" s="2"/>
       <c r="Y111" s="9"/>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z111" s="9"/>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -21340,10 +21680,11 @@
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
-      <c r="X112" s="9"/>
+      <c r="X112" s="2"/>
       <c r="Y112" s="9"/>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z112" s="9"/>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -21367,10 +21708,11 @@
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-      <c r="X113" s="9"/>
+      <c r="X113" s="2"/>
       <c r="Y113" s="9"/>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z113" s="9"/>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -21394,10 +21736,11 @@
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="9"/>
+      <c r="X114" s="2"/>
       <c r="Y114" s="9"/>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z114" s="9"/>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -21421,10 +21764,11 @@
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
-      <c r="X115" s="9"/>
+      <c r="X115" s="2"/>
       <c r="Y115" s="9"/>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z115" s="9"/>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -21448,10 +21792,11 @@
       <c r="U116" s="2"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
-      <c r="X116" s="9"/>
+      <c r="X116" s="2"/>
       <c r="Y116" s="9"/>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z116" s="9"/>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -21475,10 +21820,11 @@
       <c r="U117" s="2"/>
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
-      <c r="X117" s="9"/>
+      <c r="X117" s="2"/>
       <c r="Y117" s="9"/>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z117" s="9"/>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -21502,10 +21848,11 @@
       <c r="U118" s="2"/>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
-      <c r="X118" s="9"/>
+      <c r="X118" s="2"/>
       <c r="Y118" s="9"/>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z118" s="9"/>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -21529,10 +21876,11 @@
       <c r="U119" s="2"/>
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
-      <c r="X119" s="9"/>
+      <c r="X119" s="2"/>
       <c r="Y119" s="9"/>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z119" s="9"/>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -21556,10 +21904,11 @@
       <c r="U120" s="2"/>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
-      <c r="X120" s="9"/>
+      <c r="X120" s="2"/>
       <c r="Y120" s="9"/>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z120" s="9"/>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -21583,10 +21932,11 @@
       <c r="U121" s="2"/>
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
-      <c r="X121" s="9"/>
+      <c r="X121" s="2"/>
       <c r="Y121" s="9"/>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z121" s="9"/>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -21610,10 +21960,11 @@
       <c r="U122" s="2"/>
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
-      <c r="X122" s="9"/>
+      <c r="X122" s="2"/>
       <c r="Y122" s="9"/>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z122" s="9"/>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -21637,10 +21988,11 @@
       <c r="U123" s="2"/>
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
-      <c r="X123" s="9"/>
+      <c r="X123" s="2"/>
       <c r="Y123" s="9"/>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z123" s="9"/>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -21664,10 +22016,11 @@
       <c r="U124" s="2"/>
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
-      <c r="X124" s="9"/>
+      <c r="X124" s="2"/>
       <c r="Y124" s="9"/>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z124" s="9"/>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -21691,10 +22044,11 @@
       <c r="U125" s="2"/>
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
-      <c r="X125" s="9"/>
+      <c r="X125" s="2"/>
       <c r="Y125" s="9"/>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z125" s="9"/>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -21718,10 +22072,11 @@
       <c r="U126" s="2"/>
       <c r="V126" s="2"/>
       <c r="W126" s="2"/>
-      <c r="X126" s="9"/>
+      <c r="X126" s="2"/>
       <c r="Y126" s="9"/>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z126" s="9"/>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -21745,10 +22100,11 @@
       <c r="U127" s="2"/>
       <c r="V127" s="2"/>
       <c r="W127" s="2"/>
-      <c r="X127" s="9"/>
+      <c r="X127" s="2"/>
       <c r="Y127" s="9"/>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z127" s="9"/>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -21772,10 +22128,11 @@
       <c r="U128" s="2"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
-      <c r="X128" s="9"/>
+      <c r="X128" s="2"/>
       <c r="Y128" s="9"/>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z128" s="9"/>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -21799,10 +22156,11 @@
       <c r="U129" s="2"/>
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
-      <c r="X129" s="9"/>
+      <c r="X129" s="2"/>
       <c r="Y129" s="9"/>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z129" s="9"/>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -21826,10 +22184,11 @@
       <c r="U130" s="2"/>
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
-      <c r="X130" s="9"/>
+      <c r="X130" s="2"/>
       <c r="Y130" s="9"/>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z130" s="9"/>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -21853,10 +22212,11 @@
       <c r="U131" s="2"/>
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
-      <c r="X131" s="9"/>
+      <c r="X131" s="2"/>
       <c r="Y131" s="9"/>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z131" s="9"/>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -21880,10 +22240,11 @@
       <c r="U132" s="2"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-      <c r="X132" s="9"/>
+      <c r="X132" s="2"/>
       <c r="Y132" s="9"/>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z132" s="9"/>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -21907,10 +22268,11 @@
       <c r="U133" s="2"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-      <c r="X133" s="9"/>
+      <c r="X133" s="2"/>
       <c r="Y133" s="9"/>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z133" s="9"/>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -21934,10 +22296,11 @@
       <c r="U134" s="2"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-      <c r="X134" s="9"/>
+      <c r="X134" s="2"/>
       <c r="Y134" s="9"/>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z134" s="9"/>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -21961,10 +22324,11 @@
       <c r="U135" s="2"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-      <c r="X135" s="9"/>
+      <c r="X135" s="2"/>
       <c r="Y135" s="9"/>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z135" s="9"/>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -21988,10 +22352,11 @@
       <c r="U136" s="2"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-      <c r="X136" s="9"/>
+      <c r="X136" s="2"/>
       <c r="Y136" s="9"/>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z136" s="9"/>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -22015,10 +22380,11 @@
       <c r="U137" s="2"/>
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
-      <c r="X137" s="9"/>
+      <c r="X137" s="2"/>
       <c r="Y137" s="9"/>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z137" s="9"/>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -22042,10 +22408,11 @@
       <c r="U138" s="2"/>
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
-      <c r="X138" s="9"/>
+      <c r="X138" s="2"/>
       <c r="Y138" s="9"/>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z138" s="9"/>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -22069,10 +22436,11 @@
       <c r="U139" s="2"/>
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
-      <c r="X139" s="9"/>
+      <c r="X139" s="2"/>
       <c r="Y139" s="9"/>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z139" s="9"/>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -22096,10 +22464,11 @@
       <c r="U140" s="2"/>
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
-      <c r="X140" s="9"/>
+      <c r="X140" s="2"/>
       <c r="Y140" s="9"/>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z140" s="9"/>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -22123,10 +22492,11 @@
       <c r="U141" s="2"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-      <c r="X141" s="9"/>
+      <c r="X141" s="2"/>
       <c r="Y141" s="9"/>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z141" s="9"/>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -22150,10 +22520,11 @@
       <c r="U142" s="2"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-      <c r="X142" s="9"/>
+      <c r="X142" s="2"/>
       <c r="Y142" s="9"/>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z142" s="9"/>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -22177,10 +22548,11 @@
       <c r="U143" s="2"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-      <c r="X143" s="9"/>
+      <c r="X143" s="2"/>
       <c r="Y143" s="9"/>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z143" s="9"/>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -22204,10 +22576,11 @@
       <c r="U144" s="2"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-      <c r="X144" s="9"/>
+      <c r="X144" s="2"/>
       <c r="Y144" s="9"/>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z144" s="9"/>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -22231,10 +22604,11 @@
       <c r="U145" s="2"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-      <c r="X145" s="9"/>
+      <c r="X145" s="2"/>
       <c r="Y145" s="9"/>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z145" s="9"/>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -22258,10 +22632,11 @@
       <c r="U146" s="2"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-      <c r="X146" s="9"/>
+      <c r="X146" s="2"/>
       <c r="Y146" s="9"/>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z146" s="9"/>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -22285,10 +22660,11 @@
       <c r="U147" s="2"/>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
-      <c r="X147" s="9"/>
+      <c r="X147" s="2"/>
       <c r="Y147" s="9"/>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z147" s="9"/>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -22312,10 +22688,11 @@
       <c r="U148" s="2"/>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
-      <c r="X148" s="9"/>
+      <c r="X148" s="2"/>
       <c r="Y148" s="9"/>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z148" s="9"/>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -22339,10 +22716,11 @@
       <c r="U149" s="2"/>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
-      <c r="X149" s="9"/>
+      <c r="X149" s="2"/>
       <c r="Y149" s="9"/>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z149" s="9"/>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -22366,10 +22744,11 @@
       <c r="U150" s="2"/>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
-      <c r="X150" s="9"/>
+      <c r="X150" s="2"/>
       <c r="Y150" s="9"/>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z150" s="9"/>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -22393,10 +22772,11 @@
       <c r="U151" s="2"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-      <c r="X151" s="9"/>
+      <c r="X151" s="2"/>
       <c r="Y151" s="9"/>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z151" s="9"/>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -22420,10 +22800,11 @@
       <c r="U152" s="2"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-      <c r="X152" s="9"/>
+      <c r="X152" s="2"/>
       <c r="Y152" s="9"/>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z152" s="9"/>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -22447,10 +22828,11 @@
       <c r="U153" s="2"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-      <c r="X153" s="9"/>
+      <c r="X153" s="2"/>
       <c r="Y153" s="9"/>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z153" s="9"/>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -22474,10 +22856,11 @@
       <c r="U154" s="2"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-      <c r="X154" s="9"/>
+      <c r="X154" s="2"/>
       <c r="Y154" s="9"/>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z154" s="9"/>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -22501,10 +22884,11 @@
       <c r="U155" s="2"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-      <c r="X155" s="9"/>
+      <c r="X155" s="2"/>
       <c r="Y155" s="9"/>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z155" s="9"/>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -22528,10 +22912,11 @@
       <c r="U156" s="2"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-      <c r="X156" s="9"/>
+      <c r="X156" s="2"/>
       <c r="Y156" s="9"/>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z156" s="9"/>
+    </row>
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -22555,10 +22940,11 @@
       <c r="U157" s="2"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-      <c r="X157" s="9"/>
+      <c r="X157" s="2"/>
       <c r="Y157" s="9"/>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z157" s="9"/>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -22582,10 +22968,11 @@
       <c r="U158" s="2"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-      <c r="X158" s="9"/>
+      <c r="X158" s="2"/>
       <c r="Y158" s="9"/>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z158" s="9"/>
+    </row>
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -22609,10 +22996,11 @@
       <c r="U159" s="2"/>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
-      <c r="X159" s="9"/>
+      <c r="X159" s="2"/>
       <c r="Y159" s="9"/>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z159" s="9"/>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -22636,10 +23024,11 @@
       <c r="U160" s="2"/>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
-      <c r="X160" s="9"/>
+      <c r="X160" s="2"/>
       <c r="Y160" s="9"/>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z160" s="9"/>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -22663,10 +23052,11 @@
       <c r="U161" s="2"/>
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
-      <c r="X161" s="9"/>
+      <c r="X161" s="2"/>
       <c r="Y161" s="9"/>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z161" s="9"/>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -22690,10 +23080,11 @@
       <c r="U162" s="2"/>
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
-      <c r="X162" s="9"/>
+      <c r="X162" s="2"/>
       <c r="Y162" s="9"/>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z162" s="9"/>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -22717,10 +23108,11 @@
       <c r="U163" s="2"/>
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
-      <c r="X163" s="9"/>
+      <c r="X163" s="2"/>
       <c r="Y163" s="9"/>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z163" s="9"/>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -22744,10 +23136,11 @@
       <c r="U164" s="2"/>
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
-      <c r="X164" s="9"/>
+      <c r="X164" s="2"/>
       <c r="Y164" s="9"/>
-    </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z164" s="9"/>
+    </row>
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -22771,10 +23164,11 @@
       <c r="U165" s="2"/>
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
-      <c r="X165" s="9"/>
+      <c r="X165" s="2"/>
       <c r="Y165" s="9"/>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z165" s="9"/>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -22798,10 +23192,11 @@
       <c r="U166" s="2"/>
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
-      <c r="X166" s="9"/>
+      <c r="X166" s="2"/>
       <c r="Y166" s="9"/>
-    </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z166" s="9"/>
+    </row>
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -22825,10 +23220,11 @@
       <c r="U167" s="2"/>
       <c r="V167" s="2"/>
       <c r="W167" s="2"/>
-      <c r="X167" s="9"/>
+      <c r="X167" s="2"/>
       <c r="Y167" s="9"/>
-    </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z167" s="9"/>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -22852,10 +23248,11 @@
       <c r="U168" s="2"/>
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
-      <c r="X168" s="9"/>
+      <c r="X168" s="2"/>
       <c r="Y168" s="9"/>
-    </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z168" s="9"/>
+    </row>
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -22879,10 +23276,11 @@
       <c r="U169" s="2"/>
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
-      <c r="X169" s="9"/>
+      <c r="X169" s="2"/>
       <c r="Y169" s="9"/>
-    </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z169" s="9"/>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -22906,10 +23304,11 @@
       <c r="U170" s="2"/>
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
-      <c r="X170" s="9"/>
+      <c r="X170" s="2"/>
       <c r="Y170" s="9"/>
-    </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z170" s="9"/>
+    </row>
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -22933,10 +23332,11 @@
       <c r="U171" s="2"/>
       <c r="V171" s="2"/>
       <c r="W171" s="2"/>
-      <c r="X171" s="9"/>
+      <c r="X171" s="2"/>
       <c r="Y171" s="9"/>
-    </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z171" s="9"/>
+    </row>
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -22960,10 +23360,11 @@
       <c r="U172" s="2"/>
       <c r="V172" s="2"/>
       <c r="W172" s="2"/>
-      <c r="X172" s="9"/>
+      <c r="X172" s="2"/>
       <c r="Y172" s="9"/>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z172" s="9"/>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -22987,10 +23388,11 @@
       <c r="U173" s="2"/>
       <c r="V173" s="2"/>
       <c r="W173" s="2"/>
-      <c r="X173" s="9"/>
+      <c r="X173" s="2"/>
       <c r="Y173" s="9"/>
-    </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z173" s="9"/>
+    </row>
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -23014,10 +23416,11 @@
       <c r="U174" s="2"/>
       <c r="V174" s="2"/>
       <c r="W174" s="2"/>
-      <c r="X174" s="9"/>
+      <c r="X174" s="2"/>
       <c r="Y174" s="9"/>
-    </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z174" s="9"/>
+    </row>
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -23041,10 +23444,11 @@
       <c r="U175" s="2"/>
       <c r="V175" s="2"/>
       <c r="W175" s="2"/>
-      <c r="X175" s="9"/>
+      <c r="X175" s="2"/>
       <c r="Y175" s="9"/>
-    </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z175" s="9"/>
+    </row>
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -23068,10 +23472,11 @@
       <c r="U176" s="2"/>
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
-      <c r="X176" s="9"/>
+      <c r="X176" s="2"/>
       <c r="Y176" s="9"/>
-    </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z176" s="9"/>
+    </row>
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -23095,10 +23500,11 @@
       <c r="U177" s="2"/>
       <c r="V177" s="2"/>
       <c r="W177" s="2"/>
-      <c r="X177" s="9"/>
+      <c r="X177" s="2"/>
       <c r="Y177" s="9"/>
-    </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z177" s="9"/>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -23122,10 +23528,11 @@
       <c r="U178" s="2"/>
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
-      <c r="X178" s="9"/>
+      <c r="X178" s="2"/>
       <c r="Y178" s="9"/>
-    </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z178" s="9"/>
+    </row>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -23149,10 +23556,11 @@
       <c r="U179" s="2"/>
       <c r="V179" s="2"/>
       <c r="W179" s="2"/>
-      <c r="X179" s="9"/>
+      <c r="X179" s="2"/>
       <c r="Y179" s="9"/>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z179" s="9"/>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -23176,10 +23584,11 @@
       <c r="U180" s="2"/>
       <c r="V180" s="2"/>
       <c r="W180" s="2"/>
-      <c r="X180" s="9"/>
+      <c r="X180" s="2"/>
       <c r="Y180" s="9"/>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z180" s="9"/>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -23203,10 +23612,11 @@
       <c r="U181" s="2"/>
       <c r="V181" s="2"/>
       <c r="W181" s="2"/>
-      <c r="X181" s="9"/>
+      <c r="X181" s="2"/>
       <c r="Y181" s="9"/>
-    </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z181" s="9"/>
+    </row>
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -23230,10 +23640,11 @@
       <c r="U182" s="2"/>
       <c r="V182" s="2"/>
       <c r="W182" s="2"/>
-      <c r="X182" s="9"/>
+      <c r="X182" s="2"/>
       <c r="Y182" s="9"/>
-    </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z182" s="9"/>
+    </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -23257,10 +23668,11 @@
       <c r="U183" s="2"/>
       <c r="V183" s="2"/>
       <c r="W183" s="2"/>
-      <c r="X183" s="9"/>
+      <c r="X183" s="2"/>
       <c r="Y183" s="9"/>
-    </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z183" s="9"/>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -23284,10 +23696,11 @@
       <c r="U184" s="2"/>
       <c r="V184" s="2"/>
       <c r="W184" s="2"/>
-      <c r="X184" s="9"/>
+      <c r="X184" s="2"/>
       <c r="Y184" s="9"/>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z184" s="9"/>
+    </row>
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -23311,10 +23724,11 @@
       <c r="U185" s="2"/>
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
-      <c r="X185" s="9"/>
+      <c r="X185" s="2"/>
       <c r="Y185" s="9"/>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z185" s="9"/>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -23338,10 +23752,11 @@
       <c r="U186" s="2"/>
       <c r="V186" s="2"/>
       <c r="W186" s="2"/>
-      <c r="X186" s="9"/>
+      <c r="X186" s="2"/>
       <c r="Y186" s="9"/>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z186" s="9"/>
+    </row>
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -23365,10 +23780,11 @@
       <c r="U187" s="2"/>
       <c r="V187" s="2"/>
       <c r="W187" s="2"/>
-      <c r="X187" s="9"/>
+      <c r="X187" s="2"/>
       <c r="Y187" s="9"/>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z187" s="9"/>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -23392,10 +23808,11 @@
       <c r="U188" s="2"/>
       <c r="V188" s="2"/>
       <c r="W188" s="2"/>
-      <c r="X188" s="9"/>
+      <c r="X188" s="2"/>
       <c r="Y188" s="9"/>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z188" s="9"/>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -23419,10 +23836,11 @@
       <c r="U189" s="2"/>
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
-      <c r="X189" s="9"/>
+      <c r="X189" s="2"/>
       <c r="Y189" s="9"/>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z189" s="9"/>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -23446,10 +23864,11 @@
       <c r="U190" s="2"/>
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
-      <c r="X190" s="9"/>
+      <c r="X190" s="2"/>
       <c r="Y190" s="9"/>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z190" s="9"/>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -23473,10 +23892,11 @@
       <c r="U191" s="2"/>
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
-      <c r="X191" s="9"/>
+      <c r="X191" s="2"/>
       <c r="Y191" s="9"/>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z191" s="9"/>
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -23500,10 +23920,11 @@
       <c r="U192" s="2"/>
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
-      <c r="X192" s="9"/>
+      <c r="X192" s="2"/>
       <c r="Y192" s="9"/>
-    </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z192" s="9"/>
+    </row>
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -23527,10 +23948,11 @@
       <c r="U193" s="2"/>
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
-      <c r="X193" s="9"/>
+      <c r="X193" s="2"/>
       <c r="Y193" s="9"/>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z193" s="9"/>
+    </row>
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -23554,10 +23976,11 @@
       <c r="U194" s="2"/>
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
-      <c r="X194" s="9"/>
+      <c r="X194" s="2"/>
       <c r="Y194" s="9"/>
-    </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z194" s="9"/>
+    </row>
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -23581,10 +24004,11 @@
       <c r="U195" s="2"/>
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
-      <c r="X195" s="9"/>
+      <c r="X195" s="2"/>
       <c r="Y195" s="9"/>
-    </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z195" s="9"/>
+    </row>
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -23608,10 +24032,11 @@
       <c r="U196" s="2"/>
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
-      <c r="X196" s="9"/>
+      <c r="X196" s="2"/>
       <c r="Y196" s="9"/>
-    </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z196" s="9"/>
+    </row>
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -23635,10 +24060,11 @@
       <c r="U197" s="2"/>
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
-      <c r="X197" s="9"/>
+      <c r="X197" s="2"/>
       <c r="Y197" s="9"/>
-    </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z197" s="9"/>
+    </row>
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -23662,10 +24088,11 @@
       <c r="U198" s="2"/>
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
-      <c r="X198" s="9"/>
+      <c r="X198" s="2"/>
       <c r="Y198" s="9"/>
-    </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z198" s="9"/>
+    </row>
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -23689,10 +24116,11 @@
       <c r="U199" s="2"/>
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
-      <c r="X199" s="9"/>
+      <c r="X199" s="2"/>
       <c r="Y199" s="9"/>
-    </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z199" s="9"/>
+    </row>
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -23716,10 +24144,11 @@
       <c r="U200" s="2"/>
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
-      <c r="X200" s="9"/>
+      <c r="X200" s="2"/>
       <c r="Y200" s="9"/>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z200" s="9"/>
+    </row>
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -23743,10 +24172,11 @@
       <c r="U201" s="2"/>
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
-      <c r="X201" s="9"/>
+      <c r="X201" s="2"/>
       <c r="Y201" s="9"/>
-    </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z201" s="9"/>
+    </row>
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -23770,10 +24200,11 @@
       <c r="U202" s="2"/>
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
-      <c r="X202" s="9"/>
+      <c r="X202" s="2"/>
       <c r="Y202" s="9"/>
-    </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z202" s="9"/>
+    </row>
+    <row r="203" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -23797,43 +24228,46 @@
       <c r="U203" s="2"/>
       <c r="V203" s="2"/>
       <c r="W203" s="2"/>
-      <c r="X203" s="9"/>
+      <c r="X203" s="2"/>
       <c r="Y203" s="9"/>
+      <c r="Z203" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="i+NWJhJ/dANY4y8V6yR0b2FD2rG8VYPEOJeWH5E9k/YJLZu+zWXk6/2fi7RZql3z8q9ENi+0H/lJGiOCaKLA2g==" saltValue="hNILL3j2lqXU8lRHPxsxbw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="13">
+  <sheetProtection algorithmName="SHA-512" hashValue="hVjhyh6Wk8D69JCxodq4xhbeU4CAz9ZjZnEVQoy3iHuHI5mo86YANSQdqZbI0TIwIaHGFYUbI2dmaeglkcd9AQ==" saltValue="uNerv9QEFTtsW5Max7oWZQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="14">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="V2:X2"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 F2:F3 G3 I3 K3 Q3 Y3 R2:R3 E2:E3 X3 O3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3 G2:G3 H3 J3 L3 R3 Z3 S2:S3 F2:F3 Y3 P3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2:E3" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
-    <hyperlink ref="X3" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
-    <hyperlink ref="Y3" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
-    <hyperlink ref="F2:F3" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
-    <hyperlink ref="I3" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
-    <hyperlink ref="M3" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
-    <hyperlink ref="G3" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
-    <hyperlink ref="K3" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
-    <hyperlink ref="Q3" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
-    <hyperlink ref="O3" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
-    <hyperlink ref="R2:R3" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
+    <hyperlink ref="F2:F3" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
+    <hyperlink ref="Y3" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
+    <hyperlink ref="Z3" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
+    <hyperlink ref="G2:G3" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
+    <hyperlink ref="J3" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
+    <hyperlink ref="N3" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
+    <hyperlink ref="H3" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
+    <hyperlink ref="L3" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
+    <hyperlink ref="R3" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
+    <hyperlink ref="P3" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
+    <hyperlink ref="S2:S3" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
+    <hyperlink ref="E2:E3" r:id="rId12" location="allSpecies" display="SPECIES" xr:uid="{8CFAAA84-FBD1-4238-8363-C5D75B5F8A83}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23904,16 +24338,16 @@
       <c r="D2" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="97" t="s">
         <v>190</v>
       </c>
-      <c r="F2" s="112" t="s">
+      <c r="F2" s="97" t="s">
         <v>191</v>
       </c>
-      <c r="G2" s="112" t="s">
+      <c r="G2" s="97" t="s">
         <v>192</v>
       </c>
-      <c r="H2" s="110" t="s">
+      <c r="H2" s="112" t="s">
         <v>193</v>
       </c>
       <c r="I2" s="86" t="s">
@@ -23924,7 +24358,7 @@
         <v>70</v>
       </c>
       <c r="L2" s="85"/>
-      <c r="M2" s="110" t="s">
+      <c r="M2" s="112" t="s">
         <v>198</v>
       </c>
       <c r="N2" s="142" t="s">
@@ -23933,7 +24367,7 @@
       <c r="O2" s="142" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="110" t="s">
+      <c r="P2" s="112" t="s">
         <v>197</v>
       </c>
       <c r="Q2" s="142" t="s">
@@ -23952,10 +24386,10 @@
       <c r="B3" s="141"/>
       <c r="C3" s="141"/>
       <c r="D3" s="141"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="111"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="113"/>
       <c r="I3" s="50" t="s">
         <v>194</v>
       </c>
@@ -23968,10 +24402,10 @@
       <c r="L3" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="111"/>
+      <c r="M3" s="113"/>
       <c r="N3" s="89"/>
       <c r="O3" s="89"/>
-      <c r="P3" s="111"/>
+      <c r="P3" s="113"/>
       <c r="Q3" s="89"/>
       <c r="R3" s="89"/>
       <c r="S3" s="50" t="s">
@@ -28384,16 +28818,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="owrGYnA0RoV/U9MjDeglShzyfAHibWrOJ91U+dfsJvx7FpXhtP7KXYqD/XawmrJ8WUgOAZj9nC2wQr9dD2KQZw==" saltValue="h+hFQsEVq78bir+WDv8nRA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="H2:H3"/>
@@ -28401,6 +28825,16 @@
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 H2:H3 P2:P3 S3 J3 E2:E3 G2:G3 I3 M2:M3 T3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -36609,80 +37043,80 @@
       <c r="A2" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="103" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="102"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="105"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="96" t="s">
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="97"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="109" t="s">
+      <c r="H3" s="100"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="100" t="s">
+      <c r="L3" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="102"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="104"/>
+      <c r="P3" s="105"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="B4" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="110" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="F4" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="104" t="s">
+      <c r="G4" s="106" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="105" t="s">
+      <c r="H4" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="99" t="s">
+      <c r="I4" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="J4" s="110"/>
-      <c r="K4" s="112" t="s">
+      <c r="J4" s="112"/>
+      <c r="K4" s="97" t="s">
         <v>138</v>
       </c>
       <c r="L4" s="78" t="s">
@@ -36693,22 +37127,22 @@
         <v>19</v>
       </c>
       <c r="O4" s="78"/>
-      <c r="P4" s="103" t="s">
+      <c r="P4" s="96" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="88"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
       <c r="E5" s="89"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="113"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="98"/>
       <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
@@ -36721,7 +37155,7 @@
       <c r="O5" s="56" t="s">
         <v>249</v>
       </c>
-      <c r="P5" s="103"/>
+      <c r="P5" s="96"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -40326,11 +40760,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9TADddINtH3/s8+B+YSEyrbqN3sXm6gNvmsaihCGVKf7Pla3vF7K/W63Z2DPtXhM7gpZzMQTmkRfISjjfsW2DA==" saltValue="PE4zbTBOxopTV3TBfcOFrw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:P5"/>
@@ -40344,6 +40773,11 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="L3:P3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 J6 K4:K5 G4:I5 O5" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40404,20 +40838,20 @@
       <c r="A2" s="114" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="96" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103" t="s">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96" t="s">
         <v>230</v>
       </c>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
@@ -43191,27 +43625,27 @@
       <c r="A2" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="96" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="103"/>
-      <c r="T2" s="103"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
       <c r="U2" s="115" t="s">
         <v>231</v>
       </c>
@@ -43240,25 +43674,25 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
-      <c r="T3" s="103"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="96"/>
       <c r="U3" s="86"/>
       <c r="V3" s="118"/>
       <c r="W3" s="118"/>
@@ -43289,7 +43723,7 @@
       <c r="C4" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="109" t="s">
+      <c r="D4" s="111" t="s">
         <v>142</v>
       </c>
       <c r="E4" s="79" t="s">
@@ -43320,49 +43754,49 @@
         <v>27</v>
       </c>
       <c r="T4" s="79"/>
-      <c r="U4" s="103" t="s">
+      <c r="U4" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="W4" s="103" t="s">
+      <c r="W4" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="103" t="s">
+      <c r="X4" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="Y4" s="103" t="s">
+      <c r="Y4" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="Z4" s="103" t="s">
+      <c r="Z4" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="AA4" s="103" t="s">
+      <c r="AA4" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="103" t="s">
+      <c r="AB4" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="AC4" s="103" t="s">
+      <c r="AC4" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="AD4" s="103" t="s">
+      <c r="AD4" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="AE4" s="103" t="s">
+      <c r="AE4" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="AF4" s="103" t="s">
+      <c r="AF4" s="96" t="s">
         <v>144</v>
       </c>
-      <c r="AG4" s="103" t="s">
+      <c r="AG4" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="AH4" s="96" t="s">
+      <c r="AH4" s="99" t="s">
         <v>233</v>
       </c>
-      <c r="AI4" s="98"/>
+      <c r="AI4" s="101"/>
       <c r="AJ4" s="79" t="s">
         <v>234</v>
       </c>
@@ -43380,7 +43814,7 @@
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
-      <c r="D5" s="111"/>
+      <c r="D5" s="113"/>
       <c r="E5" s="41" t="s">
         <v>24</v>
       </c>
@@ -43427,19 +43861,19 @@
       <c r="T5" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103"/>
-      <c r="AD5" s="103"/>
-      <c r="AE5" s="103"/>
-      <c r="AF5" s="103"/>
-      <c r="AG5" s="103"/>
+      <c r="U5" s="96"/>
+      <c r="V5" s="96"/>
+      <c r="W5" s="96"/>
+      <c r="X5" s="96"/>
+      <c r="Y5" s="96"/>
+      <c r="Z5" s="96"/>
+      <c r="AA5" s="96"/>
+      <c r="AB5" s="96"/>
+      <c r="AC5" s="96"/>
+      <c r="AD5" s="96"/>
+      <c r="AE5" s="96"/>
+      <c r="AF5" s="96"/>
+      <c r="AG5" s="96"/>
       <c r="AH5" s="38" t="s">
         <v>153</v>
       </c>
@@ -52068,6 +52502,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NiKKXtjpQMePcsqc5jjUDaSQ7PwYr9+sjfqfZD87x0KbSUAFE8Baue/7fXFs4bMxVWpKhzgpmVEg8+jmkTDZbw==" saltValue="/cWUcVxNNlNaEWVwXWfzkw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH2:AO3"/>
     <mergeCell ref="D4:D5"/>
@@ -52084,20 +52532,6 @@
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 R5 AI5 AK5 AM5 L5 M5 N5 O5 P5 Q5 AO5 AJ5 AL5 AN5 AH5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -53433,13 +53867,13 @@
       <c r="A2" s="114" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="96" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
       <c r="G2" s="90" t="s">
         <v>222</v>
       </c>
@@ -53455,22 +53889,22 @@
       <c r="C3" s="95" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="104" t="s">
+      <c r="D3" s="106" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="103" t="s">
+      <c r="E3" s="96" t="s">
         <v>168</v>
       </c>
       <c r="F3" s="117" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="109" t="s">
+      <c r="G3" s="111" t="s">
         <v>164</v>
       </c>
-      <c r="H3" s="109" t="s">
+      <c r="H3" s="111" t="s">
         <v>165</v>
       </c>
-      <c r="I3" s="109" t="s">
+      <c r="I3" s="111" t="s">
         <v>166</v>
       </c>
       <c r="J3" s="121" t="s">
@@ -53481,12 +53915,12 @@
       <c r="A4" s="77"/>
       <c r="B4" s="89"/>
       <c r="C4" s="89"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="103"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="96"/>
       <c r="F4" s="87"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
       <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -55892,6 +56326,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="rbaELUtMLiFIUzK2Lo99z9d9U/+7pUd8ywEap5Et9u8xKeEcXwzK/YHzlDzNf0b31XcPQzpRtM0zLEm0RaQL/w==" saltValue="qBVdEFs3JSBOU1K55aehjA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
@@ -55899,11 +56338,6 @@
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 G3 H3 I3 J3" xr:uid="{17D462F2-8B43-4EF8-AF0E-D9F26228FDD4}">
@@ -59790,7 +60224,7 @@
       <c r="P2" s="88" t="s">
         <v>257</v>
       </c>
-      <c r="Q2" s="103" t="s">
+      <c r="Q2" s="96" t="s">
         <v>258</v>
       </c>
       <c r="R2" s="88" t="s">
@@ -59844,7 +60278,7 @@
       <c r="N3" s="86"/>
       <c r="O3" s="87"/>
       <c r="P3" s="88"/>
-      <c r="Q3" s="103"/>
+      <c r="Q3" s="96"/>
       <c r="R3" s="88"/>
       <c r="S3" s="88"/>
       <c r="T3" s="88"/>
@@ -59894,7 +60328,7 @@
         <v>48</v>
       </c>
       <c r="P4" s="88"/>
-      <c r="Q4" s="103"/>
+      <c r="Q4" s="96"/>
       <c r="R4" s="88"/>
       <c r="S4" s="39" t="s">
         <v>50</v>
@@ -66308,6 +66742,10 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="d21qlgp65jSu5W9pa5yJ5h6FXV3pmxRSPPtHFMi6kL/5Q045jK8F1FxQGWC8ChuBu/i/+ceDsCkP7hrPZBzfYg==" saltValue="OgP3geBPxDkKLe5cj3oUgQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="Y2:Z3"/>
@@ -66324,10 +66762,6 @@
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4 AA4:AD4" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4571AB7C-C7BF-4817-BEFF-33706CE4CC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFBF380-6918-4A5C-9BB1-FB3A63E6F38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="26505" windowHeight="14100" tabRatio="879" firstSheet="12" activeTab="15" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="810" yWindow="1245" windowWidth="26505" windowHeight="14100" tabRatio="879" firstSheet="12" activeTab="16" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1285,7 +1285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1449,6 +1449,12 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1542,8 +1548,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1553,6 +1560,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1601,10 +1611,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1702,13 +1708,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2048,24 +2054,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:8">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="73"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="12"/>
@@ -2115,15 +2121,15 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="18"/>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="72"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="19"/>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="G8" s="72"/>
+      <c r="G8" s="74"/>
       <c r="H8" s="20"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1">
@@ -2305,11 +2311,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1">
       <c r="B26" s="18"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="77"/>
       <c r="H26" s="20"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1">
@@ -3844,54 +3850,54 @@
       <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="116" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="114" t="s">
+      <c r="D2" s="116" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="95" t="s">
+      <c r="E2" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="114" t="s">
+      <c r="F2" s="116" t="s">
         <v>269</v>
       </c>
-      <c r="G2" s="114" t="s">
+      <c r="G2" s="116" t="s">
         <v>246</v>
       </c>
-      <c r="H2" s="114" t="s">
+      <c r="H2" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="114" t="s">
+      <c r="I2" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="90" t="s">
+      <c r="J2" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="K2" s="94"/>
-      <c r="L2" s="119" t="s">
+      <c r="K2" s="96"/>
+      <c r="L2" s="121" t="s">
         <v>241</v>
       </c>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="120"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="122"/>
     </row>
     <row r="3" spans="1:15" s="55" customFormat="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
       <c r="J3" s="42" t="s">
         <v>46</v>
       </c>
@@ -7313,17 +7319,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i54u068XThYDfxhseUVm7j5UOX6o6sLA/paOyFGBfnG2ueK1l9vp0KVJDHX+jDagofUZDK+i4w0EkGdmr+cm5A==" saltValue="YMFvCB9MnqWRAENMsMJcZw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3 M3 N3 O3" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7365,21 +7371,21 @@
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="119" t="s">
+      <c r="C2" s="121" t="s">
         <v>217</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="120"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="122"/>
     </row>
     <row r="3" spans="1:5" s="55" customFormat="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="56" t="s">
         <v>23</v>
       </c>
@@ -8831,22 +8837,22 @@
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="119" t="s">
+      <c r="C2" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="120"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="122"/>
     </row>
     <row r="3" spans="1:6" s="55" customFormat="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="56" t="s">
         <v>194</v>
       </c>
@@ -10526,89 +10532,89 @@
       <c r="Q1" s="6"/>
     </row>
     <row r="2" spans="1:17" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="119" t="s">
+      <c r="C2" s="121" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="119" t="s">
+      <c r="D2" s="127"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="121" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="125"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="100" t="s">
+      <c r="G2" s="127"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="96" t="s">
+      <c r="J2" s="102" t="s">
         <v>211</v>
       </c>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="88" t="s">
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="88" t="s">
+      <c r="O2" s="90" t="s">
         <v>216</v>
       </c>
-      <c r="P2" s="136" t="s">
+      <c r="P2" s="138" t="s">
         <v>272</v>
       </c>
-      <c r="Q2" s="135" t="s">
+      <c r="Q2" s="137" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="55" customFormat="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="114" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="120"/>
-      <c r="F3" s="114" t="s">
+      <c r="E3" s="122"/>
+      <c r="F3" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="119" t="s">
+      <c r="G3" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="H3" s="120"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="135"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="139"/>
+      <c r="Q3" s="137"/>
     </row>
     <row r="4" spans="1:17" s="55" customFormat="1">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
       <c r="D4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="77"/>
+      <c r="F4" s="79"/>
       <c r="G4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="100"/>
+      <c r="I4" s="103"/>
       <c r="J4" s="50" t="s">
         <v>210</v>
       </c>
@@ -10621,10 +10627,10 @@
       <c r="M4" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="135"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="140"/>
+      <c r="Q4" s="137"/>
     </row>
     <row r="5" spans="1:17" s="55" customFormat="1">
       <c r="A5" s="2"/>
@@ -14429,6 +14435,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="dlFj2sPqiSv9eFeao1SBDLarE133CE5VD8yNCCeOHNQfNXNZi7oFUlGnOiN0L8Mfj1AOHWL4yBs29kJ5VkLUsg==" saltValue="J7Ti7XS+RGy13SKXPsV6rA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="F2:H2"/>
@@ -14438,11 +14449,6 @@
     <mergeCell ref="J2:M3"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="P2:P4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4 M4 J4 K4 L4 Q2:Q4" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14484,20 +14490,20 @@
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="94"/>
+      <c r="D2" s="96"/>
     </row>
     <row r="3" spans="1:4" s="55" customFormat="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="42" t="s">
         <v>161</v>
       </c>
@@ -15721,21 +15727,22 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
+    <col min="5" max="6" width="10.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21">
+    <row r="1" spans="1:11" ht="21">
       <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
@@ -15747,69 +15754,75 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" spans="1:10" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:11" s="55" customFormat="1">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="141" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="140"/>
-      <c r="F2" s="135" t="s">
+      <c r="F2" s="142"/>
+      <c r="G2" s="137" t="s">
         <v>200</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="H2" s="90" t="s">
         <v>226</v>
       </c>
-      <c r="H2" s="115" t="s">
+      <c r="I2" s="117" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="116"/>
-      <c r="J2" s="117"/>
-    </row>
-    <row r="3" spans="1:10" s="55" customFormat="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="87"/>
-    </row>
-    <row r="4" spans="1:10" s="55" customFormat="1">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="56" t="s">
+      <c r="J2" s="118"/>
+      <c r="K2" s="119"/>
+    </row>
+    <row r="3" spans="1:11" s="55" customFormat="1">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="149" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="143"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="89"/>
+    </row>
+    <row r="4" spans="1:11" s="55" customFormat="1">
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="F4" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="135"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="50" t="s">
+      <c r="G4" s="137"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="J4" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="50" t="s">
+      <c r="K4" s="50" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="55" customFormat="1">
+    <row r="5" spans="1:11" s="55" customFormat="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -15820,8 +15833,9 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -15832,8 +15846,9 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -15844,8 +15859,9 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -15856,8 +15872,9 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -15868,8 +15885,9 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -15880,8 +15898,9 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -15892,8 +15911,9 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -15904,8 +15924,9 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -15916,8 +15937,9 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -15928,8 +15950,9 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -15940,8 +15963,9 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -15952,8 +15976,9 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -15964,8 +15989,9 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -15976,8 +16002,9 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -15988,8 +16015,9 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -16000,8 +16028,9 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -16012,8 +16041,9 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -16024,8 +16054,9 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -16036,8 +16067,9 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -16048,8 +16080,9 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -16060,8 +16093,9 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -16072,8 +16106,9 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -16084,8 +16119,9 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -16096,8 +16132,9 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -16108,8 +16145,9 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -16120,8 +16158,9 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -16132,8 +16171,9 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -16144,8 +16184,9 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -16156,8 +16197,9 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -16168,8 +16210,9 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -16180,8 +16223,9 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -16192,8 +16236,9 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -16204,8 +16249,9 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -16216,8 +16262,9 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -16228,8 +16275,9 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -16240,8 +16288,9 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -16252,8 +16301,9 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -16264,8 +16314,9 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -16276,8 +16327,9 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -16288,8 +16340,9 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -16300,8 +16353,9 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10">
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -16312,8 +16366,9 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10">
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -16324,8 +16379,9 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -16336,8 +16392,9 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10">
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -16348,8 +16405,9 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10">
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -16360,8 +16418,9 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10">
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -16372,8 +16431,9 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -16384,8 +16444,9 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -16396,8 +16457,9 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -16408,8 +16470,9 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:10">
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -16420,8 +16483,9 @@
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="1:10">
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -16432,8 +16496,9 @@
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="1:10">
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -16444,8 +16509,9 @@
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
-    </row>
-    <row r="58" spans="1:10">
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -16456,8 +16522,9 @@
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-    </row>
-    <row r="59" spans="1:10">
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -16468,8 +16535,9 @@
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
-    </row>
-    <row r="60" spans="1:10">
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -16480,8 +16548,9 @@
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="1:10">
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -16492,8 +16561,9 @@
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
-    </row>
-    <row r="62" spans="1:10">
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -16504,8 +16574,9 @@
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="1:10">
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -16516,8 +16587,9 @@
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-    </row>
-    <row r="64" spans="1:10">
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -16528,8 +16600,9 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-    </row>
-    <row r="65" spans="1:10">
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -16540,8 +16613,9 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-    </row>
-    <row r="66" spans="1:10">
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -16552,8 +16626,9 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="1:10">
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -16564,8 +16639,9 @@
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -16576,8 +16652,9 @@
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -16588,8 +16665,9 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -16600,8 +16678,9 @@
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10">
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -16612,8 +16691,9 @@
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="1:10">
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -16624,8 +16704,9 @@
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -16636,8 +16717,9 @@
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="1:10">
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -16648,8 +16730,9 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -16660,8 +16743,9 @@
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
-    </row>
-    <row r="76" spans="1:10">
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -16672,8 +16756,9 @@
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="1:10">
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -16684,8 +16769,9 @@
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -16696,8 +16782,9 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
-    </row>
-    <row r="79" spans="1:10">
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -16708,8 +16795,9 @@
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="K79" s="2"/>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -16720,8 +16808,9 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="1:10">
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -16732,8 +16821,9 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
-    </row>
-    <row r="82" spans="1:10">
+      <c r="K81" s="2"/>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -16744,8 +16834,9 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="1:10">
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -16756,8 +16847,9 @@
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
-    </row>
-    <row r="84" spans="1:10">
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -16768,8 +16860,9 @@
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="1:10">
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -16780,8 +16873,9 @@
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
-    </row>
-    <row r="86" spans="1:10">
+      <c r="K85" s="2"/>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -16792,8 +16886,9 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="1:10">
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -16804,8 +16899,9 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
-    </row>
-    <row r="88" spans="1:10">
+      <c r="K87" s="2"/>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -16816,8 +16912,9 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="1:10">
+      <c r="K88" s="2"/>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -16828,8 +16925,9 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
-    </row>
-    <row r="90" spans="1:10">
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -16840,8 +16938,9 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
-    </row>
-    <row r="91" spans="1:10">
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -16852,8 +16951,9 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
-    </row>
-    <row r="92" spans="1:10">
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -16864,8 +16964,9 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
-    </row>
-    <row r="93" spans="1:10">
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -16876,8 +16977,9 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
-    </row>
-    <row r="94" spans="1:10">
+      <c r="K93" s="2"/>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -16888,8 +16990,9 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="1:10">
+      <c r="K94" s="2"/>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -16900,8 +17003,9 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
-    </row>
-    <row r="96" spans="1:10">
+      <c r="K95" s="2"/>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -16912,8 +17016,9 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="1:10">
+      <c r="K96" s="2"/>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -16924,8 +17029,9 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
-    </row>
-    <row r="98" spans="1:10">
+      <c r="K97" s="2"/>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -16936,8 +17042,9 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-    </row>
-    <row r="99" spans="1:10">
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -16948,8 +17055,9 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-    </row>
-    <row r="100" spans="1:10">
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -16960,8 +17068,9 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-    </row>
-    <row r="101" spans="1:10">
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -16972,8 +17081,9 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
-    </row>
-    <row r="102" spans="1:10">
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -16984,8 +17094,9 @@
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="1:10">
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -16996,8 +17107,9 @@
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
-    </row>
-    <row r="104" spans="1:10">
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -17008,8 +17120,9 @@
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-    </row>
-    <row r="105" spans="1:10">
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -17020,8 +17133,9 @@
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
-    </row>
-    <row r="106" spans="1:10">
+      <c r="K105" s="2"/>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -17032,8 +17146,9 @@
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
-    </row>
-    <row r="107" spans="1:10">
+      <c r="K106" s="2"/>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -17044,8 +17159,9 @@
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
-    </row>
-    <row r="108" spans="1:10">
+      <c r="K107" s="2"/>
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -17056,8 +17172,9 @@
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
-    </row>
-    <row r="109" spans="1:10">
+      <c r="K108" s="2"/>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -17068,8 +17185,9 @@
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
-    </row>
-    <row r="110" spans="1:10">
+      <c r="K109" s="2"/>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -17080,8 +17198,9 @@
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
-    </row>
-    <row r="111" spans="1:10">
+      <c r="K110" s="2"/>
+    </row>
+    <row r="111" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -17092,8 +17211,9 @@
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
-    </row>
-    <row r="112" spans="1:10">
+      <c r="K111" s="2"/>
+    </row>
+    <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -17104,8 +17224,9 @@
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
-    </row>
-    <row r="113" spans="1:10">
+      <c r="K112" s="2"/>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -17116,8 +17237,9 @@
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
-    </row>
-    <row r="114" spans="1:10">
+      <c r="K113" s="2"/>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -17128,8 +17250,9 @@
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
-    </row>
-    <row r="115" spans="1:10">
+      <c r="K114" s="2"/>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -17140,8 +17263,9 @@
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
-    </row>
-    <row r="116" spans="1:10">
+      <c r="K115" s="2"/>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -17152,8 +17276,9 @@
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
-    </row>
-    <row r="117" spans="1:10">
+      <c r="K116" s="2"/>
+    </row>
+    <row r="117" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -17164,8 +17289,9 @@
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
-    </row>
-    <row r="118" spans="1:10">
+      <c r="K117" s="2"/>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -17176,8 +17302,9 @@
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
-    </row>
-    <row r="119" spans="1:10">
+      <c r="K118" s="2"/>
+    </row>
+    <row r="119" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -17188,8 +17315,9 @@
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
-    </row>
-    <row r="120" spans="1:10">
+      <c r="K119" s="2"/>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -17200,8 +17328,9 @@
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
-    </row>
-    <row r="121" spans="1:10">
+      <c r="K120" s="2"/>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -17212,8 +17341,9 @@
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
-    </row>
-    <row r="122" spans="1:10">
+      <c r="K121" s="2"/>
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -17224,8 +17354,9 @@
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
-    </row>
-    <row r="123" spans="1:10">
+      <c r="K122" s="2"/>
+    </row>
+    <row r="123" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -17236,8 +17367,9 @@
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
-    </row>
-    <row r="124" spans="1:10">
+      <c r="K123" s="2"/>
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -17248,8 +17380,9 @@
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
-    </row>
-    <row r="125" spans="1:10">
+      <c r="K124" s="2"/>
+    </row>
+    <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -17260,8 +17393,9 @@
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
-    </row>
-    <row r="126" spans="1:10">
+      <c r="K125" s="2"/>
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -17272,8 +17406,9 @@
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
-    </row>
-    <row r="127" spans="1:10">
+      <c r="K126" s="2"/>
+    </row>
+    <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -17284,8 +17419,9 @@
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
-    </row>
-    <row r="128" spans="1:10">
+      <c r="K127" s="2"/>
+    </row>
+    <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -17296,8 +17432,9 @@
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
-    </row>
-    <row r="129" spans="1:10">
+      <c r="K128" s="2"/>
+    </row>
+    <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -17308,8 +17445,9 @@
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
-    </row>
-    <row r="130" spans="1:10">
+      <c r="K129" s="2"/>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -17320,8 +17458,9 @@
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
-    </row>
-    <row r="131" spans="1:10">
+      <c r="K130" s="2"/>
+    </row>
+    <row r="131" spans="1:11">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -17332,8 +17471,9 @@
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
-    </row>
-    <row r="132" spans="1:10">
+      <c r="K131" s="2"/>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -17344,8 +17484,9 @@
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
-    </row>
-    <row r="133" spans="1:10">
+      <c r="K132" s="2"/>
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -17356,8 +17497,9 @@
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
-    </row>
-    <row r="134" spans="1:10">
+      <c r="K133" s="2"/>
+    </row>
+    <row r="134" spans="1:11">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -17368,8 +17510,9 @@
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
-    </row>
-    <row r="135" spans="1:10">
+      <c r="K134" s="2"/>
+    </row>
+    <row r="135" spans="1:11">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -17380,8 +17523,9 @@
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
-    </row>
-    <row r="136" spans="1:10">
+      <c r="K135" s="2"/>
+    </row>
+    <row r="136" spans="1:11">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -17392,8 +17536,9 @@
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
-    </row>
-    <row r="137" spans="1:10">
+      <c r="K136" s="2"/>
+    </row>
+    <row r="137" spans="1:11">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -17404,8 +17549,9 @@
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
-    </row>
-    <row r="138" spans="1:10">
+      <c r="K137" s="2"/>
+    </row>
+    <row r="138" spans="1:11">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -17416,8 +17562,9 @@
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
-    </row>
-    <row r="139" spans="1:10">
+      <c r="K138" s="2"/>
+    </row>
+    <row r="139" spans="1:11">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -17428,8 +17575,9 @@
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
-    </row>
-    <row r="140" spans="1:10">
+      <c r="K139" s="2"/>
+    </row>
+    <row r="140" spans="1:11">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -17440,8 +17588,9 @@
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
-    </row>
-    <row r="141" spans="1:10">
+      <c r="K140" s="2"/>
+    </row>
+    <row r="141" spans="1:11">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -17452,8 +17601,9 @@
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
-    </row>
-    <row r="142" spans="1:10">
+      <c r="K141" s="2"/>
+    </row>
+    <row r="142" spans="1:11">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -17464,8 +17614,9 @@
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
-    </row>
-    <row r="143" spans="1:10">
+      <c r="K142" s="2"/>
+    </row>
+    <row r="143" spans="1:11">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -17476,8 +17627,9 @@
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
-    </row>
-    <row r="144" spans="1:10">
+      <c r="K143" s="2"/>
+    </row>
+    <row r="144" spans="1:11">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -17488,8 +17640,9 @@
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
-    </row>
-    <row r="145" spans="1:10">
+      <c r="K144" s="2"/>
+    </row>
+    <row r="145" spans="1:11">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -17500,8 +17653,9 @@
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
-    </row>
-    <row r="146" spans="1:10">
+      <c r="K145" s="2"/>
+    </row>
+    <row r="146" spans="1:11">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -17512,8 +17666,9 @@
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
-    </row>
-    <row r="147" spans="1:10">
+      <c r="K146" s="2"/>
+    </row>
+    <row r="147" spans="1:11">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -17524,8 +17679,9 @@
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
-    </row>
-    <row r="148" spans="1:10">
+      <c r="K147" s="2"/>
+    </row>
+    <row r="148" spans="1:11">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -17536,8 +17692,9 @@
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
-    </row>
-    <row r="149" spans="1:10">
+      <c r="K148" s="2"/>
+    </row>
+    <row r="149" spans="1:11">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -17548,8 +17705,9 @@
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
-    </row>
-    <row r="150" spans="1:10">
+      <c r="K149" s="2"/>
+    </row>
+    <row r="150" spans="1:11">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -17560,8 +17718,9 @@
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
-    </row>
-    <row r="151" spans="1:10">
+      <c r="K150" s="2"/>
+    </row>
+    <row r="151" spans="1:11">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -17572,8 +17731,9 @@
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
-    </row>
-    <row r="152" spans="1:10">
+      <c r="K151" s="2"/>
+    </row>
+    <row r="152" spans="1:11">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -17584,8 +17744,9 @@
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
-    </row>
-    <row r="153" spans="1:10">
+      <c r="K152" s="2"/>
+    </row>
+    <row r="153" spans="1:11">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -17596,8 +17757,9 @@
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
-    </row>
-    <row r="154" spans="1:10">
+      <c r="K153" s="2"/>
+    </row>
+    <row r="154" spans="1:11">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -17608,8 +17770,9 @@
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
-    </row>
-    <row r="155" spans="1:10">
+      <c r="K154" s="2"/>
+    </row>
+    <row r="155" spans="1:11">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -17620,8 +17783,9 @@
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
-    </row>
-    <row r="156" spans="1:10">
+      <c r="K155" s="2"/>
+    </row>
+    <row r="156" spans="1:11">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -17632,8 +17796,9 @@
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
-    </row>
-    <row r="157" spans="1:10">
+      <c r="K156" s="2"/>
+    </row>
+    <row r="157" spans="1:11">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -17644,8 +17809,9 @@
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
-    </row>
-    <row r="158" spans="1:10">
+      <c r="K157" s="2"/>
+    </row>
+    <row r="158" spans="1:11">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -17656,8 +17822,9 @@
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
-    </row>
-    <row r="159" spans="1:10">
+      <c r="K158" s="2"/>
+    </row>
+    <row r="159" spans="1:11">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -17668,8 +17835,9 @@
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
-    </row>
-    <row r="160" spans="1:10">
+      <c r="K159" s="2"/>
+    </row>
+    <row r="160" spans="1:11">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -17680,8 +17848,9 @@
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
-    </row>
-    <row r="161" spans="1:10">
+      <c r="K160" s="2"/>
+    </row>
+    <row r="161" spans="1:11">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -17692,8 +17861,9 @@
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
-    </row>
-    <row r="162" spans="1:10">
+      <c r="K161" s="2"/>
+    </row>
+    <row r="162" spans="1:11">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -17704,8 +17874,9 @@
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
-    </row>
-    <row r="163" spans="1:10">
+      <c r="K162" s="2"/>
+    </row>
+    <row r="163" spans="1:11">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -17716,8 +17887,9 @@
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
-    </row>
-    <row r="164" spans="1:10">
+      <c r="K163" s="2"/>
+    </row>
+    <row r="164" spans="1:11">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -17728,8 +17900,9 @@
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
-    </row>
-    <row r="165" spans="1:10">
+      <c r="K164" s="2"/>
+    </row>
+    <row r="165" spans="1:11">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -17740,8 +17913,9 @@
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
-    </row>
-    <row r="166" spans="1:10">
+      <c r="K165" s="2"/>
+    </row>
+    <row r="166" spans="1:11">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -17752,8 +17926,9 @@
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
-    </row>
-    <row r="167" spans="1:10">
+      <c r="K166" s="2"/>
+    </row>
+    <row r="167" spans="1:11">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -17764,8 +17939,9 @@
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
-    </row>
-    <row r="168" spans="1:10">
+      <c r="K167" s="2"/>
+    </row>
+    <row r="168" spans="1:11">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -17776,8 +17952,9 @@
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
-    </row>
-    <row r="169" spans="1:10">
+      <c r="K168" s="2"/>
+    </row>
+    <row r="169" spans="1:11">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -17788,8 +17965,9 @@
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
-    </row>
-    <row r="170" spans="1:10">
+      <c r="K169" s="2"/>
+    </row>
+    <row r="170" spans="1:11">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -17800,8 +17978,9 @@
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
-    </row>
-    <row r="171" spans="1:10">
+      <c r="K170" s="2"/>
+    </row>
+    <row r="171" spans="1:11">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -17812,8 +17991,9 @@
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
-    </row>
-    <row r="172" spans="1:10">
+      <c r="K171" s="2"/>
+    </row>
+    <row r="172" spans="1:11">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -17824,8 +18004,9 @@
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
-    </row>
-    <row r="173" spans="1:10">
+      <c r="K172" s="2"/>
+    </row>
+    <row r="173" spans="1:11">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -17836,8 +18017,9 @@
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
-    </row>
-    <row r="174" spans="1:10">
+      <c r="K173" s="2"/>
+    </row>
+    <row r="174" spans="1:11">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -17848,8 +18030,9 @@
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
-    </row>
-    <row r="175" spans="1:10">
+      <c r="K174" s="2"/>
+    </row>
+    <row r="175" spans="1:11">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -17860,8 +18043,9 @@
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
-    </row>
-    <row r="176" spans="1:10">
+      <c r="K175" s="2"/>
+    </row>
+    <row r="176" spans="1:11">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -17872,8 +18056,9 @@
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
-    </row>
-    <row r="177" spans="1:10">
+      <c r="K176" s="2"/>
+    </row>
+    <row r="177" spans="1:11">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -17884,8 +18069,9 @@
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
-    </row>
-    <row r="178" spans="1:10">
+      <c r="K177" s="2"/>
+    </row>
+    <row r="178" spans="1:11">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -17896,8 +18082,9 @@
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
-    </row>
-    <row r="179" spans="1:10">
+      <c r="K178" s="2"/>
+    </row>
+    <row r="179" spans="1:11">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -17908,8 +18095,9 @@
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
-    </row>
-    <row r="180" spans="1:10">
+      <c r="K179" s="2"/>
+    </row>
+    <row r="180" spans="1:11">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -17920,8 +18108,9 @@
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
-    </row>
-    <row r="181" spans="1:10">
+      <c r="K180" s="2"/>
+    </row>
+    <row r="181" spans="1:11">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -17932,8 +18121,9 @@
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
-    </row>
-    <row r="182" spans="1:10">
+      <c r="K181" s="2"/>
+    </row>
+    <row r="182" spans="1:11">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -17944,8 +18134,9 @@
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
-    </row>
-    <row r="183" spans="1:10">
+      <c r="K182" s="2"/>
+    </row>
+    <row r="183" spans="1:11">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -17956,8 +18147,9 @@
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
-    </row>
-    <row r="184" spans="1:10">
+      <c r="K183" s="2"/>
+    </row>
+    <row r="184" spans="1:11">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -17968,8 +18160,9 @@
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
-    </row>
-    <row r="185" spans="1:10">
+      <c r="K184" s="2"/>
+    </row>
+    <row r="185" spans="1:11">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -17980,8 +18173,9 @@
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
-    </row>
-    <row r="186" spans="1:10">
+      <c r="K185" s="2"/>
+    </row>
+    <row r="186" spans="1:11">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -17992,8 +18186,9 @@
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
-    </row>
-    <row r="187" spans="1:10">
+      <c r="K186" s="2"/>
+    </row>
+    <row r="187" spans="1:11">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -18004,8 +18199,9 @@
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
-    </row>
-    <row r="188" spans="1:10">
+      <c r="K187" s="2"/>
+    </row>
+    <row r="188" spans="1:11">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -18016,8 +18212,9 @@
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
-    </row>
-    <row r="189" spans="1:10">
+      <c r="K188" s="2"/>
+    </row>
+    <row r="189" spans="1:11">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -18028,8 +18225,9 @@
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
-    </row>
-    <row r="190" spans="1:10">
+      <c r="K189" s="2"/>
+    </row>
+    <row r="190" spans="1:11">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -18040,8 +18238,9 @@
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
-    </row>
-    <row r="191" spans="1:10">
+      <c r="K190" s="2"/>
+    </row>
+    <row r="191" spans="1:11">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -18052,8 +18251,9 @@
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
-    </row>
-    <row r="192" spans="1:10">
+      <c r="K191" s="2"/>
+    </row>
+    <row r="192" spans="1:11">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -18064,8 +18264,9 @@
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
-    </row>
-    <row r="193" spans="1:10">
+      <c r="K192" s="2"/>
+    </row>
+    <row r="193" spans="1:11">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -18076,8 +18277,9 @@
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
-    </row>
-    <row r="194" spans="1:10">
+      <c r="K193" s="2"/>
+    </row>
+    <row r="194" spans="1:11">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -18088,8 +18290,9 @@
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
-    </row>
-    <row r="195" spans="1:10">
+      <c r="K194" s="2"/>
+    </row>
+    <row r="195" spans="1:11">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -18100,8 +18303,9 @@
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
-    </row>
-    <row r="196" spans="1:10">
+      <c r="K195" s="2"/>
+    </row>
+    <row r="196" spans="1:11">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -18112,8 +18316,9 @@
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
-    </row>
-    <row r="197" spans="1:10">
+      <c r="K196" s="2"/>
+    </row>
+    <row r="197" spans="1:11">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -18124,8 +18329,9 @@
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
-    </row>
-    <row r="198" spans="1:10">
+      <c r="K197" s="2"/>
+    </row>
+    <row r="198" spans="1:11">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -18136,8 +18342,9 @@
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
-    </row>
-    <row r="199" spans="1:10">
+      <c r="K198" s="2"/>
+    </row>
+    <row r="199" spans="1:11">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -18148,8 +18355,9 @@
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
-    </row>
-    <row r="200" spans="1:10">
+      <c r="K199" s="2"/>
+    </row>
+    <row r="200" spans="1:11">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -18160,8 +18368,9 @@
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
       <c r="J200" s="2"/>
-    </row>
-    <row r="201" spans="1:10">
+      <c r="K200" s="2"/>
+    </row>
+    <row r="201" spans="1:11">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -18172,8 +18381,9 @@
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
-    </row>
-    <row r="202" spans="1:10">
+      <c r="K201" s="2"/>
+    </row>
+    <row r="202" spans="1:11">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -18184,8 +18394,9 @@
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
-    </row>
-    <row r="203" spans="1:10">
+      <c r="K202" s="2"/>
+    </row>
+    <row r="203" spans="1:11">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -18196,8 +18407,9 @@
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
       <c r="J203" s="2"/>
-    </row>
-    <row r="204" spans="1:10">
+      <c r="K203" s="2"/>
+    </row>
+    <row r="204" spans="1:11">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -18208,32 +18420,34 @@
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
+      <c r="K204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cGFJ3cNieSbmGqOBbQvt+1M42j6UcXRyZ+l5X5PaCApLjlQQyeHoKCAcW/GZJWbdin9gX38HoTYP7JxDzhDHZg==" saltValue="ZIjI9ANvQEPQ04AVZVe9kw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+A1C/7WKviaQdLXEd0Jzz7hwYXOum2bfBHSKtfrwzq0kCnq7DQAfa9DPmuwgtBVwHvHIVVKstVUCn7UrK5h1IA==" saltValue="gNFG7M1us7NZepkY37n6xQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="H2:J3"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="G2:G4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="E2:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4 F2:F4 E4 D4 J4" xr:uid="{4E0B6771-5993-41A9-BE9D-F553134C1037}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4 G2:G4 F4 E4 K4" xr:uid="{4E0B6771-5993-41A9-BE9D-F553134C1037}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H4" r:id="rId1" location="weightMeasurements" xr:uid="{779410D5-0433-4C34-84B6-98A10CA2B249}"/>
-    <hyperlink ref="J4" r:id="rId2" location="weightMeasurementTools" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
-    <hyperlink ref="F2:F4" r:id="rId3" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{6D1D8620-4A5B-4D09-B9FB-01FDEF4F969A}"/>
-    <hyperlink ref="D4" r:id="rId4" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
-    <hyperlink ref="E4" r:id="rId5" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
+    <hyperlink ref="I4" r:id="rId1" location="weightMeasurements" xr:uid="{779410D5-0433-4C34-84B6-98A10CA2B249}"/>
+    <hyperlink ref="K4" r:id="rId2" location="weightMeasurementTools" xr:uid="{EB80831C-DDCE-4E4D-A605-160D23E19E90}"/>
+    <hyperlink ref="G2:G4" r:id="rId3" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{6D1D8620-4A5B-4D09-B9FB-01FDEF4F969A}"/>
+    <hyperlink ref="E4" r:id="rId4" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
+    <hyperlink ref="F4" r:id="rId5" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
+    <hyperlink ref="D3" r:id="rId6" location="allSpecies" xr:uid="{7915C09B-5FFF-4B7E-84FB-D8B7D31EA643}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -18242,38 +18456,37 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Z203"/>
+  <dimension ref="A1:Y203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.85546875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" style="3"/>
-    <col min="20" max="20" width="14.5703125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="3" customWidth="1"/>
-    <col min="22" max="22" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="23.5703125" style="3" customWidth="1"/>
-    <col min="25" max="25" width="30.7109375" customWidth="1"/>
-    <col min="26" max="26" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="3"/>
+    <col min="19" max="19" width="14.5703125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="3" customWidth="1"/>
+    <col min="21" max="21" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.5703125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="30.7109375" customWidth="1"/>
+    <col min="25" max="25" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21">
+    <row r="1" spans="1:25" ht="21">
       <c r="A1" s="4" t="s">
         <v>85</v>
       </c>
@@ -18300,130 +18513,125 @@
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="6"/>
-    </row>
-    <row r="2" spans="1:26" s="55" customFormat="1">
-      <c r="A2" s="143" t="s">
+      <c r="Y1" s="6"/>
+    </row>
+    <row r="2" spans="1:25" s="55" customFormat="1">
+      <c r="A2" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="145" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="143" t="s">
+      <c r="C2" s="145" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="143" t="s">
+      <c r="D2" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="145" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="108" t="s">
+      <c r="E2" s="111" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="108" t="s">
+      <c r="F2" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="88" t="s">
+      <c r="G2" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="96" t="s">
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="102" t="s">
         <v>205</v>
       </c>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96" t="s">
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-      <c r="S2" s="105" t="s">
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="90" t="s">
+      <c r="S2" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="U2" s="94"/>
-      <c r="V2" s="90" t="s">
+      <c r="T2" s="96"/>
+      <c r="U2" s="92" t="s">
         <v>208</v>
       </c>
-      <c r="W2" s="91"/>
-      <c r="X2" s="94"/>
-      <c r="Y2" s="96" t="s">
+      <c r="V2" s="93"/>
+      <c r="W2" s="96"/>
+      <c r="X2" s="102" t="s">
         <v>207</v>
       </c>
-      <c r="Z2" s="96"/>
-    </row>
-    <row r="3" spans="1:26" s="55" customFormat="1">
-      <c r="A3" s="144"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="56" t="s">
+      <c r="Y2" s="102"/>
+    </row>
+    <row r="3" spans="1:25" s="55" customFormat="1">
+      <c r="A3" s="146"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="H3" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="I3" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="J3" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="K3" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="L3" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="N3" s="50" t="s">
+      <c r="M3" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="O3" s="42" t="s">
+      <c r="N3" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="O3" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="Q3" s="42" t="s">
+      <c r="P3" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="R3" s="50" t="s">
+      <c r="Q3" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="S3" s="107"/>
-      <c r="T3" s="43" t="s">
+      <c r="R3" s="110"/>
+      <c r="S3" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="U3" s="43" t="s">
+      <c r="T3" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="V3" s="59" t="s">
+      <c r="U3" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="W3" s="42" t="s">
+      <c r="V3" s="148" t="s">
         <v>62</v>
       </c>
-      <c r="X3" s="42" t="s">
+      <c r="W3" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="Y3" s="50" t="s">
+      <c r="X3" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="Z3" s="50" t="s">
+      <c r="Y3" s="50" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="55" customFormat="1">
+    <row r="4" spans="1:25" s="55" customFormat="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -18447,11 +18655,10 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
+      <c r="X4" s="9"/>
       <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-    </row>
-    <row r="5" spans="1:26">
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -18475,11 +18682,10 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
+      <c r="X5" s="9"/>
       <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-    </row>
-    <row r="6" spans="1:26">
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -18503,11 +18709,10 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
+      <c r="X6" s="9"/>
       <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-    </row>
-    <row r="7" spans="1:26">
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -18531,11 +18736,10 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
+      <c r="X7" s="9"/>
       <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-    </row>
-    <row r="8" spans="1:26">
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -18559,11 +18763,10 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
+      <c r="X8" s="9"/>
       <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-    </row>
-    <row r="9" spans="1:26">
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -18587,11 +18790,10 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
+      <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-    </row>
-    <row r="10" spans="1:26">
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -18615,11 +18817,10 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
+      <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-    </row>
-    <row r="11" spans="1:26">
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -18643,11 +18844,10 @@
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
+      <c r="X11" s="9"/>
       <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-    </row>
-    <row r="12" spans="1:26">
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -18671,11 +18871,10 @@
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
+      <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-    </row>
-    <row r="13" spans="1:26">
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -18699,11 +18898,10 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
+      <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-    </row>
-    <row r="14" spans="1:26">
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -18727,11 +18925,10 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
+      <c r="X14" s="9"/>
       <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-    </row>
-    <row r="15" spans="1:26">
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -18755,11 +18952,10 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
+      <c r="X15" s="9"/>
       <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-    </row>
-    <row r="16" spans="1:26">
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -18783,11 +18979,10 @@
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
+      <c r="X16" s="9"/>
       <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-    </row>
-    <row r="17" spans="1:26">
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -18811,11 +19006,10 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
+      <c r="X17" s="9"/>
       <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
-    </row>
-    <row r="18" spans="1:26">
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -18839,11 +19033,10 @@
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
+      <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-    </row>
-    <row r="19" spans="1:26">
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -18867,11 +19060,10 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
+      <c r="X19" s="9"/>
       <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-    </row>
-    <row r="20" spans="1:26">
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -18895,11 +19087,10 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
+      <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-    </row>
-    <row r="21" spans="1:26">
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -18923,11 +19114,10 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
+      <c r="X21" s="9"/>
       <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
-    </row>
-    <row r="22" spans="1:26">
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -18951,11 +19141,10 @@
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
+      <c r="X22" s="9"/>
       <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-    </row>
-    <row r="23" spans="1:26">
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -18979,11 +19168,10 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
+      <c r="X23" s="9"/>
       <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-    </row>
-    <row r="24" spans="1:26">
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -19007,11 +19195,10 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
+      <c r="X24" s="9"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
-    </row>
-    <row r="25" spans="1:26">
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -19035,11 +19222,10 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
+      <c r="X25" s="9"/>
       <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-    </row>
-    <row r="26" spans="1:26">
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -19063,11 +19249,10 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
+      <c r="X26" s="9"/>
       <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-    </row>
-    <row r="27" spans="1:26">
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -19091,11 +19276,10 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
+      <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-    </row>
-    <row r="28" spans="1:26">
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -19119,11 +19303,10 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
+      <c r="X28" s="9"/>
       <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-    </row>
-    <row r="29" spans="1:26">
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -19147,11 +19330,10 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
+      <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
-      <c r="Z29" s="9"/>
-    </row>
-    <row r="30" spans="1:26">
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -19175,11 +19357,10 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
+      <c r="X30" s="9"/>
       <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-    </row>
-    <row r="31" spans="1:26">
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -19203,11 +19384,10 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
+      <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-    </row>
-    <row r="32" spans="1:26">
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -19231,11 +19411,10 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
+      <c r="X32" s="9"/>
       <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-    </row>
-    <row r="33" spans="1:26">
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -19259,11 +19438,10 @@
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
+      <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-    </row>
-    <row r="34" spans="1:26">
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -19287,11 +19465,10 @@
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
+      <c r="X34" s="9"/>
       <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-    </row>
-    <row r="35" spans="1:26">
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -19315,11 +19492,10 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
+      <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-    </row>
-    <row r="36" spans="1:26">
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -19343,11 +19519,10 @@
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
+      <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-    </row>
-    <row r="37" spans="1:26">
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -19371,11 +19546,10 @@
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
+      <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
-    </row>
-    <row r="38" spans="1:26">
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -19399,11 +19573,10 @@
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
+      <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-    </row>
-    <row r="39" spans="1:26">
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -19427,11 +19600,10 @@
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
+      <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-    </row>
-    <row r="40" spans="1:26">
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -19455,11 +19627,10 @@
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
-      <c r="X40" s="2"/>
+      <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
-      <c r="Z40" s="9"/>
-    </row>
-    <row r="41" spans="1:26">
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -19483,11 +19654,10 @@
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
+      <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
-    </row>
-    <row r="42" spans="1:26">
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -19511,11 +19681,10 @@
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
-      <c r="X42" s="2"/>
+      <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-    </row>
-    <row r="43" spans="1:26">
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -19539,11 +19708,10 @@
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
-      <c r="X43" s="2"/>
+      <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-    </row>
-    <row r="44" spans="1:26">
+    </row>
+    <row r="44" spans="1:25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -19567,11 +19735,10 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
-      <c r="X44" s="2"/>
+      <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
-      <c r="Z44" s="9"/>
-    </row>
-    <row r="45" spans="1:26">
+    </row>
+    <row r="45" spans="1:25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -19595,11 +19762,10 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
-      <c r="X45" s="2"/>
+      <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
-      <c r="Z45" s="9"/>
-    </row>
-    <row r="46" spans="1:26">
+    </row>
+    <row r="46" spans="1:25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -19623,11 +19789,10 @@
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
+      <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-    </row>
-    <row r="47" spans="1:26">
+    </row>
+    <row r="47" spans="1:25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -19651,11 +19816,10 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
-      <c r="X47" s="2"/>
+      <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
-      <c r="Z47" s="9"/>
-    </row>
-    <row r="48" spans="1:26">
+    </row>
+    <row r="48" spans="1:25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -19679,11 +19843,10 @@
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
-      <c r="X48" s="2"/>
+      <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
-      <c r="Z48" s="9"/>
-    </row>
-    <row r="49" spans="1:26">
+    </row>
+    <row r="49" spans="1:25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -19707,11 +19870,10 @@
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
+      <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
-      <c r="Z49" s="9"/>
-    </row>
-    <row r="50" spans="1:26">
+    </row>
+    <row r="50" spans="1:25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -19735,11 +19897,10 @@
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
+      <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-    </row>
-    <row r="51" spans="1:26">
+    </row>
+    <row r="51" spans="1:25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -19763,11 +19924,10 @@
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
+      <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-    </row>
-    <row r="52" spans="1:26">
+    </row>
+    <row r="52" spans="1:25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -19791,11 +19951,10 @@
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
-      <c r="X52" s="2"/>
+      <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
-      <c r="Z52" s="9"/>
-    </row>
-    <row r="53" spans="1:26">
+    </row>
+    <row r="53" spans="1:25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -19819,11 +19978,10 @@
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
+      <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-    </row>
-    <row r="54" spans="1:26">
+    </row>
+    <row r="54" spans="1:25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -19847,11 +20005,10 @@
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
-      <c r="X54" s="2"/>
+      <c r="X54" s="9"/>
       <c r="Y54" s="9"/>
-      <c r="Z54" s="9"/>
-    </row>
-    <row r="55" spans="1:26">
+    </row>
+    <row r="55" spans="1:25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -19875,11 +20032,10 @@
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
+      <c r="X55" s="9"/>
       <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-    </row>
-    <row r="56" spans="1:26">
+    </row>
+    <row r="56" spans="1:25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -19903,11 +20059,10 @@
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
-      <c r="X56" s="2"/>
+      <c r="X56" s="9"/>
       <c r="Y56" s="9"/>
-      <c r="Z56" s="9"/>
-    </row>
-    <row r="57" spans="1:26">
+    </row>
+    <row r="57" spans="1:25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -19931,11 +20086,10 @@
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
-      <c r="X57" s="2"/>
+      <c r="X57" s="9"/>
       <c r="Y57" s="9"/>
-      <c r="Z57" s="9"/>
-    </row>
-    <row r="58" spans="1:26">
+    </row>
+    <row r="58" spans="1:25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -19959,11 +20113,10 @@
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
+      <c r="X58" s="9"/>
       <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-    </row>
-    <row r="59" spans="1:26">
+    </row>
+    <row r="59" spans="1:25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -19987,11 +20140,10 @@
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
+      <c r="X59" s="9"/>
       <c r="Y59" s="9"/>
-      <c r="Z59" s="9"/>
-    </row>
-    <row r="60" spans="1:26">
+    </row>
+    <row r="60" spans="1:25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -20015,11 +20167,10 @@
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
-      <c r="X60" s="2"/>
+      <c r="X60" s="9"/>
       <c r="Y60" s="9"/>
-      <c r="Z60" s="9"/>
-    </row>
-    <row r="61" spans="1:26">
+    </row>
+    <row r="61" spans="1:25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -20043,11 +20194,10 @@
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
-      <c r="X61" s="2"/>
+      <c r="X61" s="9"/>
       <c r="Y61" s="9"/>
-      <c r="Z61" s="9"/>
-    </row>
-    <row r="62" spans="1:26">
+    </row>
+    <row r="62" spans="1:25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -20071,11 +20221,10 @@
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
-      <c r="X62" s="2"/>
+      <c r="X62" s="9"/>
       <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-    </row>
-    <row r="63" spans="1:26">
+    </row>
+    <row r="63" spans="1:25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -20099,11 +20248,10 @@
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
+      <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
-      <c r="Z63" s="9"/>
-    </row>
-    <row r="64" spans="1:26">
+    </row>
+    <row r="64" spans="1:25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -20127,11 +20275,10 @@
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
-      <c r="X64" s="2"/>
+      <c r="X64" s="9"/>
       <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
-    </row>
-    <row r="65" spans="1:26">
+    </row>
+    <row r="65" spans="1:25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -20155,11 +20302,10 @@
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
-      <c r="X65" s="2"/>
+      <c r="X65" s="9"/>
       <c r="Y65" s="9"/>
-      <c r="Z65" s="9"/>
-    </row>
-    <row r="66" spans="1:26">
+    </row>
+    <row r="66" spans="1:25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -20183,11 +20329,10 @@
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
+      <c r="X66" s="9"/>
       <c r="Y66" s="9"/>
-      <c r="Z66" s="9"/>
-    </row>
-    <row r="67" spans="1:26">
+    </row>
+    <row r="67" spans="1:25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -20211,11 +20356,10 @@
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
       <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
+      <c r="X67" s="9"/>
       <c r="Y67" s="9"/>
-      <c r="Z67" s="9"/>
-    </row>
-    <row r="68" spans="1:26">
+    </row>
+    <row r="68" spans="1:25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -20239,11 +20383,10 @@
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
       <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
+      <c r="X68" s="9"/>
       <c r="Y68" s="9"/>
-      <c r="Z68" s="9"/>
-    </row>
-    <row r="69" spans="1:26">
+    </row>
+    <row r="69" spans="1:25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -20267,11 +20410,10 @@
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
       <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
+      <c r="X69" s="9"/>
       <c r="Y69" s="9"/>
-      <c r="Z69" s="9"/>
-    </row>
-    <row r="70" spans="1:26">
+    </row>
+    <row r="70" spans="1:25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -20295,11 +20437,10 @@
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
       <c r="W70" s="2"/>
-      <c r="X70" s="2"/>
+      <c r="X70" s="9"/>
       <c r="Y70" s="9"/>
-      <c r="Z70" s="9"/>
-    </row>
-    <row r="71" spans="1:26">
+    </row>
+    <row r="71" spans="1:25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -20323,11 +20464,10 @@
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
+      <c r="X71" s="9"/>
       <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-    </row>
-    <row r="72" spans="1:26">
+    </row>
+    <row r="72" spans="1:25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -20351,11 +20491,10 @@
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
+      <c r="X72" s="9"/>
       <c r="Y72" s="9"/>
-      <c r="Z72" s="9"/>
-    </row>
-    <row r="73" spans="1:26">
+    </row>
+    <row r="73" spans="1:25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -20379,11 +20518,10 @@
       <c r="U73" s="2"/>
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
+      <c r="X73" s="9"/>
       <c r="Y73" s="9"/>
-      <c r="Z73" s="9"/>
-    </row>
-    <row r="74" spans="1:26">
+    </row>
+    <row r="74" spans="1:25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -20407,11 +20545,10 @@
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
-      <c r="X74" s="2"/>
+      <c r="X74" s="9"/>
       <c r="Y74" s="9"/>
-      <c r="Z74" s="9"/>
-    </row>
-    <row r="75" spans="1:26">
+    </row>
+    <row r="75" spans="1:25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -20435,11 +20572,10 @@
       <c r="U75" s="2"/>
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
-      <c r="X75" s="2"/>
+      <c r="X75" s="9"/>
       <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-    </row>
-    <row r="76" spans="1:26">
+    </row>
+    <row r="76" spans="1:25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -20463,11 +20599,10 @@
       <c r="U76" s="2"/>
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
-      <c r="X76" s="2"/>
+      <c r="X76" s="9"/>
       <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-    </row>
-    <row r="77" spans="1:26">
+    </row>
+    <row r="77" spans="1:25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -20491,11 +20626,10 @@
       <c r="U77" s="2"/>
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
-      <c r="X77" s="2"/>
+      <c r="X77" s="9"/>
       <c r="Y77" s="9"/>
-      <c r="Z77" s="9"/>
-    </row>
-    <row r="78" spans="1:26">
+    </row>
+    <row r="78" spans="1:25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -20519,11 +20653,10 @@
       <c r="U78" s="2"/>
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
+      <c r="X78" s="9"/>
       <c r="Y78" s="9"/>
-      <c r="Z78" s="9"/>
-    </row>
-    <row r="79" spans="1:26">
+    </row>
+    <row r="79" spans="1:25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -20547,11 +20680,10 @@
       <c r="U79" s="2"/>
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
+      <c r="X79" s="9"/>
       <c r="Y79" s="9"/>
-      <c r="Z79" s="9"/>
-    </row>
-    <row r="80" spans="1:26">
+    </row>
+    <row r="80" spans="1:25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -20575,11 +20707,10 @@
       <c r="U80" s="2"/>
       <c r="V80" s="2"/>
       <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
+      <c r="X80" s="9"/>
       <c r="Y80" s="9"/>
-      <c r="Z80" s="9"/>
-    </row>
-    <row r="81" spans="1:26">
+    </row>
+    <row r="81" spans="1:25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -20603,11 +20734,10 @@
       <c r="U81" s="2"/>
       <c r="V81" s="2"/>
       <c r="W81" s="2"/>
-      <c r="X81" s="2"/>
+      <c r="X81" s="9"/>
       <c r="Y81" s="9"/>
-      <c r="Z81" s="9"/>
-    </row>
-    <row r="82" spans="1:26">
+    </row>
+    <row r="82" spans="1:25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -20631,11 +20761,10 @@
       <c r="U82" s="2"/>
       <c r="V82" s="2"/>
       <c r="W82" s="2"/>
-      <c r="X82" s="2"/>
+      <c r="X82" s="9"/>
       <c r="Y82" s="9"/>
-      <c r="Z82" s="9"/>
-    </row>
-    <row r="83" spans="1:26">
+    </row>
+    <row r="83" spans="1:25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -20659,11 +20788,10 @@
       <c r="U83" s="2"/>
       <c r="V83" s="2"/>
       <c r="W83" s="2"/>
-      <c r="X83" s="2"/>
+      <c r="X83" s="9"/>
       <c r="Y83" s="9"/>
-      <c r="Z83" s="9"/>
-    </row>
-    <row r="84" spans="1:26">
+    </row>
+    <row r="84" spans="1:25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -20687,11 +20815,10 @@
       <c r="U84" s="2"/>
       <c r="V84" s="2"/>
       <c r="W84" s="2"/>
-      <c r="X84" s="2"/>
+      <c r="X84" s="9"/>
       <c r="Y84" s="9"/>
-      <c r="Z84" s="9"/>
-    </row>
-    <row r="85" spans="1:26">
+    </row>
+    <row r="85" spans="1:25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -20715,11 +20842,10 @@
       <c r="U85" s="2"/>
       <c r="V85" s="2"/>
       <c r="W85" s="2"/>
-      <c r="X85" s="2"/>
+      <c r="X85" s="9"/>
       <c r="Y85" s="9"/>
-      <c r="Z85" s="9"/>
-    </row>
-    <row r="86" spans="1:26">
+    </row>
+    <row r="86" spans="1:25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -20743,11 +20869,10 @@
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
       <c r="W86" s="2"/>
-      <c r="X86" s="2"/>
+      <c r="X86" s="9"/>
       <c r="Y86" s="9"/>
-      <c r="Z86" s="9"/>
-    </row>
-    <row r="87" spans="1:26">
+    </row>
+    <row r="87" spans="1:25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -20771,11 +20896,10 @@
       <c r="U87" s="2"/>
       <c r="V87" s="2"/>
       <c r="W87" s="2"/>
-      <c r="X87" s="2"/>
+      <c r="X87" s="9"/>
       <c r="Y87" s="9"/>
-      <c r="Z87" s="9"/>
-    </row>
-    <row r="88" spans="1:26">
+    </row>
+    <row r="88" spans="1:25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -20799,11 +20923,10 @@
       <c r="U88" s="2"/>
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
-      <c r="X88" s="2"/>
+      <c r="X88" s="9"/>
       <c r="Y88" s="9"/>
-      <c r="Z88" s="9"/>
-    </row>
-    <row r="89" spans="1:26">
+    </row>
+    <row r="89" spans="1:25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -20827,11 +20950,10 @@
       <c r="U89" s="2"/>
       <c r="V89" s="2"/>
       <c r="W89" s="2"/>
-      <c r="X89" s="2"/>
+      <c r="X89" s="9"/>
       <c r="Y89" s="9"/>
-      <c r="Z89" s="9"/>
-    </row>
-    <row r="90" spans="1:26">
+    </row>
+    <row r="90" spans="1:25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -20855,11 +20977,10 @@
       <c r="U90" s="2"/>
       <c r="V90" s="2"/>
       <c r="W90" s="2"/>
-      <c r="X90" s="2"/>
+      <c r="X90" s="9"/>
       <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-    </row>
-    <row r="91" spans="1:26">
+    </row>
+    <row r="91" spans="1:25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -20883,11 +21004,10 @@
       <c r="U91" s="2"/>
       <c r="V91" s="2"/>
       <c r="W91" s="2"/>
-      <c r="X91" s="2"/>
+      <c r="X91" s="9"/>
       <c r="Y91" s="9"/>
-      <c r="Z91" s="9"/>
-    </row>
-    <row r="92" spans="1:26">
+    </row>
+    <row r="92" spans="1:25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -20911,11 +21031,10 @@
       <c r="U92" s="2"/>
       <c r="V92" s="2"/>
       <c r="W92" s="2"/>
-      <c r="X92" s="2"/>
+      <c r="X92" s="9"/>
       <c r="Y92" s="9"/>
-      <c r="Z92" s="9"/>
-    </row>
-    <row r="93" spans="1:26">
+    </row>
+    <row r="93" spans="1:25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -20939,11 +21058,10 @@
       <c r="U93" s="2"/>
       <c r="V93" s="2"/>
       <c r="W93" s="2"/>
-      <c r="X93" s="2"/>
+      <c r="X93" s="9"/>
       <c r="Y93" s="9"/>
-      <c r="Z93" s="9"/>
-    </row>
-    <row r="94" spans="1:26">
+    </row>
+    <row r="94" spans="1:25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -20967,11 +21085,10 @@
       <c r="U94" s="2"/>
       <c r="V94" s="2"/>
       <c r="W94" s="2"/>
-      <c r="X94" s="2"/>
+      <c r="X94" s="9"/>
       <c r="Y94" s="9"/>
-      <c r="Z94" s="9"/>
-    </row>
-    <row r="95" spans="1:26">
+    </row>
+    <row r="95" spans="1:25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -20995,11 +21112,10 @@
       <c r="U95" s="2"/>
       <c r="V95" s="2"/>
       <c r="W95" s="2"/>
-      <c r="X95" s="2"/>
+      <c r="X95" s="9"/>
       <c r="Y95" s="9"/>
-      <c r="Z95" s="9"/>
-    </row>
-    <row r="96" spans="1:26">
+    </row>
+    <row r="96" spans="1:25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -21023,11 +21139,10 @@
       <c r="U96" s="2"/>
       <c r="V96" s="2"/>
       <c r="W96" s="2"/>
-      <c r="X96" s="2"/>
+      <c r="X96" s="9"/>
       <c r="Y96" s="9"/>
-      <c r="Z96" s="9"/>
-    </row>
-    <row r="97" spans="1:26">
+    </row>
+    <row r="97" spans="1:25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -21051,11 +21166,10 @@
       <c r="U97" s="2"/>
       <c r="V97" s="2"/>
       <c r="W97" s="2"/>
-      <c r="X97" s="2"/>
+      <c r="X97" s="9"/>
       <c r="Y97" s="9"/>
-      <c r="Z97" s="9"/>
-    </row>
-    <row r="98" spans="1:26">
+    </row>
+    <row r="98" spans="1:25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -21079,11 +21193,10 @@
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
       <c r="W98" s="2"/>
-      <c r="X98" s="2"/>
+      <c r="X98" s="9"/>
       <c r="Y98" s="9"/>
-      <c r="Z98" s="9"/>
-    </row>
-    <row r="99" spans="1:26">
+    </row>
+    <row r="99" spans="1:25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -21107,11 +21220,10 @@
       <c r="U99" s="2"/>
       <c r="V99" s="2"/>
       <c r="W99" s="2"/>
-      <c r="X99" s="2"/>
+      <c r="X99" s="9"/>
       <c r="Y99" s="9"/>
-      <c r="Z99" s="9"/>
-    </row>
-    <row r="100" spans="1:26">
+    </row>
+    <row r="100" spans="1:25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -21135,11 +21247,10 @@
       <c r="U100" s="2"/>
       <c r="V100" s="2"/>
       <c r="W100" s="2"/>
-      <c r="X100" s="2"/>
+      <c r="X100" s="9"/>
       <c r="Y100" s="9"/>
-      <c r="Z100" s="9"/>
-    </row>
-    <row r="101" spans="1:26">
+    </row>
+    <row r="101" spans="1:25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -21163,11 +21274,10 @@
       <c r="U101" s="2"/>
       <c r="V101" s="2"/>
       <c r="W101" s="2"/>
-      <c r="X101" s="2"/>
+      <c r="X101" s="9"/>
       <c r="Y101" s="9"/>
-      <c r="Z101" s="9"/>
-    </row>
-    <row r="102" spans="1:26">
+    </row>
+    <row r="102" spans="1:25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -21191,11 +21301,10 @@
       <c r="U102" s="2"/>
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
+      <c r="X102" s="9"/>
       <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-    </row>
-    <row r="103" spans="1:26">
+    </row>
+    <row r="103" spans="1:25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -21219,11 +21328,10 @@
       <c r="U103" s="2"/>
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
-      <c r="X103" s="2"/>
+      <c r="X103" s="9"/>
       <c r="Y103" s="9"/>
-      <c r="Z103" s="9"/>
-    </row>
-    <row r="104" spans="1:26">
+    </row>
+    <row r="104" spans="1:25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -21247,11 +21355,10 @@
       <c r="U104" s="2"/>
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
-      <c r="X104" s="2"/>
+      <c r="X104" s="9"/>
       <c r="Y104" s="9"/>
-      <c r="Z104" s="9"/>
-    </row>
-    <row r="105" spans="1:26">
+    </row>
+    <row r="105" spans="1:25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -21275,11 +21382,10 @@
       <c r="U105" s="2"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
-      <c r="X105" s="2"/>
+      <c r="X105" s="9"/>
       <c r="Y105" s="9"/>
-      <c r="Z105" s="9"/>
-    </row>
-    <row r="106" spans="1:26">
+    </row>
+    <row r="106" spans="1:25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -21303,11 +21409,10 @@
       <c r="U106" s="2"/>
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
-      <c r="X106" s="2"/>
+      <c r="X106" s="9"/>
       <c r="Y106" s="9"/>
-      <c r="Z106" s="9"/>
-    </row>
-    <row r="107" spans="1:26">
+    </row>
+    <row r="107" spans="1:25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -21331,11 +21436,10 @@
       <c r="U107" s="2"/>
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
-      <c r="X107" s="2"/>
+      <c r="X107" s="9"/>
       <c r="Y107" s="9"/>
-      <c r="Z107" s="9"/>
-    </row>
-    <row r="108" spans="1:26">
+    </row>
+    <row r="108" spans="1:25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -21359,11 +21463,10 @@
       <c r="U108" s="2"/>
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
-      <c r="X108" s="2"/>
+      <c r="X108" s="9"/>
       <c r="Y108" s="9"/>
-      <c r="Z108" s="9"/>
-    </row>
-    <row r="109" spans="1:26">
+    </row>
+    <row r="109" spans="1:25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -21387,11 +21490,10 @@
       <c r="U109" s="2"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
-      <c r="X109" s="2"/>
+      <c r="X109" s="9"/>
       <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-    </row>
-    <row r="110" spans="1:26">
+    </row>
+    <row r="110" spans="1:25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -21415,11 +21517,10 @@
       <c r="U110" s="2"/>
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
-      <c r="X110" s="2"/>
+      <c r="X110" s="9"/>
       <c r="Y110" s="9"/>
-      <c r="Z110" s="9"/>
-    </row>
-    <row r="111" spans="1:26">
+    </row>
+    <row r="111" spans="1:25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -21443,11 +21544,10 @@
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
-      <c r="X111" s="2"/>
+      <c r="X111" s="9"/>
       <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-    </row>
-    <row r="112" spans="1:26">
+    </row>
+    <row r="112" spans="1:25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -21471,11 +21571,10 @@
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
-      <c r="X112" s="2"/>
+      <c r="X112" s="9"/>
       <c r="Y112" s="9"/>
-      <c r="Z112" s="9"/>
-    </row>
-    <row r="113" spans="1:26">
+    </row>
+    <row r="113" spans="1:25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -21499,11 +21598,10 @@
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-      <c r="X113" s="2"/>
+      <c r="X113" s="9"/>
       <c r="Y113" s="9"/>
-      <c r="Z113" s="9"/>
-    </row>
-    <row r="114" spans="1:26">
+    </row>
+    <row r="114" spans="1:25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -21527,11 +21625,10 @@
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="2"/>
+      <c r="X114" s="9"/>
       <c r="Y114" s="9"/>
-      <c r="Z114" s="9"/>
-    </row>
-    <row r="115" spans="1:26">
+    </row>
+    <row r="115" spans="1:25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -21555,11 +21652,10 @@
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
-      <c r="X115" s="2"/>
+      <c r="X115" s="9"/>
       <c r="Y115" s="9"/>
-      <c r="Z115" s="9"/>
-    </row>
-    <row r="116" spans="1:26">
+    </row>
+    <row r="116" spans="1:25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -21583,11 +21679,10 @@
       <c r="U116" s="2"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
-      <c r="X116" s="2"/>
+      <c r="X116" s="9"/>
       <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-    </row>
-    <row r="117" spans="1:26">
+    </row>
+    <row r="117" spans="1:25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -21611,11 +21706,10 @@
       <c r="U117" s="2"/>
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
-      <c r="X117" s="2"/>
+      <c r="X117" s="9"/>
       <c r="Y117" s="9"/>
-      <c r="Z117" s="9"/>
-    </row>
-    <row r="118" spans="1:26">
+    </row>
+    <row r="118" spans="1:25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -21639,11 +21733,10 @@
       <c r="U118" s="2"/>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
-      <c r="X118" s="2"/>
+      <c r="X118" s="9"/>
       <c r="Y118" s="9"/>
-      <c r="Z118" s="9"/>
-    </row>
-    <row r="119" spans="1:26">
+    </row>
+    <row r="119" spans="1:25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -21667,11 +21760,10 @@
       <c r="U119" s="2"/>
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
-      <c r="X119" s="2"/>
+      <c r="X119" s="9"/>
       <c r="Y119" s="9"/>
-      <c r="Z119" s="9"/>
-    </row>
-    <row r="120" spans="1:26">
+    </row>
+    <row r="120" spans="1:25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -21695,11 +21787,10 @@
       <c r="U120" s="2"/>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
-      <c r="X120" s="2"/>
+      <c r="X120" s="9"/>
       <c r="Y120" s="9"/>
-      <c r="Z120" s="9"/>
-    </row>
-    <row r="121" spans="1:26">
+    </row>
+    <row r="121" spans="1:25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -21723,11 +21814,10 @@
       <c r="U121" s="2"/>
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
-      <c r="X121" s="2"/>
+      <c r="X121" s="9"/>
       <c r="Y121" s="9"/>
-      <c r="Z121" s="9"/>
-    </row>
-    <row r="122" spans="1:26">
+    </row>
+    <row r="122" spans="1:25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -21751,11 +21841,10 @@
       <c r="U122" s="2"/>
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
-      <c r="X122" s="2"/>
+      <c r="X122" s="9"/>
       <c r="Y122" s="9"/>
-      <c r="Z122" s="9"/>
-    </row>
-    <row r="123" spans="1:26">
+    </row>
+    <row r="123" spans="1:25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -21779,11 +21868,10 @@
       <c r="U123" s="2"/>
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
-      <c r="X123" s="2"/>
+      <c r="X123" s="9"/>
       <c r="Y123" s="9"/>
-      <c r="Z123" s="9"/>
-    </row>
-    <row r="124" spans="1:26">
+    </row>
+    <row r="124" spans="1:25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -21807,11 +21895,10 @@
       <c r="U124" s="2"/>
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
-      <c r="X124" s="2"/>
+      <c r="X124" s="9"/>
       <c r="Y124" s="9"/>
-      <c r="Z124" s="9"/>
-    </row>
-    <row r="125" spans="1:26">
+    </row>
+    <row r="125" spans="1:25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -21835,11 +21922,10 @@
       <c r="U125" s="2"/>
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
-      <c r="X125" s="2"/>
+      <c r="X125" s="9"/>
       <c r="Y125" s="9"/>
-      <c r="Z125" s="9"/>
-    </row>
-    <row r="126" spans="1:26">
+    </row>
+    <row r="126" spans="1:25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -21863,11 +21949,10 @@
       <c r="U126" s="2"/>
       <c r="V126" s="2"/>
       <c r="W126" s="2"/>
-      <c r="X126" s="2"/>
+      <c r="X126" s="9"/>
       <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-    </row>
-    <row r="127" spans="1:26">
+    </row>
+    <row r="127" spans="1:25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -21891,11 +21976,10 @@
       <c r="U127" s="2"/>
       <c r="V127" s="2"/>
       <c r="W127" s="2"/>
-      <c r="X127" s="2"/>
+      <c r="X127" s="9"/>
       <c r="Y127" s="9"/>
-      <c r="Z127" s="9"/>
-    </row>
-    <row r="128" spans="1:26">
+    </row>
+    <row r="128" spans="1:25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -21919,11 +22003,10 @@
       <c r="U128" s="2"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
-      <c r="X128" s="2"/>
+      <c r="X128" s="9"/>
       <c r="Y128" s="9"/>
-      <c r="Z128" s="9"/>
-    </row>
-    <row r="129" spans="1:26">
+    </row>
+    <row r="129" spans="1:25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -21947,11 +22030,10 @@
       <c r="U129" s="2"/>
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
-      <c r="X129" s="2"/>
+      <c r="X129" s="9"/>
       <c r="Y129" s="9"/>
-      <c r="Z129" s="9"/>
-    </row>
-    <row r="130" spans="1:26">
+    </row>
+    <row r="130" spans="1:25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -21975,11 +22057,10 @@
       <c r="U130" s="2"/>
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
-      <c r="X130" s="2"/>
+      <c r="X130" s="9"/>
       <c r="Y130" s="9"/>
-      <c r="Z130" s="9"/>
-    </row>
-    <row r="131" spans="1:26">
+    </row>
+    <row r="131" spans="1:25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -22003,11 +22084,10 @@
       <c r="U131" s="2"/>
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
-      <c r="X131" s="2"/>
+      <c r="X131" s="9"/>
       <c r="Y131" s="9"/>
-      <c r="Z131" s="9"/>
-    </row>
-    <row r="132" spans="1:26">
+    </row>
+    <row r="132" spans="1:25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -22031,11 +22111,10 @@
       <c r="U132" s="2"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-      <c r="X132" s="2"/>
+      <c r="X132" s="9"/>
       <c r="Y132" s="9"/>
-      <c r="Z132" s="9"/>
-    </row>
-    <row r="133" spans="1:26">
+    </row>
+    <row r="133" spans="1:25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -22059,11 +22138,10 @@
       <c r="U133" s="2"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-      <c r="X133" s="2"/>
+      <c r="X133" s="9"/>
       <c r="Y133" s="9"/>
-      <c r="Z133" s="9"/>
-    </row>
-    <row r="134" spans="1:26">
+    </row>
+    <row r="134" spans="1:25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -22087,11 +22165,10 @@
       <c r="U134" s="2"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-      <c r="X134" s="2"/>
+      <c r="X134" s="9"/>
       <c r="Y134" s="9"/>
-      <c r="Z134" s="9"/>
-    </row>
-    <row r="135" spans="1:26">
+    </row>
+    <row r="135" spans="1:25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -22115,11 +22192,10 @@
       <c r="U135" s="2"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-      <c r="X135" s="2"/>
+      <c r="X135" s="9"/>
       <c r="Y135" s="9"/>
-      <c r="Z135" s="9"/>
-    </row>
-    <row r="136" spans="1:26">
+    </row>
+    <row r="136" spans="1:25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -22143,11 +22219,10 @@
       <c r="U136" s="2"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-      <c r="X136" s="2"/>
+      <c r="X136" s="9"/>
       <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-    </row>
-    <row r="137" spans="1:26">
+    </row>
+    <row r="137" spans="1:25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -22171,11 +22246,10 @@
       <c r="U137" s="2"/>
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
-      <c r="X137" s="2"/>
+      <c r="X137" s="9"/>
       <c r="Y137" s="9"/>
-      <c r="Z137" s="9"/>
-    </row>
-    <row r="138" spans="1:26">
+    </row>
+    <row r="138" spans="1:25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -22199,11 +22273,10 @@
       <c r="U138" s="2"/>
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
-      <c r="X138" s="2"/>
+      <c r="X138" s="9"/>
       <c r="Y138" s="9"/>
-      <c r="Z138" s="9"/>
-    </row>
-    <row r="139" spans="1:26">
+    </row>
+    <row r="139" spans="1:25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -22227,11 +22300,10 @@
       <c r="U139" s="2"/>
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
-      <c r="X139" s="2"/>
+      <c r="X139" s="9"/>
       <c r="Y139" s="9"/>
-      <c r="Z139" s="9"/>
-    </row>
-    <row r="140" spans="1:26">
+    </row>
+    <row r="140" spans="1:25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -22255,11 +22327,10 @@
       <c r="U140" s="2"/>
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
-      <c r="X140" s="2"/>
+      <c r="X140" s="9"/>
       <c r="Y140" s="9"/>
-      <c r="Z140" s="9"/>
-    </row>
-    <row r="141" spans="1:26">
+    </row>
+    <row r="141" spans="1:25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -22283,11 +22354,10 @@
       <c r="U141" s="2"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-      <c r="X141" s="2"/>
+      <c r="X141" s="9"/>
       <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-    </row>
-    <row r="142" spans="1:26">
+    </row>
+    <row r="142" spans="1:25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -22311,11 +22381,10 @@
       <c r="U142" s="2"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-      <c r="X142" s="2"/>
+      <c r="X142" s="9"/>
       <c r="Y142" s="9"/>
-      <c r="Z142" s="9"/>
-    </row>
-    <row r="143" spans="1:26">
+    </row>
+    <row r="143" spans="1:25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -22339,11 +22408,10 @@
       <c r="U143" s="2"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-      <c r="X143" s="2"/>
+      <c r="X143" s="9"/>
       <c r="Y143" s="9"/>
-      <c r="Z143" s="9"/>
-    </row>
-    <row r="144" spans="1:26">
+    </row>
+    <row r="144" spans="1:25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -22367,11 +22435,10 @@
       <c r="U144" s="2"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-      <c r="X144" s="2"/>
+      <c r="X144" s="9"/>
       <c r="Y144" s="9"/>
-      <c r="Z144" s="9"/>
-    </row>
-    <row r="145" spans="1:26">
+    </row>
+    <row r="145" spans="1:25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -22395,11 +22462,10 @@
       <c r="U145" s="2"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-      <c r="X145" s="2"/>
+      <c r="X145" s="9"/>
       <c r="Y145" s="9"/>
-      <c r="Z145" s="9"/>
-    </row>
-    <row r="146" spans="1:26">
+    </row>
+    <row r="146" spans="1:25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -22423,11 +22489,10 @@
       <c r="U146" s="2"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-      <c r="X146" s="2"/>
+      <c r="X146" s="9"/>
       <c r="Y146" s="9"/>
-      <c r="Z146" s="9"/>
-    </row>
-    <row r="147" spans="1:26">
+    </row>
+    <row r="147" spans="1:25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -22451,11 +22516,10 @@
       <c r="U147" s="2"/>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
-      <c r="X147" s="2"/>
+      <c r="X147" s="9"/>
       <c r="Y147" s="9"/>
-      <c r="Z147" s="9"/>
-    </row>
-    <row r="148" spans="1:26">
+    </row>
+    <row r="148" spans="1:25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -22479,11 +22543,10 @@
       <c r="U148" s="2"/>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
-      <c r="X148" s="2"/>
+      <c r="X148" s="9"/>
       <c r="Y148" s="9"/>
-      <c r="Z148" s="9"/>
-    </row>
-    <row r="149" spans="1:26">
+    </row>
+    <row r="149" spans="1:25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -22507,11 +22570,10 @@
       <c r="U149" s="2"/>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
-      <c r="X149" s="2"/>
+      <c r="X149" s="9"/>
       <c r="Y149" s="9"/>
-      <c r="Z149" s="9"/>
-    </row>
-    <row r="150" spans="1:26">
+    </row>
+    <row r="150" spans="1:25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -22535,11 +22597,10 @@
       <c r="U150" s="2"/>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
-      <c r="X150" s="2"/>
+      <c r="X150" s="9"/>
       <c r="Y150" s="9"/>
-      <c r="Z150" s="9"/>
-    </row>
-    <row r="151" spans="1:26">
+    </row>
+    <row r="151" spans="1:25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -22563,11 +22624,10 @@
       <c r="U151" s="2"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-      <c r="X151" s="2"/>
+      <c r="X151" s="9"/>
       <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-    </row>
-    <row r="152" spans="1:26">
+    </row>
+    <row r="152" spans="1:25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -22591,11 +22651,10 @@
       <c r="U152" s="2"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-      <c r="X152" s="2"/>
+      <c r="X152" s="9"/>
       <c r="Y152" s="9"/>
-      <c r="Z152" s="9"/>
-    </row>
-    <row r="153" spans="1:26">
+    </row>
+    <row r="153" spans="1:25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -22619,11 +22678,10 @@
       <c r="U153" s="2"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-      <c r="X153" s="2"/>
+      <c r="X153" s="9"/>
       <c r="Y153" s="9"/>
-      <c r="Z153" s="9"/>
-    </row>
-    <row r="154" spans="1:26">
+    </row>
+    <row r="154" spans="1:25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -22647,11 +22705,10 @@
       <c r="U154" s="2"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-      <c r="X154" s="2"/>
+      <c r="X154" s="9"/>
       <c r="Y154" s="9"/>
-      <c r="Z154" s="9"/>
-    </row>
-    <row r="155" spans="1:26">
+    </row>
+    <row r="155" spans="1:25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -22675,11 +22732,10 @@
       <c r="U155" s="2"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-      <c r="X155" s="2"/>
+      <c r="X155" s="9"/>
       <c r="Y155" s="9"/>
-      <c r="Z155" s="9"/>
-    </row>
-    <row r="156" spans="1:26">
+    </row>
+    <row r="156" spans="1:25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -22703,11 +22759,10 @@
       <c r="U156" s="2"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-      <c r="X156" s="2"/>
+      <c r="X156" s="9"/>
       <c r="Y156" s="9"/>
-      <c r="Z156" s="9"/>
-    </row>
-    <row r="157" spans="1:26">
+    </row>
+    <row r="157" spans="1:25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -22731,11 +22786,10 @@
       <c r="U157" s="2"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-      <c r="X157" s="2"/>
+      <c r="X157" s="9"/>
       <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-    </row>
-    <row r="158" spans="1:26">
+    </row>
+    <row r="158" spans="1:25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -22759,11 +22813,10 @@
       <c r="U158" s="2"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-      <c r="X158" s="2"/>
+      <c r="X158" s="9"/>
       <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-    </row>
-    <row r="159" spans="1:26">
+    </row>
+    <row r="159" spans="1:25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -22787,11 +22840,10 @@
       <c r="U159" s="2"/>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
-      <c r="X159" s="2"/>
+      <c r="X159" s="9"/>
       <c r="Y159" s="9"/>
-      <c r="Z159" s="9"/>
-    </row>
-    <row r="160" spans="1:26">
+    </row>
+    <row r="160" spans="1:25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -22815,11 +22867,10 @@
       <c r="U160" s="2"/>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
-      <c r="X160" s="2"/>
+      <c r="X160" s="9"/>
       <c r="Y160" s="9"/>
-      <c r="Z160" s="9"/>
-    </row>
-    <row r="161" spans="1:26">
+    </row>
+    <row r="161" spans="1:25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -22843,11 +22894,10 @@
       <c r="U161" s="2"/>
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
-      <c r="X161" s="2"/>
+      <c r="X161" s="9"/>
       <c r="Y161" s="9"/>
-      <c r="Z161" s="9"/>
-    </row>
-    <row r="162" spans="1:26">
+    </row>
+    <row r="162" spans="1:25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -22871,11 +22921,10 @@
       <c r="U162" s="2"/>
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
-      <c r="X162" s="2"/>
+      <c r="X162" s="9"/>
       <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-    </row>
-    <row r="163" spans="1:26">
+    </row>
+    <row r="163" spans="1:25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -22899,11 +22948,10 @@
       <c r="U163" s="2"/>
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
-      <c r="X163" s="2"/>
+      <c r="X163" s="9"/>
       <c r="Y163" s="9"/>
-      <c r="Z163" s="9"/>
-    </row>
-    <row r="164" spans="1:26">
+    </row>
+    <row r="164" spans="1:25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -22927,11 +22975,10 @@
       <c r="U164" s="2"/>
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
-      <c r="X164" s="2"/>
+      <c r="X164" s="9"/>
       <c r="Y164" s="9"/>
-      <c r="Z164" s="9"/>
-    </row>
-    <row r="165" spans="1:26">
+    </row>
+    <row r="165" spans="1:25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -22955,11 +23002,10 @@
       <c r="U165" s="2"/>
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
-      <c r="X165" s="2"/>
+      <c r="X165" s="9"/>
       <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-    </row>
-    <row r="166" spans="1:26">
+    </row>
+    <row r="166" spans="1:25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -22983,11 +23029,10 @@
       <c r="U166" s="2"/>
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
-      <c r="X166" s="2"/>
+      <c r="X166" s="9"/>
       <c r="Y166" s="9"/>
-      <c r="Z166" s="9"/>
-    </row>
-    <row r="167" spans="1:26">
+    </row>
+    <row r="167" spans="1:25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -23011,11 +23056,10 @@
       <c r="U167" s="2"/>
       <c r="V167" s="2"/>
       <c r="W167" s="2"/>
-      <c r="X167" s="2"/>
+      <c r="X167" s="9"/>
       <c r="Y167" s="9"/>
-      <c r="Z167" s="9"/>
-    </row>
-    <row r="168" spans="1:26">
+    </row>
+    <row r="168" spans="1:25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -23039,11 +23083,10 @@
       <c r="U168" s="2"/>
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
-      <c r="X168" s="2"/>
+      <c r="X168" s="9"/>
       <c r="Y168" s="9"/>
-      <c r="Z168" s="9"/>
-    </row>
-    <row r="169" spans="1:26">
+    </row>
+    <row r="169" spans="1:25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -23067,11 +23110,10 @@
       <c r="U169" s="2"/>
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
-      <c r="X169" s="2"/>
+      <c r="X169" s="9"/>
       <c r="Y169" s="9"/>
-      <c r="Z169" s="9"/>
-    </row>
-    <row r="170" spans="1:26">
+    </row>
+    <row r="170" spans="1:25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -23095,11 +23137,10 @@
       <c r="U170" s="2"/>
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
-      <c r="X170" s="2"/>
+      <c r="X170" s="9"/>
       <c r="Y170" s="9"/>
-      <c r="Z170" s="9"/>
-    </row>
-    <row r="171" spans="1:26">
+    </row>
+    <row r="171" spans="1:25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -23123,11 +23164,10 @@
       <c r="U171" s="2"/>
       <c r="V171" s="2"/>
       <c r="W171" s="2"/>
-      <c r="X171" s="2"/>
+      <c r="X171" s="9"/>
       <c r="Y171" s="9"/>
-      <c r="Z171" s="9"/>
-    </row>
-    <row r="172" spans="1:26">
+    </row>
+    <row r="172" spans="1:25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -23151,11 +23191,10 @@
       <c r="U172" s="2"/>
       <c r="V172" s="2"/>
       <c r="W172" s="2"/>
-      <c r="X172" s="2"/>
+      <c r="X172" s="9"/>
       <c r="Y172" s="9"/>
-      <c r="Z172" s="9"/>
-    </row>
-    <row r="173" spans="1:26">
+    </row>
+    <row r="173" spans="1:25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -23179,11 +23218,10 @@
       <c r="U173" s="2"/>
       <c r="V173" s="2"/>
       <c r="W173" s="2"/>
-      <c r="X173" s="2"/>
+      <c r="X173" s="9"/>
       <c r="Y173" s="9"/>
-      <c r="Z173" s="9"/>
-    </row>
-    <row r="174" spans="1:26">
+    </row>
+    <row r="174" spans="1:25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -23207,11 +23245,10 @@
       <c r="U174" s="2"/>
       <c r="V174" s="2"/>
       <c r="W174" s="2"/>
-      <c r="X174" s="2"/>
+      <c r="X174" s="9"/>
       <c r="Y174" s="9"/>
-      <c r="Z174" s="9"/>
-    </row>
-    <row r="175" spans="1:26">
+    </row>
+    <row r="175" spans="1:25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -23235,11 +23272,10 @@
       <c r="U175" s="2"/>
       <c r="V175" s="2"/>
       <c r="W175" s="2"/>
-      <c r="X175" s="2"/>
+      <c r="X175" s="9"/>
       <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-    </row>
-    <row r="176" spans="1:26">
+    </row>
+    <row r="176" spans="1:25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -23263,11 +23299,10 @@
       <c r="U176" s="2"/>
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
-      <c r="X176" s="2"/>
+      <c r="X176" s="9"/>
       <c r="Y176" s="9"/>
-      <c r="Z176" s="9"/>
-    </row>
-    <row r="177" spans="1:26">
+    </row>
+    <row r="177" spans="1:25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -23291,11 +23326,10 @@
       <c r="U177" s="2"/>
       <c r="V177" s="2"/>
       <c r="W177" s="2"/>
-      <c r="X177" s="2"/>
+      <c r="X177" s="9"/>
       <c r="Y177" s="9"/>
-      <c r="Z177" s="9"/>
-    </row>
-    <row r="178" spans="1:26">
+    </row>
+    <row r="178" spans="1:25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -23319,11 +23353,10 @@
       <c r="U178" s="2"/>
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
-      <c r="X178" s="2"/>
+      <c r="X178" s="9"/>
       <c r="Y178" s="9"/>
-      <c r="Z178" s="9"/>
-    </row>
-    <row r="179" spans="1:26">
+    </row>
+    <row r="179" spans="1:25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -23347,11 +23380,10 @@
       <c r="U179" s="2"/>
       <c r="V179" s="2"/>
       <c r="W179" s="2"/>
-      <c r="X179" s="2"/>
+      <c r="X179" s="9"/>
       <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-    </row>
-    <row r="180" spans="1:26">
+    </row>
+    <row r="180" spans="1:25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -23375,11 +23407,10 @@
       <c r="U180" s="2"/>
       <c r="V180" s="2"/>
       <c r="W180" s="2"/>
-      <c r="X180" s="2"/>
+      <c r="X180" s="9"/>
       <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-    </row>
-    <row r="181" spans="1:26">
+    </row>
+    <row r="181" spans="1:25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -23403,11 +23434,10 @@
       <c r="U181" s="2"/>
       <c r="V181" s="2"/>
       <c r="W181" s="2"/>
-      <c r="X181" s="2"/>
+      <c r="X181" s="9"/>
       <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-    </row>
-    <row r="182" spans="1:26">
+    </row>
+    <row r="182" spans="1:25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -23431,11 +23461,10 @@
       <c r="U182" s="2"/>
       <c r="V182" s="2"/>
       <c r="W182" s="2"/>
-      <c r="X182" s="2"/>
+      <c r="X182" s="9"/>
       <c r="Y182" s="9"/>
-      <c r="Z182" s="9"/>
-    </row>
-    <row r="183" spans="1:26">
+    </row>
+    <row r="183" spans="1:25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -23459,11 +23488,10 @@
       <c r="U183" s="2"/>
       <c r="V183" s="2"/>
       <c r="W183" s="2"/>
-      <c r="X183" s="2"/>
+      <c r="X183" s="9"/>
       <c r="Y183" s="9"/>
-      <c r="Z183" s="9"/>
-    </row>
-    <row r="184" spans="1:26">
+    </row>
+    <row r="184" spans="1:25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -23487,11 +23515,10 @@
       <c r="U184" s="2"/>
       <c r="V184" s="2"/>
       <c r="W184" s="2"/>
-      <c r="X184" s="2"/>
+      <c r="X184" s="9"/>
       <c r="Y184" s="9"/>
-      <c r="Z184" s="9"/>
-    </row>
-    <row r="185" spans="1:26">
+    </row>
+    <row r="185" spans="1:25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -23515,11 +23542,10 @@
       <c r="U185" s="2"/>
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
-      <c r="X185" s="2"/>
+      <c r="X185" s="9"/>
       <c r="Y185" s="9"/>
-      <c r="Z185" s="9"/>
-    </row>
-    <row r="186" spans="1:26">
+    </row>
+    <row r="186" spans="1:25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -23543,11 +23569,10 @@
       <c r="U186" s="2"/>
       <c r="V186" s="2"/>
       <c r="W186" s="2"/>
-      <c r="X186" s="2"/>
+      <c r="X186" s="9"/>
       <c r="Y186" s="9"/>
-      <c r="Z186" s="9"/>
-    </row>
-    <row r="187" spans="1:26">
+    </row>
+    <row r="187" spans="1:25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -23571,11 +23596,10 @@
       <c r="U187" s="2"/>
       <c r="V187" s="2"/>
       <c r="W187" s="2"/>
-      <c r="X187" s="2"/>
+      <c r="X187" s="9"/>
       <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-    </row>
-    <row r="188" spans="1:26">
+    </row>
+    <row r="188" spans="1:25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -23599,11 +23623,10 @@
       <c r="U188" s="2"/>
       <c r="V188" s="2"/>
       <c r="W188" s="2"/>
-      <c r="X188" s="2"/>
+      <c r="X188" s="9"/>
       <c r="Y188" s="9"/>
-      <c r="Z188" s="9"/>
-    </row>
-    <row r="189" spans="1:26">
+    </row>
+    <row r="189" spans="1:25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -23627,11 +23650,10 @@
       <c r="U189" s="2"/>
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
-      <c r="X189" s="2"/>
+      <c r="X189" s="9"/>
       <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-    </row>
-    <row r="190" spans="1:26">
+    </row>
+    <row r="190" spans="1:25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -23655,11 +23677,10 @@
       <c r="U190" s="2"/>
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
-      <c r="X190" s="2"/>
+      <c r="X190" s="9"/>
       <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-    </row>
-    <row r="191" spans="1:26">
+    </row>
+    <row r="191" spans="1:25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -23683,11 +23704,10 @@
       <c r="U191" s="2"/>
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
-      <c r="X191" s="2"/>
+      <c r="X191" s="9"/>
       <c r="Y191" s="9"/>
-      <c r="Z191" s="9"/>
-    </row>
-    <row r="192" spans="1:26">
+    </row>
+    <row r="192" spans="1:25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -23711,11 +23731,10 @@
       <c r="U192" s="2"/>
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
-      <c r="X192" s="2"/>
+      <c r="X192" s="9"/>
       <c r="Y192" s="9"/>
-      <c r="Z192" s="9"/>
-    </row>
-    <row r="193" spans="1:26">
+    </row>
+    <row r="193" spans="1:25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -23739,11 +23758,10 @@
       <c r="U193" s="2"/>
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
-      <c r="X193" s="2"/>
+      <c r="X193" s="9"/>
       <c r="Y193" s="9"/>
-      <c r="Z193" s="9"/>
-    </row>
-    <row r="194" spans="1:26">
+    </row>
+    <row r="194" spans="1:25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -23767,11 +23785,10 @@
       <c r="U194" s="2"/>
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
-      <c r="X194" s="2"/>
+      <c r="X194" s="9"/>
       <c r="Y194" s="9"/>
-      <c r="Z194" s="9"/>
-    </row>
-    <row r="195" spans="1:26">
+    </row>
+    <row r="195" spans="1:25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -23795,11 +23812,10 @@
       <c r="U195" s="2"/>
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
-      <c r="X195" s="2"/>
+      <c r="X195" s="9"/>
       <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-    </row>
-    <row r="196" spans="1:26">
+    </row>
+    <row r="196" spans="1:25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -23823,11 +23839,10 @@
       <c r="U196" s="2"/>
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
-      <c r="X196" s="2"/>
+      <c r="X196" s="9"/>
       <c r="Y196" s="9"/>
-      <c r="Z196" s="9"/>
-    </row>
-    <row r="197" spans="1:26">
+    </row>
+    <row r="197" spans="1:25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -23851,11 +23866,10 @@
       <c r="U197" s="2"/>
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
-      <c r="X197" s="2"/>
+      <c r="X197" s="9"/>
       <c r="Y197" s="9"/>
-      <c r="Z197" s="9"/>
-    </row>
-    <row r="198" spans="1:26">
+    </row>
+    <row r="198" spans="1:25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -23879,11 +23893,10 @@
       <c r="U198" s="2"/>
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
-      <c r="X198" s="2"/>
+      <c r="X198" s="9"/>
       <c r="Y198" s="9"/>
-      <c r="Z198" s="9"/>
-    </row>
-    <row r="199" spans="1:26">
+    </row>
+    <row r="199" spans="1:25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -23907,11 +23920,10 @@
       <c r="U199" s="2"/>
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
-      <c r="X199" s="2"/>
+      <c r="X199" s="9"/>
       <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-    </row>
-    <row r="200" spans="1:26">
+    </row>
+    <row r="200" spans="1:25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -23935,11 +23947,10 @@
       <c r="U200" s="2"/>
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
-      <c r="X200" s="2"/>
+      <c r="X200" s="9"/>
       <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-    </row>
-    <row r="201" spans="1:26">
+    </row>
+    <row r="201" spans="1:25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -23963,11 +23974,10 @@
       <c r="U201" s="2"/>
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
-      <c r="X201" s="2"/>
+      <c r="X201" s="9"/>
       <c r="Y201" s="9"/>
-      <c r="Z201" s="9"/>
-    </row>
-    <row r="202" spans="1:26">
+    </row>
+    <row r="202" spans="1:25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -23991,11 +24001,10 @@
       <c r="U202" s="2"/>
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
-      <c r="X202" s="2"/>
+      <c r="X202" s="9"/>
       <c r="Y202" s="9"/>
-      <c r="Z202" s="9"/>
-    </row>
-    <row r="203" spans="1:26">
+    </row>
+    <row r="203" spans="1:25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -24019,46 +24028,45 @@
       <c r="U203" s="2"/>
       <c r="V203" s="2"/>
       <c r="W203" s="2"/>
-      <c r="X203" s="2"/>
+      <c r="X203" s="9"/>
       <c r="Y203" s="9"/>
-      <c r="Z203" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hVjhyh6Wk8D69JCxodq4xhbeU4CAz9ZjZnEVQoy3iHuHI5mo86YANSQdqZbI0TIwIaHGFYUbI2dmaeglkcd9AQ==" saltValue="uNerv9QEFTtsW5Max7oWZQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
-  <mergeCells count="14">
+  <sheetProtection algorithmName="SHA-512" hashValue="7+pa0g19V3o2sFv8RTetTEybSx2KNazgenxUDwxyEqjDUDQ+NPnguP5duaqdBLAk/0yuqK4mlMw+rY16CFiRlg==" saltValue="qgywiyD7PCIWt2z5aGFa8Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="13">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3 G2:G3 H3 J3 L3 R3 Z3 S2:S3 F2:F3 Y3 P3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 F2:F3 G3 I3 K3 Q3 Y3 R2:R3 E2:E3 X3 O3" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2:F3" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
-    <hyperlink ref="Y3" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
-    <hyperlink ref="Z3" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
-    <hyperlink ref="G2:G3" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
-    <hyperlink ref="J3" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
-    <hyperlink ref="N3" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
-    <hyperlink ref="H3" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
-    <hyperlink ref="L3" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
-    <hyperlink ref="R3" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
-    <hyperlink ref="P3" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
-    <hyperlink ref="S2:S3" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
-    <hyperlink ref="E2:E3" r:id="rId12" location="allSpecies" display="SPECIES" xr:uid="{8CFAAA84-FBD1-4238-8363-C5D75B5F8A83}"/>
+    <hyperlink ref="E2:E3" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
+    <hyperlink ref="X3" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
+    <hyperlink ref="Y3" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
+    <hyperlink ref="F2:F3" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
+    <hyperlink ref="I3" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
+    <hyperlink ref="M3" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
+    <hyperlink ref="G3" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
+    <hyperlink ref="K3" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
+    <hyperlink ref="Q3" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
+    <hyperlink ref="O3" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
+    <hyperlink ref="R2:R3" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
+    <hyperlink ref="U3" r:id="rId12" location="sampleTypes" xr:uid="{66503A95-2496-4FEA-BFDB-8687AAF0A03C}"/>
+    <hyperlink ref="V3" r:id="rId13" location="samplePreservationMethods" xr:uid="{9D0827D9-DDF0-4A6C-97A1-CFE63DE06B4E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24117,39 +24125,39 @@
       <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:20" s="55" customFormat="1">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="145" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="143" t="s">
+      <c r="C2" s="145" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="143" t="s">
+      <c r="D2" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="111" t="s">
         <v>190</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="111" t="s">
         <v>191</v>
       </c>
-      <c r="G2" s="108" t="s">
+      <c r="G2" s="111" t="s">
         <v>192</v>
       </c>
-      <c r="H2" s="106" t="s">
+      <c r="H2" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="I2" s="86" t="s">
+      <c r="I2" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="87"/>
-      <c r="K2" s="83" t="s">
+      <c r="J2" s="89"/>
+      <c r="K2" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="85"/>
-      <c r="M2" s="106" t="s">
+      <c r="L2" s="87"/>
+      <c r="M2" s="109" t="s">
         <v>198</v>
       </c>
       <c r="N2" s="147" t="s">
@@ -24158,7 +24166,7 @@
       <c r="O2" s="147" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="106" t="s">
+      <c r="P2" s="109" t="s">
         <v>197</v>
       </c>
       <c r="Q2" s="147" t="s">
@@ -24167,20 +24175,20 @@
       <c r="R2" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="S2" s="89" t="s">
+      <c r="S2" s="91" t="s">
         <v>207</v>
       </c>
-      <c r="T2" s="89"/>
+      <c r="T2" s="91"/>
     </row>
     <row r="3" spans="1:20" s="55" customFormat="1">
-      <c r="A3" s="144"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="107"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="110"/>
       <c r="I3" s="50" t="s">
         <v>194</v>
       </c>
@@ -24193,12 +24201,12 @@
       <c r="L3" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="107"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="91"/>
       <c r="S3" s="50" t="s">
         <v>196</v>
       </c>
@@ -28609,16 +28617,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="owrGYnA0RoV/U9MjDeglShzyfAHibWrOJ91U+dfsJvx7FpXhtP7KXYqD/XawmrJ8WUgOAZj9nC2wQr9dD2KQZw==" saltValue="h+hFQsEVq78bir+WDv8nRA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="H2:H3"/>
@@ -28626,6 +28624,16 @@
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 H2:H3 P2:P3 S3 J3 E2:E3 G2:G3 I3 M2:M3 T3" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -31394,117 +31402,117 @@
       <c r="X1" s="63"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="79" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="89" t="s">
+      <c r="C2" s="79"/>
+      <c r="D2" s="91" t="s">
         <v>173</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="80" t="s">
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="82" t="s">
         <v>228</v>
       </c>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="84"/>
       <c r="Y2" s="53"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="90" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="92" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="90" t="s">
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
-      <c r="X3" s="85"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="86"/>
+      <c r="T3" s="86"/>
+      <c r="U3" s="86"/>
+      <c r="V3" s="86"/>
+      <c r="W3" s="86"/>
+      <c r="X3" s="87"/>
       <c r="Y3" s="53"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="86" t="s">
+      <c r="A4" s="78"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="87"/>
-      <c r="F4" s="86" t="s">
+      <c r="E4" s="89"/>
+      <c r="F4" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="87"/>
-      <c r="H4" s="95" t="s">
+      <c r="G4" s="89"/>
+      <c r="H4" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="I4" s="86" t="s">
+      <c r="I4" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="J4" s="87"/>
-      <c r="K4" s="86" t="s">
+      <c r="J4" s="89"/>
+      <c r="K4" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="L4" s="87"/>
-      <c r="M4" s="92" t="s">
+      <c r="L4" s="89"/>
+      <c r="M4" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="78" t="s">
+      <c r="N4" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="O4" s="78"/>
-      <c r="P4" s="79" t="s">
+      <c r="O4" s="80"/>
+      <c r="P4" s="81" t="s">
         <v>250</v>
       </c>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79" t="s">
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81" t="s">
         <v>251</v>
       </c>
-      <c r="V4" s="79"/>
-      <c r="W4" s="79"/>
-      <c r="X4" s="79"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
     </row>
     <row r="5" spans="1:25" s="54" customFormat="1" ht="18" customHeight="1">
-      <c r="A5" s="77"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="39" t="s">
         <v>124</v>
       </c>
@@ -31523,7 +31531,7 @@
       <c r="G5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="89"/>
+      <c r="H5" s="91"/>
       <c r="I5" s="50" t="s">
         <v>131</v>
       </c>
@@ -31536,7 +31544,7 @@
       <c r="L5" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="93"/>
+      <c r="M5" s="95"/>
       <c r="N5" s="39" t="s">
         <v>5</v>
       </c>
@@ -36831,109 +36839,109 @@
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="99" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="101"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="88"/>
-      <c r="B3" s="97" t="s">
+      <c r="A3" s="90"/>
+      <c r="B3" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="110" t="s">
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="111"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="105" t="s">
+      <c r="H3" s="114"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="108" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="97" t="s">
+      <c r="L3" s="99" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="99"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
+      <c r="P3" s="101"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="88"/>
-      <c r="B4" s="88" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="103" t="s">
+      <c r="C4" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="104" t="s">
+      <c r="D4" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="96" t="s">
+      <c r="F4" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="100" t="s">
+      <c r="G4" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="101" t="s">
+      <c r="H4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="113" t="s">
+      <c r="I4" s="98" t="s">
         <v>174</v>
       </c>
-      <c r="J4" s="106"/>
-      <c r="K4" s="108" t="s">
+      <c r="J4" s="109"/>
+      <c r="K4" s="111" t="s">
         <v>138</v>
       </c>
-      <c r="L4" s="78" t="s">
+      <c r="L4" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78" t="s">
+      <c r="M4" s="80"/>
+      <c r="N4" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="78"/>
-      <c r="P4" s="96" t="s">
+      <c r="O4" s="80"/>
+      <c r="P4" s="102" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="88"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="109"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="112"/>
       <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
@@ -36946,7 +36954,7 @@
       <c r="O5" s="56" t="s">
         <v>249</v>
       </c>
-      <c r="P5" s="96"/>
+      <c r="P5" s="102"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="2"/>
@@ -40551,6 +40559,8 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9TADddINtH3/s8+B+YSEyrbqN3sXm6gNvmsaihCGVKf7Pla3vF7K/W63Z2DPtXhM7gpZzMQTmkRfISjjfsW2DA==" saltValue="PE4zbTBOxopTV3TBfcOFrw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="18">
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="A2:A5"/>
@@ -40567,8 +40577,6 @@
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5 J6 K4:K5 G4:I5 O5" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40626,47 +40634,47 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96" t="s">
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102" t="s">
         <v>230</v>
       </c>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="76"/>
-      <c r="B3" s="90" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="95" t="s">
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="90" t="s">
+      <c r="G3" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="95" t="s">
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="97" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="77"/>
+      <c r="A4" s="79"/>
       <c r="B4" s="50" t="s">
         <v>131</v>
       </c>
@@ -40679,7 +40687,7 @@
       <c r="E4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="89"/>
+      <c r="F4" s="91"/>
       <c r="G4" s="50" t="s">
         <v>131</v>
       </c>
@@ -40692,7 +40700,7 @@
       <c r="J4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="89"/>
+      <c r="K4" s="91"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2"/>
@@ -43413,199 +43421,199 @@
       <c r="AO1" s="5"/>
     </row>
     <row r="2" spans="1:41">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="102" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="115" t="s">
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
+      <c r="S2" s="102"/>
+      <c r="T2" s="102"/>
+      <c r="U2" s="117" t="s">
         <v>231</v>
       </c>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="116"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="115" t="s">
+      <c r="V2" s="118"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="118"/>
+      <c r="AD2" s="118"/>
+      <c r="AE2" s="118"/>
+      <c r="AF2" s="118"/>
+      <c r="AG2" s="119"/>
+      <c r="AH2" s="117" t="s">
         <v>232</v>
       </c>
-      <c r="AI2" s="116"/>
-      <c r="AJ2" s="116"/>
-      <c r="AK2" s="116"/>
-      <c r="AL2" s="116"/>
-      <c r="AM2" s="116"/>
-      <c r="AN2" s="116"/>
-      <c r="AO2" s="117"/>
+      <c r="AI2" s="118"/>
+      <c r="AJ2" s="118"/>
+      <c r="AK2" s="118"/>
+      <c r="AL2" s="118"/>
+      <c r="AM2" s="118"/>
+      <c r="AN2" s="118"/>
+      <c r="AO2" s="119"/>
     </row>
     <row r="3" spans="1:41">
-      <c r="A3" s="88"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="118"/>
-      <c r="X3" s="118"/>
-      <c r="Y3" s="118"/>
-      <c r="Z3" s="118"/>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="118"/>
-      <c r="AD3" s="118"/>
-      <c r="AE3" s="118"/>
-      <c r="AF3" s="118"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="86"/>
-      <c r="AI3" s="118"/>
-      <c r="AJ3" s="118"/>
-      <c r="AK3" s="118"/>
-      <c r="AL3" s="118"/>
-      <c r="AM3" s="118"/>
-      <c r="AN3" s="118"/>
-      <c r="AO3" s="87"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="120"/>
+      <c r="W3" s="120"/>
+      <c r="X3" s="120"/>
+      <c r="Y3" s="120"/>
+      <c r="Z3" s="120"/>
+      <c r="AA3" s="120"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="120"/>
+      <c r="AD3" s="120"/>
+      <c r="AE3" s="120"/>
+      <c r="AF3" s="120"/>
+      <c r="AG3" s="89"/>
+      <c r="AH3" s="88"/>
+      <c r="AI3" s="120"/>
+      <c r="AJ3" s="120"/>
+      <c r="AK3" s="120"/>
+      <c r="AL3" s="120"/>
+      <c r="AM3" s="120"/>
+      <c r="AN3" s="120"/>
+      <c r="AO3" s="89"/>
     </row>
     <row r="4" spans="1:41">
-      <c r="A4" s="88"/>
-      <c r="B4" s="95" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="97" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="95" t="s">
+      <c r="C4" s="97" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="105" t="s">
+      <c r="D4" s="108" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79" t="s">
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="95" t="s">
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="97" t="s">
         <v>171</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79" t="s">
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79" t="s">
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="79"/>
-      <c r="U4" s="96" t="s">
+      <c r="T4" s="81"/>
+      <c r="U4" s="102" t="s">
         <v>152</v>
       </c>
-      <c r="V4" s="96" t="s">
+      <c r="V4" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="W4" s="96" t="s">
+      <c r="W4" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="96" t="s">
+      <c r="X4" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="Y4" s="96" t="s">
+      <c r="Y4" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="Z4" s="96" t="s">
+      <c r="Z4" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="AA4" s="96" t="s">
+      <c r="AA4" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="96" t="s">
+      <c r="AB4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="AC4" s="96" t="s">
+      <c r="AC4" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="AD4" s="96" t="s">
+      <c r="AD4" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="AE4" s="96" t="s">
+      <c r="AE4" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="AF4" s="96" t="s">
+      <c r="AF4" s="102" t="s">
         <v>144</v>
       </c>
-      <c r="AG4" s="96" t="s">
+      <c r="AG4" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="AH4" s="110" t="s">
+      <c r="AH4" s="113" t="s">
         <v>233</v>
       </c>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="79" t="s">
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="AK4" s="79"/>
-      <c r="AL4" s="79" t="s">
+      <c r="AK4" s="81"/>
+      <c r="AL4" s="81" t="s">
         <v>235</v>
       </c>
-      <c r="AM4" s="79"/>
-      <c r="AN4" s="79" t="s">
+      <c r="AM4" s="81"/>
+      <c r="AN4" s="81" t="s">
         <v>236</v>
       </c>
-      <c r="AO4" s="79"/>
+      <c r="AO4" s="81"/>
     </row>
     <row r="5" spans="1:41">
-      <c r="A5" s="88"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="107"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="110"/>
       <c r="E5" s="41" t="s">
         <v>24</v>
       </c>
@@ -43624,7 +43632,7 @@
       <c r="J5" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="K5" s="89"/>
+      <c r="K5" s="91"/>
       <c r="L5" s="38" t="s">
         <v>143</v>
       </c>
@@ -43652,19 +43660,19 @@
       <c r="T5" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="U5" s="96"/>
-      <c r="V5" s="96"/>
-      <c r="W5" s="96"/>
-      <c r="X5" s="96"/>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96"/>
-      <c r="AB5" s="96"/>
-      <c r="AC5" s="96"/>
-      <c r="AD5" s="96"/>
-      <c r="AE5" s="96"/>
-      <c r="AF5" s="96"/>
-      <c r="AG5" s="96"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="102"/>
+      <c r="AE5" s="102"/>
+      <c r="AF5" s="102"/>
+      <c r="AG5" s="102"/>
       <c r="AH5" s="38" t="s">
         <v>153</v>
       </c>
@@ -52293,6 +52301,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NiKKXtjpQMePcsqc5jjUDaSQ7PwYr9+sjfqfZD87x0KbSUAFE8Baue/7fXFs4bMxVWpKhzgpmVEg8+jmkTDZbw==" saltValue="/cWUcVxNNlNaEWVwXWfzkw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="U2:AG3"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH2:AO3"/>
     <mergeCell ref="D4:D5"/>
@@ -52309,20 +52331,6 @@
     <mergeCell ref="AG4:AG5"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="B2:T3"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 R5 AI5 AK5 AM5 L5 M5 N5 O5 P5 Q5 AO5 AJ5 AL5 AN5 AH5" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -52374,38 +52382,38 @@
       <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="90" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="119"/>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="121"/>
+      <c r="B3" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="88" t="s">
+      <c r="D3" s="90" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="119"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="88"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="90"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="119"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="88"/>
+      <c r="A5" s="121"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="90"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2"/>
@@ -53655,64 +53663,64 @@
       <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="102" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="90" t="s">
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="92" t="s">
         <v>222</v>
       </c>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="94"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="96"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="76"/>
-      <c r="B3" s="95" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="97" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="103" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="102" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="119" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="105" t="s">
+      <c r="G3" s="108" t="s">
         <v>164</v>
       </c>
-      <c r="H3" s="105" t="s">
+      <c r="H3" s="108" t="s">
         <v>165</v>
       </c>
-      <c r="I3" s="105" t="s">
+      <c r="I3" s="108" t="s">
         <v>166</v>
       </c>
-      <c r="J3" s="121" t="s">
+      <c r="J3" s="123" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="77"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="122"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="124"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2"/>
@@ -56117,6 +56125,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="rbaELUtMLiFIUzK2Lo99z9d9U/+7pUd8ywEap5Et9u8xKeEcXwzK/YHzlDzNf0b31XcPQzpRtM0zLEm0RaQL/w==" saltValue="qBVdEFs3JSBOU1K55aehjA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
@@ -56124,11 +56137,6 @@
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 G3 H3 I3 J3" xr:uid="{17D462F2-8B43-4EF8-AF0E-D9F26228FDD4}">
@@ -56187,60 +56195,60 @@
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="115" t="s">
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="117" t="s">
         <v>238</v>
       </c>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="117"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="119"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="76"/>
-      <c r="B3" s="126" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="128" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="128" t="s">
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="130" t="s">
         <v>178</v>
       </c>
-      <c r="I3" s="126" t="s">
+      <c r="I3" s="128" t="s">
         <v>179</v>
       </c>
-      <c r="J3" s="123" t="s">
+      <c r="J3" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="118"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="87"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="89"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="77"/>
-      <c r="B4" s="127"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="129"/>
       <c r="C4" s="47" t="s">
         <v>23</v>
       </c>
@@ -56256,8 +56264,8 @@
       <c r="G4" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="129"/>
-      <c r="I4" s="127"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="129"/>
       <c r="J4" s="48" t="s">
         <v>23</v>
       </c>
@@ -59981,128 +59989,128 @@
       <c r="AD1" s="5"/>
     </row>
     <row r="2" spans="1:30" s="55" customFormat="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="119" t="s">
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="121" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="125"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="114" t="s">
+      <c r="G2" s="127"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="116" t="s">
         <v>255</v>
       </c>
-      <c r="J2" s="114" t="s">
+      <c r="J2" s="116" t="s">
         <v>256</v>
       </c>
-      <c r="K2" s="115" t="s">
+      <c r="K2" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="116"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="115" t="s">
+      <c r="L2" s="118"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="117"/>
-      <c r="P2" s="88" t="s">
+      <c r="O2" s="119"/>
+      <c r="P2" s="90" t="s">
         <v>257</v>
       </c>
-      <c r="Q2" s="96" t="s">
+      <c r="Q2" s="102" t="s">
         <v>258</v>
       </c>
-      <c r="R2" s="88" t="s">
+      <c r="R2" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="S2" s="88" t="s">
+      <c r="S2" s="90" t="s">
         <v>265</v>
       </c>
-      <c r="T2" s="88"/>
-      <c r="U2" s="133" t="s">
+      <c r="T2" s="90"/>
+      <c r="U2" s="135" t="s">
         <v>266</v>
       </c>
-      <c r="V2" s="134"/>
-      <c r="W2" s="133" t="s">
+      <c r="V2" s="136"/>
+      <c r="W2" s="135" t="s">
         <v>267</v>
       </c>
-      <c r="X2" s="134"/>
-      <c r="Y2" s="133" t="s">
+      <c r="X2" s="136"/>
+      <c r="Y2" s="135" t="s">
         <v>268</v>
       </c>
-      <c r="Z2" s="134"/>
-      <c r="AA2" s="88" t="s">
+      <c r="Z2" s="136"/>
+      <c r="AA2" s="90" t="s">
         <v>264</v>
       </c>
-      <c r="AB2" s="88"/>
-      <c r="AC2" s="88"/>
-      <c r="AD2" s="88"/>
+      <c r="AB2" s="90"/>
+      <c r="AC2" s="90"/>
+      <c r="AD2" s="90"/>
     </row>
     <row r="3" spans="1:30" s="55" customFormat="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="80" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="120"/>
-      <c r="F3" s="114" t="s">
+      <c r="E3" s="122"/>
+      <c r="F3" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="119" t="s">
+      <c r="G3" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="H3" s="120"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="85"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="85"/>
-      <c r="Y3" s="83"/>
-      <c r="Z3" s="85"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="88"/>
-      <c r="AC3" s="88"/>
-      <c r="AD3" s="88"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="90"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="90"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="87"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="90"/>
+      <c r="AB3" s="90"/>
+      <c r="AC3" s="90"/>
+      <c r="AD3" s="90"/>
     </row>
     <row r="4" spans="1:30" s="55" customFormat="1">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="83"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="85"/>
       <c r="D4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="77"/>
+      <c r="F4" s="79"/>
       <c r="G4" s="39" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
       <c r="K4" s="50" t="s">
         <v>209</v>
       </c>
@@ -60118,9 +60126,9 @@
       <c r="O4" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="88"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="90"/>
       <c r="S4" s="39" t="s">
         <v>50</v>
       </c>
@@ -66533,11 +66541,8 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="d21qlgp65jSu5W9pa5yJ5h6FXV3pmxRSPPtHFMi6kL/5Q045jK8F1FxQGWC8ChuBu/i/+ceDsCkP7hrPZBzfYg==" saltValue="OgP3geBPxDkKLe5cj3oUgQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="N2:O3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
     <mergeCell ref="Y2:Z3"/>
     <mergeCell ref="AA2:AD3"/>
     <mergeCell ref="U2:V3"/>
@@ -66547,12 +66552,15 @@
     <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="S2:T3"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="N2:O3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4 AA4:AD4" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D85421-055F-455D-89D0-5E24FF03DF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106F0932-A472-443F-9273-9E731CAEED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="30030" yWindow="1245" windowWidth="26505" windowHeight="14100" tabRatio="879" firstSheet="11" activeTab="18" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" firstSheet="1" activeTab="1" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1199,7 +1199,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1342,6 +1342,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1435,6 +1446,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1465,9 +1494,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1487,19 +1513,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1512,15 +1532,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1542,93 +1553,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1639,6 +1563,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1978,24 +1911,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="64"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
@@ -2045,15 +1978,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="62"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="62"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2235,11 +2168,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="65"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="68"/>
       <c r="H26" s="13"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3746,54 +3679,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="93" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="104" t="s">
+      <c r="D1" s="93" t="s">
         <v>229</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="104" t="s">
+      <c r="F1" s="93" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="104" t="s">
+      <c r="G1" s="93" t="s">
         <v>227</v>
       </c>
-      <c r="H1" s="104" t="s">
+      <c r="H1" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="104" t="s">
+      <c r="I1" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="80" t="s">
+      <c r="J1" s="83" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="84"/>
-      <c r="L1" s="109" t="s">
+      <c r="K1" s="87"/>
+      <c r="L1" s="108" t="s">
         <v>222</v>
       </c>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
       <c r="O1" s="110"/>
     </row>
     <row r="2" spans="1:15" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
       <c r="J2" s="35" t="s">
         <v>46</v>
       </c>
@@ -7215,17 +7148,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i4Y2GDra9B4e5ZK9IT/yAgpGu83ed66ZNnyRoFvCqT5wVfLy2Lgs30SlszSGdCdYRpnULwm3Kg2BGFX0NXPahA==" saltValue="poZcuJUx5RFD549VWAk8zg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 M2 N2 O2" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7258,21 +7191,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="108" t="s">
         <v>201</v>
       </c>
-      <c r="D1" s="111"/>
+      <c r="D1" s="109"/>
       <c r="E1" s="110"/>
     </row>
     <row r="2" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="44" t="s">
         <v>23</v>
       </c>
@@ -8714,22 +8647,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="44" t="s">
         <v>178</v>
       </c>
@@ -10388,89 +10321,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="108" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="111"/>
+      <c r="D1" s="109"/>
       <c r="E1" s="110"/>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="108" t="s">
         <v>208</v>
       </c>
-      <c r="G1" s="111"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="96" t="s">
+      <c r="I1" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="95" t="s">
+      <c r="J1" s="92" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="78" t="s">
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="78" t="s">
+      <c r="O1" s="81" t="s">
         <v>200</v>
       </c>
-      <c r="P1" s="115" t="s">
+      <c r="P1" s="118" t="s">
         <v>253</v>
       </c>
-      <c r="Q1" s="114" t="s">
+      <c r="Q1" s="117" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="104" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="104" t="s">
+      <c r="F2" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="109" t="s">
+      <c r="G2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="H2" s="110"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="114"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="117"/>
     </row>
     <row r="3" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="67"/>
+      <c r="F3" s="70"/>
       <c r="G3" s="32" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="96"/>
+      <c r="I3" s="103"/>
       <c r="J3" s="38" t="s">
         <v>194</v>
       </c>
@@ -10483,10 +10416,10 @@
       <c r="M3" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="114"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="117"/>
     </row>
     <row r="4" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -14291,6 +14224,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="j7MUMGPBrETWcazR2JxyYWg7EsALd6nWBPrG0+KpBwzqgUF6TIdENL/ZaQBEBI6zU+Z6UHRHz3zwzs6KvZx01A==" saltValue="H5P+A2rusa74O5dl1z34ZQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="F1:H1"/>
@@ -14300,11 +14238,6 @@
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I3 M3 J3 K3 L3 Q1:Q3" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14338,20 +14271,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="84"/>
+      <c r="D1" s="87"/>
     </row>
     <row r="2" spans="1:4" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="35" t="s">
         <v>145</v>
       </c>
@@ -15591,47 +15524,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="121" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="148" t="s">
+      <c r="E1" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="149"/>
-      <c r="G1" s="86" t="s">
+      <c r="F1" s="124"/>
+      <c r="G1" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="104" t="s">
+      <c r="H1" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="80" t="s">
+      <c r="I1" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="81"/>
-      <c r="K1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="87"/>
     </row>
     <row r="2" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="147"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="122"/>
       <c r="E2" s="44" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="67"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="70"/>
       <c r="I2" s="38" t="s">
         <v>186</v>
       </c>
@@ -18245,14 +18178,14 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="JA+gDfx9HL2mV0Tdxs3H6w2uRT4wHZDQJ8yXQoLv5fxFnTThYZmX+TLadTXq48/15VXPdFGIRAdSIbF5KO1tGQ==" saltValue="Z6n+HwaoylFKFjVBtH70GA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2 E2:F2 K2 G1" xr:uid="{4E0B6771-5993-41A9-BE9D-F553134C1037}">
@@ -18307,65 +18240,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="125" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="125" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="118" t="s">
+      <c r="C1" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="118" t="s">
+      <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="86" t="s">
+      <c r="E1" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="95" t="s">
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="92" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95" t="s">
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="101" t="s">
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="80" t="s">
+      <c r="S1" s="83" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="84"/>
-      <c r="U1" s="80" t="s">
+      <c r="T1" s="87"/>
+      <c r="U1" s="83" t="s">
         <v>192</v>
       </c>
-      <c r="V1" s="81"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="95" t="s">
+      <c r="V1" s="84"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="92" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="95"/>
+      <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:25" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
       <c r="G2" s="44" t="s">
         <v>23</v>
       </c>
@@ -18399,7 +18332,7 @@
       <c r="Q2" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="R2" s="103"/>
+      <c r="R2" s="91"/>
       <c r="S2" s="36" t="s">
         <v>85</v>
       </c>
@@ -23892,70 +23825,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="125" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="125" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="118" t="s">
+      <c r="C1" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="118" t="s">
+      <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="86" t="s">
+      <c r="E1" s="94" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="86" t="s">
+      <c r="G1" s="94" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="102" t="s">
+      <c r="H1" s="90" t="s">
         <v>177</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="77"/>
-      <c r="K1" s="73" t="s">
+      <c r="J1" s="80"/>
+      <c r="K1" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="102" t="s">
+      <c r="L1" s="78"/>
+      <c r="M1" s="90" t="s">
         <v>182</v>
       </c>
-      <c r="N1" s="120" t="s">
+      <c r="N1" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="120" t="s">
+      <c r="O1" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="102" t="s">
+      <c r="P1" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="Q1" s="120" t="s">
+      <c r="Q1" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="120" t="s">
+      <c r="R1" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="79" t="s">
+      <c r="S1" s="82" t="s">
         <v>191</v>
       </c>
-      <c r="T1" s="79"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:20" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="119"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="103"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="91"/>
       <c r="I2" s="38" t="s">
         <v>178</v>
       </c>
@@ -23968,12 +23901,12 @@
       <c r="L2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="103"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
       <c r="S2" s="38" t="s">
         <v>180</v>
       </c>
@@ -28384,16 +28317,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="l8KVIJiIcXBtA5Rxt+oHSTZCQcSscxoVEx71fajOPkkDzIq7y1m1u1pHAE+AUnT93CwTnM5PkUuxYj42pmVV9g==" saltValue="dsO/0LEKtl67ZZqtPejb6A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="H1:H2"/>
@@ -28401,6 +28324,16 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 H1:H2 P1:P2 S2 J2 E1:E2 G1:G2 I2 M1:M2 T2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -31126,117 +31059,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="79" t="s">
+      <c r="C1" s="70"/>
+      <c r="D1" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="70" t="s">
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="73" t="s">
         <v>210</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
-      <c r="W1" s="71"/>
-      <c r="X1" s="72"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="75"/>
       <c r="Y1" s="41"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="80" t="s">
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="75"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
+      <c r="W2" s="77"/>
+      <c r="X2" s="78"/>
       <c r="Y2" s="41"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="66"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="76" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76" t="s">
+      <c r="E3" s="80"/>
+      <c r="F3" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="85" t="s">
+      <c r="G3" s="80"/>
+      <c r="H3" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="76" t="s">
+      <c r="J3" s="80"/>
+      <c r="K3" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="77"/>
-      <c r="M3" s="82" t="s">
+      <c r="L3" s="80"/>
+      <c r="M3" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="N3" s="68" t="s">
+      <c r="N3" s="71" t="s">
         <v>233</v>
       </c>
-      <c r="O3" s="68"/>
-      <c r="P3" s="69" t="s">
+      <c r="O3" s="71"/>
+      <c r="P3" s="72" t="s">
         <v>231</v>
       </c>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69" t="s">
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72" t="s">
         <v>232</v>
       </c>
-      <c r="V3" s="69"/>
-      <c r="W3" s="69"/>
-      <c r="X3" s="69"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
     </row>
     <row r="4" spans="1:25" s="42" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
+      <c r="A4" s="70"/>
       <c r="B4" s="32" t="s">
         <v>108</v>
       </c>
@@ -31255,7 +31188,7 @@
       <c r="G4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="79"/>
+      <c r="H4" s="82"/>
       <c r="I4" s="38" t="s">
         <v>115</v>
       </c>
@@ -31268,7 +31201,7 @@
       <c r="L4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="83"/>
+      <c r="M4" s="86"/>
       <c r="N4" s="32" t="s">
         <v>5</v>
       </c>
@@ -36543,89 +36476,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="88" t="s">
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="89"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="101" t="s">
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="89" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="92" t="s">
+      <c r="L1" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="94"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="102"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="78" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="95" t="s">
+      <c r="F2" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="96" t="s">
+      <c r="G2" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="97" t="s">
+      <c r="H2" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="I2" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="102"/>
-      <c r="K2" s="86" t="s">
+      <c r="J2" s="90"/>
+      <c r="K2" s="94" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="68" t="s">
+      <c r="L2" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68" t="s">
+      <c r="M2" s="71"/>
+      <c r="N2" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="68"/>
-      <c r="P2" s="95" t="s">
+      <c r="O2" s="71"/>
+      <c r="P2" s="92" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="87"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="95"/>
       <c r="L3" s="32" t="s">
         <v>3</v>
       </c>
@@ -36638,7 +36571,7 @@
       <c r="O3" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="P3" s="95"/>
+      <c r="P3" s="92"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -40243,12 +40176,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="yP1GbBCgAdm0CH/gr8AK4RsVM1gtv82RP3HgfmHP3L5tX6iCxw/IjCz2X6Q4KidklCbEORnuuGS+Q9kp+KNj3w==" saltValue="R0+mSYCgXyR4udjvNYppsg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -40260,6 +40187,12 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 J4 K2:K3 G2:I3 O3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40302,47 +40235,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="92" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95" t="s">
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="80" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="85" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="85" t="s">
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="38" t="s">
         <v>115</v>
       </c>
@@ -40355,7 +40288,7 @@
       <c r="E3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="79"/>
+      <c r="F3" s="82"/>
       <c r="G3" s="38" t="s">
         <v>115</v>
       </c>
@@ -40368,7 +40301,7 @@
       <c r="J3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="79"/>
+      <c r="K3" s="82"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -43044,156 +42977,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="83" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="80" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="84"/>
-      <c r="AH1" s="80" t="s">
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+      <c r="Z1" s="84"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AD1" s="84"/>
+      <c r="AE1" s="84"/>
+      <c r="AF1" s="84"/>
+      <c r="AG1" s="87"/>
+      <c r="AH1" s="83" t="s">
         <v>214</v>
       </c>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="84"/>
+      <c r="AI1" s="84"/>
+      <c r="AJ1" s="84"/>
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
+      <c r="AM1" s="84"/>
+      <c r="AN1" s="84"/>
+      <c r="AO1" s="87"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="85" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="101" t="s">
+      <c r="D2" s="89" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69" t="s">
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="85" t="s">
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="L2" s="69" t="s">
+      <c r="L2" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69" t="s">
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69" t="s">
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="69"/>
-      <c r="U2" s="95" t="s">
+      <c r="T2" s="72"/>
+      <c r="U2" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="95" t="s">
+      <c r="V2" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="95" t="s">
+      <c r="W2" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="95" t="s">
+      <c r="X2" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="95" t="s">
+      <c r="Y2" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="95" t="s">
+      <c r="Z2" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="95" t="s">
+      <c r="AA2" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="95" t="s">
+      <c r="AB2" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="95" t="s">
+      <c r="AC2" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="95" t="s">
+      <c r="AD2" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="95" t="s">
+      <c r="AE2" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="95" t="s">
+      <c r="AF2" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="AG2" s="95" t="s">
+      <c r="AG2" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="88" t="s">
+      <c r="AH2" s="96" t="s">
         <v>215</v>
       </c>
-      <c r="AI2" s="90"/>
-      <c r="AJ2" s="69" t="s">
+      <c r="AI2" s="98"/>
+      <c r="AJ2" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="AK2" s="69"/>
-      <c r="AL2" s="69" t="s">
+      <c r="AK2" s="72"/>
+      <c r="AL2" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="69" t="s">
+      <c r="AM2" s="72"/>
+      <c r="AN2" s="72" t="s">
         <v>218</v>
       </c>
-      <c r="AO2" s="69"/>
+      <c r="AO2" s="72"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="103"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="91"/>
       <c r="E3" s="34" t="s">
         <v>24</v>
       </c>
@@ -43212,7 +43145,7 @@
       <c r="J3" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="K3" s="79"/>
+      <c r="K3" s="82"/>
       <c r="L3" s="31" t="s">
         <v>127</v>
       </c>
@@ -43240,19 +43173,19 @@
       <c r="T3" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="U3" s="95"/>
-      <c r="V3" s="95"/>
-      <c r="W3" s="95"/>
-      <c r="X3" s="95"/>
-      <c r="Y3" s="95"/>
-      <c r="Z3" s="95"/>
-      <c r="AA3" s="95"/>
-      <c r="AB3" s="95"/>
-      <c r="AC3" s="95"/>
-      <c r="AD3" s="95"/>
-      <c r="AE3" s="95"/>
-      <c r="AF3" s="95"/>
-      <c r="AG3" s="95"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="92"/>
       <c r="AH3" s="31" t="s">
         <v>137</v>
       </c>
@@ -51881,6 +51814,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wxJYPTS1M8YrpE+F5HXpzPvhVkWn+uzvbhQbX4zWGt7tgJJAc6rvipv1/0hraJgXbUY0X5vYRquC66cBDOGcbg==" saltValue="RWTcEymG3DdteXmtyGeu4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -51897,20 +51844,6 @@
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 R3 AI3 AK3 AM3 L3 M3 N3 O3 P3 Q3 AO3 AJ3 AL3 AN3 AH3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -51954,17 +51887,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
+      <c r="A2" s="70"/>
       <c r="B2" s="32" t="s">
         <v>165</v>
       </c>
@@ -53206,25 +53139,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="92" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="80" t="s">
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="83" t="s">
         <v>206</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="87"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
+      <c r="A2" s="70"/>
       <c r="B2" s="50" t="s">
         <v>145</v>
       </c>
@@ -55697,96 +55630,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="122" t="s">
+      <c r="B1" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="125" t="s">
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="111" t="s">
         <v>219</v>
       </c>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="127"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="113"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="128"/>
-      <c r="B2" s="121" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="93" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="129" t="s">
+      <c r="C2" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="132" t="s">
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="J2" s="133" t="s">
+      <c r="J2" s="83" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="134"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="137"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="80"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="138"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="139" t="s">
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="140" t="s">
+      <c r="D3" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="141" t="s">
+      <c r="E3" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="140" t="s">
+      <c r="F3" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="141" t="s">
+      <c r="G3" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="142"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="143" t="s">
+      <c r="H3" s="82"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="143" t="s">
+      <c r="K3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="144" t="s">
+      <c r="L3" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="M3" s="145" t="s">
+      <c r="M3" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="N3" s="145" t="s">
+      <c r="N3" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="O3" s="145" t="s">
+      <c r="O3" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="P3" s="145" t="s">
+      <c r="P3" s="33" t="s">
         <v>169</v>
       </c>
     </row>
@@ -59457,128 +59390,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="109" t="s">
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="111"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="104" t="s">
+      <c r="I1" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="104" t="s">
+      <c r="J1" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="K1" s="105" t="s">
+      <c r="K1" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="105" t="s">
+      <c r="L1" s="112"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="107"/>
-      <c r="P1" s="78" t="s">
+      <c r="O1" s="113"/>
+      <c r="P1" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="95" t="s">
+      <c r="Q1" s="92" t="s">
         <v>239</v>
       </c>
-      <c r="R1" s="78" t="s">
+      <c r="R1" s="81" t="s">
         <v>240</v>
       </c>
-      <c r="S1" s="78" t="s">
+      <c r="S1" s="81" t="s">
         <v>246</v>
       </c>
-      <c r="T1" s="78"/>
-      <c r="U1" s="112" t="s">
+      <c r="T1" s="81"/>
+      <c r="U1" s="115" t="s">
         <v>247</v>
       </c>
-      <c r="V1" s="113"/>
-      <c r="W1" s="112" t="s">
+      <c r="V1" s="116"/>
+      <c r="W1" s="115" t="s">
         <v>248</v>
       </c>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="112" t="s">
+      <c r="X1" s="116"/>
+      <c r="Y1" s="115" t="s">
         <v>249</v>
       </c>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="78" t="s">
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
     </row>
     <row r="2" spans="1:30" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="70" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="104" t="s">
+      <c r="F2" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="109" t="s">
+      <c r="G2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="H2" s="110"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="75"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="75"/>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="75"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="78"/>
-      <c r="AC2" s="78"/>
-      <c r="AD2" s="78"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="76"/>
+      <c r="Z2" s="78"/>
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="81"/>
     </row>
     <row r="3" spans="1:30" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="73"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="76"/>
       <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="67"/>
+      <c r="F3" s="70"/>
       <c r="G3" s="32" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
       <c r="K3" s="38" t="s">
         <v>193</v>
       </c>
@@ -59594,9 +59527,9 @@
       <c r="O3" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="78"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="81"/>
       <c r="S3" s="32" t="s">
         <v>50</v>
       </c>
@@ -66009,12 +65942,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9xCUSnOba9+kjRTP4aA+IhYIhPNTdofqr3mLiTZOPQAzcWWZifDmPOI/0ItUaLA4hSjA/rC4jIft53nJzygclQ==" saltValue="aTfUQq44C7asIKTaLqEvww==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="Y1:Z2"/>
     <mergeCell ref="AA1:AD2"/>
     <mergeCell ref="U1:V2"/>
@@ -66024,11 +65956,12 @@
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="S1:T2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106F0932-A472-443F-9273-9E731CAEED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4050EE-B9A4-4B1D-B2EE-22A34FC302D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" firstSheet="1" activeTab="1" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1254,9 +1254,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1446,21 +1443,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1494,6 +1476,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1512,6 +1497,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1574,6 +1571,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1911,24 +1909,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="61"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="64"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
@@ -1978,15 +1976,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="65"/>
+      <c r="D8" s="64"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="65" t="s">
+      <c r="F8" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="65"/>
+      <c r="G8" s="64"/>
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2108,7 +2106,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="11"/>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D20" s="21"/>
@@ -2119,7 +2117,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="11"/>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="127" t="s">
         <v>107</v>
       </c>
       <c r="D21" s="21"/>
@@ -2168,11 +2166,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="68"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="67"/>
       <c r="H26" s="13"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2189,7 +2187,7 @@
       <c r="D28" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fECAul9Xub1IkDhYUJjwJS9OzYzo0I9Z1C6jwPBr+eEjzIjgSDIhJ1EXiZzgp9q6fPNfWYq+aXIj8dGPnToVoA==" saltValue="U4C95otBxdOcIHYcesbhsA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2204,9 +2202,10 @@
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="entities" xr:uid="{384D1750-687F-4E8E-BDBD-927F2E2E470C}"/>
     <hyperlink ref="C20" r:id="rId2" location="fleets" xr:uid="{07140C16-0A83-41FD-984B-2B188EE4EBA5}"/>
+    <hyperlink ref="C21" r:id="rId3" location="sourcesRO" xr:uid="{14D27D57-85D2-43E5-9AF0-D8C32445BC32}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2225,24 +2224,24 @@
     <col min="5" max="5" width="19.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="47" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3678,71 +3677,71 @@
     <col min="12" max="15" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:15" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="93" t="s">
+      <c r="C1" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="93" t="s">
+      <c r="D1" s="88" t="s">
         <v>229</v>
       </c>
-      <c r="E1" s="88" t="s">
+      <c r="E1" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="93" t="s">
+      <c r="F1" s="88" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="93" t="s">
+      <c r="G1" s="88" t="s">
         <v>227</v>
       </c>
-      <c r="H1" s="93" t="s">
+      <c r="H1" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="93" t="s">
+      <c r="I1" s="88" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="83" t="s">
+      <c r="J1" s="82" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="87"/>
-      <c r="L1" s="108" t="s">
+      <c r="K1" s="86"/>
+      <c r="L1" s="107" t="s">
         <v>222</v>
       </c>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="110"/>
-    </row>
-    <row r="2" spans="1:15" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="35" t="s">
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="109"/>
+    </row>
+    <row r="2" spans="1:15" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="35" t="s">
+      <c r="K2" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="43" t="s">
         <v>224</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="O2" s="44" t="s">
+      <c r="O2" s="43" t="s">
         <v>226</v>
       </c>
     </row>
@@ -7190,29 +7189,29 @@
     <col min="5" max="5" width="14.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="107" t="s">
         <v>201</v>
       </c>
-      <c r="D1" s="109"/>
-      <c r="E1" s="110"/>
-    </row>
-    <row r="2" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="44" t="s">
+      <c r="D1" s="108"/>
+      <c r="E1" s="109"/>
+    </row>
+    <row r="2" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>52</v>
       </c>
     </row>
@@ -8646,33 +8645,33 @@
     <col min="6" max="6" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
-    </row>
-    <row r="2" spans="1:6" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="44" t="s">
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109"/>
+    </row>
+    <row r="2" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="34" t="s">
         <v>53</v>
       </c>
     </row>
@@ -10320,108 +10319,108 @@
     <col min="17" max="17" width="27.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="107" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="109"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="108" t="s">
+      <c r="D1" s="108"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="103" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="92" t="s">
+      <c r="J1" s="98" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="81" t="s">
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="81" t="s">
+      <c r="O1" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="P1" s="118" t="s">
+      <c r="P1" s="117" t="s">
         <v>253</v>
       </c>
-      <c r="Q1" s="117" t="s">
+      <c r="Q1" s="116" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="93" t="s">
+    <row r="2" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="107" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="93" t="s">
+      <c r="E2" s="109"/>
+      <c r="F2" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="108" t="s">
+      <c r="G2" s="107" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="110"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="117"/>
-    </row>
-    <row r="3" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="32" t="s">
+      <c r="H2" s="109"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="116"/>
+    </row>
+    <row r="3" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="70"/>
-      <c r="G3" s="32" t="s">
+      <c r="F3" s="69"/>
+      <c r="G3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="103"/>
-      <c r="J3" s="38" t="s">
+      <c r="I3" s="99"/>
+      <c r="J3" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="117"/>
-    </row>
-    <row r="4" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="119"/>
+      <c r="Q3" s="116"/>
+    </row>
+    <row r="4" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -14270,25 +14269,25 @@
     <col min="4" max="4" width="21.7109375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:4" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="87"/>
-    </row>
-    <row r="2" spans="1:4" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="35" t="s">
+      <c r="D1" s="86"/>
+    </row>
+    <row r="2" spans="1:4" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="34" t="s">
         <v>185</v>
       </c>
     </row>
@@ -15523,59 +15522,59 @@
     <col min="11" max="11" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="93" t="s">
+      <c r="C1" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="121" t="s">
+      <c r="D1" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="E1" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="94" t="s">
+      <c r="F1" s="123"/>
+      <c r="G1" s="89" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="93" t="s">
+      <c r="H1" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="87"/>
-    </row>
-    <row r="2" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="44" t="s">
+      <c r="J1" s="83"/>
+      <c r="K1" s="86"/>
+    </row>
+    <row r="2" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="38" t="s">
+      <c r="G2" s="90"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="37" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -18239,123 +18238,123 @@
     <col min="25" max="25" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="124" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="125" t="s">
+      <c r="C1" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="125" t="s">
+      <c r="D1" s="124" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="94" t="s">
+      <c r="E1" s="89" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="94" t="s">
+      <c r="F1" s="89" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="92" t="s">
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="98" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92" t="s">
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="89" t="s">
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="83" t="s">
+      <c r="S1" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="87"/>
-      <c r="U1" s="83" t="s">
+      <c r="T1" s="86"/>
+      <c r="U1" s="82" t="s">
         <v>192</v>
       </c>
-      <c r="V1" s="84"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="92" t="s">
+      <c r="V1" s="83"/>
+      <c r="W1" s="86"/>
+      <c r="X1" s="98" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="92"/>
-    </row>
-    <row r="2" spans="1:25" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="44" t="s">
+      <c r="Y1" s="98"/>
+    </row>
+    <row r="2" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="35" t="s">
+      <c r="L2" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="O2" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="P2" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="Q2" s="38" t="s">
+      <c r="Q2" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="R2" s="91"/>
-      <c r="S2" s="36" t="s">
+      <c r="R2" s="106"/>
+      <c r="S2" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="36" t="s">
+      <c r="T2" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="U2" s="55" t="s">
+      <c r="U2" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="V2" s="55" t="s">
+      <c r="V2" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="W2" s="35" t="s">
+      <c r="W2" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="X2" s="38" t="s">
+      <c r="X2" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Y2" s="37" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -23824,97 +23823,97 @@
     <col min="19" max="20" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:20" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="124" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="125" t="s">
+      <c r="C1" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="125" t="s">
+      <c r="D1" s="124" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="94" t="s">
+      <c r="E1" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="94" t="s">
+      <c r="F1" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="94" t="s">
+      <c r="G1" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="90" t="s">
+      <c r="H1" s="105" t="s">
         <v>177</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="80"/>
-      <c r="K1" s="76" t="s">
+      <c r="J1" s="79"/>
+      <c r="K1" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="78"/>
-      <c r="M1" s="90" t="s">
+      <c r="L1" s="77"/>
+      <c r="M1" s="105" t="s">
         <v>182</v>
       </c>
-      <c r="N1" s="127" t="s">
+      <c r="N1" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="127" t="s">
+      <c r="O1" s="126" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="90" t="s">
+      <c r="P1" s="105" t="s">
         <v>181</v>
       </c>
-      <c r="Q1" s="127" t="s">
+      <c r="Q1" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="127" t="s">
+      <c r="R1" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="82" t="s">
+      <c r="S1" s="81" t="s">
         <v>191</v>
       </c>
-      <c r="T1" s="82"/>
-    </row>
-    <row r="2" spans="1:20" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="38" t="s">
+      <c r="T1" s="81"/>
+    </row>
+    <row r="2" spans="1:20" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="L2" s="35" t="s">
+      <c r="L2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="91"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="38" t="s">
+      <c r="M2" s="106"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="37" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="43" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -28375,55 +28374,55 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="34" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-    </row>
-    <row r="3" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+    </row>
+    <row r="3" spans="1:11" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -31059,180 +31058,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="82" t="s">
+      <c r="C1" s="69"/>
+      <c r="D1" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="73" t="s">
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="72" t="s">
         <v>210</v>
       </c>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="41"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="40"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="83" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="83" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="41"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="40"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="69"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="79" t="s">
+      <c r="A3" s="68"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="79" t="s">
+      <c r="E3" s="79"/>
+      <c r="F3" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="88" t="s">
+      <c r="G3" s="79"/>
+      <c r="H3" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="79" t="s">
+      <c r="J3" s="79"/>
+      <c r="K3" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="80"/>
-      <c r="M3" s="85" t="s">
+      <c r="L3" s="79"/>
+      <c r="M3" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="70" t="s">
         <v>233</v>
       </c>
-      <c r="O3" s="71"/>
-      <c r="P3" s="72" t="s">
+      <c r="O3" s="70"/>
+      <c r="P3" s="71" t="s">
         <v>231</v>
       </c>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72" t="s">
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71" t="s">
         <v>232</v>
       </c>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-    </row>
-    <row r="4" spans="1:25" s="42" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="32" t="s">
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+    </row>
+    <row r="4" spans="1:25" s="41" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="69"/>
+      <c r="B4" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="38" t="s">
+      <c r="H4" s="81"/>
+      <c r="I4" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="L4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="86"/>
-      <c r="N4" s="32" t="s">
+      <c r="M4" s="85"/>
+      <c r="N4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="32" t="s">
+      <c r="O4" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="35" t="s">
+      <c r="Q4" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="35" t="s">
+      <c r="R4" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="35" t="s">
+      <c r="S4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="35" t="s">
+      <c r="T4" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="31" t="s">
+      <c r="U4" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="V4" s="31" t="s">
+      <c r="V4" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="W4" s="31" t="s">
+      <c r="W4" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="X4" s="31" t="s">
+      <c r="X4" s="30" t="s">
         <v>119</v>
       </c>
     </row>
@@ -36476,102 +36475,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="96" t="s">
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="89" t="s">
+      <c r="H1" s="92"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="100" t="s">
+      <c r="L1" s="95" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="102"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="97"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="81" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="106" t="s">
+      <c r="C2" s="102" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="D2" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="103" t="s">
+      <c r="G2" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="104" t="s">
+      <c r="H2" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="90"/>
-      <c r="K2" s="94" t="s">
+      <c r="J2" s="105"/>
+      <c r="K2" s="89" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="71" t="s">
+      <c r="L2" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71" t="s">
+      <c r="M2" s="70"/>
+      <c r="N2" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="71"/>
-      <c r="P2" s="92" t="s">
+      <c r="O2" s="70"/>
+      <c r="P2" s="98" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="32" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="44" t="s">
+      <c r="M3" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="44" t="s">
+      <c r="O3" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="P3" s="92"/>
+      <c r="P3" s="98"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -40174,8 +40173,13 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yP1GbBCgAdm0CH/gr8AK4RsVM1gtv82RP3HgfmHP3L5tX6iCxw/IjCz2X6Q4KidklCbEORnuuGS+Q9kp+KNj3w==" saltValue="R0+mSYCgXyR4udjvNYppsg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CVc9Y6zTViK+qNBvkHM6Vw9LbbIcQvJhEGHDobnK2WxxzdUIpXEi5D/0B5vCJa09eTPUkAUYi73wUk86TeXIgw==" saltValue="8ea3UICepsiuwTlX9cWVdA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -40188,11 +40192,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="J1:J3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 J4 K2:K3 G2:I3 O3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40208,6 +40207,7 @@
     <hyperlink ref="H2" r:id="rId6" display="PORT_CODE" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
     <hyperlink ref="K2:K3" r:id="rId7" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{ADDD99C7-B692-4517-AF11-C5F4715C3781}"/>
     <hyperlink ref="H2:H3" r:id="rId8" location="Ports" display="PORT" xr:uid="{4BCE8909-E3DB-4961-B5C5-527D383D1926}"/>
+    <hyperlink ref="J1:J3" r:id="rId9" location="targetSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{8145BEA5-06D1-4F1F-890E-1ACE66463F94}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40235,73 +40235,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="98" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92" t="s">
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="83" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="88" t="s">
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="88" t="s">
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="38" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="82"/>
-      <c r="G3" s="38" t="s">
+      <c r="F3" s="81"/>
+      <c r="G3" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="82"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -42977,237 +42977,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="83" t="s">
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="86"/>
+      <c r="U1" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
-      <c r="Z1" s="84"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="84"/>
-      <c r="AD1" s="84"/>
-      <c r="AE1" s="84"/>
-      <c r="AF1" s="84"/>
-      <c r="AG1" s="87"/>
-      <c r="AH1" s="83" t="s">
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="83"/>
+      <c r="AF1" s="83"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="AI1" s="84"/>
-      <c r="AJ1" s="84"/>
-      <c r="AK1" s="84"/>
-      <c r="AL1" s="84"/>
-      <c r="AM1" s="84"/>
-      <c r="AN1" s="84"/>
-      <c r="AO1" s="87"/>
+      <c r="AI1" s="83"/>
+      <c r="AJ1" s="83"/>
+      <c r="AK1" s="83"/>
+      <c r="AL1" s="83"/>
+      <c r="AM1" s="83"/>
+      <c r="AN1" s="83"/>
+      <c r="AO1" s="86"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="88" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="104" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="71" t="s">
         <v>172</v>
       </c>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72" t="s">
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="88" t="s">
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="L2" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72" t="s">
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72" t="s">
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="72"/>
-      <c r="U2" s="92" t="s">
+      <c r="T2" s="71"/>
+      <c r="U2" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="92" t="s">
+      <c r="V2" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="92" t="s">
+      <c r="W2" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="92" t="s">
+      <c r="X2" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="92" t="s">
+      <c r="Y2" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="92" t="s">
+      <c r="Z2" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="92" t="s">
+      <c r="AA2" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="92" t="s">
+      <c r="AB2" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="92" t="s">
+      <c r="AC2" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="92" t="s">
+      <c r="AD2" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="92" t="s">
+      <c r="AE2" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="92" t="s">
+      <c r="AF2" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="AG2" s="92" t="s">
+      <c r="AG2" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="96" t="s">
+      <c r="AH2" s="91" t="s">
         <v>215</v>
       </c>
-      <c r="AI2" s="98"/>
-      <c r="AJ2" s="72" t="s">
+      <c r="AI2" s="93"/>
+      <c r="AJ2" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="72" t="s">
+      <c r="AK2" s="71"/>
+      <c r="AL2" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="AM2" s="72"/>
-      <c r="AN2" s="72" t="s">
+      <c r="AM2" s="71"/>
+      <c r="AN2" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="AO2" s="72"/>
+      <c r="AO2" s="71"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="34" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="K3" s="82"/>
-      <c r="L3" s="31" t="s">
+      <c r="K3" s="81"/>
+      <c r="L3" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="M3" s="31" t="s">
+      <c r="M3" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="Q3" s="31" t="s">
+      <c r="Q3" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="31" t="s">
+      <c r="R3" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="S3" s="34" t="s">
+      <c r="S3" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="37" t="s">
+      <c r="T3" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="92"/>
-      <c r="AE3" s="92"/>
-      <c r="AF3" s="92"/>
-      <c r="AG3" s="92"/>
-      <c r="AH3" s="31" t="s">
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
+      <c r="X3" s="98"/>
+      <c r="Y3" s="98"/>
+      <c r="Z3" s="98"/>
+      <c r="AA3" s="98"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="98"/>
+      <c r="AD3" s="98"/>
+      <c r="AE3" s="98"/>
+      <c r="AF3" s="98"/>
+      <c r="AG3" s="98"/>
+      <c r="AH3" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="AI3" s="31" t="s">
+      <c r="AI3" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="AJ3" s="31" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="AK3" s="31" t="s">
+      <c r="AK3" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="AL3" s="31" t="s">
+      <c r="AL3" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="AM3" s="31" t="s">
+      <c r="AM3" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="AN3" s="31" t="s">
+      <c r="AN3" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="AO3" s="31" t="s">
+      <c r="AO3" s="30" t="s">
         <v>144</v>
       </c>
     </row>
@@ -51887,30 +51887,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="32" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="31" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="30"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
@@ -53139,50 +53139,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="98" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="83" t="s">
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="82" t="s">
         <v>206</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="87"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="86"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="50" t="s">
+      <c r="A2" s="69"/>
+      <c r="B2" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="53" t="s">
         <v>151</v>
       </c>
     </row>
@@ -55630,96 +55630,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="107" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="111" t="s">
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="110" t="s">
         <v>219</v>
       </c>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="113"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="112"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="93" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="88" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="88" t="s">
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="87" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="93" t="s">
+      <c r="I2" s="88" t="s">
         <v>163</v>
       </c>
-      <c r="J2" s="83" t="s">
+      <c r="J2" s="82" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="87"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="80"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="79"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="56" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="82"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="57" t="s">
+      <c r="H3" s="81"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="58" t="s">
+      <c r="L3" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="M3" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="O3" s="33" t="s">
+      <c r="O3" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="P3" s="33" t="s">
+      <c r="P3" s="32" t="s">
         <v>169</v>
       </c>
     </row>
@@ -59389,181 +59389,181 @@
     <col min="27" max="30" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:30" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="108" t="s">
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="107" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="93" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="88" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="93" t="s">
+      <c r="J1" s="88" t="s">
         <v>237</v>
       </c>
-      <c r="K1" s="111" t="s">
+      <c r="K1" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="112"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="111" t="s">
+      <c r="L1" s="111"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="113"/>
-      <c r="P1" s="81" t="s">
+      <c r="O1" s="112"/>
+      <c r="P1" s="80" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="92" t="s">
+      <c r="Q1" s="98" t="s">
         <v>239</v>
       </c>
-      <c r="R1" s="81" t="s">
+      <c r="R1" s="80" t="s">
         <v>240</v>
       </c>
-      <c r="S1" s="81" t="s">
+      <c r="S1" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="T1" s="81"/>
-      <c r="U1" s="115" t="s">
+      <c r="T1" s="80"/>
+      <c r="U1" s="114" t="s">
         <v>247</v>
       </c>
-      <c r="V1" s="116"/>
-      <c r="W1" s="115" t="s">
+      <c r="V1" s="115"/>
+      <c r="W1" s="114" t="s">
         <v>248</v>
       </c>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="115" t="s">
+      <c r="X1" s="115"/>
+      <c r="Y1" s="114" t="s">
         <v>249</v>
       </c>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="81" t="s">
+      <c r="Z1" s="115"/>
+      <c r="AA1" s="80" t="s">
         <v>245</v>
       </c>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-    </row>
-    <row r="2" spans="1:30" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="73" t="s">
+      <c r="AB1" s="80"/>
+      <c r="AC1" s="80"/>
+      <c r="AD1" s="80"/>
+    </row>
+    <row r="2" spans="1:30" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="107" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="93" t="s">
+      <c r="E2" s="109"/>
+      <c r="F2" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="108" t="s">
+      <c r="G2" s="107" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="110"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="76"/>
-      <c r="Z2" s="78"/>
-      <c r="AA2" s="81"/>
-      <c r="AB2" s="81"/>
-      <c r="AC2" s="81"/>
-      <c r="AD2" s="81"/>
-    </row>
-    <row r="3" spans="1:30" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="32" t="s">
+      <c r="H2" s="109"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="75"/>
+      <c r="V2" s="77"/>
+      <c r="W2" s="75"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="75"/>
+      <c r="Z2" s="77"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+    </row>
+    <row r="3" spans="1:30" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="70"/>
-      <c r="G3" s="32" t="s">
+      <c r="F3" s="69"/>
+      <c r="G3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="38" t="s">
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="L3" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="46" t="s">
         <v>235</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O3" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="32" t="s">
+      <c r="P3" s="80"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="T3" s="35" t="s">
+      <c r="T3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="32" t="s">
+      <c r="U3" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="32" t="s">
+      <c r="V3" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="32" t="s">
+      <c r="W3" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="X3" s="32" t="s">
+      <c r="X3" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="Y3" s="32" t="s">
+      <c r="Y3" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="AA3" s="44" t="s">
+      <c r="AA3" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="AB3" s="38" t="s">
+      <c r="AB3" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="AC3" s="38" t="s">
+      <c r="AC3" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="AD3" s="38" t="s">
+      <c r="AD3" s="37" t="s">
         <v>244</v>
       </c>
     </row>
@@ -65942,11 +65942,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9xCUSnOba9+kjRTP4aA+IhYIhPNTdofqr3mLiTZOPQAzcWWZifDmPOI/0ItUaLA4hSjA/rC4jIft53nJzygclQ==" saltValue="aTfUQq44C7asIKTaLqEvww==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="Y1:Z2"/>
     <mergeCell ref="AA1:AD2"/>
     <mergeCell ref="U1:V2"/>
@@ -65956,12 +65957,11 @@
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="S1:T2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C89900C-EF76-D441-AF45-22BC54F716E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30757A4F-25A2-024E-9738-058DEC4BF661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="20600" windowHeight="16840" tabRatio="879" firstSheet="12" activeTab="16" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="20600" windowHeight="16740" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1444,33 +1444,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1479,6 +1452,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1508,6 +1484,30 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2187,7 +2187,7 @@
       <c r="D28" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fECAul9Xub1IkDhYUJjwJS9OzYzo0I9Z1C6jwPBr+eEjzIjgSDIhJ1EXiZzgp9q6fPNfWYq+aXIj8dGPnToVoA==" saltValue="U4C95otBxdOcIHYcesbhsA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VIfDg2WohYGRVvx5zqMrfh4BXiRpBl1td1Y9U6PHWJ1pGeKKR+gXQbKZJDQ/YWc4MD0MC9jcrqZ/EkrKFAS80A==" saltValue="Hg2Qqh/bMr3HGqPu0bqrTw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -3678,31 +3678,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="90" t="s">
+      <c r="C1" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="101" t="s">
         <v>229</v>
       </c>
       <c r="E1" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="101" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="90" t="s">
+      <c r="G1" s="101" t="s">
         <v>227</v>
       </c>
-      <c r="H1" s="90" t="s">
+      <c r="H1" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="90" t="s">
+      <c r="I1" s="101" t="s">
         <v>93</v>
       </c>
       <c r="J1" s="83" t="s">
@@ -7147,17 +7147,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i4Y2GDra9B4e5ZK9IT/yAgpGu83ed66ZNnyRoFvCqT5wVfLy2Lgs30SlszSGdCdYRpnULwm3Kg2BGFX0NXPahA==" saltValue="poZcuJUx5RFD549VWAk8zg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 M2 N2 O2" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7190,10 +7190,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -8645,10 +8645,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -10319,10 +10319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -10335,15 +10335,15 @@
       </c>
       <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="100" t="s">
+      <c r="I1" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="89" t="s">
+      <c r="J1" s="92" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
       <c r="N1" s="81" t="s">
         <v>57</v>
       </c>
@@ -10360,25 +10360,25 @@
     <row r="2" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
       <c r="B2" s="69"/>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="101" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="90" t="s">
+      <c r="F2" s="101" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="H2" s="110"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
       <c r="N2" s="81"/>
       <c r="O2" s="81"/>
       <c r="P2" s="119"/>
@@ -10401,7 +10401,7 @@
       <c r="H3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="100"/>
+      <c r="I3" s="93"/>
       <c r="J3" s="37" t="s">
         <v>194</v>
       </c>
@@ -14222,6 +14222,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="XFozxK9hJMWP6ySEAZQ3h3enG2BhQeHoAidLHumULHWCGWuk01gbtIGf+HTrIiPiIpU+5yeeijnd0s/LDXPnUw==" saltValue="w5vF1VniVgRmNU/Yweiy+Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="F1:H1"/>
@@ -14231,11 +14236,6 @@
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I3 M3 J3 K3 L3 Q1:Q3" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14269,10 +14269,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="83" t="s">
@@ -15522,13 +15522,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="90" t="s">
+      <c r="C1" s="101" t="s">
         <v>94</v>
       </c>
       <c r="D1" s="121" t="s">
@@ -15538,10 +15538,10 @@
         <v>89</v>
       </c>
       <c r="F1" s="124"/>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="102" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="90" t="s">
+      <c r="H1" s="101" t="s">
         <v>209</v>
       </c>
       <c r="I1" s="83" t="s">
@@ -15561,7 +15561,7 @@
       <c r="F2" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="92"/>
+      <c r="G2" s="103"/>
       <c r="H2" s="70"/>
       <c r="I2" s="37" t="s">
         <v>186</v>
@@ -18251,10 +18251,10 @@
       <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="91" t="s">
+      <c r="E1" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="102" t="s">
         <v>184</v>
       </c>
       <c r="G1" s="81" t="s">
@@ -18263,18 +18263,18 @@
       <c r="H1" s="81"/>
       <c r="I1" s="81"/>
       <c r="J1" s="81"/>
-      <c r="K1" s="89" t="s">
+      <c r="K1" s="92" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89" t="s">
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="105" t="s">
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="98" t="s">
         <v>61</v>
       </c>
       <c r="S1" s="83" t="s">
@@ -18286,18 +18286,18 @@
       </c>
       <c r="V1" s="84"/>
       <c r="W1" s="87"/>
-      <c r="X1" s="89" t="s">
+      <c r="X1" s="92" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="89"/>
+      <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
       <c r="G2" s="43" t="s">
         <v>23</v>
       </c>
@@ -18331,7 +18331,7 @@
       <c r="Q2" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="R2" s="107"/>
+      <c r="R2" s="100"/>
       <c r="S2" s="35" t="s">
         <v>85</v>
       </c>
@@ -23835,16 +23835,16 @@
       <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="91" t="s">
+      <c r="E1" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="106" t="s">
+      <c r="H1" s="99" t="s">
         <v>177</v>
       </c>
       <c r="I1" s="79" t="s">
@@ -23855,7 +23855,7 @@
         <v>70</v>
       </c>
       <c r="L1" s="78"/>
-      <c r="M1" s="106" t="s">
+      <c r="M1" s="99" t="s">
         <v>182</v>
       </c>
       <c r="N1" s="127" t="s">
@@ -23864,7 +23864,7 @@
       <c r="O1" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="106" t="s">
+      <c r="P1" s="99" t="s">
         <v>181</v>
       </c>
       <c r="Q1" s="127" t="s">
@@ -23883,10 +23883,10 @@
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="107"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="100"/>
       <c r="I2" s="37" t="s">
         <v>178</v>
       </c>
@@ -23899,10 +23899,10 @@
       <c r="L2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="107"/>
+      <c r="M2" s="100"/>
       <c r="N2" s="82"/>
       <c r="O2" s="82"/>
-      <c r="P2" s="107"/>
+      <c r="P2" s="100"/>
       <c r="Q2" s="82"/>
       <c r="R2" s="82"/>
       <c r="S2" s="37" t="s">
@@ -28315,16 +28315,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="l8KVIJiIcXBtA5Rxt+oHSTZCQcSscxoVEx71fajOPkkDzIq7y1m1u1pHAE+AUnT93CwTnM5PkUuxYj42pmVV9g==" saltValue="dsO/0LEKtl67ZZqtPejb6A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="H1:H2"/>
@@ -28332,6 +28322,16 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 H1:H2 P1:P2 S2 J2 E1:E2 G1:G2 I2 M1:M2 T2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -36474,63 +36474,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="93" t="s">
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="105" t="s">
+      <c r="H1" s="105"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="98" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="97" t="s">
+      <c r="L1" s="89" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="99"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="91"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
       <c r="B2" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="97" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="89" t="s">
+      <c r="F2" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="100" t="s">
+      <c r="G2" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="101" t="s">
+      <c r="H2" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="96" t="s">
+      <c r="I2" s="107" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="106"/>
-      <c r="K2" s="91" t="s">
+      <c r="J2" s="99"/>
+      <c r="K2" s="102" t="s">
         <v>122</v>
       </c>
       <c r="L2" s="71" t="s">
@@ -36541,22 +36541,22 @@
         <v>19</v>
       </c>
       <c r="O2" s="71"/>
-      <c r="P2" s="89" t="s">
+      <c r="P2" s="92" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="70"/>
       <c r="B3" s="81"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="97"/>
       <c r="E3" s="82"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="103"/>
       <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
@@ -36569,7 +36569,7 @@
       <c r="O3" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="P3" s="89"/>
+      <c r="P3" s="92"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -40174,6 +40174,10 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="CVc9Y6zTViK+qNBvkHM6Vw9LbbIcQvJhEGHDobnK2WxxzdUIpXEi5D/0B5vCJa09eTPUkAUYi73wUk86TeXIgw==" saltValue="8ea3UICepsiuwTlX9cWVdA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -40187,10 +40191,6 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 J4 K2:K3 G2:I3 O3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40234,23 +40234,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="92" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89" t="s">
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
@@ -42976,7 +42976,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="83" t="s">
@@ -43034,7 +43034,7 @@
       <c r="C2" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="105" t="s">
+      <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
       <c r="E2" s="72" t="s">
@@ -43065,49 +43065,49 @@
         <v>27</v>
       </c>
       <c r="T2" s="72"/>
-      <c r="U2" s="89" t="s">
+      <c r="U2" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="89" t="s">
+      <c r="V2" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="89" t="s">
+      <c r="W2" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="89" t="s">
+      <c r="X2" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="89" t="s">
+      <c r="Y2" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="89" t="s">
+      <c r="Z2" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="89" t="s">
+      <c r="AA2" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="89" t="s">
+      <c r="AB2" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="89" t="s">
+      <c r="AC2" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="89" t="s">
+      <c r="AD2" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="89" t="s">
+      <c r="AE2" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="89" t="s">
+      <c r="AF2" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="AG2" s="89" t="s">
+      <c r="AG2" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="93" t="s">
+      <c r="AH2" s="104" t="s">
         <v>215</v>
       </c>
-      <c r="AI2" s="95"/>
+      <c r="AI2" s="106"/>
       <c r="AJ2" s="72" t="s">
         <v>216</v>
       </c>
@@ -43125,7 +43125,7 @@
       <c r="A3" s="70"/>
       <c r="B3" s="82"/>
       <c r="C3" s="82"/>
-      <c r="D3" s="107"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="33" t="s">
         <v>24</v>
       </c>
@@ -43172,19 +43172,19 @@
       <c r="T3" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
-      <c r="AA3" s="89"/>
-      <c r="AB3" s="89"/>
-      <c r="AC3" s="89"/>
-      <c r="AD3" s="89"/>
-      <c r="AE3" s="89"/>
-      <c r="AF3" s="89"/>
-      <c r="AG3" s="89"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="92"/>
       <c r="AH3" s="30" t="s">
         <v>137</v>
       </c>
@@ -51813,6 +51813,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wxJYPTS1M8YrpE+F5HXpzPvhVkWn+uzvbhQbX4zWGt7tgJJAc6rvipv1/0hraJgXbUY0X5vYRquC66cBDOGcbg==" saltValue="RWTcEymG3DdteXmtyGeu4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -51829,20 +51843,6 @@
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 R3 AI3 AK3 AM3 L3 M3 N3 O3 P3 Q3 AO3 AJ3 AL3 AN3 AH3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -51886,7 +51886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="81" t="s">
@@ -53138,16 +53138,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="92" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
       <c r="G1" s="83" t="s">
         <v>206</v>
       </c>
@@ -55629,7 +55629,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="108" t="s">
@@ -55654,20 +55654,20 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="101" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="99"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="91"/>
       <c r="H2" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="101" t="s">
         <v>163</v>
       </c>
       <c r="J2" s="83" t="s">
@@ -59389,10 +59389,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="101" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="81" t="s">
@@ -59405,10 +59405,10 @@
       </c>
       <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="90" t="s">
+      <c r="I1" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="90" t="s">
+      <c r="J1" s="101" t="s">
         <v>237</v>
       </c>
       <c r="K1" s="111" t="s">
@@ -59423,7 +59423,7 @@
       <c r="P1" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="89" t="s">
+      <c r="Q1" s="92" t="s">
         <v>239</v>
       </c>
       <c r="R1" s="81" t="s">
@@ -59462,7 +59462,7 @@
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="90" t="s">
+      <c r="F2" s="101" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="108" t="s">
@@ -59477,7 +59477,7 @@
       <c r="N2" s="79"/>
       <c r="O2" s="80"/>
       <c r="P2" s="81"/>
-      <c r="Q2" s="89"/>
+      <c r="Q2" s="92"/>
       <c r="R2" s="81"/>
       <c r="S2" s="81"/>
       <c r="T2" s="81"/>
@@ -59527,7 +59527,7 @@
         <v>48</v>
       </c>
       <c r="P3" s="81"/>
-      <c r="Q3" s="89"/>
+      <c r="Q3" s="92"/>
       <c r="R3" s="81"/>
       <c r="S3" s="31" t="s">
         <v>50</v>
@@ -65941,11 +65941,8 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9xCUSnOba9+kjRTP4aA+IhYIhPNTdofqr3mLiTZOPQAzcWWZifDmPOI/0ItUaLA4hSjA/rC4jIft53nJzygclQ==" saltValue="aTfUQq44C7asIKTaLqEvww==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="Y1:Z2"/>
     <mergeCell ref="AA1:AD2"/>
     <mergeCell ref="U1:V2"/>
@@ -65955,12 +65952,15 @@
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="S1:T2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30757A4F-25A2-024E-9738-058DEC4BF661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB19908E-E8C6-2F49-8A36-62E01249F779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="20600" windowHeight="16740" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="24680" windowHeight="16680" tabRatio="879" firstSheet="5" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1444,6 +1444,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1484,30 +1508,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3678,31 +3678,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="89" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="89" t="s">
         <v>229</v>
       </c>
       <c r="E1" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="101" t="s">
+      <c r="F1" s="89" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="101" t="s">
+      <c r="G1" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="H1" s="101" t="s">
+      <c r="H1" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="101" t="s">
+      <c r="I1" s="89" t="s">
         <v>93</v>
       </c>
       <c r="J1" s="83" t="s">
@@ -7147,17 +7147,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i4Y2GDra9B4e5ZK9IT/yAgpGu83ed66ZNnyRoFvCqT5wVfLy2Lgs30SlszSGdCdYRpnULwm3Kg2BGFX0NXPahA==" saltValue="poZcuJUx5RFD549VWAk8zg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="I1:I2"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 M2 N2 O2" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7190,10 +7190,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -8645,10 +8645,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -10319,10 +10319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -10335,15 +10335,15 @@
       </c>
       <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="93" t="s">
+      <c r="I1" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="92" t="s">
+      <c r="J1" s="99" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
       <c r="N1" s="81" t="s">
         <v>57</v>
       </c>
@@ -10360,25 +10360,25 @@
     <row r="2" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
       <c r="B2" s="69"/>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="89" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="101" t="s">
+      <c r="F2" s="89" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="H2" s="110"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
       <c r="N2" s="81"/>
       <c r="O2" s="81"/>
       <c r="P2" s="119"/>
@@ -10401,7 +10401,7 @@
       <c r="H3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="93"/>
+      <c r="I3" s="100"/>
       <c r="J3" s="37" t="s">
         <v>194</v>
       </c>
@@ -14222,11 +14222,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="XFozxK9hJMWP6ySEAZQ3h3enG2BhQeHoAidLHumULHWCGWuk01gbtIGf+HTrIiPiIpU+5yeeijnd0s/LDXPnUw==" saltValue="w5vF1VniVgRmNU/Yweiy+Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="F1:H1"/>
@@ -14236,6 +14231,11 @@
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="P1:P3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I3 M3 J3 K3 L3 Q1:Q3" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14269,10 +14269,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="83" t="s">
@@ -15522,13 +15522,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="89" t="s">
         <v>94</v>
       </c>
       <c r="D1" s="121" t="s">
@@ -15538,10 +15538,10 @@
         <v>89</v>
       </c>
       <c r="F1" s="124"/>
-      <c r="G1" s="102" t="s">
+      <c r="G1" s="90" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="101" t="s">
+      <c r="H1" s="89" t="s">
         <v>209</v>
       </c>
       <c r="I1" s="83" t="s">
@@ -15561,7 +15561,7 @@
       <c r="F2" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="103"/>
+      <c r="G2" s="91"/>
       <c r="H2" s="70"/>
       <c r="I2" s="37" t="s">
         <v>186</v>
@@ -18251,10 +18251,10 @@
       <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="90" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="90" t="s">
         <v>184</v>
       </c>
       <c r="G1" s="81" t="s">
@@ -18263,18 +18263,18 @@
       <c r="H1" s="81"/>
       <c r="I1" s="81"/>
       <c r="J1" s="81"/>
-      <c r="K1" s="92" t="s">
+      <c r="K1" s="99" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92" t="s">
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="98" t="s">
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="105" t="s">
         <v>61</v>
       </c>
       <c r="S1" s="83" t="s">
@@ -18286,18 +18286,18 @@
       </c>
       <c r="V1" s="84"/>
       <c r="W1" s="87"/>
-      <c r="X1" s="92" t="s">
+      <c r="X1" s="99" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="92"/>
+      <c r="Y1" s="99"/>
     </row>
     <row r="2" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
       <c r="G2" s="43" t="s">
         <v>23</v>
       </c>
@@ -18331,7 +18331,7 @@
       <c r="Q2" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="R2" s="100"/>
+      <c r="R2" s="107"/>
       <c r="S2" s="35" t="s">
         <v>85</v>
       </c>
@@ -23835,16 +23835,16 @@
       <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="90" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="102" t="s">
+      <c r="G1" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="99" t="s">
+      <c r="H1" s="106" t="s">
         <v>177</v>
       </c>
       <c r="I1" s="79" t="s">
@@ -23855,7 +23855,7 @@
         <v>70</v>
       </c>
       <c r="L1" s="78"/>
-      <c r="M1" s="99" t="s">
+      <c r="M1" s="106" t="s">
         <v>182</v>
       </c>
       <c r="N1" s="127" t="s">
@@ -23864,7 +23864,7 @@
       <c r="O1" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="99" t="s">
+      <c r="P1" s="106" t="s">
         <v>181</v>
       </c>
       <c r="Q1" s="127" t="s">
@@ -23883,10 +23883,10 @@
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="100"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="107"/>
       <c r="I2" s="37" t="s">
         <v>178</v>
       </c>
@@ -23899,10 +23899,10 @@
       <c r="L2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="100"/>
+      <c r="M2" s="107"/>
       <c r="N2" s="82"/>
       <c r="O2" s="82"/>
-      <c r="P2" s="100"/>
+      <c r="P2" s="107"/>
       <c r="Q2" s="82"/>
       <c r="R2" s="82"/>
       <c r="S2" s="37" t="s">
@@ -28315,6 +28315,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="l8KVIJiIcXBtA5Rxt+oHSTZCQcSscxoVEx71fajOPkkDzIq7y1m1u1pHAE+AUnT93CwTnM5PkUuxYj42pmVV9g==" saltValue="dsO/0LEKtl67ZZqtPejb6A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="H1:H2"/>
@@ -28322,16 +28332,6 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 H1:H2 P1:P2 S2 J2 E1:E2 G1:G2 I2 M1:M2 T2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -36474,63 +36474,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="104" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="105"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="98" t="s">
+      <c r="H1" s="93"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="105" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="89" t="s">
+      <c r="L1" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="91"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="98"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
       <c r="B2" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="104" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="93" t="s">
+      <c r="G2" s="100" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="94" t="s">
+      <c r="H2" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="95" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="99"/>
-      <c r="K2" s="102" t="s">
+      <c r="J2" s="106"/>
+      <c r="K2" s="90" t="s">
         <v>122</v>
       </c>
       <c r="L2" s="71" t="s">
@@ -36541,22 +36541,22 @@
         <v>19</v>
       </c>
       <c r="O2" s="71"/>
-      <c r="P2" s="92" t="s">
+      <c r="P2" s="99" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="70"/>
       <c r="B3" s="81"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="82"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="103"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="91"/>
       <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
@@ -36569,7 +36569,7 @@
       <c r="O3" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="P3" s="92"/>
+      <c r="P3" s="99"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -40172,8 +40172,9 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CVc9Y6zTViK+qNBvkHM6Vw9LbbIcQvJhEGHDobnK2WxxzdUIpXEi5D/0B5vCJa09eTPUkAUYi73wUk86TeXIgw==" saltValue="8ea3UICepsiuwTlX9cWVdA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CgzEmPt3Hk/Mhl0UL9A2LlPy9AK4yG5OneGJhJUq4FdJtqq7lG98GOjE3DOYWxyUk/x/OG6IB9bbOiXFzMXJrw==" saltValue="nv5eOc6x2cuQYecC/aOIFA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="G1:I1"/>
@@ -40190,7 +40191,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="J1:J3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 J4 K2:K3 G2:I3 O3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40206,7 +40206,7 @@
     <hyperlink ref="H2" r:id="rId6" display="PORT_CODE" xr:uid="{C4D05E8A-B26C-4196-BF44-6883318591EB}"/>
     <hyperlink ref="K2:K3" r:id="rId7" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{ADDD99C7-B692-4517-AF11-C5F4715C3781}"/>
     <hyperlink ref="H2:H3" r:id="rId8" location="Ports" display="PORT" xr:uid="{4BCE8909-E3DB-4961-B5C5-527D383D1926}"/>
-    <hyperlink ref="J1:J3" r:id="rId9" location="targetSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{8145BEA5-06D1-4F1F-890E-1ACE66463F94}"/>
+    <hyperlink ref="J1:J3" r:id="rId9" location="allSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{8145BEA5-06D1-4F1F-890E-1ACE66463F94}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40234,23 +40234,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="99" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92" t="s">
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
@@ -42976,7 +42976,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="83" t="s">
@@ -43034,7 +43034,7 @@
       <c r="C2" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="105" t="s">
         <v>126</v>
       </c>
       <c r="E2" s="72" t="s">
@@ -43065,49 +43065,49 @@
         <v>27</v>
       </c>
       <c r="T2" s="72"/>
-      <c r="U2" s="92" t="s">
+      <c r="U2" s="99" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="92" t="s">
+      <c r="V2" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="92" t="s">
+      <c r="W2" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="92" t="s">
+      <c r="X2" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="92" t="s">
+      <c r="Y2" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="92" t="s">
+      <c r="Z2" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="92" t="s">
+      <c r="AA2" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="92" t="s">
+      <c r="AB2" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="92" t="s">
+      <c r="AC2" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="92" t="s">
+      <c r="AD2" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="92" t="s">
+      <c r="AE2" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="92" t="s">
+      <c r="AF2" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="AG2" s="92" t="s">
+      <c r="AG2" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="104" t="s">
+      <c r="AH2" s="92" t="s">
         <v>215</v>
       </c>
-      <c r="AI2" s="106"/>
+      <c r="AI2" s="94"/>
       <c r="AJ2" s="72" t="s">
         <v>216</v>
       </c>
@@ -43125,7 +43125,7 @@
       <c r="A3" s="70"/>
       <c r="B3" s="82"/>
       <c r="C3" s="82"/>
-      <c r="D3" s="100"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="33" t="s">
         <v>24</v>
       </c>
@@ -43172,19 +43172,19 @@
       <c r="T3" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="92"/>
-      <c r="AE3" s="92"/>
-      <c r="AF3" s="92"/>
-      <c r="AG3" s="92"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99"/>
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+      <c r="AB3" s="99"/>
+      <c r="AC3" s="99"/>
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="99"/>
+      <c r="AG3" s="99"/>
       <c r="AH3" s="30" t="s">
         <v>137</v>
       </c>
@@ -51813,20 +51813,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wxJYPTS1M8YrpE+F5HXpzPvhVkWn+uzvbhQbX4zWGt7tgJJAc6rvipv1/0hraJgXbUY0X5vYRquC66cBDOGcbg==" saltValue="RWTcEymG3DdteXmtyGeu4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -51843,6 +51829,20 @@
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 R3 AI3 AK3 AM3 L3 M3 N3 O3 P3 Q3 AO3 AJ3 AL3 AN3 AH3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -51886,7 +51886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="81" t="s">
@@ -53138,16 +53138,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="99" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
       <c r="G1" s="83" t="s">
         <v>206</v>
       </c>
@@ -55629,7 +55629,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="108" t="s">
@@ -55654,20 +55654,20 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="89" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="91"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="98"/>
       <c r="H2" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="89" t="s">
         <v>163</v>
       </c>
       <c r="J2" s="83" t="s">
@@ -59389,10 +59389,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="81" t="s">
@@ -59405,10 +59405,10 @@
       </c>
       <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="101" t="s">
+      <c r="I1" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="101" t="s">
+      <c r="J1" s="89" t="s">
         <v>237</v>
       </c>
       <c r="K1" s="111" t="s">
@@ -59423,7 +59423,7 @@
       <c r="P1" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="92" t="s">
+      <c r="Q1" s="99" t="s">
         <v>239</v>
       </c>
       <c r="R1" s="81" t="s">
@@ -59462,7 +59462,7 @@
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="101" t="s">
+      <c r="F2" s="89" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="108" t="s">
@@ -59477,7 +59477,7 @@
       <c r="N2" s="79"/>
       <c r="O2" s="80"/>
       <c r="P2" s="81"/>
-      <c r="Q2" s="92"/>
+      <c r="Q2" s="99"/>
       <c r="R2" s="81"/>
       <c r="S2" s="81"/>
       <c r="T2" s="81"/>
@@ -59527,7 +59527,7 @@
         <v>48</v>
       </c>
       <c r="P3" s="81"/>
-      <c r="Q3" s="92"/>
+      <c r="Q3" s="99"/>
       <c r="R3" s="81"/>
       <c r="S3" s="31" t="s">
         <v>50</v>
@@ -65939,8 +65939,12 @@
       <c r="B203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9xCUSnOba9+kjRTP4aA+IhYIhPNTdofqr3mLiTZOPQAzcWWZifDmPOI/0ItUaLA4hSjA/rC4jIft53nJzygclQ==" saltValue="aTfUQq44C7asIKTaLqEvww==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WuDPT1+slParW8lK5SfJrIiCuXUqugKfunXVVDY0YB00pOtHXcdvDQyUD/jzqYTc2x6TyFXXd8XFSXwF4cqxTw==" saltValue="kHXwsv450+CnM8/ussNlMw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="Y1:Z2"/>
@@ -65957,10 +65961,6 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">
@@ -65968,10 +65968,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AA3" r:id="rId1" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{2BC6450F-A7B4-4044-BEA6-59E54066E449}"/>
-    <hyperlink ref="AB3" r:id="rId2" location="targetSpecies" display="SPECIES_2_CODE" xr:uid="{9EEA8352-0631-4B4E-BB1B-FF880D8B8ED2}"/>
-    <hyperlink ref="AC3" r:id="rId3" location="targetSpecies" display="SPECIES_3_CODE" xr:uid="{B78A1E77-3003-40C6-9B0C-101A94179479}"/>
-    <hyperlink ref="AD3" r:id="rId4" location="targetSpecies" display="SPECIES_4_CODE" xr:uid="{22DD36F0-D891-4763-8CC9-508C73D63CC9}"/>
+    <hyperlink ref="AA3" r:id="rId1" location="allSpecies" xr:uid="{2BC6450F-A7B4-4044-BEA6-59E54066E449}"/>
+    <hyperlink ref="AB3" r:id="rId2" location="allSpecies" xr:uid="{9EEA8352-0631-4B4E-BB1B-FF880D8B8ED2}"/>
+    <hyperlink ref="AC3" r:id="rId3" location="allSpecies" xr:uid="{B78A1E77-3003-40C6-9B0C-101A94179479}"/>
+    <hyperlink ref="AD3" r:id="rId4" location="allSpecies" xr:uid="{22DD36F0-D891-4763-8CC9-508C73D63CC9}"/>
     <hyperlink ref="K3" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{53874CDA-60F7-44F3-A738-546AA82ACA2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB19908E-E8C6-2F49-8A36-62E01249F779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715C7FB4-8E0B-6B44-9CE8-C92F48F088E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="24680" windowHeight="16680" tabRatio="879" firstSheet="5" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="8080" yWindow="740" windowWidth="20920" windowHeight="16680" tabRatio="879" firstSheet="11" activeTab="15" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -1444,6 +1444,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1476,9 +1479,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3678,31 +3678,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="90" t="s">
         <v>229</v>
       </c>
       <c r="E1" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="90" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="89" t="s">
+      <c r="G1" s="90" t="s">
         <v>227</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="89" t="s">
+      <c r="I1" s="90" t="s">
         <v>93</v>
       </c>
       <c r="J1" s="83" t="s">
@@ -7147,17 +7147,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i4Y2GDra9B4e5ZK9IT/yAgpGu83ed66ZNnyRoFvCqT5wVfLy2Lgs30SlszSGdCdYRpnULwm3Kg2BGFX0NXPahA==" saltValue="poZcuJUx5RFD549VWAk8zg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 M2 N2 O2" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7190,10 +7190,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -8645,10 +8645,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -10319,10 +10319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="108" t="s">
@@ -10338,12 +10338,12 @@
       <c r="I1" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="99" t="s">
+      <c r="J1" s="89" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
       <c r="N1" s="81" t="s">
         <v>57</v>
       </c>
@@ -10360,14 +10360,14 @@
     <row r="2" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
       <c r="B2" s="69"/>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="90" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="108" t="s">
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="89" t="s">
+      <c r="F2" s="90" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="108" t="s">
@@ -10375,10 +10375,10 @@
       </c>
       <c r="H2" s="110"/>
       <c r="I2" s="100"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
       <c r="N2" s="81"/>
       <c r="O2" s="81"/>
       <c r="P2" s="119"/>
@@ -14222,6 +14222,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="XFozxK9hJMWP6ySEAZQ3h3enG2BhQeHoAidLHumULHWCGWuk01gbtIGf+HTrIiPiIpU+5yeeijnd0s/LDXPnUw==" saltValue="w5vF1VniVgRmNU/Yweiy+Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="F1:H1"/>
@@ -14231,11 +14236,6 @@
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I3 M3 J3 K3 L3 Q1:Q3" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14269,10 +14269,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="83" t="s">
@@ -15522,13 +15522,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="90" t="s">
         <v>94</v>
       </c>
       <c r="D1" s="121" t="s">
@@ -15538,10 +15538,10 @@
         <v>89</v>
       </c>
       <c r="F1" s="124"/>
-      <c r="G1" s="90" t="s">
+      <c r="G1" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="90" t="s">
         <v>209</v>
       </c>
       <c r="I1" s="83" t="s">
@@ -15561,7 +15561,7 @@
       <c r="F2" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="91"/>
+      <c r="G2" s="92"/>
       <c r="H2" s="70"/>
       <c r="I2" s="37" t="s">
         <v>186</v>
@@ -18174,7 +18174,7 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cIPMEB/7FdMJ59GLwUBjIJq7Z/ouJdnlvwNMkIwQQWO7k50m2ZyZ15EcA5FLZczYTiVocNtetk4wR+pQEJ425w==" saltValue="SnUtD4HRD9laqxb+y5V31A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fTPkI9qmI0rPQTpef4UOHdSjNfD2cKgp41nTyI6DmyUhtwK/gK7x3ceTGV0x+9YGBk8Txgzr/CZn7PiM7+29PA==" saltValue="dNKoS5Q8OasFDXsltDFa1Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -18196,7 +18196,7 @@
     <hyperlink ref="E2" r:id="rId3" location="typesOfFate" xr:uid="{F8152E0B-B9D5-4E81-A374-4985E0AF2D58}"/>
     <hyperlink ref="F2" r:id="rId4" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
     <hyperlink ref="D1" r:id="rId5" location="allSpecies" xr:uid="{7915C09B-5FFF-4B7E-84FB-D8B7D31EA643}"/>
-    <hyperlink ref="G1:G2" r:id="rId6" location="samplingProtocols" display="SAMPLING_METHOD" xr:uid="{C3154411-BFD2-3A41-99A0-2ECAAC5C9F3C}"/>
+    <hyperlink ref="G1:G2" r:id="rId6" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD" xr:uid="{C3154411-BFD2-3A41-99A0-2ECAAC5C9F3C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
@@ -18251,10 +18251,10 @@
       <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="91" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="91" t="s">
         <v>184</v>
       </c>
       <c r="G1" s="81" t="s">
@@ -18263,17 +18263,17 @@
       <c r="H1" s="81"/>
       <c r="I1" s="81"/>
       <c r="J1" s="81"/>
-      <c r="K1" s="99" t="s">
+      <c r="K1" s="89" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99" t="s">
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
       <c r="R1" s="105" t="s">
         <v>61</v>
       </c>
@@ -18286,18 +18286,18 @@
       </c>
       <c r="V1" s="84"/>
       <c r="W1" s="87"/>
-      <c r="X1" s="99" t="s">
+      <c r="X1" s="89" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="99"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
       <c r="G2" s="43" t="s">
         <v>23</v>
       </c>
@@ -23835,13 +23835,13 @@
       <c r="D1" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="90" t="s">
+      <c r="E1" s="91" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="90" t="s">
+      <c r="F1" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="90" t="s">
+      <c r="G1" s="91" t="s">
         <v>176</v>
       </c>
       <c r="H1" s="106" t="s">
@@ -23883,9 +23883,9 @@
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
       <c r="H2" s="107"/>
       <c r="I2" s="37" t="s">
         <v>178</v>
@@ -28315,16 +28315,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="l8KVIJiIcXBtA5Rxt+oHSTZCQcSscxoVEx71fajOPkkDzIq7y1m1u1pHAE+AUnT93CwTnM5PkUuxYj42pmVV9g==" saltValue="dsO/0LEKtl67ZZqtPejb6A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="H1:H2"/>
@@ -28332,6 +28322,16 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 H1:H2 P1:P2 S2 J2 E1:E2 G1:G2 I2 M1:M2 T2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -36474,34 +36474,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="92" t="s">
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="93"/>
-      <c r="I1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="95"/>
       <c r="J1" s="105" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="96" t="s">
+      <c r="L1" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="99"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
@@ -36517,7 +36517,7 @@
       <c r="E2" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="99" t="s">
+      <c r="F2" s="89" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="100" t="s">
@@ -36526,11 +36526,11 @@
       <c r="H2" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="95" t="s">
+      <c r="I2" s="96" t="s">
         <v>158</v>
       </c>
       <c r="J2" s="106"/>
-      <c r="K2" s="90" t="s">
+      <c r="K2" s="91" t="s">
         <v>122</v>
       </c>
       <c r="L2" s="71" t="s">
@@ -36541,7 +36541,7 @@
         <v>19</v>
       </c>
       <c r="O2" s="71"/>
-      <c r="P2" s="99" t="s">
+      <c r="P2" s="89" t="s">
         <v>20</v>
       </c>
     </row>
@@ -36551,12 +36551,12 @@
       <c r="C3" s="103"/>
       <c r="D3" s="104"/>
       <c r="E3" s="82"/>
-      <c r="F3" s="99"/>
+      <c r="F3" s="89"/>
       <c r="G3" s="100"/>
       <c r="H3" s="102"/>
-      <c r="I3" s="95"/>
+      <c r="I3" s="96"/>
       <c r="J3" s="107"/>
-      <c r="K3" s="91"/>
+      <c r="K3" s="92"/>
       <c r="L3" s="31" t="s">
         <v>3</v>
       </c>
@@ -36569,7 +36569,7 @@
       <c r="O3" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="P3" s="99"/>
+      <c r="P3" s="89"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -40174,11 +40174,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="CgzEmPt3Hk/Mhl0UL9A2LlPy9AK4yG5OneGJhJUq4FdJtqq7lG98GOjE3DOYWxyUk/x/OG6IB9bbOiXFzMXJrw==" saltValue="nv5eOc6x2cuQYecC/aOIFA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -40191,6 +40186,11 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="J1:J3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 J4 K2:K3 G2:I3 O3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40234,23 +40234,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="89" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99" t="s">
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
@@ -42976,7 +42976,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="83" t="s">
@@ -43065,49 +43065,49 @@
         <v>27</v>
       </c>
       <c r="T2" s="72"/>
-      <c r="U2" s="99" t="s">
+      <c r="U2" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="V2" s="99" t="s">
+      <c r="V2" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="99" t="s">
+      <c r="W2" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="99" t="s">
+      <c r="X2" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="99" t="s">
+      <c r="Y2" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="99" t="s">
+      <c r="Z2" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="99" t="s">
+      <c r="AA2" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="99" t="s">
+      <c r="AB2" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="99" t="s">
+      <c r="AC2" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="99" t="s">
+      <c r="AD2" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="99" t="s">
+      <c r="AE2" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="99" t="s">
+      <c r="AF2" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="AG2" s="99" t="s">
+      <c r="AG2" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="92" t="s">
+      <c r="AH2" s="93" t="s">
         <v>215</v>
       </c>
-      <c r="AI2" s="94"/>
+      <c r="AI2" s="95"/>
       <c r="AJ2" s="72" t="s">
         <v>216</v>
       </c>
@@ -43172,19 +43172,19 @@
       <c r="T3" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99"/>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="99"/>
-      <c r="AG3" s="99"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="89"/>
+      <c r="AB3" s="89"/>
+      <c r="AC3" s="89"/>
+      <c r="AD3" s="89"/>
+      <c r="AE3" s="89"/>
+      <c r="AF3" s="89"/>
+      <c r="AG3" s="89"/>
       <c r="AH3" s="30" t="s">
         <v>137</v>
       </c>
@@ -51813,6 +51813,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wxJYPTS1M8YrpE+F5HXpzPvhVkWn+uzvbhQbX4zWGt7tgJJAc6rvipv1/0hraJgXbUY0X5vYRquC66cBDOGcbg==" saltValue="RWTcEymG3DdteXmtyGeu4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -51829,20 +51843,6 @@
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 R3 AI3 AK3 AM3 L3 M3 N3 O3 P3 Q3 AO3 AJ3 AL3 AN3 AH3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -51886,7 +51886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="81" t="s">
@@ -53138,16 +53138,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="89" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
       <c r="G1" s="83" t="s">
         <v>206</v>
       </c>
@@ -55629,7 +55629,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="108" t="s">
@@ -55654,20 +55654,20 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="99"/>
       <c r="H2" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="90" t="s">
         <v>163</v>
       </c>
       <c r="J2" s="83" t="s">
@@ -59389,10 +59389,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="42" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="90" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="81" t="s">
@@ -59405,10 +59405,10 @@
       </c>
       <c r="G1" s="109"/>
       <c r="H1" s="110"/>
-      <c r="I1" s="89" t="s">
+      <c r="I1" s="90" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="89" t="s">
+      <c r="J1" s="90" t="s">
         <v>237</v>
       </c>
       <c r="K1" s="111" t="s">
@@ -59423,7 +59423,7 @@
       <c r="P1" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="99" t="s">
+      <c r="Q1" s="89" t="s">
         <v>239</v>
       </c>
       <c r="R1" s="81" t="s">
@@ -59462,7 +59462,7 @@
         <v>79</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="89" t="s">
+      <c r="F2" s="90" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="108" t="s">
@@ -59477,7 +59477,7 @@
       <c r="N2" s="79"/>
       <c r="O2" s="80"/>
       <c r="P2" s="81"/>
-      <c r="Q2" s="99"/>
+      <c r="Q2" s="89"/>
       <c r="R2" s="81"/>
       <c r="S2" s="81"/>
       <c r="T2" s="81"/>
@@ -59527,7 +59527,7 @@
         <v>48</v>
       </c>
       <c r="P3" s="81"/>
-      <c r="Q3" s="99"/>
+      <c r="Q3" s="89"/>
       <c r="R3" s="81"/>
       <c r="S3" s="31" t="s">
         <v>50</v>
@@ -65941,12 +65941,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="WuDPT1+slParW8lK5SfJrIiCuXUqugKfunXVVDY0YB00pOtHXcdvDQyUD/jzqYTc2x6TyFXXd8XFSXwF4cqxTw==" saltValue="kHXwsv450+CnM8/ussNlMw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="Y1:Z2"/>
     <mergeCell ref="AA1:AD2"/>
     <mergeCell ref="U1:V2"/>
@@ -65956,11 +65955,12 @@
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="S1:T2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D907510-87CC-44C4-8B53-6CD82AD9A939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3611A48B-6C62-4FFF-9CBD-E5F471BDC6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" activeTab="1" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="879" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -660,9 +660,6 @@
     <t>NUMBER_BRANCHLINE_HAULINGS_OBSERVED</t>
   </si>
   <si>
-    <t>HOOKS</t>
-  </si>
-  <si>
     <t>NUMBER_OF_LIGHTS</t>
   </si>
   <si>
@@ -817,6 +814,9 @@
   </si>
   <si>
     <t>NUMBER_OF_HOOKS_RETRIEVED_DURING_OBSERVATION</t>
+  </si>
+  <si>
+    <t>HOOKS AND TERMINAL DEVICES</t>
   </si>
 </sst>
 </file>
@@ -1347,75 +1347,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,29 +1389,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1487,6 +1448,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1516,6 +1480,30 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1558,6 +1546,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1905,24 +1905,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="70"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="79"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="73"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
@@ -1972,15 +1972,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="10"/>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="74"/>
+      <c r="D8" s="83"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="74"/>
+      <c r="G8" s="83"/>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2162,11 +2162,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="77"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="86"/>
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2237,10 +2237,10 @@
         <v>23</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.25">
@@ -3680,54 +3680,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="99" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" s="99" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="59" t="s">
-        <v>229</v>
-      </c>
-      <c r="E1" s="93" t="s">
+      <c r="E1" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="59" t="s">
-        <v>250</v>
+      <c r="F1" s="99" t="s">
+        <v>249</v>
       </c>
-      <c r="G1" s="59" t="s">
-        <v>227</v>
+      <c r="G1" s="99" t="s">
+        <v>226</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="71" t="s">
+        <v>220</v>
+      </c>
+      <c r="K1" s="75"/>
+      <c r="L1" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="63"/>
-      <c r="L1" s="110" t="s">
-        <v>222</v>
-      </c>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="112"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="108"/>
     </row>
     <row r="2" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
       <c r="J2" s="33" t="s">
         <v>46</v>
       </c>
@@ -3735,16 +3735,16 @@
         <v>80</v>
       </c>
       <c r="L2" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="M2" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="M2" s="42" t="s">
+      <c r="N2" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="42" t="s">
         <v>225</v>
-      </c>
-      <c r="O2" s="42" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -7149,17 +7149,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="i4Y2GDra9B4e5ZK9IT/yAgpGu83ed66ZNnyRoFvCqT5wVfLy2Lgs30SlszSGdCdYRpnULwm3Kg2BGFX0NXPahA==" saltValue="poZcuJUx5RFD549VWAk8zg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 M2 N2 O2" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7192,21 +7192,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="110" t="s">
-        <v>201</v>
+      <c r="C1" s="106" t="s">
+        <v>253</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="42" t="s">
         <v>23</v>
       </c>
@@ -8618,14 +8618,14 @@
       <c r="E202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7L7ysxAlvpkBotAvp596sYOylpEuvb/Ta11TwryFzRR9JnFyu2qT+9lTo+vY+D8FgTspPzRmMhpOG+a3DGDtGA==" saltValue="tiHQmWEfnba1P++46Gyl1g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SQW7Q+33fdeDxG4TZIWTcU/SvXZv2fX44vfby4iEcWtzZJTELGljGngkulk/4h40hVG9bmnvmfePke5awPVcqg==" saltValue="YyrlZm1PvFilAGwS6CjaGw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="hookTypes" display="TYPE_CODE" xr:uid="{76A15B78-243E-4A2E-A5A4-5CE8931F7C0B}"/>
+    <hyperlink ref="C2" r:id="rId1" location="hookAndTerminalDevices" xr:uid="{76A15B78-243E-4A2E-A5A4-5CE8931F7C0B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8647,22 +8647,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="110" t="s">
+      <c r="C1" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="112"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
     </row>
     <row r="2" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="42" t="s">
         <v>178</v>
       </c>
@@ -10321,89 +10321,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="110" t="s">
+      <c r="C1" s="106" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="106" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="110" t="s">
-        <v>208</v>
-      </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="102" t="s">
+      <c r="G1" s="107"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="94" t="s">
+      <c r="J1" s="90" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="89" t="s">
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="89" t="s">
+      <c r="O1" s="69" t="s">
         <v>200</v>
       </c>
-      <c r="P1" s="120" t="s">
-        <v>253</v>
+      <c r="P1" s="116" t="s">
+        <v>252</v>
       </c>
-      <c r="Q1" s="119" t="s">
+      <c r="Q1" s="115" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="59" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="D2" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="112"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="110" t="s">
+      <c r="G2" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="112"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="119"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="115"/>
     </row>
     <row r="3" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
       <c r="D3" s="30" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="60"/>
+      <c r="F3" s="58"/>
       <c r="G3" s="30" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="102"/>
+      <c r="I3" s="91"/>
       <c r="J3" s="36" t="s">
         <v>194</v>
       </c>
@@ -10416,10 +10416,10 @@
       <c r="M3" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="119"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="118"/>
+      <c r="Q3" s="115"/>
     </row>
     <row r="4" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -14224,6 +14224,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="XFozxK9hJMWP6ySEAZQ3h3enG2BhQeHoAidLHumULHWCGWuk01gbtIGf+HTrIiPiIpU+5yeeijnd0s/LDXPnUw==" saltValue="w5vF1VniVgRmNU/Yweiy+Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="F1:H1"/>
@@ -14233,11 +14238,6 @@
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I3 M3 J3 K3 L3 Q1:Q3" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14271,20 +14271,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="63"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="2" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="33" t="s">
         <v>145</v>
       </c>
@@ -15524,47 +15524,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="119" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="57" t="s">
+      <c r="F1" s="122"/>
+      <c r="G1" s="100" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="59" t="s">
-        <v>209</v>
+      <c r="H1" s="99" t="s">
+        <v>208</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="I1" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="62"/>
-      <c r="K1" s="63"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="75"/>
     </row>
     <row r="2" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="65"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="120"/>
       <c r="E2" s="42" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="60"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="58"/>
       <c r="I2" s="36" t="s">
         <v>186</v>
       </c>
@@ -15572,7 +15572,7 @@
         <v>59</v>
       </c>
       <c r="K2" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
@@ -18253,53 +18253,53 @@
       <c r="D1" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="100" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="89" t="s">
+      <c r="G1" s="69" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="94" t="s">
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="90" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94" t="s">
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="107" t="s">
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="S1" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="63"/>
-      <c r="U1" s="61" t="s">
+      <c r="T1" s="75"/>
+      <c r="U1" s="71" t="s">
         <v>192</v>
       </c>
-      <c r="V1" s="62"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="94" t="s">
+      <c r="V1" s="72"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="90" t="s">
         <v>191</v>
       </c>
-      <c r="Y1" s="94"/>
+      <c r="Y1" s="90"/>
     </row>
     <row r="2" spans="1:25" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="124"/>
       <c r="B2" s="124"/>
       <c r="C2" s="124"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
       <c r="G2" s="42" t="s">
         <v>23</v>
       </c>
@@ -18331,9 +18331,9 @@
         <v>59</v>
       </c>
       <c r="Q2" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
-      <c r="R2" s="109"/>
+      <c r="R2" s="98"/>
       <c r="S2" s="34" t="s">
         <v>85</v>
       </c>
@@ -23837,27 +23837,27 @@
       <c r="D1" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="57" t="s">
+      <c r="G1" s="100" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="108" t="s">
+      <c r="H1" s="97" t="s">
         <v>177</v>
       </c>
-      <c r="I1" s="87" t="s">
+      <c r="I1" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="88"/>
-      <c r="K1" s="84" t="s">
+      <c r="J1" s="68"/>
+      <c r="K1" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="86"/>
-      <c r="M1" s="108" t="s">
+      <c r="L1" s="66"/>
+      <c r="M1" s="97" t="s">
         <v>182</v>
       </c>
       <c r="N1" s="125" t="s">
@@ -23866,7 +23866,7 @@
       <c r="O1" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="108" t="s">
+      <c r="P1" s="97" t="s">
         <v>181</v>
       </c>
       <c r="Q1" s="125" t="s">
@@ -23875,20 +23875,20 @@
       <c r="R1" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="90" t="s">
+      <c r="S1" s="70" t="s">
         <v>191</v>
       </c>
-      <c r="T1" s="90"/>
+      <c r="T1" s="70"/>
     </row>
     <row r="2" spans="1:20" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="124"/>
       <c r="B2" s="124"/>
       <c r="C2" s="124"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="109"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="98"/>
       <c r="I2" s="36" t="s">
         <v>178</v>
       </c>
@@ -23901,12 +23901,12 @@
       <c r="L2" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="109"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
       <c r="S2" s="36" t="s">
         <v>180</v>
       </c>
@@ -28317,16 +28317,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="LYFU8JE4J8WBzpl/b4zqaQPLnLsCDSe2zWW+8dNgs/2PHOZq06/1QnNdJiP29gcTnH4LQIS1HvbDau5S5pjwdg==" saltValue="bo/QzTypvgnDcZydb/HXQw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="H1:H2"/>
@@ -28334,6 +28324,16 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 H1:H2 P1:P2 S2 J2 E1:E2 G1:G2 I2 M1:M2 T2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -28398,10 +28398,10 @@
         <v>23</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J1" s="33" t="s">
         <v>110</v>
@@ -31059,117 +31059,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="90" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="81" t="s">
-        <v>210</v>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="61" t="s">
+        <v>209</v>
       </c>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="83"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="63"/>
       <c r="Y1" s="39"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="61" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="86"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="66"/>
       <c r="Y2" s="39"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="78"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="87" t="s">
+      <c r="A3" s="57"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="87" t="s">
+      <c r="E3" s="68"/>
+      <c r="F3" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="88"/>
-      <c r="H3" s="93" t="s">
+      <c r="G3" s="68"/>
+      <c r="H3" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="87" t="s">
+      <c r="I3" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="87" t="s">
+      <c r="J3" s="68"/>
+      <c r="K3" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="88"/>
-      <c r="M3" s="91" t="s">
+      <c r="L3" s="68"/>
+      <c r="M3" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="N3" s="79" t="s">
-        <v>233</v>
+      <c r="N3" s="59" t="s">
+        <v>232</v>
       </c>
-      <c r="O3" s="79"/>
-      <c r="P3" s="80" t="s">
+      <c r="O3" s="59"/>
+      <c r="P3" s="60" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60" t="s">
         <v>231</v>
       </c>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80" t="s">
-        <v>232</v>
-      </c>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
     </row>
     <row r="4" spans="1:25" s="40" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="30" t="s">
         <v>108</v>
       </c>
@@ -31188,7 +31188,7 @@
       <c r="G4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="90"/>
+      <c r="H4" s="70"/>
       <c r="I4" s="36" t="s">
         <v>115</v>
       </c>
@@ -31201,7 +31201,7 @@
       <c r="L4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="92"/>
+      <c r="M4" s="74"/>
       <c r="N4" s="30" t="s">
         <v>5</v>
       </c>
@@ -36476,102 +36476,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="95" t="s">
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="96"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="107" t="s">
+      <c r="H1" s="103"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="96" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="99" t="s">
+      <c r="L1" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="101"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="89"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="89" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="94" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="106" t="s">
+      <c r="D2" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="94" t="s">
+      <c r="F2" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="102" t="s">
+      <c r="G2" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="H2" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="98" t="s">
+      <c r="I2" s="105" t="s">
         <v>158</v>
       </c>
-      <c r="J2" s="108"/>
-      <c r="K2" s="57" t="s">
+      <c r="J2" s="97"/>
+      <c r="K2" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79" t="s">
+      <c r="M2" s="59"/>
+      <c r="N2" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="79"/>
-      <c r="P2" s="94" t="s">
+      <c r="O2" s="59"/>
+      <c r="P2" s="90" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="58"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="101"/>
       <c r="L3" s="30" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
-      <c r="P3" s="94"/>
+      <c r="P3" s="90"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -40175,6 +40175,10 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="1cicS5Lfrk+5Ikf7QAPb58hz7eEpXXWrVfI0HjUb1ZSCRmF1spVwuukBA70xdhXph1ojRMo4vKzKONUJgs2EdA==" saltValue="VZjUWywuY51JVfym8Ql6fg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:P3"/>
@@ -40188,10 +40192,6 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I2:I3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 K2:K3 G2:I3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40235,47 +40235,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="90" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94" t="s">
-        <v>212</v>
-      </c>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="93" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="93" t="s">
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="76" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
+      <c r="A3" s="58"/>
       <c r="B3" s="36" t="s">
         <v>115</v>
       </c>
@@ -40288,7 +40288,7 @@
       <c r="E3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="90"/>
+      <c r="F3" s="70"/>
       <c r="G3" s="36" t="s">
         <v>115</v>
       </c>
@@ -40301,7 +40301,7 @@
       <c r="J3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="90"/>
+      <c r="K3" s="70"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -42977,156 +42977,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="71" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="61" t="s">
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="71" t="s">
+        <v>212</v>
+      </c>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="75"/>
+      <c r="AH1" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="63"/>
-      <c r="AH1" s="61" t="s">
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
+      <c r="AM1" s="72"/>
+      <c r="AN1" s="72"/>
+      <c r="AO1" s="75"/>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A2" s="57"/>
+      <c r="B2" s="76" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="76" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="96" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="76" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="60"/>
+      <c r="U2" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="V2" s="90" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="90" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="90" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="90" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB2" s="90" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC2" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD2" s="90" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE2" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG2" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH2" s="102" t="s">
         <v>214</v>
       </c>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="63"/>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="93" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="107" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="80" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="L2" s="80" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="80"/>
-      <c r="U2" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="94" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="94" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="94" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="94" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB2" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC2" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD2" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE2" s="94" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF2" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="AG2" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH2" s="95" t="s">
+      <c r="AI2" s="104"/>
+      <c r="AJ2" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="AI2" s="97"/>
-      <c r="AJ2" s="80" t="s">
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60" t="s">
         <v>216</v>
       </c>
-      <c r="AK2" s="80"/>
-      <c r="AL2" s="80" t="s">
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="AM2" s="80"/>
-      <c r="AN2" s="80" t="s">
-        <v>218</v>
-      </c>
-      <c r="AO2" s="80"/>
+      <c r="AO2" s="60"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="109"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="98"/>
       <c r="E3" s="32" t="s">
         <v>24</v>
       </c>
@@ -43145,7 +43145,7 @@
       <c r="J3" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="K3" s="90"/>
+      <c r="K3" s="70"/>
       <c r="L3" s="29" t="s">
         <v>127</v>
       </c>
@@ -43173,19 +43173,19 @@
       <c r="T3" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="U3" s="94"/>
-      <c r="V3" s="94"/>
-      <c r="W3" s="94"/>
-      <c r="X3" s="94"/>
-      <c r="Y3" s="94"/>
-      <c r="Z3" s="94"/>
-      <c r="AA3" s="94"/>
-      <c r="AB3" s="94"/>
-      <c r="AC3" s="94"/>
-      <c r="AD3" s="94"/>
-      <c r="AE3" s="94"/>
-      <c r="AF3" s="94"/>
-      <c r="AG3" s="94"/>
+      <c r="U3" s="90"/>
+      <c r="V3" s="90"/>
+      <c r="W3" s="90"/>
+      <c r="X3" s="90"/>
+      <c r="Y3" s="90"/>
+      <c r="Z3" s="90"/>
+      <c r="AA3" s="90"/>
+      <c r="AB3" s="90"/>
+      <c r="AC3" s="90"/>
+      <c r="AD3" s="90"/>
+      <c r="AE3" s="90"/>
+      <c r="AF3" s="90"/>
+      <c r="AG3" s="90"/>
       <c r="AH3" s="29" t="s">
         <v>137</v>
       </c>
@@ -51814,6 +51814,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="wxJYPTS1M8YrpE+F5HXpzPvhVkWn+uzvbhQbX4zWGt7tgJJAc6rvipv1/0hraJgXbUY0X5vYRquC66cBDOGcbg==" saltValue="RWTcEymG3DdteXmtyGeu4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -51830,20 +51844,6 @@
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 R3 AI3 AK3 AM3 L3 M3 N3 O3 P3 Q3 AO3 AJ3 AL3 AN3 AH3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -51887,17 +51887,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="69" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
+      <c r="A2" s="58"/>
       <c r="B2" s="30" t="s">
         <v>165</v>
       </c>
@@ -53139,25 +53139,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="90" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="71" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="63"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
+      <c r="A2" s="58"/>
       <c r="B2" s="47" t="s">
         <v>145</v>
       </c>
@@ -55630,60 +55630,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="106" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="113" t="s">
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="111"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="57"/>
+      <c r="B2" s="99" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="76" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>163</v>
+      </c>
+      <c r="J2" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="115"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="99" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="93" t="s">
-        <v>162</v>
-      </c>
-      <c r="I2" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="J2" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="88"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="68"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
       <c r="C3" s="53" t="s">
         <v>23</v>
       </c>
@@ -55699,8 +55699,8 @@
       <c r="G3" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="90"/>
-      <c r="I3" s="60"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="58"/>
       <c r="J3" s="54" t="s">
         <v>23</v>
       </c>
@@ -59390,136 +59390,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="110" t="s">
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="111"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="59" t="s">
+      <c r="G1" s="107"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="99" t="s">
+        <v>235</v>
+      </c>
+      <c r="J1" s="99" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="K1" s="109" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="110"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="109" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="111"/>
+      <c r="P1" s="69" t="s">
         <v>237</v>
       </c>
-      <c r="K1" s="113" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="114"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="113" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1" s="115"/>
-      <c r="P1" s="89" t="s">
+      <c r="Q1" s="90" t="s">
         <v>238</v>
       </c>
-      <c r="Q1" s="94" t="s">
+      <c r="R1" s="69" t="s">
         <v>239</v>
       </c>
-      <c r="R1" s="89" t="s">
-        <v>240</v>
+      <c r="S1" s="69" t="s">
+        <v>245</v>
       </c>
-      <c r="S1" s="89" t="s">
+      <c r="T1" s="69"/>
+      <c r="U1" s="113" t="s">
         <v>246</v>
       </c>
-      <c r="T1" s="89"/>
-      <c r="U1" s="117" t="s">
+      <c r="V1" s="114"/>
+      <c r="W1" s="113" t="s">
         <v>247</v>
       </c>
-      <c r="V1" s="118"/>
-      <c r="W1" s="117" t="s">
+      <c r="X1" s="114"/>
+      <c r="Y1" s="113" t="s">
         <v>248</v>
       </c>
-      <c r="X1" s="118"/>
-      <c r="Y1" s="117" t="s">
-        <v>249</v>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="69" t="s">
+        <v>244</v>
       </c>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="89" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB1" s="89"/>
-      <c r="AC1" s="89"/>
-      <c r="AD1" s="89"/>
+      <c r="AB1" s="69"/>
+      <c r="AC1" s="69"/>
+      <c r="AD1" s="69"/>
     </row>
     <row r="2" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="81" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="D2" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="112"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="108"/>
+      <c r="F2" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="110" t="s">
+      <c r="G2" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="112"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-      <c r="U2" s="84"/>
-      <c r="V2" s="86"/>
-      <c r="W2" s="84"/>
-      <c r="X2" s="86"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="86"/>
-      <c r="AA2" s="89"/>
-      <c r="AB2" s="89"/>
-      <c r="AC2" s="89"/>
-      <c r="AD2" s="89"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="90"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="66"/>
+      <c r="AA2" s="69"/>
+      <c r="AB2" s="69"/>
+      <c r="AC2" s="69"/>
+      <c r="AD2" s="69"/>
     </row>
     <row r="3" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="84"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="64"/>
       <c r="D3" s="30" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="60"/>
+      <c r="F3" s="58"/>
       <c r="G3" s="30" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="36" t="s">
         <v>193</v>
       </c>
       <c r="L3" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N3" s="33" t="s">
         <v>47</v>
@@ -59527,9 +59527,9 @@
       <c r="O3" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="94"/>
-      <c r="R3" s="89"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="90"/>
+      <c r="R3" s="69"/>
       <c r="S3" s="30" t="s">
         <v>50</v>
       </c>
@@ -59555,16 +59555,16 @@
         <v>129</v>
       </c>
       <c r="AA3" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB3" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="AB3" s="36" t="s">
+      <c r="AC3" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AD3" s="36" t="s">
         <v>243</v>
-      </c>
-      <c r="AD3" s="36" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -65942,11 +65942,8 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="WuDPT1+slParW8lK5SfJrIiCuXUqugKfunXVVDY0YB00pOtHXcdvDQyUD/jzqYTc2x6TyFXXd8XFSXwF4cqxTw==" saltValue="kHXwsv450+CnM8/ussNlMw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="Y1:Z2"/>
     <mergeCell ref="AA1:AD2"/>
     <mergeCell ref="U1:V2"/>
@@ -65956,12 +65953,15 @@
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="S1:T2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBED03F8-E4E0-2E4D-A39C-9C4EC90B3CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41AC23C-707C-1F4C-9D41-8D5151EB332F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="15280" yWindow="740" windowWidth="13760" windowHeight="16560" tabRatio="879" activeTab="2" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="9700" yWindow="740" windowWidth="19340" windowHeight="16560" tabRatio="879" firstSheet="14" activeTab="16" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="253">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -268,9 +268,6 @@
   </si>
   <si>
     <t>LEADER</t>
-  </si>
-  <si>
-    <t>IS_STRAIGHT</t>
   </si>
   <si>
     <t>LIGHT_ATTACHED</t>
@@ -1199,7 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1459,6 +1456,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1502,30 +1523,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1547,12 +1544,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1560,6 +1551,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1600,6 +1597,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1940,7 +1940,7 @@
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="63" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="64"/>
       <c r="D2" s="64"/>
@@ -1961,14 +1961,14 @@
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
@@ -1987,7 +1987,7 @@
     <row r="6" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
       <c r="C6" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -2007,12 +2007,12 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="10"/>
       <c r="C8" s="69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D8" s="69"/>
       <c r="E8" s="11"/>
       <c r="F8" s="69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G8" s="69"/>
       <c r="H8" s="12"/>
@@ -2020,12 +2020,12 @@
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="10"/>
       <c r="C9" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="11"/>
       <c r="F9" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="12"/>
@@ -2033,12 +2033,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="10"/>
       <c r="C10" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="12"/>
@@ -2055,7 +2055,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="10"/>
       <c r="C12" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="11"/>
@@ -2066,7 +2066,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="10"/>
       <c r="C13" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="11"/>
@@ -2095,7 +2095,7 @@
     <row r="16" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="10"/>
       <c r="C16" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -2115,7 +2115,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="10"/>
       <c r="C18" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="11"/>
@@ -2126,7 +2126,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="11"/>
@@ -2137,7 +2137,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="10"/>
       <c r="C20" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="11"/>
@@ -2148,7 +2148,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="10"/>
       <c r="C21" s="56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="11"/>
@@ -2177,7 +2177,7 @@
     <row r="24" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B24" s="10"/>
       <c r="C24" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="11"/>
@@ -2262,19 +2262,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C1" s="42" t="s">
         <v>23</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -3678,7 +3678,7 @@
       <c r="E201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DLCB63B23U6U/lvPjFBDwEw54SvWavVGd/ry1Nz6DhxUhtPs0tekL39KhQ3y1urH3e4XUVdLFm8IJdMQYhrtZw==" saltValue="998QCynidC46at4wkVVL1A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QB4qv4KWmi8AKpOm/fsHmFj67JpIjuEeSW49PLwPomI30J0RJk2G77ldjvpebTVdCg6Ph3QuJxrI6vixEyZ6wg==" saltValue="wxXFjpqr6oTGyZgmU5AtSA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 D1" xr:uid="{B060D15A-6570-447A-A9A0-240DB07B3A95}">
       <formula1>"&lt;0&gt;0"</formula1>
@@ -3714,39 +3714,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
-      <c r="C1" s="105" t="s">
+      <c r="C1" s="93" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="93" t="s">
         <v>226</v>
-      </c>
-      <c r="D1" s="105" t="s">
-        <v>227</v>
       </c>
       <c r="E1" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="105" t="s">
-        <v>248</v>
+      <c r="F1" s="93" t="s">
+        <v>247</v>
       </c>
-      <c r="G1" s="105" t="s">
-        <v>225</v>
+      <c r="G1" s="93" t="s">
+        <v>224</v>
       </c>
-      <c r="H1" s="105" t="s">
+      <c r="H1" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="105" t="s">
-        <v>93</v>
+      <c r="I1" s="93" t="s">
+        <v>92</v>
       </c>
       <c r="J1" s="87" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K1" s="91"/>
       <c r="L1" s="112" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M1" s="113"/>
       <c r="N1" s="113"/>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="2" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
-      <c r="B2" s="123"/>
+      <c r="B2" s="121"/>
       <c r="C2" s="74"/>
       <c r="D2" s="74"/>
       <c r="E2" s="86"/>
@@ -3766,19 +3766,19 @@
         <v>46</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L2" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="M2" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="M2" s="42" t="s">
+      <c r="N2" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="42" t="s">
         <v>223</v>
-      </c>
-      <c r="O2" s="42" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -7181,19 +7181,19 @@
       <c r="O202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="baPXpgv3RLDr1X/OL0/u95N0yGUjmYbEPR98MG9WGr4cLRtXThci5CqqpLAjGFcppPJrTQ2e0R0G8Y/lpP/L1w==" saltValue="DISKlLYHwnp/Jq48K56kEA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1fmYkNASk0PME9obSWEOXJjBymc/5o6Nr334dtAFOVXWwoRNq0Kv2M8XCusIKCG4bzATE1HQx1dwjunRzj0r1g==" saltValue="294bpzd/5y5PNSnEY3E1qg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 M2 N2 O2" xr:uid="{35387E2C-FBDF-4B0A-A0B5-EF76A6744ABB}">
@@ -7201,10 +7201,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" location="mitigationDevices" display="MEASURE_1_CODE" xr:uid="{17ECAAFC-23EF-4442-A795-3CBE28E725C7}"/>
-    <hyperlink ref="M2" r:id="rId2" location="mitigationDevices" display="MEASURE_2_CODE" xr:uid="{9E2DB471-3AB8-4107-8E8F-4EEB9D605CB0}"/>
-    <hyperlink ref="N2" r:id="rId3" location="mitigationDevices" display="MEASURE_3_CODE" xr:uid="{E3EEDC36-CCD8-469B-B57B-741ACBCA7B8A}"/>
-    <hyperlink ref="O2" r:id="rId4" location="mitigationDevices" display="MEASURE_4_CODE" xr:uid="{34CD3D2C-B05C-4091-9584-AC3E1DEA70BA}"/>
+    <hyperlink ref="L2" r:id="rId1" location="mitigationDevices" xr:uid="{17ECAAFC-23EF-4442-A795-3CBE28E725C7}"/>
+    <hyperlink ref="M2" r:id="rId2" location="mitigationDevices" xr:uid="{9E2DB471-3AB8-4107-8E8F-4EEB9D605CB0}"/>
+    <hyperlink ref="N2" r:id="rId3" location="mitigationDevices" xr:uid="{E3EEDC36-CCD8-469B-B57B-741ACBCA7B8A}"/>
+    <hyperlink ref="O2" r:id="rId4" location="mitigationDevices" xr:uid="{34CD3D2C-B05C-4091-9584-AC3E1DEA70BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7226,21 +7226,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
       <c r="C1" s="112" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D1" s="113"/>
       <c r="E1" s="114"/>
     </row>
     <row r="2" spans="1:5" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
-      <c r="B2" s="123"/>
+      <c r="B2" s="121"/>
       <c r="C2" s="42" t="s">
         <v>23</v>
       </c>
@@ -8652,7 +8652,7 @@
       <c r="E202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SQSXCmB8k91CC4wqOZlRugG2WySBCTOkKAx/bdBAvGnIu08EuxETgZ4086Y9pchYCiPBvLV/ghZrn4oWmxAN5A==" saltValue="KJp7cW4sExRqUllEXzQNbg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="97Vmxzc3aN/FSgL5c5GTiQhFVBHjxMsP+4A6xC8uBWLXLRDLidZCElQB7H8fQwsezr1qCzcOKu0E+HWGYRCbUw==" saltValue="pcCm0N46Z280pqJcw2wj+A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A1:A2"/>
@@ -8681,11 +8681,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
       <c r="C1" s="112" t="s">
         <v>69</v>
@@ -8696,12 +8696,12 @@
     </row>
     <row r="2" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
-      <c r="B2" s="123"/>
+      <c r="B2" s="121"/>
       <c r="C2" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E2" s="30" t="s">
         <v>51</v>
@@ -10311,7 +10311,7 @@
       <c r="F202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="2U1Dtk5D13gIckotshSgCCkDT6dFqNZ9h8l12nT4KPtEaMWn4JmqDNWRFE+ya2jXYCGF2qBgMUcx3t5cAHOPLg==" saltValue="nkx/6pW5BHtA3UJRQtoQvw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WOL0dANPm8tljqjnIymLj1w192lgSRYTwNoW22IzS26e/szqwsb3/zVE7keHtpIgknDhP5a4dvQradG0oTJQmQ==" saltValue="kFcV0ziJS8n65gnB/uqsZg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A1:A2"/>
@@ -10323,8 +10323,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" location="baits" display="SPECIES_CODE" xr:uid="{D849EFD5-707B-4C7E-BB2A-B091E478F30F}"/>
-    <hyperlink ref="C2" r:id="rId2" location="baitConditions" display="CONDITION_CODE" xr:uid="{677A485E-282F-407D-9CFC-1AB91778C9AC}"/>
+    <hyperlink ref="D2" r:id="rId1" location="baits" xr:uid="{D849EFD5-707B-4C7E-BB2A-B091E478F30F}"/>
+    <hyperlink ref="C2" r:id="rId2" location="baitConditions" xr:uid="{677A485E-282F-407D-9CFC-1AB91778C9AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10355,66 +10355,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
       <c r="C1" s="112" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D1" s="113"/>
       <c r="E1" s="114"/>
       <c r="F1" s="112" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G1" s="113"/>
       <c r="H1" s="114"/>
-      <c r="I1" s="97" t="s">
+      <c r="I1" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="96" t="s">
-        <v>194</v>
+      <c r="J1" s="103" t="s">
+        <v>193</v>
       </c>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
       <c r="N1" s="85" t="s">
         <v>57</v>
       </c>
       <c r="O1" s="85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P1" s="125" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q1" s="124" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="73"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="105" t="s">
-        <v>81</v>
+      <c r="B2" s="120"/>
+      <c r="C2" s="93" t="s">
+        <v>80</v>
       </c>
       <c r="D2" s="112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" s="114"/>
-      <c r="F2" s="105" t="s">
-        <v>81</v>
+      <c r="F2" s="93" t="s">
+        <v>80</v>
       </c>
       <c r="G2" s="112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" s="114"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
       <c r="N2" s="85"/>
       <c r="O2" s="85"/>
       <c r="P2" s="126"/>
@@ -10422,7 +10422,7 @@
     </row>
     <row r="3" spans="1:17" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="74"/>
-      <c r="B3" s="123"/>
+      <c r="B3" s="121"/>
       <c r="C3" s="74"/>
       <c r="D3" s="30" t="s">
         <v>0</v>
@@ -10437,18 +10437,18 @@
       <c r="H3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="97"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K3" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="L3" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="M3" s="36" t="s">
         <v>196</v>
-      </c>
-      <c r="M3" s="36" t="s">
-        <v>197</v>
       </c>
       <c r="N3" s="85"/>
       <c r="O3" s="85"/>
@@ -14256,8 +14256,13 @@
       <c r="Q203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="srv8pW+3Z2AJOXP1CItheJ8G7+DSSCun/A7fMYIGGHavMwCPp115h0B/Ovfj34Cx0OVquASFSSBNdsKQm3ExvA==" saltValue="f+k975S3CukG6KHPjTx5MA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="v9/r9AHf3IXtAUKjnFIWMs9fQf8bbXQFk2+w8Obr7jv9Lp+se/Sz+3k3XKSdDtG1PsrsU5eYTWKIw/DXpku1HA==" saltValue="W+kb8UB2ilTByBvFSwBwyQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="Q1:Q3"/>
     <mergeCell ref="O1:O3"/>
     <mergeCell ref="F1:H1"/>
@@ -14267,11 +14272,6 @@
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="P1:P3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I3 M3 J3 K3 L3 Q1:Q3" xr:uid="{2FBCC481-6114-481E-B036-95624C9F7883}">
@@ -14305,11 +14305,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
       <c r="C1" s="87" t="s">
         <v>47</v>
@@ -14318,12 +14318,12 @@
     </row>
     <row r="2" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
-      <c r="B2" s="123"/>
+      <c r="B2" s="121"/>
       <c r="C2" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -15558,27 +15558,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
-      <c r="C1" s="105" t="s">
-        <v>94</v>
+      <c r="C1" s="93" t="s">
+        <v>93</v>
       </c>
       <c r="D1" s="128" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E1" s="130" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F1" s="131"/>
-      <c r="G1" s="106" t="s">
-        <v>183</v>
+      <c r="G1" s="94" t="s">
+        <v>182</v>
       </c>
-      <c r="H1" s="105" t="s">
-        <v>207</v>
+      <c r="H1" s="93" t="s">
+        <v>206</v>
       </c>
       <c r="I1" s="87" t="s">
         <v>58</v>
@@ -15588,25 +15588,25 @@
     </row>
     <row r="2" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
-      <c r="B2" s="123"/>
+      <c r="B2" s="121"/>
       <c r="C2" s="74"/>
       <c r="D2" s="129"/>
       <c r="E2" s="42" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
-      <c r="G2" s="107"/>
+      <c r="G2" s="95"/>
       <c r="H2" s="74"/>
       <c r="I2" s="36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J2" s="33" t="s">
         <v>59</v>
       </c>
       <c r="K2" s="36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -18210,7 +18210,7 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ItxdRvZU8N5JrAp7lripv3MW4swKnWX0P52+M9r4JxitXraHmE74OxekoaD6XCxXsae6OyzRtRSKWKjAhaOGOw==" saltValue="eoJpQ9QoBgKVr7Nl+Yk+kw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oleO8rCrXOnYdnUYNQrosG7tya+5pJKE3BtAxJ3elcUTj16qe0gmxDgIEdhpHX7WiEk6qdEq/pUkfxDh2nbX0Q==" saltValue="VX7/e/8sT39M3ZEJeEzxug==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -18233,9 +18233,10 @@
     <hyperlink ref="F2" r:id="rId4" location="fates" xr:uid="{5DE917A8-1BC5-48A5-BE95-3206B5EEB7AC}"/>
     <hyperlink ref="D1" r:id="rId5" location="allSpecies" xr:uid="{7915C09B-5FFF-4B7E-84FB-D8B7D31EA643}"/>
     <hyperlink ref="G1:G2" r:id="rId6" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD" xr:uid="{C3154411-BFD2-3A41-99A0-2ECAAC5C9F3C}"/>
+    <hyperlink ref="D1:D2" r:id="rId7" location="allSpecies" display="SPECIES" xr:uid="{3971EE03-AC8D-CE4D-834E-C52424A80322}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -18244,7 +18245,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Y202"/>
+  <dimension ref="A1:W202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -18256,84 +18257,80 @@
     <col min="7" max="7" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.83203125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.1640625" style="3"/>
-    <col min="19" max="19" width="14.5" style="3" customWidth="1"/>
-    <col min="20" max="20" width="12.5" style="3" customWidth="1"/>
-    <col min="21" max="21" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.5" style="3" customWidth="1"/>
-    <col min="24" max="24" width="30.6640625" customWidth="1"/>
-    <col min="25" max="25" width="29.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="3" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.83203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" style="3"/>
+    <col min="17" max="17" width="14.5" style="3" customWidth="1"/>
+    <col min="18" max="18" width="12.5" style="3" customWidth="1"/>
+    <col min="19" max="19" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.5" style="3" customWidth="1"/>
+    <col min="22" max="22" width="30.6640625" customWidth="1"/>
+    <col min="23" max="23" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="41" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="134" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C1" s="132" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="132" t="s">
-        <v>95</v>
+      <c r="E1" s="94" t="s">
+        <v>181</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="F1" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="106" t="s">
-        <v>183</v>
-      </c>
       <c r="G1" s="85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H1" s="85"/>
       <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="96" t="s">
-        <v>188</v>
+      <c r="J1" s="103" t="s">
+        <v>187</v>
       </c>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96" t="s">
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="102" t="s">
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="109" t="s">
         <v>61</v>
       </c>
+      <c r="Q1" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="R1" s="91"/>
       <c r="S1" s="87" t="s">
-        <v>87</v>
-      </c>
-      <c r="T1" s="91"/>
-      <c r="U1" s="87" t="s">
-        <v>191</v>
-      </c>
-      <c r="V1" s="88"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="Y1" s="96"/>
-    </row>
-    <row r="2" spans="1:25" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T1" s="88"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="103" t="s">
+        <v>189</v>
+      </c>
+      <c r="W1" s="103"/>
+    </row>
+    <row r="2" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="133"/>
       <c r="B2" s="135"/>
       <c r="C2" s="133"/>
       <c r="D2" s="133"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
       <c r="G2" s="42" t="s">
         <v>23</v>
       </c>
@@ -18341,56 +18338,50 @@
         <v>60</v>
       </c>
       <c r="I2" s="42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="36" t="s">
+      <c r="J2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="K2" s="33" t="s">
         <v>60</v>
       </c>
+      <c r="L2" s="36" t="s">
+        <v>186</v>
+      </c>
       <c r="M2" s="36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="O2" s="36" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
-      <c r="P2" s="33" t="s">
-        <v>59</v>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="34" t="s">
+        <v>84</v>
       </c>
-      <c r="Q2" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="R2" s="104"/>
-      <c r="S2" s="34" t="s">
+      <c r="R2" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="U2" s="52" t="s">
+      <c r="S2" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="V2" s="52" t="s">
+      <c r="T2" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="W2" s="33" t="s">
-        <v>189</v>
+      <c r="U2" s="33" t="s">
+        <v>188</v>
       </c>
-      <c r="X2" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y2" s="36" t="s">
+      <c r="V2" s="36" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" s="41" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="W2" s="36" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="59"/>
       <c r="C3" s="2"/>
@@ -18414,10 +18405,8 @@
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="59"/>
       <c r="C4" s="2"/>
@@ -18441,10 +18430,8 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="59"/>
       <c r="C5" s="2"/>
@@ -18468,10 +18455,8 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="59"/>
       <c r="C6" s="2"/>
@@ -18495,10 +18480,8 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="59"/>
       <c r="C7" s="2"/>
@@ -18522,10 +18505,8 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="59"/>
       <c r="C8" s="2"/>
@@ -18549,10 +18530,8 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="59"/>
       <c r="C9" s="2"/>
@@ -18576,10 +18555,8 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="59"/>
       <c r="C10" s="2"/>
@@ -18603,10 +18580,8 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="59"/>
       <c r="C11" s="2"/>
@@ -18630,10 +18605,8 @@
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="59"/>
       <c r="C12" s="2"/>
@@ -18657,10 +18630,8 @@
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="59"/>
       <c r="C13" s="2"/>
@@ -18684,10 +18655,8 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="59"/>
       <c r="C14" s="2"/>
@@ -18711,10 +18680,8 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="59"/>
       <c r="C15" s="2"/>
@@ -18738,10 +18705,8 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="59"/>
       <c r="C16" s="2"/>
@@ -18765,10 +18730,8 @@
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="59"/>
       <c r="C17" s="2"/>
@@ -18792,10 +18755,8 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="59"/>
       <c r="C18" s="2"/>
@@ -18819,10 +18780,8 @@
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="59"/>
       <c r="C19" s="2"/>
@@ -18846,10 +18805,8 @@
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="59"/>
       <c r="C20" s="2"/>
@@ -18873,10 +18830,8 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="59"/>
       <c r="C21" s="2"/>
@@ -18900,10 +18855,8 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="59"/>
       <c r="C22" s="2"/>
@@ -18927,10 +18880,8 @@
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="59"/>
       <c r="C23" s="2"/>
@@ -18954,10 +18905,8 @@
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="59"/>
       <c r="C24" s="2"/>
@@ -18981,10 +18930,8 @@
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="59"/>
       <c r="C25" s="2"/>
@@ -19008,10 +18955,8 @@
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="59"/>
       <c r="C26" s="2"/>
@@ -19035,10 +18980,8 @@
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="59"/>
       <c r="C27" s="2"/>
@@ -19062,10 +19005,8 @@
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="59"/>
       <c r="C28" s="2"/>
@@ -19089,10 +19030,8 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="59"/>
       <c r="C29" s="2"/>
@@ -19116,10 +19055,8 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="59"/>
       <c r="C30" s="2"/>
@@ -19143,10 +19080,8 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="59"/>
       <c r="C31" s="2"/>
@@ -19170,10 +19105,8 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="59"/>
       <c r="C32" s="2"/>
@@ -19197,10 +19130,8 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="59"/>
       <c r="C33" s="2"/>
@@ -19224,10 +19155,8 @@
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="59"/>
       <c r="C34" s="2"/>
@@ -19251,10 +19180,8 @@
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="2"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="59"/>
       <c r="C35" s="2"/>
@@ -19278,10 +19205,8 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
-      <c r="Y35" s="2"/>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="59"/>
       <c r="C36" s="2"/>
@@ -19305,10 +19230,8 @@
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-      <c r="Y36" s="2"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="59"/>
       <c r="C37" s="2"/>
@@ -19332,10 +19255,8 @@
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
-      <c r="Y37" s="2"/>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="59"/>
       <c r="C38" s="2"/>
@@ -19359,10 +19280,8 @@
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="59"/>
       <c r="C39" s="2"/>
@@ -19386,10 +19305,8 @@
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-      <c r="Y39" s="2"/>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="59"/>
       <c r="C40" s="2"/>
@@ -19413,10 +19330,8 @@
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
-      <c r="X40" s="2"/>
-      <c r="Y40" s="2"/>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="59"/>
       <c r="C41" s="2"/>
@@ -19440,10 +19355,8 @@
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="59"/>
       <c r="C42" s="2"/>
@@ -19467,10 +19380,8 @@
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
-      <c r="X42" s="2"/>
-      <c r="Y42" s="2"/>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="59"/>
       <c r="C43" s="2"/>
@@ -19494,10 +19405,8 @@
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
-      <c r="X43" s="2"/>
-      <c r="Y43" s="2"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="59"/>
       <c r="C44" s="2"/>
@@ -19521,10 +19430,8 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
-      <c r="X44" s="2"/>
-      <c r="Y44" s="2"/>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="59"/>
       <c r="C45" s="2"/>
@@ -19548,10 +19455,8 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
-      <c r="X45" s="2"/>
-      <c r="Y45" s="2"/>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="59"/>
       <c r="C46" s="2"/>
@@ -19575,10 +19480,8 @@
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="59"/>
       <c r="C47" s="2"/>
@@ -19602,10 +19505,8 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="59"/>
       <c r="C48" s="2"/>
@@ -19629,10 +19530,8 @@
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
-      <c r="X48" s="2"/>
-      <c r="Y48" s="2"/>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="59"/>
       <c r="C49" s="2"/>
@@ -19656,10 +19555,8 @@
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="59"/>
       <c r="C50" s="2"/>
@@ -19683,10 +19580,8 @@
       <c r="U50" s="2"/>
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="59"/>
       <c r="C51" s="2"/>
@@ -19710,10 +19605,8 @@
       <c r="U51" s="2"/>
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="59"/>
       <c r="C52" s="2"/>
@@ -19737,10 +19630,8 @@
       <c r="U52" s="2"/>
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
-      <c r="X52" s="2"/>
-      <c r="Y52" s="2"/>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="59"/>
       <c r="C53" s="2"/>
@@ -19764,10 +19655,8 @@
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="59"/>
       <c r="C54" s="2"/>
@@ -19791,10 +19680,8 @@
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
-      <c r="X54" s="2"/>
-      <c r="Y54" s="2"/>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="59"/>
       <c r="C55" s="2"/>
@@ -19818,10 +19705,8 @@
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
-      <c r="X55" s="2"/>
-      <c r="Y55" s="2"/>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="59"/>
       <c r="C56" s="2"/>
@@ -19845,10 +19730,8 @@
       <c r="U56" s="2"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
-      <c r="X56" s="2"/>
-      <c r="Y56" s="2"/>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="59"/>
       <c r="C57" s="2"/>
@@ -19872,10 +19755,8 @@
       <c r="U57" s="2"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
-      <c r="X57" s="2"/>
-      <c r="Y57" s="2"/>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="59"/>
       <c r="C58" s="2"/>
@@ -19899,10 +19780,8 @@
       <c r="U58" s="2"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="59"/>
       <c r="C59" s="2"/>
@@ -19926,10 +19805,8 @@
       <c r="U59" s="2"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="59"/>
       <c r="C60" s="2"/>
@@ -19953,10 +19830,8 @@
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
-      <c r="X60" s="2"/>
-      <c r="Y60" s="2"/>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="59"/>
       <c r="C61" s="2"/>
@@ -19980,10 +19855,8 @@
       <c r="U61" s="2"/>
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
-      <c r="X61" s="2"/>
-      <c r="Y61" s="2"/>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="59"/>
       <c r="C62" s="2"/>
@@ -20007,10 +19880,8 @@
       <c r="U62" s="2"/>
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
-      <c r="X62" s="2"/>
-      <c r="Y62" s="2"/>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="59"/>
       <c r="C63" s="2"/>
@@ -20034,10 +19905,8 @@
       <c r="U63" s="2"/>
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
-      <c r="X63" s="2"/>
-      <c r="Y63" s="2"/>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="59"/>
       <c r="C64" s="2"/>
@@ -20061,10 +19930,8 @@
       <c r="U64" s="2"/>
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
-      <c r="X64" s="2"/>
-      <c r="Y64" s="2"/>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="59"/>
       <c r="C65" s="2"/>
@@ -20088,10 +19955,8 @@
       <c r="U65" s="2"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
-      <c r="X65" s="2"/>
-      <c r="Y65" s="2"/>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="59"/>
       <c r="C66" s="2"/>
@@ -20115,10 +19980,8 @@
       <c r="U66" s="2"/>
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
-      <c r="Y66" s="2"/>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="59"/>
       <c r="C67" s="2"/>
@@ -20142,10 +20005,8 @@
       <c r="U67" s="2"/>
       <c r="V67" s="2"/>
       <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
-      <c r="Y67" s="2"/>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="59"/>
       <c r="C68" s="2"/>
@@ -20169,10 +20030,8 @@
       <c r="U68" s="2"/>
       <c r="V68" s="2"/>
       <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
-      <c r="Y68" s="2"/>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="59"/>
       <c r="C69" s="2"/>
@@ -20196,10 +20055,8 @@
       <c r="U69" s="2"/>
       <c r="V69" s="2"/>
       <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
-      <c r="Y69" s="2"/>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="59"/>
       <c r="C70" s="2"/>
@@ -20223,10 +20080,8 @@
       <c r="U70" s="2"/>
       <c r="V70" s="2"/>
       <c r="W70" s="2"/>
-      <c r="X70" s="2"/>
-      <c r="Y70" s="2"/>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="59"/>
       <c r="C71" s="2"/>
@@ -20250,10 +20105,8 @@
       <c r="U71" s="2"/>
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
-      <c r="Y71" s="2"/>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="59"/>
       <c r="C72" s="2"/>
@@ -20277,10 +20130,8 @@
       <c r="U72" s="2"/>
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
-      <c r="Y72" s="2"/>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="59"/>
       <c r="C73" s="2"/>
@@ -20304,10 +20155,8 @@
       <c r="U73" s="2"/>
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="59"/>
       <c r="C74" s="2"/>
@@ -20331,10 +20180,8 @@
       <c r="U74" s="2"/>
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
-      <c r="X74" s="2"/>
-      <c r="Y74" s="2"/>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="59"/>
       <c r="C75" s="2"/>
@@ -20358,10 +20205,8 @@
       <c r="U75" s="2"/>
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
-      <c r="X75" s="2"/>
-      <c r="Y75" s="2"/>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="59"/>
       <c r="C76" s="2"/>
@@ -20385,10 +20230,8 @@
       <c r="U76" s="2"/>
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
-      <c r="X76" s="2"/>
-      <c r="Y76" s="2"/>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="59"/>
       <c r="C77" s="2"/>
@@ -20412,10 +20255,8 @@
       <c r="U77" s="2"/>
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
-      <c r="X77" s="2"/>
-      <c r="Y77" s="2"/>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="59"/>
       <c r="C78" s="2"/>
@@ -20439,10 +20280,8 @@
       <c r="U78" s="2"/>
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="59"/>
       <c r="C79" s="2"/>
@@ -20466,10 +20305,8 @@
       <c r="U79" s="2"/>
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
-      <c r="Y79" s="2"/>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="59"/>
       <c r="C80" s="2"/>
@@ -20493,10 +20330,8 @@
       <c r="U80" s="2"/>
       <c r="V80" s="2"/>
       <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
-      <c r="Y80" s="2"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="59"/>
       <c r="C81" s="2"/>
@@ -20520,10 +20355,8 @@
       <c r="U81" s="2"/>
       <c r="V81" s="2"/>
       <c r="W81" s="2"/>
-      <c r="X81" s="2"/>
-      <c r="Y81" s="2"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="59"/>
       <c r="C82" s="2"/>
@@ -20547,10 +20380,8 @@
       <c r="U82" s="2"/>
       <c r="V82" s="2"/>
       <c r="W82" s="2"/>
-      <c r="X82" s="2"/>
-      <c r="Y82" s="2"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="59"/>
       <c r="C83" s="2"/>
@@ -20574,10 +20405,8 @@
       <c r="U83" s="2"/>
       <c r="V83" s="2"/>
       <c r="W83" s="2"/>
-      <c r="X83" s="2"/>
-      <c r="Y83" s="2"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="59"/>
       <c r="C84" s="2"/>
@@ -20601,10 +20430,8 @@
       <c r="U84" s="2"/>
       <c r="V84" s="2"/>
       <c r="W84" s="2"/>
-      <c r="X84" s="2"/>
-      <c r="Y84" s="2"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="59"/>
       <c r="C85" s="2"/>
@@ -20628,10 +20455,8 @@
       <c r="U85" s="2"/>
       <c r="V85" s="2"/>
       <c r="W85" s="2"/>
-      <c r="X85" s="2"/>
-      <c r="Y85" s="2"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="59"/>
       <c r="C86" s="2"/>
@@ -20655,10 +20480,8 @@
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
       <c r="W86" s="2"/>
-      <c r="X86" s="2"/>
-      <c r="Y86" s="2"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="59"/>
       <c r="C87" s="2"/>
@@ -20682,10 +20505,8 @@
       <c r="U87" s="2"/>
       <c r="V87" s="2"/>
       <c r="W87" s="2"/>
-      <c r="X87" s="2"/>
-      <c r="Y87" s="2"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="59"/>
       <c r="C88" s="2"/>
@@ -20709,10 +20530,8 @@
       <c r="U88" s="2"/>
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
-      <c r="X88" s="2"/>
-      <c r="Y88" s="2"/>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="59"/>
       <c r="C89" s="2"/>
@@ -20736,10 +20555,8 @@
       <c r="U89" s="2"/>
       <c r="V89" s="2"/>
       <c r="W89" s="2"/>
-      <c r="X89" s="2"/>
-      <c r="Y89" s="2"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="59"/>
       <c r="C90" s="2"/>
@@ -20763,10 +20580,8 @@
       <c r="U90" s="2"/>
       <c r="V90" s="2"/>
       <c r="W90" s="2"/>
-      <c r="X90" s="2"/>
-      <c r="Y90" s="2"/>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="59"/>
       <c r="C91" s="2"/>
@@ -20790,10 +20605,8 @@
       <c r="U91" s="2"/>
       <c r="V91" s="2"/>
       <c r="W91" s="2"/>
-      <c r="X91" s="2"/>
-      <c r="Y91" s="2"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="59"/>
       <c r="C92" s="2"/>
@@ -20817,10 +20630,8 @@
       <c r="U92" s="2"/>
       <c r="V92" s="2"/>
       <c r="W92" s="2"/>
-      <c r="X92" s="2"/>
-      <c r="Y92" s="2"/>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="59"/>
       <c r="C93" s="2"/>
@@ -20844,10 +20655,8 @@
       <c r="U93" s="2"/>
       <c r="V93" s="2"/>
       <c r="W93" s="2"/>
-      <c r="X93" s="2"/>
-      <c r="Y93" s="2"/>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="59"/>
       <c r="C94" s="2"/>
@@ -20871,10 +20680,8 @@
       <c r="U94" s="2"/>
       <c r="V94" s="2"/>
       <c r="W94" s="2"/>
-      <c r="X94" s="2"/>
-      <c r="Y94" s="2"/>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="59"/>
       <c r="C95" s="2"/>
@@ -20898,10 +20705,8 @@
       <c r="U95" s="2"/>
       <c r="V95" s="2"/>
       <c r="W95" s="2"/>
-      <c r="X95" s="2"/>
-      <c r="Y95" s="2"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="59"/>
       <c r="C96" s="2"/>
@@ -20925,10 +20730,8 @@
       <c r="U96" s="2"/>
       <c r="V96" s="2"/>
       <c r="W96" s="2"/>
-      <c r="X96" s="2"/>
-      <c r="Y96" s="2"/>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="59"/>
       <c r="C97" s="2"/>
@@ -20952,10 +20755,8 @@
       <c r="U97" s="2"/>
       <c r="V97" s="2"/>
       <c r="W97" s="2"/>
-      <c r="X97" s="2"/>
-      <c r="Y97" s="2"/>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="59"/>
       <c r="C98" s="2"/>
@@ -20979,10 +20780,8 @@
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
       <c r="W98" s="2"/>
-      <c r="X98" s="2"/>
-      <c r="Y98" s="2"/>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="59"/>
       <c r="C99" s="2"/>
@@ -21006,10 +20805,8 @@
       <c r="U99" s="2"/>
       <c r="V99" s="2"/>
       <c r="W99" s="2"/>
-      <c r="X99" s="2"/>
-      <c r="Y99" s="2"/>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="59"/>
       <c r="C100" s="2"/>
@@ -21033,10 +20830,8 @@
       <c r="U100" s="2"/>
       <c r="V100" s="2"/>
       <c r="W100" s="2"/>
-      <c r="X100" s="2"/>
-      <c r="Y100" s="2"/>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="59"/>
       <c r="C101" s="2"/>
@@ -21060,10 +20855,8 @@
       <c r="U101" s="2"/>
       <c r="V101" s="2"/>
       <c r="W101" s="2"/>
-      <c r="X101" s="2"/>
-      <c r="Y101" s="2"/>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="59"/>
       <c r="C102" s="2"/>
@@ -21087,10 +20880,8 @@
       <c r="U102" s="2"/>
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
-      <c r="Y102" s="2"/>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="59"/>
       <c r="C103" s="2"/>
@@ -21114,10 +20905,8 @@
       <c r="U103" s="2"/>
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
-      <c r="X103" s="2"/>
-      <c r="Y103" s="2"/>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="59"/>
       <c r="C104" s="2"/>
@@ -21141,10 +20930,8 @@
       <c r="U104" s="2"/>
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
-      <c r="X104" s="2"/>
-      <c r="Y104" s="2"/>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="59"/>
       <c r="C105" s="2"/>
@@ -21168,10 +20955,8 @@
       <c r="U105" s="2"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
-      <c r="X105" s="2"/>
-      <c r="Y105" s="2"/>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="59"/>
       <c r="C106" s="2"/>
@@ -21195,10 +20980,8 @@
       <c r="U106" s="2"/>
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
-      <c r="X106" s="2"/>
-      <c r="Y106" s="2"/>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="59"/>
       <c r="C107" s="2"/>
@@ -21222,10 +21005,8 @@
       <c r="U107" s="2"/>
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
-      <c r="X107" s="2"/>
-      <c r="Y107" s="2"/>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="59"/>
       <c r="C108" s="2"/>
@@ -21249,10 +21030,8 @@
       <c r="U108" s="2"/>
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
-      <c r="X108" s="2"/>
-      <c r="Y108" s="2"/>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="59"/>
       <c r="C109" s="2"/>
@@ -21276,10 +21055,8 @@
       <c r="U109" s="2"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
-      <c r="X109" s="2"/>
-      <c r="Y109" s="2"/>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="59"/>
       <c r="C110" s="2"/>
@@ -21303,10 +21080,8 @@
       <c r="U110" s="2"/>
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
-      <c r="X110" s="2"/>
-      <c r="Y110" s="2"/>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="59"/>
       <c r="C111" s="2"/>
@@ -21330,10 +21105,8 @@
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
-      <c r="X111" s="2"/>
-      <c r="Y111" s="2"/>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="59"/>
       <c r="C112" s="2"/>
@@ -21357,10 +21130,8 @@
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
-      <c r="X112" s="2"/>
-      <c r="Y112" s="2"/>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="59"/>
       <c r="C113" s="2"/>
@@ -21384,10 +21155,8 @@
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-      <c r="X113" s="2"/>
-      <c r="Y113" s="2"/>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="59"/>
       <c r="C114" s="2"/>
@@ -21411,10 +21180,8 @@
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="2"/>
-      <c r="Y114" s="2"/>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="59"/>
       <c r="C115" s="2"/>
@@ -21438,10 +21205,8 @@
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
-      <c r="X115" s="2"/>
-      <c r="Y115" s="2"/>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="59"/>
       <c r="C116" s="2"/>
@@ -21465,10 +21230,8 @@
       <c r="U116" s="2"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
-      <c r="X116" s="2"/>
-      <c r="Y116" s="2"/>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="59"/>
       <c r="C117" s="2"/>
@@ -21492,10 +21255,8 @@
       <c r="U117" s="2"/>
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
-      <c r="X117" s="2"/>
-      <c r="Y117" s="2"/>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="59"/>
       <c r="C118" s="2"/>
@@ -21519,10 +21280,8 @@
       <c r="U118" s="2"/>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
-      <c r="X118" s="2"/>
-      <c r="Y118" s="2"/>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="59"/>
       <c r="C119" s="2"/>
@@ -21546,10 +21305,8 @@
       <c r="U119" s="2"/>
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
-      <c r="X119" s="2"/>
-      <c r="Y119" s="2"/>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="59"/>
       <c r="C120" s="2"/>
@@ -21573,10 +21330,8 @@
       <c r="U120" s="2"/>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
-      <c r="X120" s="2"/>
-      <c r="Y120" s="2"/>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="59"/>
       <c r="C121" s="2"/>
@@ -21600,10 +21355,8 @@
       <c r="U121" s="2"/>
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
-      <c r="X121" s="2"/>
-      <c r="Y121" s="2"/>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="59"/>
       <c r="C122" s="2"/>
@@ -21627,10 +21380,8 @@
       <c r="U122" s="2"/>
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
-      <c r="X122" s="2"/>
-      <c r="Y122" s="2"/>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="59"/>
       <c r="C123" s="2"/>
@@ -21654,10 +21405,8 @@
       <c r="U123" s="2"/>
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
-      <c r="X123" s="2"/>
-      <c r="Y123" s="2"/>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="59"/>
       <c r="C124" s="2"/>
@@ -21681,10 +21430,8 @@
       <c r="U124" s="2"/>
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
-      <c r="X124" s="2"/>
-      <c r="Y124" s="2"/>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="59"/>
       <c r="C125" s="2"/>
@@ -21708,10 +21455,8 @@
       <c r="U125" s="2"/>
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
-      <c r="X125" s="2"/>
-      <c r="Y125" s="2"/>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="59"/>
       <c r="C126" s="2"/>
@@ -21735,10 +21480,8 @@
       <c r="U126" s="2"/>
       <c r="V126" s="2"/>
       <c r="W126" s="2"/>
-      <c r="X126" s="2"/>
-      <c r="Y126" s="2"/>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="59"/>
       <c r="C127" s="2"/>
@@ -21762,10 +21505,8 @@
       <c r="U127" s="2"/>
       <c r="V127" s="2"/>
       <c r="W127" s="2"/>
-      <c r="X127" s="2"/>
-      <c r="Y127" s="2"/>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="59"/>
       <c r="C128" s="2"/>
@@ -21789,10 +21530,8 @@
       <c r="U128" s="2"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
-      <c r="X128" s="2"/>
-      <c r="Y128" s="2"/>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="59"/>
       <c r="C129" s="2"/>
@@ -21816,10 +21555,8 @@
       <c r="U129" s="2"/>
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
-      <c r="X129" s="2"/>
-      <c r="Y129" s="2"/>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="59"/>
       <c r="C130" s="2"/>
@@ -21843,10 +21580,8 @@
       <c r="U130" s="2"/>
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
-      <c r="X130" s="2"/>
-      <c r="Y130" s="2"/>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="59"/>
       <c r="C131" s="2"/>
@@ -21870,10 +21605,8 @@
       <c r="U131" s="2"/>
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
-      <c r="X131" s="2"/>
-      <c r="Y131" s="2"/>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="59"/>
       <c r="C132" s="2"/>
@@ -21897,10 +21630,8 @@
       <c r="U132" s="2"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-      <c r="X132" s="2"/>
-      <c r="Y132" s="2"/>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="59"/>
       <c r="C133" s="2"/>
@@ -21924,10 +21655,8 @@
       <c r="U133" s="2"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-      <c r="X133" s="2"/>
-      <c r="Y133" s="2"/>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="59"/>
       <c r="C134" s="2"/>
@@ -21951,10 +21680,8 @@
       <c r="U134" s="2"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-      <c r="X134" s="2"/>
-      <c r="Y134" s="2"/>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="59"/>
       <c r="C135" s="2"/>
@@ -21978,10 +21705,8 @@
       <c r="U135" s="2"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-      <c r="X135" s="2"/>
-      <c r="Y135" s="2"/>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="59"/>
       <c r="C136" s="2"/>
@@ -22005,10 +21730,8 @@
       <c r="U136" s="2"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-      <c r="X136" s="2"/>
-      <c r="Y136" s="2"/>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="59"/>
       <c r="C137" s="2"/>
@@ -22032,10 +21755,8 @@
       <c r="U137" s="2"/>
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
-      <c r="X137" s="2"/>
-      <c r="Y137" s="2"/>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="59"/>
       <c r="C138" s="2"/>
@@ -22059,10 +21780,8 @@
       <c r="U138" s="2"/>
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
-      <c r="X138" s="2"/>
-      <c r="Y138" s="2"/>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="59"/>
       <c r="C139" s="2"/>
@@ -22086,10 +21805,8 @@
       <c r="U139" s="2"/>
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
-      <c r="X139" s="2"/>
-      <c r="Y139" s="2"/>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="59"/>
       <c r="C140" s="2"/>
@@ -22113,10 +21830,8 @@
       <c r="U140" s="2"/>
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
-      <c r="X140" s="2"/>
-      <c r="Y140" s="2"/>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="59"/>
       <c r="C141" s="2"/>
@@ -22140,10 +21855,8 @@
       <c r="U141" s="2"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-      <c r="X141" s="2"/>
-      <c r="Y141" s="2"/>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="59"/>
       <c r="C142" s="2"/>
@@ -22167,10 +21880,8 @@
       <c r="U142" s="2"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-      <c r="X142" s="2"/>
-      <c r="Y142" s="2"/>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="59"/>
       <c r="C143" s="2"/>
@@ -22194,10 +21905,8 @@
       <c r="U143" s="2"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-      <c r="X143" s="2"/>
-      <c r="Y143" s="2"/>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="59"/>
       <c r="C144" s="2"/>
@@ -22221,10 +21930,8 @@
       <c r="U144" s="2"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-      <c r="X144" s="2"/>
-      <c r="Y144" s="2"/>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="59"/>
       <c r="C145" s="2"/>
@@ -22248,10 +21955,8 @@
       <c r="U145" s="2"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-      <c r="X145" s="2"/>
-      <c r="Y145" s="2"/>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="59"/>
       <c r="C146" s="2"/>
@@ -22275,10 +21980,8 @@
       <c r="U146" s="2"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-      <c r="X146" s="2"/>
-      <c r="Y146" s="2"/>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="59"/>
       <c r="C147" s="2"/>
@@ -22302,10 +22005,8 @@
       <c r="U147" s="2"/>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
-      <c r="X147" s="2"/>
-      <c r="Y147" s="2"/>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="59"/>
       <c r="C148" s="2"/>
@@ -22329,10 +22030,8 @@
       <c r="U148" s="2"/>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
-      <c r="X148" s="2"/>
-      <c r="Y148" s="2"/>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="59"/>
       <c r="C149" s="2"/>
@@ -22356,10 +22055,8 @@
       <c r="U149" s="2"/>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
-      <c r="X149" s="2"/>
-      <c r="Y149" s="2"/>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="59"/>
       <c r="C150" s="2"/>
@@ -22383,10 +22080,8 @@
       <c r="U150" s="2"/>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
-      <c r="X150" s="2"/>
-      <c r="Y150" s="2"/>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="59"/>
       <c r="C151" s="2"/>
@@ -22410,10 +22105,8 @@
       <c r="U151" s="2"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-      <c r="X151" s="2"/>
-      <c r="Y151" s="2"/>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="59"/>
       <c r="C152" s="2"/>
@@ -22437,10 +22130,8 @@
       <c r="U152" s="2"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-      <c r="X152" s="2"/>
-      <c r="Y152" s="2"/>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="59"/>
       <c r="C153" s="2"/>
@@ -22464,10 +22155,8 @@
       <c r="U153" s="2"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-      <c r="X153" s="2"/>
-      <c r="Y153" s="2"/>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="59"/>
       <c r="C154" s="2"/>
@@ -22491,10 +22180,8 @@
       <c r="U154" s="2"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-      <c r="X154" s="2"/>
-      <c r="Y154" s="2"/>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="59"/>
       <c r="C155" s="2"/>
@@ -22518,10 +22205,8 @@
       <c r="U155" s="2"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-      <c r="X155" s="2"/>
-      <c r="Y155" s="2"/>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="59"/>
       <c r="C156" s="2"/>
@@ -22545,10 +22230,8 @@
       <c r="U156" s="2"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-      <c r="X156" s="2"/>
-      <c r="Y156" s="2"/>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="59"/>
       <c r="C157" s="2"/>
@@ -22572,10 +22255,8 @@
       <c r="U157" s="2"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-      <c r="X157" s="2"/>
-      <c r="Y157" s="2"/>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="59"/>
       <c r="C158" s="2"/>
@@ -22599,10 +22280,8 @@
       <c r="U158" s="2"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-      <c r="X158" s="2"/>
-      <c r="Y158" s="2"/>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="59"/>
       <c r="C159" s="2"/>
@@ -22626,10 +22305,8 @@
       <c r="U159" s="2"/>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
-      <c r="X159" s="2"/>
-      <c r="Y159" s="2"/>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="59"/>
       <c r="C160" s="2"/>
@@ -22653,10 +22330,8 @@
       <c r="U160" s="2"/>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
-      <c r="X160" s="2"/>
-      <c r="Y160" s="2"/>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="59"/>
       <c r="C161" s="2"/>
@@ -22680,10 +22355,8 @@
       <c r="U161" s="2"/>
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
-      <c r="X161" s="2"/>
-      <c r="Y161" s="2"/>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="59"/>
       <c r="C162" s="2"/>
@@ -22707,10 +22380,8 @@
       <c r="U162" s="2"/>
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
-      <c r="X162" s="2"/>
-      <c r="Y162" s="2"/>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="59"/>
       <c r="C163" s="2"/>
@@ -22734,10 +22405,8 @@
       <c r="U163" s="2"/>
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
-      <c r="X163" s="2"/>
-      <c r="Y163" s="2"/>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="59"/>
       <c r="C164" s="2"/>
@@ -22761,10 +22430,8 @@
       <c r="U164" s="2"/>
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
-      <c r="X164" s="2"/>
-      <c r="Y164" s="2"/>
-    </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="59"/>
       <c r="C165" s="2"/>
@@ -22788,10 +22455,8 @@
       <c r="U165" s="2"/>
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
-      <c r="X165" s="2"/>
-      <c r="Y165" s="2"/>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="59"/>
       <c r="C166" s="2"/>
@@ -22815,10 +22480,8 @@
       <c r="U166" s="2"/>
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
-      <c r="X166" s="2"/>
-      <c r="Y166" s="2"/>
-    </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="59"/>
       <c r="C167" s="2"/>
@@ -22842,10 +22505,8 @@
       <c r="U167" s="2"/>
       <c r="V167" s="2"/>
       <c r="W167" s="2"/>
-      <c r="X167" s="2"/>
-      <c r="Y167" s="2"/>
-    </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="59"/>
       <c r="C168" s="2"/>
@@ -22869,10 +22530,8 @@
       <c r="U168" s="2"/>
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
-      <c r="X168" s="2"/>
-      <c r="Y168" s="2"/>
-    </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="59"/>
       <c r="C169" s="2"/>
@@ -22896,10 +22555,8 @@
       <c r="U169" s="2"/>
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
-      <c r="X169" s="2"/>
-      <c r="Y169" s="2"/>
-    </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="59"/>
       <c r="C170" s="2"/>
@@ -22923,10 +22580,8 @@
       <c r="U170" s="2"/>
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
-      <c r="X170" s="2"/>
-      <c r="Y170" s="2"/>
-    </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="59"/>
       <c r="C171" s="2"/>
@@ -22950,10 +22605,8 @@
       <c r="U171" s="2"/>
       <c r="V171" s="2"/>
       <c r="W171" s="2"/>
-      <c r="X171" s="2"/>
-      <c r="Y171" s="2"/>
-    </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="59"/>
       <c r="C172" s="2"/>
@@ -22977,10 +22630,8 @@
       <c r="U172" s="2"/>
       <c r="V172" s="2"/>
       <c r="W172" s="2"/>
-      <c r="X172" s="2"/>
-      <c r="Y172" s="2"/>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="59"/>
       <c r="C173" s="2"/>
@@ -23004,10 +22655,8 @@
       <c r="U173" s="2"/>
       <c r="V173" s="2"/>
       <c r="W173" s="2"/>
-      <c r="X173" s="2"/>
-      <c r="Y173" s="2"/>
-    </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="59"/>
       <c r="C174" s="2"/>
@@ -23031,10 +22680,8 @@
       <c r="U174" s="2"/>
       <c r="V174" s="2"/>
       <c r="W174" s="2"/>
-      <c r="X174" s="2"/>
-      <c r="Y174" s="2"/>
-    </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="59"/>
       <c r="C175" s="2"/>
@@ -23058,10 +22705,8 @@
       <c r="U175" s="2"/>
       <c r="V175" s="2"/>
       <c r="W175" s="2"/>
-      <c r="X175" s="2"/>
-      <c r="Y175" s="2"/>
-    </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="59"/>
       <c r="C176" s="2"/>
@@ -23085,10 +22730,8 @@
       <c r="U176" s="2"/>
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
-      <c r="X176" s="2"/>
-      <c r="Y176" s="2"/>
-    </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="59"/>
       <c r="C177" s="2"/>
@@ -23112,10 +22755,8 @@
       <c r="U177" s="2"/>
       <c r="V177" s="2"/>
       <c r="W177" s="2"/>
-      <c r="X177" s="2"/>
-      <c r="Y177" s="2"/>
-    </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="59"/>
       <c r="C178" s="2"/>
@@ -23139,10 +22780,8 @@
       <c r="U178" s="2"/>
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
-      <c r="X178" s="2"/>
-      <c r="Y178" s="2"/>
-    </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="59"/>
       <c r="C179" s="2"/>
@@ -23166,10 +22805,8 @@
       <c r="U179" s="2"/>
       <c r="V179" s="2"/>
       <c r="W179" s="2"/>
-      <c r="X179" s="2"/>
-      <c r="Y179" s="2"/>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="59"/>
       <c r="C180" s="2"/>
@@ -23193,10 +22830,8 @@
       <c r="U180" s="2"/>
       <c r="V180" s="2"/>
       <c r="W180" s="2"/>
-      <c r="X180" s="2"/>
-      <c r="Y180" s="2"/>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="59"/>
       <c r="C181" s="2"/>
@@ -23220,10 +22855,8 @@
       <c r="U181" s="2"/>
       <c r="V181" s="2"/>
       <c r="W181" s="2"/>
-      <c r="X181" s="2"/>
-      <c r="Y181" s="2"/>
-    </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="59"/>
       <c r="C182" s="2"/>
@@ -23247,10 +22880,8 @@
       <c r="U182" s="2"/>
       <c r="V182" s="2"/>
       <c r="W182" s="2"/>
-      <c r="X182" s="2"/>
-      <c r="Y182" s="2"/>
-    </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="59"/>
       <c r="C183" s="2"/>
@@ -23274,10 +22905,8 @@
       <c r="U183" s="2"/>
       <c r="V183" s="2"/>
       <c r="W183" s="2"/>
-      <c r="X183" s="2"/>
-      <c r="Y183" s="2"/>
-    </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="59"/>
       <c r="C184" s="2"/>
@@ -23301,10 +22930,8 @@
       <c r="U184" s="2"/>
       <c r="V184" s="2"/>
       <c r="W184" s="2"/>
-      <c r="X184" s="2"/>
-      <c r="Y184" s="2"/>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="59"/>
       <c r="C185" s="2"/>
@@ -23328,10 +22955,8 @@
       <c r="U185" s="2"/>
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
-      <c r="X185" s="2"/>
-      <c r="Y185" s="2"/>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="59"/>
       <c r="C186" s="2"/>
@@ -23355,10 +22980,8 @@
       <c r="U186" s="2"/>
       <c r="V186" s="2"/>
       <c r="W186" s="2"/>
-      <c r="X186" s="2"/>
-      <c r="Y186" s="2"/>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="59"/>
       <c r="C187" s="2"/>
@@ -23382,10 +23005,8 @@
       <c r="U187" s="2"/>
       <c r="V187" s="2"/>
       <c r="W187" s="2"/>
-      <c r="X187" s="2"/>
-      <c r="Y187" s="2"/>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="59"/>
       <c r="C188" s="2"/>
@@ -23409,10 +23030,8 @@
       <c r="U188" s="2"/>
       <c r="V188" s="2"/>
       <c r="W188" s="2"/>
-      <c r="X188" s="2"/>
-      <c r="Y188" s="2"/>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="59"/>
       <c r="C189" s="2"/>
@@ -23436,10 +23055,8 @@
       <c r="U189" s="2"/>
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
-      <c r="X189" s="2"/>
-      <c r="Y189" s="2"/>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="59"/>
       <c r="C190" s="2"/>
@@ -23463,10 +23080,8 @@
       <c r="U190" s="2"/>
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
-      <c r="X190" s="2"/>
-      <c r="Y190" s="2"/>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="59"/>
       <c r="C191" s="2"/>
@@ -23490,10 +23105,8 @@
       <c r="U191" s="2"/>
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
-      <c r="X191" s="2"/>
-      <c r="Y191" s="2"/>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="59"/>
       <c r="C192" s="2"/>
@@ -23517,10 +23130,8 @@
       <c r="U192" s="2"/>
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
-      <c r="X192" s="2"/>
-      <c r="Y192" s="2"/>
-    </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="59"/>
       <c r="C193" s="2"/>
@@ -23544,10 +23155,8 @@
       <c r="U193" s="2"/>
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
-      <c r="X193" s="2"/>
-      <c r="Y193" s="2"/>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="59"/>
       <c r="C194" s="2"/>
@@ -23571,10 +23180,8 @@
       <c r="U194" s="2"/>
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
-      <c r="X194" s="2"/>
-      <c r="Y194" s="2"/>
-    </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="59"/>
       <c r="C195" s="2"/>
@@ -23598,10 +23205,8 @@
       <c r="U195" s="2"/>
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
-      <c r="X195" s="2"/>
-      <c r="Y195" s="2"/>
-    </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="59"/>
       <c r="C196" s="2"/>
@@ -23625,10 +23230,8 @@
       <c r="U196" s="2"/>
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
-      <c r="X196" s="2"/>
-      <c r="Y196" s="2"/>
-    </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="59"/>
       <c r="C197" s="2"/>
@@ -23652,10 +23255,8 @@
       <c r="U197" s="2"/>
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
-      <c r="X197" s="2"/>
-      <c r="Y197" s="2"/>
-    </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="59"/>
       <c r="C198" s="2"/>
@@ -23679,10 +23280,8 @@
       <c r="U198" s="2"/>
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
-      <c r="X198" s="2"/>
-      <c r="Y198" s="2"/>
-    </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="59"/>
       <c r="C199" s="2"/>
@@ -23706,10 +23305,8 @@
       <c r="U199" s="2"/>
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
-      <c r="X199" s="2"/>
-      <c r="Y199" s="2"/>
-    </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="59"/>
       <c r="C200" s="2"/>
@@ -23733,10 +23330,8 @@
       <c r="U200" s="2"/>
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
-      <c r="X200" s="2"/>
-      <c r="Y200" s="2"/>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="59"/>
       <c r="C201" s="2"/>
@@ -23760,10 +23355,8 @@
       <c r="U201" s="2"/>
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
-      <c r="X201" s="2"/>
-      <c r="Y201" s="2"/>
-    </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="59"/>
       <c r="C202" s="2"/>
@@ -23787,45 +23380,44 @@
       <c r="U202" s="2"/>
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
-      <c r="X202" s="2"/>
-      <c r="Y202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vgb8VlENxsUKxUfc/XPDtcJkXSBRPYhk1El0fwutytGxKcaxgANOm1k+mlW+vFas6jRfUoyZcgU3N1zN/jtlyQ==" saltValue="iyYdmxDw557W2wXbuXlKlQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="F2CCbX3HvobuHAv3TON4LCgdb6GVdma/N0DKGpsZHOThojF6/ZxZPCjN6yzB/qraOG4oOGVJcXdVecJg+gWUeA==" saltValue="mY33tca8+VczFeEs52HsoQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="13">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="S1:U1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 F1:F2 G2 I2 K2 Q2 Y2 R1:R2 E1:E2 X2 O2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 F1:F2 G2 I2 J2 O2 W2 P1:P2 E1:E2 V2 M2" xr:uid="{CF79E0B9-452F-42D7-82F9-4325C7CCE12E}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E1:E2" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD_CODE" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
-    <hyperlink ref="X2" r:id="rId2" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
-    <hyperlink ref="Y2" r:id="rId3" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
-    <hyperlink ref="F1:F2" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
-    <hyperlink ref="I2" r:id="rId5" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
-    <hyperlink ref="M2" r:id="rId6" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
-    <hyperlink ref="G2" r:id="rId7" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
-    <hyperlink ref="K2" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
-    <hyperlink ref="Q2" r:id="rId9" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
-    <hyperlink ref="O2" r:id="rId10" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
-    <hyperlink ref="R1:R2" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
-    <hyperlink ref="U2" r:id="rId12" location="biologicalMaterials" xr:uid="{66503A95-2496-4FEA-BFDB-8687AAF0A03C}"/>
-    <hyperlink ref="V2" r:id="rId13" location="samplePreservationMethods" xr:uid="{9D0827D9-DDF0-4A6C-97A1-CFE63DE06B4E}"/>
+    <hyperlink ref="E1:E2" r:id="rId1" location="samplingPeriods" display="SAMPLING_PERIOD" xr:uid="{C0407D03-A3E9-4479-BB66-8329070009A1}"/>
+    <hyperlink ref="V2" r:id="rId2" location="depredationSources" xr:uid="{5248D097-7FB7-4BF7-908D-893A3BF91D4F}"/>
+    <hyperlink ref="W2" r:id="rId3" location="predators" xr:uid="{16A7B676-4806-46E0-B05E-266794DC9A6F}"/>
+    <hyperlink ref="F1:F2" r:id="rId4" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD" xr:uid="{863AF79D-449A-4B35-AC8D-9C415D8A32B9}"/>
+    <hyperlink ref="I2" r:id="rId5" location="lengthMeasurementTools" xr:uid="{776CD30A-4D78-4230-9891-093ADBA1D96D}"/>
+    <hyperlink ref="L2" r:id="rId6" location="lengthMeasurementTools" xr:uid="{3DE19339-45B9-47B8-B5FB-D4012AD9C532}"/>
+    <hyperlink ref="G2" r:id="rId7" location="lengthMeasurementTypes" xr:uid="{4F273766-A7DB-428C-A222-09DB4E6495A6}"/>
+    <hyperlink ref="J2" r:id="rId8" location="lengthMeasurements" xr:uid="{50D5D995-3D3B-46CA-9856-C3BF09F867B6}"/>
+    <hyperlink ref="O2" r:id="rId9" location="weightEstimationMethods" xr:uid="{6830A97A-B177-4E61-8434-B97D80589AB0}"/>
+    <hyperlink ref="M2" r:id="rId10" location="fishProcessingTypes" xr:uid="{4C80F85B-DC5E-4379-AEDD-32355F2C04AE}"/>
+    <hyperlink ref="P1:P2" r:id="rId11" location="sex" display="SEX" xr:uid="{06582CBC-0354-4030-B121-DACE171DCC1B}"/>
+    <hyperlink ref="S2" r:id="rId12" location="biologicalMaterials" xr:uid="{66503A95-2496-4FEA-BFDB-8687AAF0A03C}"/>
+    <hyperlink ref="T2" r:id="rId13" location="samplePreservationMethods" xr:uid="{9D0827D9-DDF0-4A6C-97A1-CFE63DE06B4E}"/>
+    <hyperlink ref="R2" r:id="rId14" location="maturityStages" xr:uid="{D007000D-ADF9-D84F-B041-EFF385F65FDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23860,28 +23452,28 @@
   <sheetData>
     <row r="1" spans="1:20" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="134" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C1" s="132" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="132" t="s">
-        <v>95</v>
+      <c r="E1" s="94" t="s">
+        <v>172</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="F1" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="G1" s="94" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="H1" s="110" t="s">
         <v>175</v>
-      </c>
-      <c r="H1" s="103" t="s">
-        <v>176</v>
       </c>
       <c r="I1" s="83" t="s">
         <v>69</v>
@@ -23891,17 +23483,17 @@
         <v>70</v>
       </c>
       <c r="L1" s="82"/>
-      <c r="M1" s="103" t="s">
-        <v>181</v>
+      <c r="M1" s="110" t="s">
+        <v>180</v>
       </c>
       <c r="N1" s="136" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O1" s="136" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="103" t="s">
-        <v>180</v>
+      <c r="P1" s="110" t="s">
+        <v>179</v>
       </c>
       <c r="Q1" s="136" t="s">
         <v>67</v>
@@ -23910,7 +23502,7 @@
         <v>68</v>
       </c>
       <c r="S1" s="86" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T1" s="86"/>
     </row>
@@ -23919,33 +23511,33 @@
       <c r="B2" s="135"/>
       <c r="C2" s="133"/>
       <c r="D2" s="133"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="104"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="111"/>
       <c r="I2" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J2" s="36" t="s">
         <v>23</v>
       </c>
       <c r="K2" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="104"/>
+      <c r="M2" s="111"/>
       <c r="N2" s="86"/>
       <c r="O2" s="86"/>
-      <c r="P2" s="104"/>
+      <c r="P2" s="111"/>
       <c r="Q2" s="86"/>
       <c r="R2" s="86"/>
       <c r="S2" s="36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T2" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:20" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -28351,16 +27943,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="rUY+tQClaCe56pFj2gdqQGuB4mIoJ5tT4LwmpiwLEWZaiO5dMlpEyYHjKOIHEyhphvBk5cz5XlXNO1/S25ywZQ==" saltValue="QHHuqJar+B2gy88TYNv68g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="H1:H2"/>
@@ -28368,6 +27950,16 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F2 H1:H2 P1:P2 S2 J2 E1:E2 G1:G2 I2 M1:M2 T2" xr:uid="{D35AC15C-DF5E-4A91-9A87-73B80C6F3218}">
@@ -28412,16 +28004,16 @@
   <sheetData>
     <row r="1" spans="1:11" s="39" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D1" s="46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" s="33" t="s">
         <v>63</v>
@@ -28433,16 +28025,16 @@
         <v>23</v>
       </c>
       <c r="H1" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="I1" s="33" t="s">
-        <v>250</v>
-      </c>
       <c r="J1" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K1" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="39" customFormat="1" x14ac:dyDescent="0.2">
@@ -31095,14 +30687,14 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="74" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C1" s="74"/>
       <c r="D1" s="86" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E1" s="86"/>
       <c r="F1" s="86"/>
@@ -31114,7 +30706,7 @@
       <c r="L1" s="86"/>
       <c r="M1" s="86"/>
       <c r="N1" s="77" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O1" s="78"/>
       <c r="P1" s="78"/>
@@ -31133,14 +30725,14 @@
       <c r="B2" s="85"/>
       <c r="C2" s="85"/>
       <c r="D2" s="87" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="88"/>
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
       <c r="H2" s="91"/>
       <c r="I2" s="87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J2" s="88"/>
       <c r="K2" s="88"/>
@@ -31164,40 +30756,40 @@
       <c r="B3" s="85"/>
       <c r="C3" s="85"/>
       <c r="D3" s="83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="84"/>
       <c r="F3" s="83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="84"/>
       <c r="H3" s="92" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I3" s="83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J3" s="84"/>
       <c r="K3" s="83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L3" s="84"/>
       <c r="M3" s="89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3" s="75" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O3" s="75"/>
       <c r="P3" s="76" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q3" s="76"/>
       <c r="R3" s="76"/>
       <c r="S3" s="76"/>
       <c r="T3" s="76"/>
       <c r="U3" s="76" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V3" s="76"/>
       <c r="W3" s="76"/>
@@ -31206,13 +30798,13 @@
     <row r="4" spans="1:25" s="40" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="74"/>
       <c r="B4" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E4" s="36" t="s">
         <v>4</v>
@@ -31225,7 +30817,7 @@
       </c>
       <c r="H4" s="86"/>
       <c r="I4" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J4" s="36" t="s">
         <v>4</v>
@@ -31259,16 +30851,16 @@
         <v>10</v>
       </c>
       <c r="U4" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="V4" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="V4" s="29" t="s">
+      <c r="W4" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="X4" s="29" t="s">
         <v>118</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -36511,64 +36103,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="108" t="s">
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="109"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="102" t="s">
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="109" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
-      <c r="L1" s="93" t="s">
-        <v>109</v>
+      <c r="L1" s="100" t="s">
+        <v>108</v>
       </c>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="95"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="102"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="73"/>
       <c r="B2" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="100" t="s">
-        <v>120</v>
+      <c r="C2" s="107" t="s">
+        <v>119</v>
       </c>
-      <c r="D2" s="101" t="s">
+      <c r="D2" s="108" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="97" t="s">
-        <v>115</v>
+      <c r="G2" s="104" t="s">
+        <v>114</v>
       </c>
-      <c r="H2" s="98" t="s">
+      <c r="H2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="111" t="s">
-        <v>157</v>
+      <c r="I2" s="99" t="s">
+        <v>156</v>
       </c>
-      <c r="J2" s="103"/>
-      <c r="K2" s="106" t="s">
-        <v>122</v>
+      <c r="J2" s="110"/>
+      <c r="K2" s="94" t="s">
+        <v>121</v>
       </c>
       <c r="L2" s="75" t="s">
         <v>18</v>
@@ -36578,35 +36170,35 @@
         <v>19</v>
       </c>
       <c r="O2" s="75"/>
-      <c r="P2" s="96" t="s">
+      <c r="P2" s="103" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="74"/>
       <c r="B3" s="85"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="101"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="108"/>
       <c r="E3" s="86"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="107"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="95"/>
       <c r="L3" s="30" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
-      <c r="P3" s="96"/>
+      <c r="P3" s="103"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -40208,8 +39800,9 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="igO11AcmgHLNHDmBwkxrcwFkfFcrOqisqWMWX8+4/TwA3DjoaZzl7aBUcPHYWTRbmZ/2ruUlzWiOnQXYejn3dg==" saltValue="BVXY+qET3W4zfSzvwbUY/A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="G1:I1"/>
@@ -40226,7 +39819,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="J1:J3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 O3 K2:K3 G2:I3" xr:uid="{ACED21EE-BC8F-4262-88C6-C5B6A4D7F4AF}">
@@ -40271,23 +39863,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="103" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96" t="s">
-        <v>210</v>
-      </c>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="73"/>
@@ -40298,7 +39890,7 @@
       <c r="D2" s="88"/>
       <c r="E2" s="88"/>
       <c r="F2" s="92" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G2" s="87" t="s">
         <v>4</v>
@@ -40307,13 +39899,13 @@
       <c r="I2" s="88"/>
       <c r="J2" s="91"/>
       <c r="K2" s="92" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="74"/>
       <c r="B3" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>4</v>
@@ -40326,7 +39918,7 @@
       </c>
       <c r="F3" s="86"/>
       <c r="G3" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H3" s="36" t="s">
         <v>4</v>
@@ -42940,7 +42532,7 @@
       <c r="K203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VDEUXHKES7jz/Sopv6FbsktRKD/KUS9euZuBL/BvjbYiPG0GJE2/wv9owi98WXq1V7nOtwQ0vIb3G6a2TWEzwQ==" saltValue="jkCjp5IBEfdUA5vbgfcogg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NtuOXXR3qE8dOTN1tI4CYOY3++zraGODe03zaKmJdkJ1/g/DcJgQ833jCPfs53cAEkSbSov91l4NpDayqSLyZA==" saltValue="prIiT2Lg0uWZXYs3Pcw7Vg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:F1"/>
@@ -42956,8 +42548,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
-    <hyperlink ref="G3" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
+    <hyperlink ref="B3" r:id="rId1" location="countries" xr:uid="{D6E7062F-2D43-4596-8E73-CC2381D61A2B}"/>
+    <hyperlink ref="G3" r:id="rId2" location="countries" xr:uid="{DE99A7AA-576F-4966-8C9A-C1F406C63AE0}"/>
     <hyperlink ref="C3" r:id="rId3" location="Ports" xr:uid="{93F08CEF-34DB-46A0-A09B-203AF008B136}"/>
     <hyperlink ref="H3" r:id="rId4" location="Ports" xr:uid="{2CDE38A1-7DD3-42DB-B597-7777F42628DA}"/>
   </hyperlinks>
@@ -43013,11 +42605,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
       <c r="B1" s="87" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C1" s="88"/>
       <c r="D1" s="88"/>
@@ -43038,7 +42630,7 @@
       <c r="S1" s="88"/>
       <c r="T1" s="91"/>
       <c r="U1" s="87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="V1" s="88"/>
       <c r="W1" s="88"/>
@@ -43053,7 +42645,7 @@
       <c r="AF1" s="88"/>
       <c r="AG1" s="91"/>
       <c r="AH1" s="87" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AI1" s="88"/>
       <c r="AJ1" s="88"/>
@@ -43066,26 +42658,26 @@
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" s="73"/>
       <c r="B2" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="D2" s="109" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="102" t="s">
-        <v>126</v>
-      </c>
       <c r="E2" s="76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F2" s="76"/>
       <c r="G2" s="76"/>
       <c r="H2" s="76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I2" s="76"/>
       <c r="J2" s="76"/>
       <c r="K2" s="92" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L2" s="76" t="s">
         <v>26</v>
@@ -43102,59 +42694,59 @@
         <v>27</v>
       </c>
       <c r="T2" s="76"/>
-      <c r="U2" s="96" t="s">
-        <v>136</v>
+      <c r="U2" s="103" t="s">
+        <v>135</v>
       </c>
-      <c r="V2" s="96" t="s">
+      <c r="V2" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="96" t="s">
+      <c r="W2" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="96" t="s">
+      <c r="X2" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="96" t="s">
+      <c r="Y2" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="96" t="s">
+      <c r="Z2" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="96" t="s">
+      <c r="AA2" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="96" t="s">
+      <c r="AB2" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="96" t="s">
+      <c r="AC2" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="96" t="s">
+      <c r="AD2" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="96" t="s">
+      <c r="AE2" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="96" t="s">
-        <v>128</v>
+      <c r="AF2" s="103" t="s">
+        <v>127</v>
       </c>
-      <c r="AG2" s="96" t="s">
+      <c r="AG2" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="108" t="s">
+      <c r="AH2" s="96" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI2" s="98"/>
+      <c r="AJ2" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="AI2" s="110"/>
-      <c r="AJ2" s="76" t="s">
-        <v>214</v>
       </c>
       <c r="AK2" s="76"/>
       <c r="AL2" s="76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AM2" s="76"/>
       <c r="AN2" s="76" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AO2" s="76"/>
     </row>
@@ -43162,7 +42754,7 @@
       <c r="A3" s="74"/>
       <c r="B3" s="86"/>
       <c r="C3" s="86"/>
-      <c r="D3" s="104"/>
+      <c r="D3" s="111"/>
       <c r="E3" s="32" t="s">
         <v>24</v>
       </c>
@@ -43170,7 +42762,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>24</v>
@@ -43179,72 +42771,72 @@
         <v>25</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K3" s="86"/>
       <c r="L3" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M3" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="N3" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="O3" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="P3" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="Q3" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="R3" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="S3" s="32" t="s">
         <v>22</v>
       </c>
       <c r="T3" s="35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="96"/>
-      <c r="AD3" s="96"/>
-      <c r="AE3" s="96"/>
-      <c r="AF3" s="96"/>
-      <c r="AG3" s="96"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103"/>
+      <c r="AA3" s="103"/>
+      <c r="AB3" s="103"/>
+      <c r="AC3" s="103"/>
+      <c r="AD3" s="103"/>
+      <c r="AE3" s="103"/>
+      <c r="AF3" s="103"/>
+      <c r="AG3" s="103"/>
       <c r="AH3" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI3" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="AI3" s="29" t="s">
+      <c r="AJ3" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="AJ3" s="29" t="s">
+      <c r="AK3" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="AK3" s="29" t="s">
+      <c r="AL3" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AM3" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="AM3" s="29" t="s">
+      <c r="AN3" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="AN3" s="29" t="s">
+      <c r="AO3" s="29" t="s">
         <v>143</v>
-      </c>
-      <c r="AO3" s="29" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -51848,8 +51440,22 @@
       <c r="AO203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DglQ3GkZdqklZtniCzWo0ug7RamL8fg/XjsgFQSLdo4j/VzwSZU8z2HL2HhDcREH3eRguSe9Md5gzKlV3gXHSw==" saltValue="BMZmca5GDyiJr+AnVIRF5w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="mmLbj8VNPRQUPPbUHFuZC3W7KY5odKQ3NPjg6u0MfE8Fq4A3G3bF1UGQjPoMW6FqWQape5RiXVqfLiDVSVCejg==" saltValue="pghT3JOfKDfV6l/286+G7g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="K2:K3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="U1:AG1"/>
@@ -51866,20 +51472,6 @@
     <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AD2:AD3"/>
     <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 R3 AI3 AK3 AM3 L3 M3 N3 O3 P3 Q3 AO3 AJ3 AL3 AN3 AH3" xr:uid="{7AE1CE56-A690-401C-B311-F5FE2246C553}">
@@ -51887,22 +51479,22 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2:D3" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL_CODE" xr:uid="{67410786-49B8-4FAC-82C7-693110607986}"/>
-    <hyperlink ref="L3" r:id="rId2" location="fishPreservationMethods" display="METHOD_1_CODE" xr:uid="{1302D005-C0D4-48F4-9067-8DB21E13C99E}"/>
-    <hyperlink ref="M3" r:id="rId3" location="fishPreservationMethods" display="METHOD_2_CODE" xr:uid="{EEBE083B-4312-4FA4-A951-C9F9A824B321}"/>
-    <hyperlink ref="N3" r:id="rId4" location="fishPreservationMethods" display="METHOD_3_CODE" xr:uid="{30064C75-6784-480A-88EC-D543ED3C0DC7}"/>
-    <hyperlink ref="O3" r:id="rId5" location="fishPreservationMethods" display="METHOD_4_CODE" xr:uid="{57D15D5E-41AB-40B4-A2E0-8E05FF890560}"/>
-    <hyperlink ref="P3" r:id="rId6" location="fishStorageTypes" display="TYPE_1_CODE" xr:uid="{632D3564-65D3-45E5-BF57-3CF8FD5ACBAF}"/>
-    <hyperlink ref="Q3" r:id="rId7" location="fishStorageTypes" display="TYPE_2_CODE" xr:uid="{BB5616AB-C383-462B-A9E4-AB799B92F802}"/>
-    <hyperlink ref="R3" r:id="rId8" location="fishStorageTypes" display="TYPE_3_CODE" xr:uid="{94329445-F648-4E10-BD21-D3B467B1D303}"/>
+    <hyperlink ref="D2:D3" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL" xr:uid="{67410786-49B8-4FAC-82C7-693110607986}"/>
+    <hyperlink ref="L3" r:id="rId2" location="fishPreservationMethods" xr:uid="{1302D005-C0D4-48F4-9067-8DB21E13C99E}"/>
+    <hyperlink ref="M3" r:id="rId3" location="fishPreservationMethods" xr:uid="{EEBE083B-4312-4FA4-A951-C9F9A824B321}"/>
+    <hyperlink ref="N3" r:id="rId4" location="fishPreservationMethods" xr:uid="{30064C75-6784-480A-88EC-D543ED3C0DC7}"/>
+    <hyperlink ref="O3" r:id="rId5" location="fishPreservationMethods" xr:uid="{57D15D5E-41AB-40B4-A2E0-8E05FF890560}"/>
+    <hyperlink ref="P3" r:id="rId6" location="fishStorageTypes" xr:uid="{632D3564-65D3-45E5-BF57-3CF8FD5ACBAF}"/>
+    <hyperlink ref="Q3" r:id="rId7" location="fishStorageTypes" xr:uid="{BB5616AB-C383-462B-A9E4-AB799B92F802}"/>
+    <hyperlink ref="R3" r:id="rId8" location="fishStorageTypes" xr:uid="{94329445-F648-4E10-BD21-D3B467B1D303}"/>
     <hyperlink ref="AH3" r:id="rId9" location="wasteCategories" xr:uid="{8F0155CB-37EC-4CEC-9EB0-B85C65274EA0}"/>
     <hyperlink ref="AJ3" r:id="rId10" location="wasteCategories" xr:uid="{4AA42787-D2A9-4627-B1FB-A30392A207EB}"/>
     <hyperlink ref="AL3" r:id="rId11" location="wasteCategories" xr:uid="{1E0ACA01-E9CF-41A3-B227-90B65C435EBC}"/>
     <hyperlink ref="AN3" r:id="rId12" location="wasteCategories" xr:uid="{80DD5EEA-21EE-47E6-8164-69AF6D6A721F}"/>
-    <hyperlink ref="AI3" r:id="rId13" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_1_CODE" xr:uid="{734552DB-2913-470A-98E7-9E5085684410}"/>
-    <hyperlink ref="AK3" r:id="rId14" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_2_CODE" xr:uid="{435FF06B-B974-4B37-BA60-C79659E1631E}"/>
-    <hyperlink ref="AM3" r:id="rId15" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_3_CODE" xr:uid="{B45A5879-026B-4247-B2B8-15EF712B3716}"/>
-    <hyperlink ref="AO3" r:id="rId16" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_4_CODE" xr:uid="{5B7BDC52-01F7-456B-A7FF-5F257DD246CF}"/>
+    <hyperlink ref="AI3" r:id="rId13" location="wasteDisposalMethods" xr:uid="{734552DB-2913-470A-98E7-9E5085684410}"/>
+    <hyperlink ref="AK3" r:id="rId14" location="wasteDisposalMethods" xr:uid="{435FF06B-B974-4B37-BA60-C79659E1631E}"/>
+    <hyperlink ref="AM3" r:id="rId15" location="wasteDisposalMethods" xr:uid="{B45A5879-026B-4247-B2B8-15EF712B3716}"/>
+    <hyperlink ref="AO3" r:id="rId16" location="wasteDisposalMethods" xr:uid="{5B7BDC52-01F7-456B-A7FF-5F257DD246CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -51923,11 +51515,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
       <c r="B1" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C1" s="85"/>
       <c r="D1" s="85"/>
@@ -51935,7 +51527,7 @@
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
       <c r="B2" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C2" s="50" t="s">
         <v>40</v>
@@ -53175,18 +52767,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="103" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="87" t="s">
         <v>203</v>
-      </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="87" t="s">
-        <v>204</v>
       </c>
       <c r="H1" s="88"/>
       <c r="I1" s="88"/>
@@ -53195,31 +52787,31 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="74"/>
       <c r="B2" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="D2" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="E2" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="31" t="s">
+      <c r="H2" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="I2" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="J2" s="51" t="s">
         <v>150</v>
-      </c>
-      <c r="J2" s="51" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -55623,7 +55215,7 @@
       <c r="J202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ezlhouH4jWtVlFHtnlTUdULZErjDxNnEcyqcdodYXkawq+iQLA0wXnbN7L/M9K1Gd2RS6yKnKLqwNVzphDl/wQ==" saltValue="I1dHPbf36EdK7DQQW+XxaQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IYfD3VEAR8PHU4myV+SyS3xaR1R3XUWw9e+RyBrteZZRygOFEN/QCjczAl88/CKfaqs6FPKlLc+A5ZV16jQWfQ==" saltValue="VFT13eXTH/PmpgXE66QcNg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="A1:A2"/>
@@ -55635,11 +55227,11 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" location="lineMaterialTypes" display="MATERIAL_TYPE_CODE" xr:uid="{46A86ECA-083A-460B-BEC7-C7B89DFBDF29}"/>
-    <hyperlink ref="G2" r:id="rId2" location="branchlineStorages" display="STORAGE_1_CODE" xr:uid="{977E6CDC-B302-4BDB-9F22-244BEC62ADA2}"/>
-    <hyperlink ref="H2" r:id="rId3" location="branchlineStorages" display="STORAGE_2_CODE" xr:uid="{3AC152D8-4579-4E77-8942-BECAB07592B8}"/>
-    <hyperlink ref="I2" r:id="rId4" location="branchlineStorages" display="STORAGE_3_CODE" xr:uid="{F9A4BCAF-D054-4AEA-B4D7-27043098B43A}"/>
-    <hyperlink ref="J2" r:id="rId5" location="branchlineStorages" display="STORAGE_4_CODE" xr:uid="{B88F43F0-3266-44A5-8257-02CEEF0AA3D6}"/>
+    <hyperlink ref="D2" r:id="rId1" location="lineMaterialTypes" xr:uid="{46A86ECA-083A-460B-BEC7-C7B89DFBDF29}"/>
+    <hyperlink ref="G2" r:id="rId2" location="branchlineStorages" xr:uid="{977E6CDC-B302-4BDB-9F22-244BEC62ADA2}"/>
+    <hyperlink ref="H2" r:id="rId3" location="branchlineStorages" xr:uid="{3AC152D8-4579-4E77-8942-BECAB07592B8}"/>
+    <hyperlink ref="I2" r:id="rId4" location="branchlineStorages" xr:uid="{F9A4BCAF-D054-4AEA-B4D7-27043098B43A}"/>
+    <hyperlink ref="J2" r:id="rId5" location="branchlineStorages" xr:uid="{B88F43F0-3266-44A5-8257-02CEEF0AA3D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -55666,11 +55258,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
       <c r="B1" s="112" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C1" s="113"/>
       <c r="D1" s="113"/>
@@ -55682,7 +55274,7 @@
       <c r="J1" s="113"/>
       <c r="K1" s="114"/>
       <c r="L1" s="115" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M1" s="116"/>
       <c r="N1" s="116"/>
@@ -55691,24 +55283,24 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="73"/>
-      <c r="B2" s="105" t="s">
-        <v>253</v>
+      <c r="B2" s="93" t="s">
+        <v>252</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="95"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="102"/>
       <c r="H2" s="92" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="105" t="s">
-        <v>162</v>
-      </c>
       <c r="J2" s="87" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K2" s="91"/>
       <c r="L2" s="83"/>
@@ -55727,10 +55319,10 @@
         <v>45</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G3" s="48" t="s">
         <v>44</v>
@@ -55744,19 +55336,19 @@
         <v>15</v>
       </c>
       <c r="L3" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M3" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="O3" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="P3" s="31" t="s">
         <v>167</v>
-      </c>
-      <c r="P3" s="31" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -59360,7 +58952,7 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uABnzePaRwNJmP5GnCNh91yxfgYuWGN7jr93+Cq/P2vwlhGdMo0irQ3L5XubIQziVhw9YDRFONrZiyCFn4Ejeg==" saltValue="Trtaf8ZOBTMeXPnN/MlR1w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ACcaeNs3f8aqGq3+0OMTWawRFuqFW4H2XvJsXp5c85AcvXMHcScc0SshvOkrO2vYIvO5urIAEZ4Q0V6Yrclycg==" saltValue="fSt5GYJYk66IWXP4yUrqPQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="B1:K1"/>
@@ -59377,12 +58969,12 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" location="streamerTypes" display="TYPE_CODE" xr:uid="{F5B00754-CAA7-4970-9267-C564E10BAB15}"/>
-    <hyperlink ref="L3" r:id="rId2" location="mitigationDevices" display="DEVICE_1_CODE" xr:uid="{E64F730D-939F-45B5-880D-5F6B514D9768}"/>
-    <hyperlink ref="M3" r:id="rId3" location="mitigationDevices" display="DEVICE_2_CODE" xr:uid="{9ED9D614-FD6F-49CD-865E-6F4E2F134AB8}"/>
-    <hyperlink ref="N3" r:id="rId4" location="mitigationDevices" display="DEVICE_3_CODE" xr:uid="{FD249156-8181-4617-AA2E-7D78285B2BA7}"/>
-    <hyperlink ref="O3" r:id="rId5" location="mitigationDevices" display="DEVICE_4_CODE" xr:uid="{93C2D1ED-DD7E-4C3A-94FD-7C83A902B4EA}"/>
-    <hyperlink ref="P3" r:id="rId6" location="mitigationDevices" display="DEVICE_5_CODE" xr:uid="{468402CE-24B4-4147-BA53-73E2855BBFD5}"/>
+    <hyperlink ref="C3" r:id="rId1" location="streamerTypes" xr:uid="{F5B00754-CAA7-4970-9267-C564E10BAB15}"/>
+    <hyperlink ref="L3" r:id="rId2" location="mitigationDevices" xr:uid="{E64F730D-939F-45B5-880D-5F6B514D9768}"/>
+    <hyperlink ref="M3" r:id="rId3" location="mitigationDevices" xr:uid="{9ED9D614-FD6F-49CD-865E-6F4E2F134AB8}"/>
+    <hyperlink ref="N3" r:id="rId4" location="mitigationDevices" xr:uid="{FD249156-8181-4617-AA2E-7D78285B2BA7}"/>
+    <hyperlink ref="O3" r:id="rId5" location="mitigationDevices" xr:uid="{93C2D1ED-DD7E-4C3A-94FD-7C83A902B4EA}"/>
+    <hyperlink ref="P3" r:id="rId6" location="mitigationDevices" xr:uid="{468402CE-24B4-4147-BA53-73E2855BBFD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -59426,27 +59018,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
-        <v>90</v>
+      <c r="A1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>92</v>
+      <c r="B1" s="119" t="s">
+        <v>91</v>
       </c>
       <c r="C1" s="85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1" s="85"/>
       <c r="E1" s="85"/>
       <c r="F1" s="112" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G1" s="113"/>
       <c r="H1" s="114"/>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="J1" s="93" t="s">
         <v>234</v>
-      </c>
-      <c r="J1" s="105" t="s">
-        <v>235</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>42</v>
@@ -59458,32 +59050,32 @@
       </c>
       <c r="O1" s="117"/>
       <c r="P1" s="85" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q1" s="103" t="s">
         <v>236</v>
       </c>
-      <c r="Q1" s="96" t="s">
+      <c r="R1" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="R1" s="85" t="s">
-        <v>238</v>
+      <c r="S1" s="85" t="s">
+        <v>243</v>
       </c>
-      <c r="S1" s="85" t="s">
+      <c r="T1" s="85"/>
+      <c r="U1" s="122" t="s">
         <v>244</v>
       </c>
-      <c r="T1" s="85"/>
-      <c r="U1" s="119" t="s">
+      <c r="V1" s="123"/>
+      <c r="W1" s="122" t="s">
         <v>245</v>
       </c>
-      <c r="V1" s="120"/>
-      <c r="W1" s="119" t="s">
+      <c r="X1" s="123"/>
+      <c r="Y1" s="122" t="s">
         <v>246</v>
       </c>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="119" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z1" s="120"/>
+      <c r="Z1" s="123"/>
       <c r="AA1" s="85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AB1" s="85"/>
       <c r="AC1" s="85"/>
@@ -59491,19 +59083,19 @@
     </row>
     <row r="2" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="73"/>
-      <c r="B2" s="122"/>
+      <c r="B2" s="120"/>
       <c r="C2" s="77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" s="114"/>
-      <c r="F2" s="105" t="s">
-        <v>81</v>
+      <c r="F2" s="93" t="s">
+        <v>80</v>
       </c>
       <c r="G2" s="112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2" s="114"/>
       <c r="I2" s="73"/>
@@ -59514,7 +59106,7 @@
       <c r="N2" s="83"/>
       <c r="O2" s="84"/>
       <c r="P2" s="85"/>
-      <c r="Q2" s="96"/>
+      <c r="Q2" s="103"/>
       <c r="R2" s="85"/>
       <c r="S2" s="85"/>
       <c r="T2" s="85"/>
@@ -59531,7 +59123,7 @@
     </row>
     <row r="3" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="74"/>
-      <c r="B3" s="123"/>
+      <c r="B3" s="121"/>
       <c r="C3" s="80"/>
       <c r="D3" s="30" t="s">
         <v>0</v>
@@ -59549,13 +59141,13 @@
       <c r="I3" s="74"/>
       <c r="J3" s="74"/>
       <c r="K3" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L3" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N3" s="33" t="s">
         <v>47</v>
@@ -59564,7 +59156,7 @@
         <v>48</v>
       </c>
       <c r="P3" s="85"/>
-      <c r="Q3" s="96"/>
+      <c r="Q3" s="103"/>
       <c r="R3" s="85"/>
       <c r="S3" s="30" t="s">
         <v>50</v>
@@ -59582,25 +59174,25 @@
         <v>22</v>
       </c>
       <c r="X3" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y3" s="30" t="s">
         <v>22</v>
       </c>
       <c r="Z3" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA3" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB3" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="AB3" s="36" t="s">
+      <c r="AC3" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AD3" s="36" t="s">
         <v>241</v>
-      </c>
-      <c r="AD3" s="36" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
@@ -65976,8 +65568,12 @@
       <c r="B203" s="59"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8G7lESFXiUC0JuN/2ssKWQVyPUnKNolMdHv7H4MUGKXEhoW+vNAYSSaigKIuo5sKq45/g177pYA4FrYPgx7VQQ==" saltValue="lLK5Fw/VZxxRDxWwiAxL4w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FpwA99+lZ3tcetgbufn/FDC8HQLhHeenUtUDopBd7olIgbOkNoNGn9spTr6VyjbhJ25LGDZVYLCeDv+4Ep88iQ==" saltValue="ZbPAwiTrvBPOJT2KMdL6dA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="20">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="Y1:Z2"/>
@@ -65994,10 +65590,6 @@
     <mergeCell ref="N1:O2"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 AA3:AD3" xr:uid="{BB3B8D3D-2F24-4FC4-9101-48D8CFEF3D7F}">
@@ -66009,7 +65601,7 @@
     <hyperlink ref="AB3" r:id="rId2" location="allSpecies" xr:uid="{9EEA8352-0631-4B4E-BB1B-FF880D8B8ED2}"/>
     <hyperlink ref="AC3" r:id="rId3" location="allSpecies" xr:uid="{B78A1E77-3003-40C6-9B0C-101A94179479}"/>
     <hyperlink ref="AD3" r:id="rId4" location="allSpecies" xr:uid="{22DD36F0-D891-4763-8CC9-508C73D63CC9}"/>
-    <hyperlink ref="K3" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{53874CDA-60F7-44F3-A738-546AA82ACA2B}"/>
+    <hyperlink ref="K3" r:id="rId5" location="lineMaterialTypes" xr:uid="{53874CDA-60F7-44F3-A738-546AA82ACA2B}"/>
     <hyperlink ref="U3" r:id="rId6" location="lineMaterialTypes" xr:uid="{7EF57AEF-2AD1-4676-A048-1EB51C0592B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/form_reporting_templates/ros/Form-ROS-LL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-LL.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41AC23C-707C-1F4C-9D41-8D5151EB332F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1F8842-1046-E642-B393-59FBA0E4B7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="ZfpSTEX8tJoLKKS/2QPKxpUICc4sIZ3kzl8g4yv5govFiOeUEO9yg+BUjdxWSjUCwnz/IYo7CkpdetcZ9hh01Q==" workbookSaltValue="1lt51vMgZ/EPbNjf80VAWA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="9700" yWindow="740" windowWidth="19340" windowHeight="16560" tabRatio="879" firstSheet="14" activeTab="16" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="9700" yWindow="740" windowWidth="19340" windowHeight="16560" tabRatio="879" firstSheet="15" activeTab="18" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="25" r:id="rId1"/>
@@ -27941,7 +27941,7 @@
       <c r="T202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rUY+tQClaCe56pFj2gdqQGuB4mIoJ5tT4LwmpiwLEWZaiO5dMlpEyYHjKOIHEyhphvBk5cz5XlXNO1/S25ywZQ==" saltValue="QHHuqJar+B2gy88TYNv68g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kXOeHCBTFnCtabQyw7O55TP9a8AtJjVhE7XETtAeO+Co3py+tqGGNXv7bXrlaakMVsOkhIkZGHoHgY9k2AWjiA==" saltValue="UsZRgL6D2EJ1jxbu9hza1w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="S1:T1"/>
@@ -27967,19 +27967,19 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G1:G2" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
-    <hyperlink ref="H1:H2" r:id="rId2" location="hookTypes" display="HOOK_TYPE_CODE" xr:uid="{FC3E5B48-31F4-4395-B266-CAE8F0285CBE}"/>
-    <hyperlink ref="I2" r:id="rId3" location="baitConditions" display="CONDITION_CODE" xr:uid="{A5E5073A-7EA6-4050-99BD-3A2C3C210913}"/>
-    <hyperlink ref="M1:M2" r:id="rId4" location="dehookerTypes" display="DE_HOOKER_DEVICE_CODE" xr:uid="{223FF70D-0F50-400C-91DF-40947EEFC402}"/>
-    <hyperlink ref="K2" r:id="rId5" location="lineMaterialTypes" display="MATERIAL_CODE" xr:uid="{8BD5CD8E-6908-4DE0-9B07-7CCA6FB5C649}"/>
-    <hyperlink ref="P1:P2" r:id="rId6" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
-    <hyperlink ref="J2" r:id="rId7" location="baitTypes" display="TYPE_CODE" xr:uid="{8E341D36-948A-422D-9D66-B4F0241035EC}"/>
+    <hyperlink ref="G1:G2" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION" xr:uid="{4D21FAB4-D1ED-49FA-A8E9-1A452DA8E255}"/>
+    <hyperlink ref="H1:H2" r:id="rId2" location="hookTypes" display="HOOK_TYPE" xr:uid="{FC3E5B48-31F4-4395-B266-CAE8F0285CBE}"/>
+    <hyperlink ref="I2" r:id="rId3" location="baitConditions" xr:uid="{A5E5073A-7EA6-4050-99BD-3A2C3C210913}"/>
+    <hyperlink ref="M1:M2" r:id="rId4" location="dehookerTypes" display="DEHOOKER_DEVICE" xr:uid="{223FF70D-0F50-400C-91DF-40947EEFC402}"/>
+    <hyperlink ref="K2" r:id="rId5" location="lineMaterialTypes" xr:uid="{8BD5CD8E-6908-4DE0-9B07-7CCA6FB5C649}"/>
+    <hyperlink ref="P1:P2" r:id="rId6" location="handlingMethods" display="HANDLING_METHOD" xr:uid="{4AAC5290-0C1E-413E-9063-304F215E9866}"/>
+    <hyperlink ref="J2" r:id="rId7" location="baitTypes" xr:uid="{8E341D36-948A-422D-9D66-B4F0241035EC}"/>
     <hyperlink ref="E1" r:id="rId8" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{26B5C55C-6931-4D84-B6B4-4AA585019D2E}"/>
     <hyperlink ref="F1" r:id="rId9" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{312D6457-0D67-4610-B478-F5AE649B98F6}"/>
-    <hyperlink ref="S2" r:id="rId10" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
-    <hyperlink ref="T2" r:id="rId11" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{AD1EB751-9874-431A-A9CC-CB89B7E2E48C}"/>
-    <hyperlink ref="F1:F2" r:id="rId12" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{7022269F-0B3D-487B-821A-D8677291ECA9}"/>
-    <hyperlink ref="E1:E2" r:id="rId13" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{46C1F397-FDC9-4F56-B765-948CEB3929A4}"/>
+    <hyperlink ref="S2" r:id="rId10" location="depredationSources" xr:uid="{11FAA504-1FFB-4306-A7A1-4F548FAD3A87}"/>
+    <hyperlink ref="T2" r:id="rId11" location="predators" xr:uid="{AD1EB751-9874-431A-A9CC-CB89B7E2E48C}"/>
+    <hyperlink ref="F1:F2" r:id="rId12" location="individualConditions" display="CONDITION_AT_RELEASE" xr:uid="{7022269F-0B3D-487B-821A-D8677291ECA9}"/>
+    <hyperlink ref="E1:E2" r:id="rId13" location="individualConditions" display="CONDITION_AT_CAPTURE" xr:uid="{46C1F397-FDC9-4F56-B765-948CEB3929A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
@@ -30638,14 +30638,14 @@
       <c r="K201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sc0sg9zRQqpBIofVhsR5+kC48Udkqp2594lydPh/qKBc2JOh5a4aBROzbHfQkEv2hSJ1rewAXhl3Tk3oozlC3w==" saltValue="I8ZoipR+EyahaPD0QcrY3w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JBK1mPS6tH34+qt3w/2MDQbgaqyjgF1tRRl0dpJ3c52a/El8PHK7eAlzkd24YyqoiEUMow/qPk7w5zBmEgqV+A==" saltValue="CDC0CdkX1rJDPSQ0OW+KPA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{4FDCD393-A02F-41DC-AAE5-5D41DD47867C}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G1" r:id="rId1" location="tagTypes" display="TYPE_CODE" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
+    <hyperlink ref="G1" r:id="rId1" location="tagTypes" xr:uid="{ECAFC5F2-6FEB-4806-8763-D5FABB0EB5EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
